--- a/MaestraPLU_Rotiseria.xlsx
+++ b/MaestraPLU_Rotiseria.xlsx
@@ -421,19 +421,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>633212</v>
+        <v>633285</v>
       </c>
       <c r="B2" t="str">
-        <v>QUESO GAUDA ASTURIANA KG</v>
+        <v>SUCEDANEO QUESO TIPO GOUDA 1 KG</v>
       </c>
       <c r="C2" t="str">
         <v/>
       </c>
       <c r="D2" t="str">
-        <v>33212</v>
+        <v>33285</v>
       </c>
       <c r="E2" t="str">
-        <v>7560</v>
+        <v>6360</v>
       </c>
       <c r="F2" t="str">
         <v>Por peso</v>
@@ -441,19 +441,19 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>633285</v>
+        <v>633211</v>
       </c>
       <c r="B3" t="str">
-        <v>SUCEDANEO QUESO TIPO GOUDA 1 KG</v>
+        <v>QUESO EDAM ASTURIANA KG</v>
       </c>
       <c r="C3" t="str">
         <v/>
       </c>
       <c r="D3" t="str">
-        <v>33285</v>
+        <v>33211</v>
       </c>
       <c r="E3" t="str">
-        <v>6360</v>
+        <v>7160</v>
       </c>
       <c r="F3" t="str">
         <v>Por peso</v>
@@ -461,19 +461,19 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>633485</v>
+        <v>631082</v>
       </c>
       <c r="B4" t="str">
-        <v>QUESO GAUDA SOPROLE KG</v>
+        <v>QUESO GAUDA HOLANDES KG</v>
       </c>
       <c r="C4" t="str">
         <v/>
       </c>
       <c r="D4" t="str">
-        <v>33485</v>
+        <v>31082</v>
       </c>
       <c r="E4" t="str">
-        <v>7960</v>
+        <v>8760</v>
       </c>
       <c r="F4" t="str">
         <v>Por peso</v>
@@ -481,19 +481,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>631277</v>
+        <v>633032</v>
       </c>
       <c r="B5" t="str">
-        <v>JAMON PIERNA G1 RDA K9 KG</v>
+        <v>QUESO MANTECOSO QUILQUE PIEZA 8 KG</v>
       </c>
       <c r="C5" t="str">
         <v/>
       </c>
       <c r="D5" t="str">
-        <v>31277</v>
+        <v>33032</v>
       </c>
       <c r="E5" t="str">
-        <v>9996</v>
+        <v>8360</v>
       </c>
       <c r="F5" t="str">
         <v>Por peso</v>
@@ -501,19 +501,19 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>632166</v>
+        <v>635702</v>
       </c>
       <c r="B6" t="str">
-        <v>JAMON ARTESANAL G2 SJ KG</v>
+        <v>QUESO MANTECOSO RIO BUENO KG</v>
       </c>
       <c r="C6" t="str">
         <v/>
       </c>
       <c r="D6" t="str">
-        <v>32166</v>
+        <v>35702</v>
       </c>
       <c r="E6" t="str">
-        <v>6796</v>
+        <v>9160</v>
       </c>
       <c r="F6" t="str">
         <v>Por peso</v>
@@ -521,19 +521,19 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>636391</v>
+        <v>631000</v>
       </c>
       <c r="B7" t="str">
-        <v>LONGANIZA CHILENA PACEL KG</v>
+        <v>QUESO MANTECOSO RIO BUENO LAMINADO 5KG</v>
       </c>
       <c r="C7" t="str">
         <v/>
       </c>
       <c r="D7" t="str">
-        <v>36391</v>
+        <v>31000</v>
       </c>
       <c r="E7" t="str">
-        <v>6996</v>
+        <v>10760</v>
       </c>
       <c r="F7" t="str">
         <v>Por peso</v>
@@ -541,19 +541,19 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>632005</v>
+        <v>631030</v>
       </c>
       <c r="B8" t="str">
-        <v>SALAME AHUMADO CORT. SJ KG</v>
+        <v>QUESO RANCO LAMINADO COLUN KG</v>
       </c>
       <c r="C8" t="str">
         <v/>
       </c>
       <c r="D8" t="str">
-        <v>32005</v>
+        <v>31030</v>
       </c>
       <c r="E8" t="str">
-        <v>11996</v>
+        <v>9960</v>
       </c>
       <c r="F8" t="str">
         <v>Por peso</v>
@@ -561,19 +561,19 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>632643</v>
+        <v>633133</v>
       </c>
       <c r="B9" t="str">
-        <v>SALAME ITALIANO CORT. SAN JORGE KG</v>
+        <v>QUESO RANCO PIEZA COLUN KG</v>
       </c>
       <c r="C9" t="str">
         <v/>
       </c>
       <c r="D9" t="str">
-        <v>32643</v>
+        <v>33133</v>
       </c>
       <c r="E9" t="str">
-        <v>11996</v>
+        <v>7960</v>
       </c>
       <c r="F9" t="str">
         <v>Por peso</v>
@@ -581,19 +581,19 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>632071</v>
+        <v>634032</v>
       </c>
       <c r="B10" t="str">
-        <v>JAMON SANDWICH SUPER KG</v>
+        <v>QUESO CHANCO LAS PARCELAS DE VALDIVIA LAM.KG</v>
       </c>
       <c r="C10" t="str">
         <v/>
       </c>
       <c r="D10" t="str">
-        <v>32071</v>
+        <v>34032</v>
       </c>
       <c r="E10" t="str">
-        <v>5196</v>
+        <v>9960</v>
       </c>
       <c r="F10" t="str">
         <v>Por peso</v>
@@ -601,19 +601,19 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>631395</v>
+        <v>631277</v>
       </c>
       <c r="B11" t="str">
-        <v>MORTAD. JAMONADA RDA KG</v>
+        <v>JAMON PIERNA G1 RDA K9 KG</v>
       </c>
       <c r="C11" t="str">
         <v/>
       </c>
       <c r="D11" t="str">
-        <v>31395</v>
+        <v>31277</v>
       </c>
       <c r="E11" t="str">
-        <v>7196</v>
+        <v>9996</v>
       </c>
       <c r="F11" t="str">
         <v>Por peso</v>
@@ -621,19 +621,19 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>631422</v>
+        <v>632669</v>
       </c>
       <c r="B12" t="str">
-        <v>SALCHICHON CERV. LP KG</v>
+        <v>JAMON COLONIAL SJ KG</v>
       </c>
       <c r="C12" t="str">
         <v/>
       </c>
       <c r="D12" t="str">
-        <v>31422</v>
+        <v>32669</v>
       </c>
       <c r="E12" t="str">
-        <v>7960</v>
+        <v>8996</v>
       </c>
       <c r="F12" t="str">
         <v>Por peso</v>
@@ -641,19 +641,19 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>631391</v>
+        <v>632166</v>
       </c>
       <c r="B13" t="str">
-        <v>JAMON PIERNA ARTESANAL LP KG</v>
+        <v>JAMON ARTESANAL G2 SJ KG</v>
       </c>
       <c r="C13" t="str">
         <v/>
       </c>
       <c r="D13" t="str">
-        <v>31391</v>
+        <v>32166</v>
       </c>
       <c r="E13" t="str">
-        <v>9996</v>
+        <v>6796</v>
       </c>
       <c r="F13" t="str">
         <v>Por peso</v>
@@ -661,19 +661,19 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>635545</v>
+        <v>632063</v>
       </c>
       <c r="B14" t="str">
-        <v>JAMON PIERNA ARTESANAL SUPER CERDO KG</v>
+        <v>JAMON PIERNA G2 JP PF KILO</v>
       </c>
       <c r="C14" t="str">
         <v/>
       </c>
       <c r="D14" t="str">
-        <v>35545</v>
+        <v>32063</v>
       </c>
       <c r="E14" t="str">
-        <v>7396</v>
+        <v>7196</v>
       </c>
       <c r="F14" t="str">
         <v>Por peso</v>
@@ -681,19 +681,19 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>632063</v>
+        <v>631521</v>
       </c>
       <c r="B15" t="str">
-        <v>JAMON PIERNA G2 JP PF KILO</v>
+        <v>PECHUGA PAVO ACAR. LP KG</v>
       </c>
       <c r="C15" t="str">
         <v/>
       </c>
       <c r="D15" t="str">
-        <v>32063</v>
+        <v>31521</v>
       </c>
       <c r="E15" t="str">
-        <v>7196</v>
+        <v>11996</v>
       </c>
       <c r="F15" t="str">
         <v>Por peso</v>
@@ -701,16 +701,16 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>631521</v>
+        <v>634464</v>
       </c>
       <c r="B16" t="str">
-        <v>PECHUGA PAVO ACAR. LP KG</v>
+        <v>PECHUGA PAVO AHUM. LP KG</v>
       </c>
       <c r="C16" t="str">
         <v/>
       </c>
       <c r="D16" t="str">
-        <v>31521</v>
+        <v>34464</v>
       </c>
       <c r="E16" t="str">
         <v>11996</v>
@@ -721,16 +721,16 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>634464</v>
+        <v>631191</v>
       </c>
       <c r="B17" t="str">
-        <v>PECHUGA PAVO AHUM. LP KG</v>
+        <v>PECHUGA PAVO COCIDA LP KG</v>
       </c>
       <c r="C17" t="str">
         <v/>
       </c>
       <c r="D17" t="str">
-        <v>34464</v>
+        <v>31191</v>
       </c>
       <c r="E17" t="str">
         <v>11996</v>
@@ -741,19 +741,19 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>631191</v>
+        <v>631238</v>
       </c>
       <c r="B18" t="str">
-        <v>PECHUGA PAVO COCIDA LP KG</v>
+        <v>PECHUGA POLLO ASADA PF KG</v>
       </c>
       <c r="C18" t="str">
         <v/>
       </c>
       <c r="D18" t="str">
-        <v>31191</v>
+        <v>31238</v>
       </c>
       <c r="E18" t="str">
-        <v>11996</v>
+        <v>7996</v>
       </c>
       <c r="F18" t="str">
         <v>Por peso</v>
@@ -761,16 +761,16 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>631238</v>
+        <v>631236</v>
       </c>
       <c r="B19" t="str">
-        <v>PECHUGA POLLO ASADA PF KG</v>
+        <v>PECHUGA POLLO COCIDA H9 PF</v>
       </c>
       <c r="C19" t="str">
         <v/>
       </c>
       <c r="D19" t="str">
-        <v>31238</v>
+        <v>31236</v>
       </c>
       <c r="E19" t="str">
         <v>7996</v>
@@ -781,19 +781,19 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>631236</v>
+        <v>633100</v>
       </c>
       <c r="B20" t="str">
-        <v>PECHUGA POLLO COCIDA H9 PF</v>
+        <v>LONGANIZA ARTESANAL DON RODRIGO KG</v>
       </c>
       <c r="C20" t="str">
         <v/>
       </c>
       <c r="D20" t="str">
-        <v>31236</v>
+        <v>03100</v>
       </c>
       <c r="E20" t="str">
-        <v>7996</v>
+        <v>6796</v>
       </c>
       <c r="F20" t="str">
         <v>Por peso</v>
@@ -801,19 +801,19 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>633100</v>
+        <v>632005</v>
       </c>
       <c r="B21" t="str">
-        <v>LONGANIZA ARTESANAL DON RODRIGO KG</v>
+        <v>SALAME AHUMADO CORT. SJ KG</v>
       </c>
       <c r="C21" t="str">
         <v/>
       </c>
       <c r="D21" t="str">
-        <v>03100</v>
+        <v>32005</v>
       </c>
       <c r="E21" t="str">
-        <v>6796</v>
+        <v>11996</v>
       </c>
       <c r="F21" t="str">
         <v>Por peso</v>
@@ -821,19 +821,19 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>632096</v>
+        <v>632643</v>
       </c>
       <c r="B22" t="str">
-        <v>MORTAD. LISA SJ KG</v>
+        <v>SALAME ITALIANO CORT. SAN JORGE KG</v>
       </c>
       <c r="C22" t="str">
         <v/>
       </c>
       <c r="D22" t="str">
-        <v>32096</v>
+        <v>32643</v>
       </c>
       <c r="E22" t="str">
-        <v>3996</v>
+        <v>11996</v>
       </c>
       <c r="F22" t="str">
         <v>Por peso</v>
@@ -841,19 +841,19 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>631960</v>
+        <v>632096</v>
       </c>
       <c r="B23" t="str">
-        <v>QUESO CABEZA PACEL KG</v>
+        <v>MORTAD. LISA SJ KG</v>
       </c>
       <c r="C23" t="str">
         <v/>
       </c>
       <c r="D23" t="str">
-        <v>31960</v>
+        <v>32096</v>
       </c>
       <c r="E23" t="str">
-        <v>8796</v>
+        <v>3996</v>
       </c>
       <c r="F23" t="str">
         <v>Por peso</v>
@@ -861,19 +861,19 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>634446</v>
+        <v>631395</v>
       </c>
       <c r="B24" t="str">
-        <v>ARROLLADO HUASO PF GA KG</v>
+        <v>MORTAD. JAMONADA RDA KG</v>
       </c>
       <c r="C24" t="str">
         <v/>
       </c>
       <c r="D24" t="str">
-        <v>34446</v>
+        <v>31395</v>
       </c>
       <c r="E24" t="str">
-        <v>7596</v>
+        <v>7196</v>
       </c>
       <c r="F24" t="str">
         <v>Por peso</v>
@@ -881,19 +881,19 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>632172</v>
+        <v>633485</v>
       </c>
       <c r="B25" t="str">
-        <v>ARROLLADO LOMO CAJI SJ KG</v>
+        <v>QUESO GAUDA SOPROLE KG</v>
       </c>
       <c r="C25" t="str">
         <v/>
       </c>
       <c r="D25" t="str">
-        <v>32172</v>
+        <v>33485</v>
       </c>
       <c r="E25" t="str">
-        <v>7596</v>
+        <v>7960</v>
       </c>
       <c r="F25" t="str">
         <v>Por peso</v>
@@ -901,19 +901,19 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>632669</v>
+        <v>634011</v>
       </c>
       <c r="B26" t="str">
-        <v>JAMON COLONIAL SJ KG</v>
+        <v>QUESO MANTECOSO LAS PARCELAS DE VALDIVIA KG</v>
       </c>
       <c r="C26" t="str">
         <v/>
       </c>
       <c r="D26" t="str">
-        <v>32669</v>
+        <v>34011</v>
       </c>
       <c r="E26" t="str">
-        <v>8996</v>
+        <v>11960</v>
       </c>
       <c r="F26" t="str">
         <v>Por peso</v>
@@ -921,19 +921,19 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>634011</v>
+        <v>633212</v>
       </c>
       <c r="B27" t="str">
-        <v>QUESO MANTECOSO LAS PARCELAS DE VALDIVIA KG</v>
+        <v>QUESO GAUDA ASTURIANA KG</v>
       </c>
       <c r="C27" t="str">
         <v/>
       </c>
       <c r="D27" t="str">
-        <v>34011</v>
+        <v>33212</v>
       </c>
       <c r="E27" t="str">
-        <v>11960</v>
+        <v>7560</v>
       </c>
       <c r="F27" t="str">
         <v>Por peso</v>
@@ -941,19 +941,19 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>633211</v>
+        <v>636391</v>
       </c>
       <c r="B28" t="str">
-        <v>QUESO EDAM ASTURIANA KG</v>
+        <v>LONGANIZA CHILENA PACEL KG</v>
       </c>
       <c r="C28" t="str">
         <v/>
       </c>
       <c r="D28" t="str">
-        <v>33211</v>
+        <v>36391</v>
       </c>
       <c r="E28" t="str">
-        <v>7160</v>
+        <v>6996</v>
       </c>
       <c r="F28" t="str">
         <v>Por peso</v>
@@ -961,19 +961,19 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>631082</v>
+        <v>632071</v>
       </c>
       <c r="B29" t="str">
-        <v>QUESO GAUDA HOLANDES KG</v>
+        <v>JAMON SANDWICH SUPER KG</v>
       </c>
       <c r="C29" t="str">
         <v/>
       </c>
       <c r="D29" t="str">
-        <v>31082</v>
+        <v>32071</v>
       </c>
       <c r="E29" t="str">
-        <v>8760</v>
+        <v>5196</v>
       </c>
       <c r="F29" t="str">
         <v>Por peso</v>
@@ -981,19 +981,19 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>633032</v>
+        <v>631960</v>
       </c>
       <c r="B30" t="str">
-        <v>QUESO MANTECOSO QUILQUE PIEZA 8 KG</v>
+        <v>QUESO CABEZA PACEL KG</v>
       </c>
       <c r="C30" t="str">
         <v/>
       </c>
       <c r="D30" t="str">
-        <v>33032</v>
+        <v>31960</v>
       </c>
       <c r="E30" t="str">
-        <v>8360</v>
+        <v>8796</v>
       </c>
       <c r="F30" t="str">
         <v>Por peso</v>
@@ -1001,19 +1001,19 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>635702</v>
+        <v>634446</v>
       </c>
       <c r="B31" t="str">
-        <v>QUESO MANTECOSO RIO BUENO KG</v>
+        <v>ARROLLADO HUASO PF GA KG</v>
       </c>
       <c r="C31" t="str">
         <v/>
       </c>
       <c r="D31" t="str">
-        <v>35702</v>
+        <v>34446</v>
       </c>
       <c r="E31" t="str">
-        <v>9160</v>
+        <v>7596</v>
       </c>
       <c r="F31" t="str">
         <v>Por peso</v>
@@ -1021,19 +1021,19 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>631000</v>
+        <v>632172</v>
       </c>
       <c r="B32" t="str">
-        <v>QUESO MANTECOSO RIO BUENO LAMINADO 5KG</v>
+        <v>ARROLLADO LOMO CAJI SJ KG</v>
       </c>
       <c r="C32" t="str">
         <v/>
       </c>
       <c r="D32" t="str">
-        <v>31000</v>
+        <v>32172</v>
       </c>
       <c r="E32" t="str">
-        <v>10760</v>
+        <v>7596</v>
       </c>
       <c r="F32" t="str">
         <v>Por peso</v>
@@ -1041,19 +1041,19 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>631030</v>
+        <v>631422</v>
       </c>
       <c r="B33" t="str">
-        <v>QUESO RANCO LAMINADO COLUN KG</v>
+        <v>SALCHICHON CERV. LP KG</v>
       </c>
       <c r="C33" t="str">
         <v/>
       </c>
       <c r="D33" t="str">
-        <v>31030</v>
+        <v>31422</v>
       </c>
       <c r="E33" t="str">
-        <v>9960</v>
+        <v>7960</v>
       </c>
       <c r="F33" t="str">
         <v>Por peso</v>
@@ -1061,19 +1061,19 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>633133</v>
+        <v>631391</v>
       </c>
       <c r="B34" t="str">
-        <v>QUESO RANCO PIEZA COLUN KG</v>
+        <v>JAMON PIERNA ARTESANAL LP KG</v>
       </c>
       <c r="C34" t="str">
         <v/>
       </c>
       <c r="D34" t="str">
-        <v>33133</v>
+        <v>31391</v>
       </c>
       <c r="E34" t="str">
-        <v>7960</v>
+        <v>9996</v>
       </c>
       <c r="F34" t="str">
         <v>Por peso</v>
@@ -1081,19 +1081,19 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>634032</v>
+        <v>635545</v>
       </c>
       <c r="B35" t="str">
-        <v>QUESO CHANCO LAS PARCELAS DE VALDIVIA LAM.KG</v>
+        <v>JAMON PIERNA ARTESANAL SUPER CERDO KG</v>
       </c>
       <c r="C35" t="str">
         <v/>
       </c>
       <c r="D35" t="str">
-        <v>34032</v>
+        <v>35545</v>
       </c>
       <c r="E35" t="str">
-        <v>9960</v>
+        <v>7396</v>
       </c>
       <c r="F35" t="str">
         <v>Por peso</v>

--- a/MaestraPLU_Rotiseria.xlsx
+++ b/MaestraPLU_Rotiseria.xlsx
@@ -7213,7 +7213,7 @@
         <v>33336</v>
       </c>
       <c r="E341" t="str">
-        <v>14360</v>
+        <v>13160</v>
       </c>
       <c r="F341" t="str">
         <v>Por peso</v>
@@ -8673,7 +8673,7 @@
         <v>33337</v>
       </c>
       <c r="E414" t="str">
-        <v>14360</v>
+        <v>13160</v>
       </c>
       <c r="F414" t="str">
         <v>Por peso</v>

--- a/MaestraPLU_Rotiseria.xlsx
+++ b/MaestraPLU_Rotiseria.xlsx
@@ -441,19 +441,19 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>633211</v>
+        <v>633032</v>
       </c>
       <c r="B3" t="str">
-        <v>QUESO EDAM ASTURIANA KG</v>
+        <v>QUESO MANTECOSO QUILQUE PIEZA 8 KG</v>
       </c>
       <c r="C3" t="str">
         <v/>
       </c>
       <c r="D3" t="str">
-        <v>33211</v>
+        <v>33032</v>
       </c>
       <c r="E3" t="str">
-        <v>7160</v>
+        <v>8360</v>
       </c>
       <c r="F3" t="str">
         <v>Por peso</v>
@@ -461,19 +461,19 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>631082</v>
+        <v>635702</v>
       </c>
       <c r="B4" t="str">
-        <v>QUESO GAUDA HOLANDES KG</v>
+        <v>QUESO MANTECOSO RIO BUENO KG</v>
       </c>
       <c r="C4" t="str">
         <v/>
       </c>
       <c r="D4" t="str">
-        <v>31082</v>
+        <v>35702</v>
       </c>
       <c r="E4" t="str">
-        <v>8760</v>
+        <v>9160</v>
       </c>
       <c r="F4" t="str">
         <v>Por peso</v>
@@ -481,19 +481,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>633032</v>
+        <v>631000</v>
       </c>
       <c r="B5" t="str">
-        <v>QUESO MANTECOSO QUILQUE PIEZA 8 KG</v>
+        <v>QUESO MANTECOSO RIO BUENO LAMINADO 5KG</v>
       </c>
       <c r="C5" t="str">
         <v/>
       </c>
       <c r="D5" t="str">
-        <v>33032</v>
+        <v>31000</v>
       </c>
       <c r="E5" t="str">
-        <v>8360</v>
+        <v>10760</v>
       </c>
       <c r="F5" t="str">
         <v>Por peso</v>
@@ -501,19 +501,19 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>635702</v>
+        <v>631030</v>
       </c>
       <c r="B6" t="str">
-        <v>QUESO MANTECOSO RIO BUENO KG</v>
+        <v>QUESO RANCO LAMINADO COLUN KG</v>
       </c>
       <c r="C6" t="str">
         <v/>
       </c>
       <c r="D6" t="str">
-        <v>35702</v>
+        <v>31030</v>
       </c>
       <c r="E6" t="str">
-        <v>9160</v>
+        <v>9960</v>
       </c>
       <c r="F6" t="str">
         <v>Por peso</v>
@@ -521,19 +521,19 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>631000</v>
+        <v>633133</v>
       </c>
       <c r="B7" t="str">
-        <v>QUESO MANTECOSO RIO BUENO LAMINADO 5KG</v>
+        <v>QUESO RANCO PIEZA COLUN KG</v>
       </c>
       <c r="C7" t="str">
         <v/>
       </c>
       <c r="D7" t="str">
-        <v>31000</v>
+        <v>33133</v>
       </c>
       <c r="E7" t="str">
-        <v>10760</v>
+        <v>7960</v>
       </c>
       <c r="F7" t="str">
         <v>Por peso</v>
@@ -541,16 +541,16 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>631030</v>
+        <v>634032</v>
       </c>
       <c r="B8" t="str">
-        <v>QUESO RANCO LAMINADO COLUN KG</v>
+        <v>QUESO CHANCO LAS PARCELAS DE VALDIVIA LAM.KG</v>
       </c>
       <c r="C8" t="str">
         <v/>
       </c>
       <c r="D8" t="str">
-        <v>31030</v>
+        <v>34032</v>
       </c>
       <c r="E8" t="str">
         <v>9960</v>
@@ -561,19 +561,19 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>633133</v>
+        <v>631277</v>
       </c>
       <c r="B9" t="str">
-        <v>QUESO RANCO PIEZA COLUN KG</v>
+        <v>JAMON PIERNA G1 RDA K9 KG</v>
       </c>
       <c r="C9" t="str">
         <v/>
       </c>
       <c r="D9" t="str">
-        <v>33133</v>
+        <v>31277</v>
       </c>
       <c r="E9" t="str">
-        <v>7960</v>
+        <v>9996</v>
       </c>
       <c r="F9" t="str">
         <v>Por peso</v>
@@ -581,19 +581,19 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>634032</v>
+        <v>632669</v>
       </c>
       <c r="B10" t="str">
-        <v>QUESO CHANCO LAS PARCELAS DE VALDIVIA LAM.KG</v>
+        <v>JAMON COLONIAL SJ KG</v>
       </c>
       <c r="C10" t="str">
         <v/>
       </c>
       <c r="D10" t="str">
-        <v>34032</v>
+        <v>32669</v>
       </c>
       <c r="E10" t="str">
-        <v>9960</v>
+        <v>8996</v>
       </c>
       <c r="F10" t="str">
         <v>Por peso</v>
@@ -601,19 +601,19 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>631277</v>
+        <v>632166</v>
       </c>
       <c r="B11" t="str">
-        <v>JAMON PIERNA G1 RDA K9 KG</v>
+        <v>JAMON ARTESANAL G2 SJ KG</v>
       </c>
       <c r="C11" t="str">
         <v/>
       </c>
       <c r="D11" t="str">
-        <v>31277</v>
+        <v>32166</v>
       </c>
       <c r="E11" t="str">
-        <v>9996</v>
+        <v>6796</v>
       </c>
       <c r="F11" t="str">
         <v>Por peso</v>
@@ -621,19 +621,19 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>632669</v>
+        <v>632063</v>
       </c>
       <c r="B12" t="str">
-        <v>JAMON COLONIAL SJ KG</v>
+        <v>JAMON PIERNA G2 JP PF KILO</v>
       </c>
       <c r="C12" t="str">
         <v/>
       </c>
       <c r="D12" t="str">
-        <v>32669</v>
+        <v>32063</v>
       </c>
       <c r="E12" t="str">
-        <v>8996</v>
+        <v>7196</v>
       </c>
       <c r="F12" t="str">
         <v>Por peso</v>
@@ -641,19 +641,19 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>632166</v>
+        <v>631521</v>
       </c>
       <c r="B13" t="str">
-        <v>JAMON ARTESANAL G2 SJ KG</v>
+        <v>PECHUGA PAVO ACAR. LP KG</v>
       </c>
       <c r="C13" t="str">
         <v/>
       </c>
       <c r="D13" t="str">
-        <v>32166</v>
+        <v>31521</v>
       </c>
       <c r="E13" t="str">
-        <v>6796</v>
+        <v>11996</v>
       </c>
       <c r="F13" t="str">
         <v>Por peso</v>
@@ -661,19 +661,19 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>632063</v>
+        <v>634464</v>
       </c>
       <c r="B14" t="str">
-        <v>JAMON PIERNA G2 JP PF KILO</v>
+        <v>PECHUGA PAVO AHUM. LP KG</v>
       </c>
       <c r="C14" t="str">
         <v/>
       </c>
       <c r="D14" t="str">
-        <v>32063</v>
+        <v>34464</v>
       </c>
       <c r="E14" t="str">
-        <v>7196</v>
+        <v>11996</v>
       </c>
       <c r="F14" t="str">
         <v>Por peso</v>
@@ -681,16 +681,16 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>631521</v>
+        <v>631191</v>
       </c>
       <c r="B15" t="str">
-        <v>PECHUGA PAVO ACAR. LP KG</v>
+        <v>PECHUGA PAVO COCIDA LP KG</v>
       </c>
       <c r="C15" t="str">
         <v/>
       </c>
       <c r="D15" t="str">
-        <v>31521</v>
+        <v>31191</v>
       </c>
       <c r="E15" t="str">
         <v>11996</v>
@@ -701,19 +701,19 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>634464</v>
+        <v>631238</v>
       </c>
       <c r="B16" t="str">
-        <v>PECHUGA PAVO AHUM. LP KG</v>
+        <v>PECHUGA POLLO ASADA PF KG</v>
       </c>
       <c r="C16" t="str">
         <v/>
       </c>
       <c r="D16" t="str">
-        <v>34464</v>
+        <v>31238</v>
       </c>
       <c r="E16" t="str">
-        <v>11996</v>
+        <v>7996</v>
       </c>
       <c r="F16" t="str">
         <v>Por peso</v>
@@ -721,19 +721,19 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>631191</v>
+        <v>631236</v>
       </c>
       <c r="B17" t="str">
-        <v>PECHUGA PAVO COCIDA LP KG</v>
+        <v>PECHUGA POLLO COCIDA H9 PF</v>
       </c>
       <c r="C17" t="str">
         <v/>
       </c>
       <c r="D17" t="str">
-        <v>31191</v>
+        <v>31236</v>
       </c>
       <c r="E17" t="str">
-        <v>11996</v>
+        <v>7996</v>
       </c>
       <c r="F17" t="str">
         <v>Por peso</v>
@@ -741,19 +741,19 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>631238</v>
+        <v>633100</v>
       </c>
       <c r="B18" t="str">
-        <v>PECHUGA POLLO ASADA PF KG</v>
+        <v>LONGANIZA ARTESANAL DON RODRIGO KG</v>
       </c>
       <c r="C18" t="str">
         <v/>
       </c>
       <c r="D18" t="str">
-        <v>31238</v>
+        <v>03100</v>
       </c>
       <c r="E18" t="str">
-        <v>7996</v>
+        <v>6796</v>
       </c>
       <c r="F18" t="str">
         <v>Por peso</v>
@@ -761,19 +761,19 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>631236</v>
+        <v>632005</v>
       </c>
       <c r="B19" t="str">
-        <v>PECHUGA POLLO COCIDA H9 PF</v>
+        <v>SALAME AHUMADO CORT. SJ KG</v>
       </c>
       <c r="C19" t="str">
         <v/>
       </c>
       <c r="D19" t="str">
-        <v>31236</v>
+        <v>32005</v>
       </c>
       <c r="E19" t="str">
-        <v>7996</v>
+        <v>11996</v>
       </c>
       <c r="F19" t="str">
         <v>Por peso</v>
@@ -781,19 +781,19 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>633100</v>
+        <v>632643</v>
       </c>
       <c r="B20" t="str">
-        <v>LONGANIZA ARTESANAL DON RODRIGO KG</v>
+        <v>SALAME ITALIANO CORT. SAN JORGE KG</v>
       </c>
       <c r="C20" t="str">
         <v/>
       </c>
       <c r="D20" t="str">
-        <v>03100</v>
+        <v>32643</v>
       </c>
       <c r="E20" t="str">
-        <v>6796</v>
+        <v>11996</v>
       </c>
       <c r="F20" t="str">
         <v>Por peso</v>
@@ -801,19 +801,19 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>632005</v>
+        <v>632096</v>
       </c>
       <c r="B21" t="str">
-        <v>SALAME AHUMADO CORT. SJ KG</v>
+        <v>MORTAD. LISA SJ KG</v>
       </c>
       <c r="C21" t="str">
         <v/>
       </c>
       <c r="D21" t="str">
-        <v>32005</v>
+        <v>32096</v>
       </c>
       <c r="E21" t="str">
-        <v>11996</v>
+        <v>3996</v>
       </c>
       <c r="F21" t="str">
         <v>Por peso</v>
@@ -821,19 +821,19 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>632643</v>
+        <v>631395</v>
       </c>
       <c r="B22" t="str">
-        <v>SALAME ITALIANO CORT. SAN JORGE KG</v>
+        <v>MORTAD. JAMONADA RDA KG</v>
       </c>
       <c r="C22" t="str">
         <v/>
       </c>
       <c r="D22" t="str">
-        <v>32643</v>
+        <v>31395</v>
       </c>
       <c r="E22" t="str">
-        <v>11996</v>
+        <v>7196</v>
       </c>
       <c r="F22" t="str">
         <v>Por peso</v>
@@ -841,19 +841,19 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>632096</v>
+        <v>633485</v>
       </c>
       <c r="B23" t="str">
-        <v>MORTAD. LISA SJ KG</v>
+        <v>QUESO GAUDA SOPROLE KG</v>
       </c>
       <c r="C23" t="str">
         <v/>
       </c>
       <c r="D23" t="str">
-        <v>32096</v>
+        <v>33485</v>
       </c>
       <c r="E23" t="str">
-        <v>3996</v>
+        <v>7960</v>
       </c>
       <c r="F23" t="str">
         <v>Por peso</v>
@@ -861,19 +861,19 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>631395</v>
+        <v>634011</v>
       </c>
       <c r="B24" t="str">
-        <v>MORTAD. JAMONADA RDA KG</v>
+        <v>QUESO MANTECOSO LAS PARCELAS DE VALDIVIA KG</v>
       </c>
       <c r="C24" t="str">
         <v/>
       </c>
       <c r="D24" t="str">
-        <v>31395</v>
+        <v>34011</v>
       </c>
       <c r="E24" t="str">
-        <v>7196</v>
+        <v>11960</v>
       </c>
       <c r="F24" t="str">
         <v>Por peso</v>
@@ -881,19 +881,19 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>633485</v>
+        <v>633212</v>
       </c>
       <c r="B25" t="str">
-        <v>QUESO GAUDA SOPROLE KG</v>
+        <v>QUESO GAUDA ASTURIANA KG</v>
       </c>
       <c r="C25" t="str">
         <v/>
       </c>
       <c r="D25" t="str">
-        <v>33485</v>
+        <v>33212</v>
       </c>
       <c r="E25" t="str">
-        <v>7960</v>
+        <v>7560</v>
       </c>
       <c r="F25" t="str">
         <v>Por peso</v>
@@ -901,19 +901,19 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>634011</v>
+        <v>636391</v>
       </c>
       <c r="B26" t="str">
-        <v>QUESO MANTECOSO LAS PARCELAS DE VALDIVIA KG</v>
+        <v>LONGANIZA CHILENA PACEL KG</v>
       </c>
       <c r="C26" t="str">
         <v/>
       </c>
       <c r="D26" t="str">
-        <v>34011</v>
+        <v>36391</v>
       </c>
       <c r="E26" t="str">
-        <v>11960</v>
+        <v>6996</v>
       </c>
       <c r="F26" t="str">
         <v>Por peso</v>
@@ -921,19 +921,19 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>633212</v>
+        <v>632071</v>
       </c>
       <c r="B27" t="str">
-        <v>QUESO GAUDA ASTURIANA KG</v>
+        <v>JAMON SANDWICH SUPER KG</v>
       </c>
       <c r="C27" t="str">
         <v/>
       </c>
       <c r="D27" t="str">
-        <v>33212</v>
+        <v>32071</v>
       </c>
       <c r="E27" t="str">
-        <v>7560</v>
+        <v>5196</v>
       </c>
       <c r="F27" t="str">
         <v>Por peso</v>
@@ -941,19 +941,19 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>636391</v>
+        <v>631960</v>
       </c>
       <c r="B28" t="str">
-        <v>LONGANIZA CHILENA PACEL KG</v>
+        <v>QUESO CABEZA PACEL KG</v>
       </c>
       <c r="C28" t="str">
         <v/>
       </c>
       <c r="D28" t="str">
-        <v>36391</v>
+        <v>31960</v>
       </c>
       <c r="E28" t="str">
-        <v>6996</v>
+        <v>8796</v>
       </c>
       <c r="F28" t="str">
         <v>Por peso</v>
@@ -961,19 +961,19 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>632071</v>
+        <v>634446</v>
       </c>
       <c r="B29" t="str">
-        <v>JAMON SANDWICH SUPER KG</v>
+        <v>ARROLLADO HUASO PF GA KG</v>
       </c>
       <c r="C29" t="str">
         <v/>
       </c>
       <c r="D29" t="str">
-        <v>32071</v>
+        <v>34446</v>
       </c>
       <c r="E29" t="str">
-        <v>5196</v>
+        <v>7596</v>
       </c>
       <c r="F29" t="str">
         <v>Por peso</v>
@@ -981,19 +981,19 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>631960</v>
+        <v>632172</v>
       </c>
       <c r="B30" t="str">
-        <v>QUESO CABEZA PACEL KG</v>
+        <v>ARROLLADO LOMO CAJI SJ KG</v>
       </c>
       <c r="C30" t="str">
         <v/>
       </c>
       <c r="D30" t="str">
-        <v>31960</v>
+        <v>32172</v>
       </c>
       <c r="E30" t="str">
-        <v>8796</v>
+        <v>7596</v>
       </c>
       <c r="F30" t="str">
         <v>Por peso</v>
@@ -1001,19 +1001,19 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>634446</v>
+        <v>631422</v>
       </c>
       <c r="B31" t="str">
-        <v>ARROLLADO HUASO PF GA KG</v>
+        <v>SALCHICHON CERV. LP KG</v>
       </c>
       <c r="C31" t="str">
         <v/>
       </c>
       <c r="D31" t="str">
-        <v>34446</v>
+        <v>31422</v>
       </c>
       <c r="E31" t="str">
-        <v>7596</v>
+        <v>7960</v>
       </c>
       <c r="F31" t="str">
         <v>Por peso</v>
@@ -1021,19 +1021,19 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>632172</v>
+        <v>631391</v>
       </c>
       <c r="B32" t="str">
-        <v>ARROLLADO LOMO CAJI SJ KG</v>
+        <v>JAMON PIERNA ARTESANAL LP KG</v>
       </c>
       <c r="C32" t="str">
         <v/>
       </c>
       <c r="D32" t="str">
-        <v>32172</v>
+        <v>31391</v>
       </c>
       <c r="E32" t="str">
-        <v>7596</v>
+        <v>9996</v>
       </c>
       <c r="F32" t="str">
         <v>Por peso</v>
@@ -1041,19 +1041,19 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>631422</v>
+        <v>635545</v>
       </c>
       <c r="B33" t="str">
-        <v>SALCHICHON CERV. LP KG</v>
+        <v>JAMON PIERNA ARTESANAL SUPER CERDO KG</v>
       </c>
       <c r="C33" t="str">
         <v/>
       </c>
       <c r="D33" t="str">
-        <v>31422</v>
+        <v>35545</v>
       </c>
       <c r="E33" t="str">
-        <v>7960</v>
+        <v>7396</v>
       </c>
       <c r="F33" t="str">
         <v>Por peso</v>
@@ -1061,19 +1061,19 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>631391</v>
+        <v>633119</v>
       </c>
       <c r="B34" t="str">
-        <v>JAMON PIERNA ARTESANAL LP KG</v>
+        <v>ACEITUNA S/AMARGO 100/120 BOLSA</v>
       </c>
       <c r="C34" t="str">
         <v/>
       </c>
       <c r="D34" t="str">
-        <v>31391</v>
+        <v>33119</v>
       </c>
       <c r="E34" t="str">
-        <v>9996</v>
+        <v>3996</v>
       </c>
       <c r="F34" t="str">
         <v>Por peso</v>
@@ -1081,19 +1081,19 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>635545</v>
+        <v>631085</v>
       </c>
       <c r="B35" t="str">
-        <v>JAMON PIERNA ARTESANAL SUPER CERDO KG</v>
+        <v>AJI EN ESCABECHE</v>
       </c>
       <c r="C35" t="str">
         <v/>
       </c>
       <c r="D35" t="str">
-        <v>35545</v>
+        <v>41085</v>
       </c>
       <c r="E35" t="str">
-        <v>7396</v>
+        <v>1390</v>
       </c>
       <c r="F35" t="str">
         <v>Por peso</v>
@@ -1101,19 +1101,19 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>633119</v>
+        <v>632698</v>
       </c>
       <c r="B36" t="str">
-        <v>ACEITUNA S/AMARGO 100/120 BOLSA</v>
+        <v>MORTAD. ALEMANA ARUNA ARTESANAL</v>
       </c>
       <c r="C36" t="str">
         <v/>
       </c>
       <c r="D36" t="str">
-        <v>33119</v>
+        <v>32698</v>
       </c>
       <c r="E36" t="str">
-        <v>3996</v>
+        <v>1996</v>
       </c>
       <c r="F36" t="str">
         <v>Por peso</v>
@@ -1121,19 +1121,19 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>631085</v>
+        <v>632680</v>
       </c>
       <c r="B37" t="str">
-        <v>AJI EN ESCABECHE</v>
+        <v>MORTAD. LISA ARUNA ARTESANAL</v>
       </c>
       <c r="C37" t="str">
         <v/>
       </c>
       <c r="D37" t="str">
-        <v>41085</v>
+        <v>32680</v>
       </c>
       <c r="E37" t="str">
-        <v>1390</v>
+        <v>1196</v>
       </c>
       <c r="F37" t="str">
         <v>Por peso</v>
@@ -1141,39 +1141,39 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>632698</v>
+        <v>632652</v>
       </c>
       <c r="B38" t="str">
-        <v>MORTAD. ALEMANA ARUNA ARTESANAL</v>
+        <v>SALCHICHON CERV. ARUNA ARTESANAL</v>
       </c>
       <c r="C38" t="str">
         <v/>
       </c>
       <c r="D38" t="str">
-        <v>32698</v>
+        <v>32652</v>
       </c>
       <c r="E38" t="str">
-        <v>1996</v>
+        <v>3290</v>
       </c>
       <c r="F38" t="str">
-        <v>Por peso</v>
+        <v>Por cantidad</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>632680</v>
+        <v>632158</v>
       </c>
       <c r="B39" t="str">
-        <v>MORTAD. LISA ARUNA ARTESANAL</v>
+        <v>PICKLE GRANEL KG. SEVILLANA</v>
       </c>
       <c r="C39" t="str">
         <v/>
       </c>
       <c r="D39" t="str">
-        <v>32680</v>
+        <v>32158</v>
       </c>
       <c r="E39" t="str">
-        <v>1196</v>
+        <v>1476</v>
       </c>
       <c r="F39" t="str">
         <v>Por peso</v>
@@ -1181,39 +1181,39 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>632652</v>
+        <v>632161</v>
       </c>
       <c r="B40" t="str">
-        <v>SALCHICHON CERV. ARUNA ARTESANAL</v>
+        <v>AMERICANA GRANEL</v>
       </c>
       <c r="C40" t="str">
         <v/>
       </c>
       <c r="D40" t="str">
-        <v>32652</v>
+        <v>32161</v>
       </c>
       <c r="E40" t="str">
-        <v>3290</v>
+        <v>1490</v>
       </c>
       <c r="F40" t="str">
-        <v>Por cantidad</v>
+        <v>Por peso</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>632158</v>
+        <v>632163</v>
       </c>
       <c r="B41" t="str">
-        <v>PICKLE GRANEL KG. SEVILLANA</v>
+        <v>ACEITUNA SEVILLANA KG SOLIS</v>
       </c>
       <c r="C41" t="str">
         <v/>
       </c>
       <c r="D41" t="str">
-        <v>32158</v>
+        <v>32163</v>
       </c>
       <c r="E41" t="str">
-        <v>1476</v>
+        <v>9396</v>
       </c>
       <c r="F41" t="str">
         <v>Por peso</v>
@@ -1221,19 +1221,19 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>632161</v>
+        <v>632008</v>
       </c>
       <c r="B42" t="str">
-        <v>AMERICANA GRANEL</v>
+        <v>ACEITUNAS EXTRA AZAPA KG.</v>
       </c>
       <c r="C42" t="str">
         <v/>
       </c>
       <c r="D42" t="str">
-        <v>32161</v>
+        <v>32008</v>
       </c>
       <c r="E42" t="str">
-        <v>1490</v>
+        <v>2396</v>
       </c>
       <c r="F42" t="str">
         <v>Por peso</v>
@@ -1241,19 +1241,19 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>632163</v>
+        <v>632525</v>
       </c>
       <c r="B43" t="str">
-        <v>ACEITUNA SEVILLANA KG SOLIS</v>
+        <v>ACEITUNA AZAPA BANQUETE</v>
       </c>
       <c r="C43" t="str">
         <v/>
       </c>
       <c r="D43" t="str">
-        <v>32163</v>
+        <v>32525</v>
       </c>
       <c r="E43" t="str">
-        <v>9396</v>
+        <v>3765</v>
       </c>
       <c r="F43" t="str">
         <v>Por peso</v>
@@ -1261,19 +1261,19 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>632008</v>
+        <v>632518</v>
       </c>
       <c r="B44" t="str">
-        <v>ACEITUNAS EXTRA AZAPA KG.</v>
+        <v>ACEITUNAS SEVILLANA COCKTEIL KL</v>
       </c>
       <c r="C44" t="str">
         <v/>
       </c>
       <c r="D44" t="str">
-        <v>32008</v>
+        <v>32518</v>
       </c>
       <c r="E44" t="str">
-        <v>2396</v>
+        <v>2169</v>
       </c>
       <c r="F44" t="str">
         <v>Por peso</v>
@@ -1281,19 +1281,19 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>632525</v>
+        <v>632576</v>
       </c>
       <c r="B45" t="str">
-        <v>ACEITUNA AZAPA BANQUETE</v>
+        <v>ACEITUNA DESHUESADA NEGRA KG</v>
       </c>
       <c r="C45" t="str">
         <v/>
       </c>
       <c r="D45" t="str">
-        <v>32525</v>
+        <v>32576</v>
       </c>
       <c r="E45" t="str">
-        <v>3765</v>
+        <v>3596</v>
       </c>
       <c r="F45" t="str">
         <v>Por peso</v>
@@ -1301,19 +1301,19 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>632518</v>
+        <v>634454</v>
       </c>
       <c r="B46" t="str">
-        <v>ACEITUNAS SEVILLANA COCKTEIL KL</v>
+        <v>CEBOLLA PERLA GRANEL KG SOL</v>
       </c>
       <c r="C46" t="str">
         <v/>
       </c>
       <c r="D46" t="str">
-        <v>32518</v>
+        <v>34454</v>
       </c>
       <c r="E46" t="str">
-        <v>2169</v>
+        <v>2229</v>
       </c>
       <c r="F46" t="str">
         <v>Por peso</v>
@@ -1321,19 +1321,19 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>632576</v>
+        <v>631253</v>
       </c>
       <c r="B47" t="str">
-        <v>ACEITUNA DESHUESADA NEGRA KG</v>
+        <v>AJI ORO GRANEL SOL KG</v>
       </c>
       <c r="C47" t="str">
         <v/>
       </c>
       <c r="D47" t="str">
-        <v>32576</v>
+        <v>31253</v>
       </c>
       <c r="E47" t="str">
-        <v>3596</v>
+        <v>1290</v>
       </c>
       <c r="F47" t="str">
         <v>Por peso</v>
@@ -1341,19 +1341,19 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>634454</v>
+        <v>632151</v>
       </c>
       <c r="B48" t="str">
-        <v>CEBOLLA PERLA GRANEL KG SOL</v>
+        <v>ACEITUNA VERDE GRANEL</v>
       </c>
       <c r="C48" t="str">
         <v/>
       </c>
       <c r="D48" t="str">
-        <v>34454</v>
+        <v>32151</v>
       </c>
       <c r="E48" t="str">
-        <v>2229</v>
+        <v>2596</v>
       </c>
       <c r="F48" t="str">
         <v>Por peso</v>
@@ -1361,19 +1361,19 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>631253</v>
+        <v>632516</v>
       </c>
       <c r="B49" t="str">
-        <v>AJI ORO GRANEL SOL KG</v>
+        <v>PICKLE KG</v>
       </c>
       <c r="C49" t="str">
         <v/>
       </c>
       <c r="D49" t="str">
-        <v>31253</v>
+        <v>32516</v>
       </c>
       <c r="E49" t="str">
-        <v>1290</v>
+        <v>990</v>
       </c>
       <c r="F49" t="str">
         <v>Por peso</v>
@@ -1381,19 +1381,19 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>632151</v>
+        <v>632513</v>
       </c>
       <c r="B50" t="str">
-        <v>ACEITUNA VERDE GRANEL</v>
+        <v>ACEITUNA P/PINCHANGA KG</v>
       </c>
       <c r="C50" t="str">
         <v/>
       </c>
       <c r="D50" t="str">
-        <v>32151</v>
+        <v>32513</v>
       </c>
       <c r="E50" t="str">
-        <v>2596</v>
+        <v>1190</v>
       </c>
       <c r="F50" t="str">
         <v>Por peso</v>
@@ -1401,19 +1401,19 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>632516</v>
+        <v>632103</v>
       </c>
       <c r="B51" t="str">
-        <v>PICKLE KG</v>
+        <v>LONGANIZA VON UNGER 4 UNI</v>
       </c>
       <c r="C51" t="str">
         <v/>
       </c>
       <c r="D51" t="str">
-        <v>32516</v>
+        <v>32103</v>
       </c>
       <c r="E51" t="str">
-        <v>990</v>
+        <v>1990</v>
       </c>
       <c r="F51" t="str">
         <v>Por peso</v>
@@ -1421,19 +1421,19 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>632513</v>
+        <v>632451</v>
       </c>
       <c r="B52" t="str">
-        <v>ACEITUNA P/PINCHANGA KG</v>
+        <v>MORTAD.AVE PIMENTON ARUNA</v>
       </c>
       <c r="C52" t="str">
         <v/>
       </c>
       <c r="D52" t="str">
-        <v>32513</v>
+        <v>32451</v>
       </c>
       <c r="E52" t="str">
-        <v>1190</v>
+        <v>1596</v>
       </c>
       <c r="F52" t="str">
         <v>Por peso</v>
@@ -1441,19 +1441,19 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>632103</v>
+        <v>631728</v>
       </c>
       <c r="B53" t="str">
-        <v>LONGANIZA VON UNGER 4 UNI</v>
+        <v>MALAYA DE VACUNO ARUNA ART.</v>
       </c>
       <c r="C53" t="str">
         <v/>
       </c>
       <c r="D53" t="str">
-        <v>32103</v>
+        <v>31728</v>
       </c>
       <c r="E53" t="str">
-        <v>1990</v>
+        <v>3696</v>
       </c>
       <c r="F53" t="str">
         <v>Por peso</v>
@@ -1461,19 +1461,19 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>632451</v>
+        <v>632421</v>
       </c>
       <c r="B54" t="str">
-        <v>MORTAD.AVE PIMENTON ARUNA</v>
+        <v>ARROLLADO HUASITO VON UNGER KG</v>
       </c>
       <c r="C54" t="str">
         <v/>
       </c>
       <c r="D54" t="str">
-        <v>32451</v>
+        <v>32421</v>
       </c>
       <c r="E54" t="str">
-        <v>1596</v>
+        <v>4196</v>
       </c>
       <c r="F54" t="str">
         <v>Por peso</v>
@@ -1481,19 +1481,19 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>631728</v>
+        <v>632703</v>
       </c>
       <c r="B55" t="str">
-        <v>MALAYA DE VACUNO ARUNA ART.</v>
+        <v>ARROLLADO DE COPA ARUNA ARTESANAL</v>
       </c>
       <c r="C55" t="str">
         <v/>
       </c>
       <c r="D55" t="str">
-        <v>31728</v>
+        <v>32703</v>
       </c>
       <c r="E55" t="str">
-        <v>3696</v>
+        <v>1990</v>
       </c>
       <c r="F55" t="str">
         <v>Por peso</v>
@@ -1501,19 +1501,19 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>632421</v>
+        <v>632658</v>
       </c>
       <c r="B56" t="str">
-        <v>ARROLLADO HUASITO VON UNGER KG</v>
+        <v>GORDAS ARTESANAL KG ARUNA</v>
       </c>
       <c r="C56" t="str">
         <v/>
       </c>
       <c r="D56" t="str">
-        <v>32421</v>
+        <v>32658</v>
       </c>
       <c r="E56" t="str">
-        <v>4196</v>
+        <v>1890</v>
       </c>
       <c r="F56" t="str">
         <v>Por peso</v>
@@ -1521,19 +1521,19 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>632703</v>
+        <v>631027</v>
       </c>
       <c r="B57" t="str">
-        <v>ARROLLADO DE COPA ARUNA ARTESANAL</v>
+        <v>PERNIL ARUNA ARTESANAL</v>
       </c>
       <c r="C57" t="str">
         <v/>
       </c>
       <c r="D57" t="str">
-        <v>32703</v>
+        <v>31027</v>
       </c>
       <c r="E57" t="str">
-        <v>1990</v>
+        <v>1890</v>
       </c>
       <c r="F57" t="str">
         <v>Por peso</v>
@@ -1541,19 +1541,19 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>632658</v>
+        <v>632153</v>
       </c>
       <c r="B58" t="str">
-        <v>GORDAS ARTESANAL KG ARUNA</v>
+        <v>PRIETA KG PAULINA</v>
       </c>
       <c r="C58" t="str">
         <v/>
       </c>
       <c r="D58" t="str">
-        <v>32658</v>
+        <v>32153</v>
       </c>
       <c r="E58" t="str">
-        <v>1890</v>
+        <v>2716</v>
       </c>
       <c r="F58" t="str">
         <v>Por peso</v>
@@ -1561,19 +1561,19 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>631027</v>
+        <v>632191</v>
       </c>
       <c r="B59" t="str">
-        <v>PERNIL ARUNA ARTESANAL</v>
+        <v>LONGANIZA KG PAULINA</v>
       </c>
       <c r="C59" t="str">
         <v/>
       </c>
       <c r="D59" t="str">
-        <v>31027</v>
+        <v>32191</v>
       </c>
       <c r="E59" t="str">
-        <v>1890</v>
+        <v>1916</v>
       </c>
       <c r="F59" t="str">
         <v>Por peso</v>
@@ -1581,19 +1581,19 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>632153</v>
+        <v>632537</v>
       </c>
       <c r="B60" t="str">
-        <v>PRIETA KG PAULINA</v>
+        <v>LONGANIZA FASTDELI (317) KG.</v>
       </c>
       <c r="C60" t="str">
         <v/>
       </c>
       <c r="D60" t="str">
-        <v>32153</v>
+        <v>32537</v>
       </c>
       <c r="E60" t="str">
-        <v>2716</v>
+        <v>1676</v>
       </c>
       <c r="F60" t="str">
         <v>Por peso</v>
@@ -1601,19 +1601,19 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>632191</v>
+        <v>632033</v>
       </c>
       <c r="B61" t="str">
-        <v>LONGANIZA KG PAULINA</v>
+        <v>CHORIZO PARRILLERO SUPER</v>
       </c>
       <c r="C61" t="str">
         <v/>
       </c>
       <c r="D61" t="str">
-        <v>32191</v>
+        <v>32033</v>
       </c>
       <c r="E61" t="str">
-        <v>1916</v>
+        <v>3116</v>
       </c>
       <c r="F61" t="str">
         <v>Por peso</v>
@@ -1621,19 +1621,19 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>632537</v>
+        <v>632329</v>
       </c>
       <c r="B62" t="str">
-        <v>LONGANIZA FASTDELI (317) KG.</v>
+        <v>CHORIZO VALDIVIA KILO</v>
       </c>
       <c r="C62" t="str">
         <v/>
       </c>
       <c r="D62" t="str">
-        <v>32537</v>
+        <v>32329</v>
       </c>
       <c r="E62" t="str">
-        <v>1676</v>
+        <v>2990</v>
       </c>
       <c r="F62" t="str">
         <v>Por peso</v>
@@ -1641,19 +1641,19 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>632033</v>
+        <v>632538</v>
       </c>
       <c r="B63" t="str">
-        <v>CHORIZO PARRILLERO SUPER</v>
+        <v>CHORIZO FASTDELI (319) KG.</v>
       </c>
       <c r="C63" t="str">
         <v/>
       </c>
       <c r="D63" t="str">
-        <v>32033</v>
+        <v>32538</v>
       </c>
       <c r="E63" t="str">
-        <v>3116</v>
+        <v>2396</v>
       </c>
       <c r="F63" t="str">
         <v>Por peso</v>
@@ -1661,19 +1661,19 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>632329</v>
+        <v>631900</v>
       </c>
       <c r="B64" t="str">
-        <v>CHORIZO VALDIVIA KILO</v>
+        <v>CHORIZO RECETA ALEMANA 5 UNID.</v>
       </c>
       <c r="C64" t="str">
         <v/>
       </c>
       <c r="D64" t="str">
-        <v>32329</v>
+        <v>01900</v>
       </c>
       <c r="E64" t="str">
-        <v>2990</v>
+        <v>1590</v>
       </c>
       <c r="F64" t="str">
         <v>Por peso</v>
@@ -1681,19 +1681,19 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>632538</v>
+        <v>632093</v>
       </c>
       <c r="B65" t="str">
-        <v>CHORIZO FASTDELI (319) KG.</v>
+        <v>MORTAD. JAMONADA POLLO SUPER KG</v>
       </c>
       <c r="C65" t="str">
         <v/>
       </c>
       <c r="D65" t="str">
-        <v>32538</v>
+        <v>32093</v>
       </c>
       <c r="E65" t="str">
-        <v>2396</v>
+        <v>7596</v>
       </c>
       <c r="F65" t="str">
         <v>Por peso</v>
@@ -1701,19 +1701,19 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>631900</v>
+        <v>632539</v>
       </c>
       <c r="B66" t="str">
-        <v>CHORIZO RECETA ALEMANA 5 UNID.</v>
+        <v>MORT. JAMONADA FASTD.(331)KG</v>
       </c>
       <c r="C66" t="str">
         <v/>
       </c>
       <c r="D66" t="str">
-        <v>01900</v>
+        <v>32539</v>
       </c>
       <c r="E66" t="str">
-        <v>1590</v>
+        <v>1940</v>
       </c>
       <c r="F66" t="str">
         <v>Por peso</v>
@@ -1721,19 +1721,19 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>632093</v>
+        <v>632088</v>
       </c>
       <c r="B67" t="str">
-        <v>MORTAD. JAMONADA POLLO SUPER KG</v>
+        <v>MORTAD. FINA PF</v>
       </c>
       <c r="C67" t="str">
         <v/>
       </c>
       <c r="D67" t="str">
-        <v>32093</v>
+        <v>32088</v>
       </c>
       <c r="E67" t="str">
-        <v>7596</v>
+        <v>4996</v>
       </c>
       <c r="F67" t="str">
         <v>Por peso</v>
@@ -1741,19 +1741,19 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>632539</v>
+        <v>632079</v>
       </c>
       <c r="B68" t="str">
-        <v>MORT. JAMONADA FASTD.(331)KG</v>
+        <v>MILANESA HUEVO J.K.</v>
       </c>
       <c r="C68" t="str">
         <v/>
       </c>
       <c r="D68" t="str">
-        <v>32539</v>
+        <v>32079</v>
       </c>
       <c r="E68" t="str">
-        <v>1940</v>
+        <v>3002</v>
       </c>
       <c r="F68" t="str">
         <v>Por peso</v>
@@ -1761,19 +1761,19 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>632088</v>
+        <v>632365</v>
       </c>
       <c r="B69" t="str">
-        <v>MORTAD. FINA PF</v>
+        <v>MARISCAL CUGAT</v>
       </c>
       <c r="C69" t="str">
         <v/>
       </c>
       <c r="D69" t="str">
-        <v>32088</v>
+        <v>32365</v>
       </c>
       <c r="E69" t="str">
-        <v>4996</v>
+        <v>2996</v>
       </c>
       <c r="F69" t="str">
         <v>Por peso</v>
@@ -1781,19 +1781,19 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>632079</v>
+        <v>632174</v>
       </c>
       <c r="B70" t="str">
-        <v>MILANESA HUEVO J.K.</v>
+        <v>JAMONADA SJ KG</v>
       </c>
       <c r="C70" t="str">
         <v/>
       </c>
       <c r="D70" t="str">
-        <v>32079</v>
+        <v>32174</v>
       </c>
       <c r="E70" t="str">
-        <v>3002</v>
+        <v>7196</v>
       </c>
       <c r="F70" t="str">
         <v>Por peso</v>
@@ -1801,19 +1801,19 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>632365</v>
+        <v>632073</v>
       </c>
       <c r="B71" t="str">
-        <v>MARISCAL CUGAT</v>
+        <v>JAMONADA DE POLLO D9 PF KG.</v>
       </c>
       <c r="C71" t="str">
         <v/>
       </c>
       <c r="D71" t="str">
-        <v>32365</v>
+        <v>32073</v>
       </c>
       <c r="E71" t="str">
-        <v>2996</v>
+        <v>9996</v>
       </c>
       <c r="F71" t="str">
         <v>Por peso</v>
@@ -1821,19 +1821,19 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>632174</v>
+        <v>632149</v>
       </c>
       <c r="B72" t="str">
-        <v>JAMONADA SJ KG</v>
+        <v>ARROLLADO ITALIANO S.JORGE</v>
       </c>
       <c r="C72" t="str">
         <v/>
       </c>
       <c r="D72" t="str">
-        <v>32174</v>
+        <v>32149</v>
       </c>
       <c r="E72" t="str">
-        <v>7196</v>
+        <v>2916</v>
       </c>
       <c r="F72" t="str">
         <v>Por peso</v>
@@ -1841,19 +1841,19 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>632073</v>
+        <v>632061</v>
       </c>
       <c r="B73" t="str">
-        <v>JAMONADA DE POLLO D9 PF KG.</v>
+        <v>JAMON AHUMADO SUPER KG</v>
       </c>
       <c r="C73" t="str">
         <v/>
       </c>
       <c r="D73" t="str">
-        <v>32073</v>
+        <v>32061</v>
       </c>
       <c r="E73" t="str">
-        <v>9996</v>
+        <v>8796</v>
       </c>
       <c r="F73" t="str">
         <v>Por peso</v>
@@ -1861,19 +1861,19 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>632149</v>
+        <v>632068</v>
       </c>
       <c r="B74" t="str">
-        <v>ARROLLADO ITALIANO S.JORGE</v>
+        <v>JAMON PIERNA ACARAM. G1 WINTERKG</v>
       </c>
       <c r="C74" t="str">
         <v/>
       </c>
       <c r="D74" t="str">
-        <v>32149</v>
+        <v>32068</v>
       </c>
       <c r="E74" t="str">
-        <v>2916</v>
+        <v>11996</v>
       </c>
       <c r="F74" t="str">
         <v>Por peso</v>
@@ -1881,19 +1881,19 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>632061</v>
+        <v>632171</v>
       </c>
       <c r="B75" t="str">
-        <v>JAMON AHUMADO SUPER KG</v>
+        <v>ARROLLADO HUASO CON AJI SJ KG</v>
       </c>
       <c r="C75" t="str">
         <v/>
       </c>
       <c r="D75" t="str">
-        <v>32061</v>
+        <v>32171</v>
       </c>
       <c r="E75" t="str">
-        <v>8796</v>
+        <v>9596</v>
       </c>
       <c r="F75" t="str">
         <v>Por peso</v>
@@ -1901,19 +1901,19 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>632068</v>
+        <v>632533</v>
       </c>
       <c r="B76" t="str">
-        <v>JAMON PIERNA ACARAM. G1 WINTERKG</v>
+        <v>JAMON COCIDO FASTDELLI KG.</v>
       </c>
       <c r="C76" t="str">
         <v/>
       </c>
       <c r="D76" t="str">
-        <v>32068</v>
+        <v>32533</v>
       </c>
       <c r="E76" t="str">
-        <v>11996</v>
+        <v>2396</v>
       </c>
       <c r="F76" t="str">
         <v>Por peso</v>
@@ -1921,19 +1921,19 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>632171</v>
+        <v>632058</v>
       </c>
       <c r="B77" t="str">
-        <v>ARROLLADO HUASO CON AJI SJ KG</v>
+        <v>FIAMBRE JAMON SANDWICH WINTER KG</v>
       </c>
       <c r="C77" t="str">
         <v/>
       </c>
       <c r="D77" t="str">
-        <v>32171</v>
+        <v>32058</v>
       </c>
       <c r="E77" t="str">
-        <v>9596</v>
+        <v>7996</v>
       </c>
       <c r="F77" t="str">
         <v>Por peso</v>
@@ -1941,19 +1941,19 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>632533</v>
+        <v>632052</v>
       </c>
       <c r="B78" t="str">
-        <v>JAMON COCIDO FASTDELLI KG.</v>
+        <v>FIAMBRE JAMON SANDWICH SJ KG</v>
       </c>
       <c r="C78" t="str">
         <v/>
       </c>
       <c r="D78" t="str">
-        <v>32533</v>
+        <v>32052</v>
       </c>
       <c r="E78" t="str">
-        <v>2396</v>
+        <v>7196</v>
       </c>
       <c r="F78" t="str">
         <v>Por peso</v>
@@ -1961,19 +1961,19 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>632058</v>
+        <v>632123</v>
       </c>
       <c r="B79" t="str">
-        <v>FIAMBRE JAMON SANDWICH WINTER KG</v>
+        <v>SALCHICHON CERV. PF CS DELGADO</v>
       </c>
       <c r="C79" t="str">
         <v/>
       </c>
       <c r="D79" t="str">
-        <v>32058</v>
+        <v>32123</v>
       </c>
       <c r="E79" t="str">
-        <v>7996</v>
+        <v>8996</v>
       </c>
       <c r="F79" t="str">
         <v>Por peso</v>
@@ -1981,19 +1981,19 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>632052</v>
+        <v>632125</v>
       </c>
       <c r="B80" t="str">
-        <v>FIAMBRE JAMON SANDWICH SJ KG</v>
+        <v>SALCHICHON CERV. WINTER KG</v>
       </c>
       <c r="C80" t="str">
         <v/>
       </c>
       <c r="D80" t="str">
-        <v>32052</v>
+        <v>32125</v>
       </c>
       <c r="E80" t="str">
-        <v>7196</v>
+        <v>6996</v>
       </c>
       <c r="F80" t="str">
         <v>Por peso</v>
@@ -2001,19 +2001,19 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>632123</v>
+        <v>632563</v>
       </c>
       <c r="B81" t="str">
-        <v>SALCHICHON CERV. PF CS DELGADO</v>
+        <v>SALCHICHON CERV. PAULINA KG.</v>
       </c>
       <c r="C81" t="str">
         <v/>
       </c>
       <c r="D81" t="str">
-        <v>32123</v>
+        <v>32563</v>
       </c>
       <c r="E81" t="str">
-        <v>8996</v>
+        <v>3396</v>
       </c>
       <c r="F81" t="str">
         <v>Por peso</v>
@@ -2021,19 +2021,19 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>632125</v>
+        <v>632016</v>
       </c>
       <c r="B82" t="str">
-        <v>SALCHICHON CERV. WINTER KG</v>
+        <v>COPPA ITALIANA IT PF</v>
       </c>
       <c r="C82" t="str">
         <v/>
       </c>
       <c r="D82" t="str">
-        <v>32125</v>
+        <v>32016</v>
       </c>
       <c r="E82" t="str">
-        <v>6996</v>
+        <v>7196</v>
       </c>
       <c r="F82" t="str">
         <v>Por peso</v>
@@ -2041,19 +2041,19 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>632563</v>
+        <v>632117</v>
       </c>
       <c r="B83" t="str">
-        <v>SALCHICHON CERV. PAULINA KG.</v>
+        <v>SALAMIN AHUMADO SUPER</v>
       </c>
       <c r="C83" t="str">
         <v/>
       </c>
       <c r="D83" t="str">
-        <v>32563</v>
+        <v>32117</v>
       </c>
       <c r="E83" t="str">
-        <v>3396</v>
+        <v>4636</v>
       </c>
       <c r="F83" t="str">
         <v>Por peso</v>
@@ -2061,19 +2061,19 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>632016</v>
+        <v>632011</v>
       </c>
       <c r="B84" t="str">
-        <v>COPPA ITALIANA IT PF</v>
+        <v>BRAZUELO 1</v>
       </c>
       <c r="C84" t="str">
         <v/>
       </c>
       <c r="D84" t="str">
-        <v>32016</v>
+        <v>32011</v>
       </c>
       <c r="E84" t="str">
-        <v>7196</v>
+        <v>1541</v>
       </c>
       <c r="F84" t="str">
         <v>Por peso</v>
@@ -2081,19 +2081,19 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>632117</v>
+        <v>632312</v>
       </c>
       <c r="B85" t="str">
-        <v>SALAMIN AHUMADO SUPER</v>
+        <v>PECHUGA COCIDA SOPRAVAL KG</v>
       </c>
       <c r="C85" t="str">
         <v/>
       </c>
       <c r="D85" t="str">
-        <v>32117</v>
+        <v>32312</v>
       </c>
       <c r="E85" t="str">
-        <v>4636</v>
+        <v>12996</v>
       </c>
       <c r="F85" t="str">
         <v>Por peso</v>
@@ -2101,19 +2101,19 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>632011</v>
+        <v>632313</v>
       </c>
       <c r="B86" t="str">
-        <v>BRAZUELO 1</v>
+        <v>PECHUGA ASADA SOPRAVAL KG</v>
       </c>
       <c r="C86" t="str">
         <v/>
       </c>
       <c r="D86" t="str">
-        <v>32011</v>
+        <v>32313</v>
       </c>
       <c r="E86" t="str">
-        <v>1541</v>
+        <v>12996</v>
       </c>
       <c r="F86" t="str">
         <v>Por peso</v>
@@ -2121,19 +2121,19 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>632312</v>
+        <v>632097</v>
       </c>
       <c r="B87" t="str">
-        <v>PECHUGA COCIDA SOPRAVAL KG</v>
+        <v>MORTAD. POLLO PIMENTON SUPER KG</v>
       </c>
       <c r="C87" t="str">
         <v/>
       </c>
       <c r="D87" t="str">
-        <v>32312</v>
+        <v>32097</v>
       </c>
       <c r="E87" t="str">
-        <v>12996</v>
+        <v>6196</v>
       </c>
       <c r="F87" t="str">
         <v>Por peso</v>
@@ -2141,19 +2141,19 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>632313</v>
+        <v>632415</v>
       </c>
       <c r="B88" t="str">
-        <v>PECHUGA ASADA SOPRAVAL KG</v>
+        <v>PECHUGA PAVO AHUM.ARIZTIA KG 8011BF</v>
       </c>
       <c r="C88" t="str">
         <v/>
       </c>
       <c r="D88" t="str">
-        <v>32313</v>
+        <v>32415</v>
       </c>
       <c r="E88" t="str">
-        <v>12996</v>
+        <v>13996</v>
       </c>
       <c r="F88" t="str">
         <v>Por peso</v>
@@ -2161,19 +2161,19 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>632097</v>
+        <v>632087</v>
       </c>
       <c r="B89" t="str">
-        <v>MORTAD. POLLO PIMENTON SUPER KG</v>
+        <v>MORTAD. LISA C/PEREJIL JK KG</v>
       </c>
       <c r="C89" t="str">
         <v/>
       </c>
       <c r="D89" t="str">
-        <v>32097</v>
+        <v>32087</v>
       </c>
       <c r="E89" t="str">
-        <v>6196</v>
+        <v>1396</v>
       </c>
       <c r="F89" t="str">
         <v>Por peso</v>
@@ -2181,19 +2181,19 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>632415</v>
+        <v>632402</v>
       </c>
       <c r="B90" t="str">
-        <v>PECHUGA PAVO AHUM.ARIZTIA KG 8011BF</v>
+        <v>MORTAD.LISA 200GR</v>
       </c>
       <c r="C90" t="str">
         <v/>
       </c>
       <c r="D90" t="str">
-        <v>32415</v>
+        <v>32402</v>
       </c>
       <c r="E90" t="str">
-        <v>13996</v>
+        <v>779</v>
       </c>
       <c r="F90" t="str">
         <v>Por peso</v>
@@ -2201,19 +2201,19 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>632087</v>
+        <v>634513</v>
       </c>
       <c r="B91" t="str">
-        <v>MORTAD. LISA C/PEREJIL JK KG</v>
+        <v>ARROLLADO LOMO S AJI SJ KG</v>
       </c>
       <c r="C91" t="str">
         <v/>
       </c>
       <c r="D91" t="str">
-        <v>32087</v>
+        <v>34513</v>
       </c>
       <c r="E91" t="str">
-        <v>1396</v>
+        <v>9596</v>
       </c>
       <c r="F91" t="str">
         <v>Por peso</v>
@@ -2221,19 +2221,19 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>632402</v>
+        <v>634505</v>
       </c>
       <c r="B92" t="str">
-        <v>MORTAD.LISA 200GR</v>
+        <v>JAMON PIERNA ACAR. G1 JG PF KILO</v>
       </c>
       <c r="C92" t="str">
         <v/>
       </c>
       <c r="D92" t="str">
-        <v>32402</v>
+        <v>34505</v>
       </c>
       <c r="E92" t="str">
-        <v>779</v>
+        <v>12396</v>
       </c>
       <c r="F92" t="str">
         <v>Por peso</v>
@@ -2241,19 +2241,19 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>634513</v>
+        <v>634506</v>
       </c>
       <c r="B93" t="str">
-        <v>ARROLLADO LOMO S AJI SJ KG</v>
+        <v>JAMON PAVO ACAR.SOPRAVAL KG</v>
       </c>
       <c r="C93" t="str">
         <v/>
       </c>
       <c r="D93" t="str">
-        <v>34513</v>
+        <v>34506</v>
       </c>
       <c r="E93" t="str">
-        <v>9596</v>
+        <v>14996</v>
       </c>
       <c r="F93" t="str">
         <v>Por peso</v>
@@ -2261,19 +2261,19 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>634505</v>
+        <v>634496</v>
       </c>
       <c r="B94" t="str">
-        <v>JAMON PIERNA ACAR. G1 JG PF KILO</v>
+        <v>PECHUGA AHUMADA POLLO SUPER KG</v>
       </c>
       <c r="C94" t="str">
         <v/>
       </c>
       <c r="D94" t="str">
-        <v>34505</v>
+        <v>34496</v>
       </c>
       <c r="E94" t="str">
-        <v>12396</v>
+        <v>10996</v>
       </c>
       <c r="F94" t="str">
         <v>Por peso</v>
@@ -2281,19 +2281,19 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>634506</v>
+        <v>634495</v>
       </c>
       <c r="B95" t="str">
-        <v>JAMON PAVO ACAR.SOPRAVAL KG</v>
+        <v>PECHUGA ACARAMELADA POLLO SUPER KG</v>
       </c>
       <c r="C95" t="str">
         <v/>
       </c>
       <c r="D95" t="str">
-        <v>34506</v>
+        <v>34495</v>
       </c>
       <c r="E95" t="str">
-        <v>14996</v>
+        <v>10996</v>
       </c>
       <c r="F95" t="str">
         <v>Por peso</v>
@@ -2301,19 +2301,19 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>634496</v>
+        <v>632603</v>
       </c>
       <c r="B96" t="str">
-        <v>PECHUGA AHUMADA POLLO SUPER KG</v>
+        <v>ARROLLADO LOMO PORCIONADO DON RODRIGO</v>
       </c>
       <c r="C96" t="str">
         <v/>
       </c>
       <c r="D96" t="str">
-        <v>34496</v>
+        <v>32603</v>
       </c>
       <c r="E96" t="str">
-        <v>10996</v>
+        <v>7960</v>
       </c>
       <c r="F96" t="str">
         <v>Por peso</v>
@@ -2321,19 +2321,19 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>634495</v>
+        <v>632119</v>
       </c>
       <c r="B97" t="str">
-        <v>PECHUGA ACARAMELADA POLLO SUPER KG</v>
+        <v>SALCHICHON CERVEZA EXT.DOMENCH</v>
       </c>
       <c r="C97" t="str">
         <v/>
       </c>
       <c r="D97" t="str">
-        <v>34495</v>
+        <v>32119</v>
       </c>
       <c r="E97" t="str">
-        <v>10996</v>
+        <v>2916</v>
       </c>
       <c r="F97" t="str">
         <v>Por peso</v>
@@ -2341,19 +2341,19 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>632603</v>
+        <v>632167</v>
       </c>
       <c r="B98" t="str">
-        <v>ARROLLADO LOMO PORCIONADO DON RODRIGO</v>
+        <v>SALCHICHON CERV.PAVO DOMENCH</v>
       </c>
       <c r="C98" t="str">
         <v/>
       </c>
       <c r="D98" t="str">
-        <v>32603</v>
+        <v>32167</v>
       </c>
       <c r="E98" t="str">
-        <v>7960</v>
+        <v>1478</v>
       </c>
       <c r="F98" t="str">
         <v>Por peso</v>
@@ -2361,19 +2361,19 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>632119</v>
+        <v>632602</v>
       </c>
       <c r="B99" t="str">
-        <v>SALCHICHON CERVEZA EXT.DOMENCH</v>
+        <v>MORT.JAMONADA EL POZO KG</v>
       </c>
       <c r="C99" t="str">
         <v/>
       </c>
       <c r="D99" t="str">
-        <v>32119</v>
+        <v>32602</v>
       </c>
       <c r="E99" t="str">
-        <v>2916</v>
+        <v>1996</v>
       </c>
       <c r="F99" t="str">
         <v>Por peso</v>
@@ -2381,19 +2381,19 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>632167</v>
+        <v>631592</v>
       </c>
       <c r="B100" t="str">
-        <v>SALCHICHON CERV.PAVO DOMENCH</v>
+        <v>JAMON PLANCHADO CATALANA KG</v>
       </c>
       <c r="C100" t="str">
         <v/>
       </c>
       <c r="D100" t="str">
-        <v>32167</v>
+        <v>31592</v>
       </c>
       <c r="E100" t="str">
-        <v>1478</v>
+        <v>4760</v>
       </c>
       <c r="F100" t="str">
         <v>Por peso</v>
@@ -2401,19 +2401,19 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>632602</v>
+        <v>631058</v>
       </c>
       <c r="B101" t="str">
-        <v>MORT.JAMONADA EL POZO KG</v>
+        <v>PICHANGA ECONOMICA CUGAT KG</v>
       </c>
       <c r="C101" t="str">
         <v/>
       </c>
       <c r="D101" t="str">
-        <v>32602</v>
+        <v>31058</v>
       </c>
       <c r="E101" t="str">
-        <v>1996</v>
+        <v>4996</v>
       </c>
       <c r="F101" t="str">
         <v>Por peso</v>
@@ -2421,39 +2421,39 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>631592</v>
+        <v>631623</v>
       </c>
       <c r="B102" t="str">
-        <v>JAMON PLANCHADO CATALANA KG</v>
+        <v>PATITAS DE CERDO COCIDA DEVA</v>
       </c>
       <c r="C102" t="str">
         <v/>
       </c>
       <c r="D102" t="str">
-        <v>31592</v>
+        <v>31623</v>
       </c>
       <c r="E102" t="str">
-        <v>4760</v>
+        <v>490</v>
       </c>
       <c r="F102" t="str">
-        <v>Por peso</v>
+        <v>Por cantidad</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>631058</v>
+        <v>632780</v>
       </c>
       <c r="B103" t="str">
-        <v>PICHANGA ECONOMICA CUGAT KG</v>
+        <v>MORTAD. JAMONADA MYLPAN</v>
       </c>
       <c r="C103" t="str">
         <v/>
       </c>
       <c r="D103" t="str">
-        <v>31058</v>
+        <v>32780</v>
       </c>
       <c r="E103" t="str">
-        <v>4996</v>
+        <v>2796</v>
       </c>
       <c r="F103" t="str">
         <v>Por peso</v>
@@ -2461,39 +2461,39 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>631623</v>
+        <v>632740</v>
       </c>
       <c r="B104" t="str">
-        <v>PATITAS DE CERDO COCIDA DEVA</v>
+        <v>ARROLLADO HUASO MYLPAN</v>
       </c>
       <c r="C104" t="str">
         <v/>
       </c>
       <c r="D104" t="str">
-        <v>31623</v>
+        <v>32740</v>
       </c>
       <c r="E104" t="str">
-        <v>490</v>
+        <v>3196</v>
       </c>
       <c r="F104" t="str">
-        <v>Por cantidad</v>
+        <v>Por peso</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>632780</v>
+        <v>632750</v>
       </c>
       <c r="B105" t="str">
-        <v>MORTAD. JAMONADA MYLPAN</v>
+        <v>ARROLLADO LOMO MYLPAN</v>
       </c>
       <c r="C105" t="str">
         <v/>
       </c>
       <c r="D105" t="str">
-        <v>32780</v>
+        <v>32750</v>
       </c>
       <c r="E105" t="str">
-        <v>2796</v>
+        <v>3196</v>
       </c>
       <c r="F105" t="str">
         <v>Por peso</v>
@@ -2501,19 +2501,19 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>632740</v>
+        <v>632760</v>
       </c>
       <c r="B106" t="str">
-        <v>ARROLLADO HUASO MYLPAN</v>
+        <v>SALCHICHON CERV. MYLPAN KG</v>
       </c>
       <c r="C106" t="str">
         <v/>
       </c>
       <c r="D106" t="str">
-        <v>32740</v>
+        <v>32760</v>
       </c>
       <c r="E106" t="str">
-        <v>3196</v>
+        <v>2796</v>
       </c>
       <c r="F106" t="str">
         <v>Por peso</v>
@@ -2521,19 +2521,19 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>632750</v>
+        <v>631059</v>
       </c>
       <c r="B107" t="str">
-        <v>ARROLLADO LOMO MYLPAN</v>
+        <v>PICHANGA ESPECIAL CUGAT KG</v>
       </c>
       <c r="C107" t="str">
         <v/>
       </c>
       <c r="D107" t="str">
-        <v>32750</v>
+        <v>31059</v>
       </c>
       <c r="E107" t="str">
-        <v>3196</v>
+        <v>6796</v>
       </c>
       <c r="F107" t="str">
         <v>Por peso</v>
@@ -2541,19 +2541,19 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>632760</v>
+        <v>632631</v>
       </c>
       <c r="B108" t="str">
-        <v>SALCHICHON CERV. MYLPAN KG</v>
+        <v>JAMONADA ARUNA ARTESANAL</v>
       </c>
       <c r="C108" t="str">
         <v/>
       </c>
       <c r="D108" t="str">
-        <v>32760</v>
+        <v>32631</v>
       </c>
       <c r="E108" t="str">
-        <v>2796</v>
+        <v>2196</v>
       </c>
       <c r="F108" t="str">
         <v>Por peso</v>
@@ -2561,19 +2561,19 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>631059</v>
+        <v>631626</v>
       </c>
       <c r="B109" t="str">
-        <v>PICHANGA ESPECIAL CUGAT KG</v>
+        <v>CHULETA CENTRO AHUMADO DEVA KG</v>
       </c>
       <c r="C109" t="str">
         <v/>
       </c>
       <c r="D109" t="str">
-        <v>31059</v>
+        <v>31626</v>
       </c>
       <c r="E109" t="str">
-        <v>6796</v>
+        <v>3990</v>
       </c>
       <c r="F109" t="str">
         <v>Por peso</v>
@@ -2581,19 +2581,19 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>632631</v>
+        <v>632622</v>
       </c>
       <c r="B110" t="str">
-        <v>JAMONADA ARUNA ARTESANAL</v>
+        <v>PERNIL COCIDO DEVA KG</v>
       </c>
       <c r="C110" t="str">
         <v/>
       </c>
       <c r="D110" t="str">
-        <v>32631</v>
+        <v>32622</v>
       </c>
       <c r="E110" t="str">
-        <v>2196</v>
+        <v>1990</v>
       </c>
       <c r="F110" t="str">
         <v>Por peso</v>
@@ -2601,19 +2601,19 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>631626</v>
+        <v>631190</v>
       </c>
       <c r="B111" t="str">
-        <v>CHULETA CENTRO AHUMADO DEVA KG</v>
+        <v>JAMON PIERNA MOLDE DEVA KG.</v>
       </c>
       <c r="C111" t="str">
         <v/>
       </c>
       <c r="D111" t="str">
-        <v>31626</v>
+        <v>31190</v>
       </c>
       <c r="E111" t="str">
-        <v>3990</v>
+        <v>6396</v>
       </c>
       <c r="F111" t="str">
         <v>Por peso</v>
@@ -2621,19 +2621,19 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>632622</v>
+        <v>631261</v>
       </c>
       <c r="B112" t="str">
-        <v>PERNIL COCIDO DEVA KG</v>
+        <v>CEBOLLA PERLA KILO LAS LOMAS</v>
       </c>
       <c r="C112" t="str">
         <v/>
       </c>
       <c r="D112" t="str">
-        <v>32622</v>
+        <v>31261</v>
       </c>
       <c r="E112" t="str">
-        <v>1990</v>
+        <v>4996</v>
       </c>
       <c r="F112" t="str">
         <v>Por peso</v>
@@ -2641,19 +2641,19 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>631190</v>
+        <v>631398</v>
       </c>
       <c r="B113" t="str">
-        <v>JAMON PIERNA MOLDE DEVA KG.</v>
+        <v>ACEITUNA SEVILLANA SAJ. KILO</v>
       </c>
       <c r="C113" t="str">
         <v/>
       </c>
       <c r="D113" t="str">
-        <v>31190</v>
+        <v>31398</v>
       </c>
       <c r="E113" t="str">
-        <v>6396</v>
+        <v>1669</v>
       </c>
       <c r="F113" t="str">
         <v>Por peso</v>
@@ -2661,16 +2661,16 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>631261</v>
+        <v>631353</v>
       </c>
       <c r="B114" t="str">
-        <v>CEBOLLA PERLA KILO LAS LOMAS</v>
+        <v>ACEITUNA RELLENA C/AJI</v>
       </c>
       <c r="C114" t="str">
         <v/>
       </c>
       <c r="D114" t="str">
-        <v>31261</v>
+        <v>31353</v>
       </c>
       <c r="E114" t="str">
         <v>4996</v>
@@ -2681,19 +2681,19 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>631398</v>
+        <v>632657</v>
       </c>
       <c r="B115" t="str">
-        <v>ACEITUNA SEVILLANA SAJ. KILO</v>
+        <v>CHORIZO 500GR SAN PABLO</v>
       </c>
       <c r="C115" t="str">
         <v/>
       </c>
       <c r="D115" t="str">
-        <v>31398</v>
+        <v>32657</v>
       </c>
       <c r="E115" t="str">
-        <v>1669</v>
+        <v>1436</v>
       </c>
       <c r="F115" t="str">
         <v>Por peso</v>
@@ -2701,19 +2701,19 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>631353</v>
+        <v>634489</v>
       </c>
       <c r="B116" t="str">
-        <v>ACEITUNA RELLENA C/AJI</v>
+        <v>COPA SAN PABLO KG</v>
       </c>
       <c r="C116" t="str">
         <v/>
       </c>
       <c r="D116" t="str">
-        <v>31353</v>
+        <v>34489</v>
       </c>
       <c r="E116" t="str">
-        <v>4996</v>
+        <v>6996</v>
       </c>
       <c r="F116" t="str">
         <v>Por peso</v>
@@ -2721,19 +2721,19 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>632657</v>
+        <v>631549</v>
       </c>
       <c r="B117" t="str">
-        <v>CHORIZO 500GR SAN PABLO</v>
+        <v>ARROLLADO LOMO CATALANA C/AJI</v>
       </c>
       <c r="C117" t="str">
         <v/>
       </c>
       <c r="D117" t="str">
-        <v>32657</v>
+        <v>31549</v>
       </c>
       <c r="E117" t="str">
-        <v>1436</v>
+        <v>4360</v>
       </c>
       <c r="F117" t="str">
         <v>Por peso</v>
@@ -2741,19 +2741,19 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>634489</v>
+        <v>631591</v>
       </c>
       <c r="B118" t="str">
-        <v>COPA SAN PABLO KG</v>
+        <v>ARROLLADO LOMO CATALANA S/AJI KG</v>
       </c>
       <c r="C118" t="str">
         <v/>
       </c>
       <c r="D118" t="str">
-        <v>34489</v>
+        <v>31591</v>
       </c>
       <c r="E118" t="str">
-        <v>6996</v>
+        <v>4360</v>
       </c>
       <c r="F118" t="str">
         <v>Por peso</v>
@@ -2761,19 +2761,19 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>631549</v>
+        <v>632676</v>
       </c>
       <c r="B119" t="str">
-        <v>ARROLLADO LOMO CATALANA C/AJI</v>
+        <v>JAMONADA DE AVE SJ KG</v>
       </c>
       <c r="C119" t="str">
         <v/>
       </c>
       <c r="D119" t="str">
-        <v>31549</v>
+        <v>32676</v>
       </c>
       <c r="E119" t="str">
-        <v>4360</v>
+        <v>6996</v>
       </c>
       <c r="F119" t="str">
         <v>Por peso</v>
@@ -2781,19 +2781,19 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>631591</v>
+        <v>632671</v>
       </c>
       <c r="B120" t="str">
-        <v>ARROLLADO LOMO CATALANA S/AJI KG</v>
+        <v>JAMON ACARAMELADO SJ KG</v>
       </c>
       <c r="C120" t="str">
         <v/>
       </c>
       <c r="D120" t="str">
-        <v>31591</v>
+        <v>32671</v>
       </c>
       <c r="E120" t="str">
-        <v>4360</v>
+        <v>12996</v>
       </c>
       <c r="F120" t="str">
         <v>Por peso</v>
@@ -2801,19 +2801,19 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>632676</v>
+        <v>632674</v>
       </c>
       <c r="B121" t="str">
-        <v>JAMONADA DE AVE SJ KG</v>
+        <v>MORTAD. POLLO SJ KG</v>
       </c>
       <c r="C121" t="str">
         <v/>
       </c>
       <c r="D121" t="str">
-        <v>32676</v>
+        <v>32674</v>
       </c>
       <c r="E121" t="str">
-        <v>6996</v>
+        <v>4996</v>
       </c>
       <c r="F121" t="str">
         <v>Por peso</v>
@@ -2821,19 +2821,19 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>632671</v>
+        <v>632568</v>
       </c>
       <c r="B122" t="str">
-        <v>JAMON ACARAMELADO SJ KG</v>
+        <v>MORTAD. JAMONADA WINTER KG</v>
       </c>
       <c r="C122" t="str">
         <v/>
       </c>
       <c r="D122" t="str">
-        <v>32671</v>
+        <v>32568</v>
       </c>
       <c r="E122" t="str">
-        <v>12996</v>
+        <v>6196</v>
       </c>
       <c r="F122" t="str">
         <v>Por peso</v>
@@ -2841,19 +2841,19 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>632674</v>
+        <v>631003</v>
       </c>
       <c r="B123" t="str">
-        <v>MORTAD. POLLO SJ KG</v>
+        <v>PATE DE PAVO SOPRAVAL 125.</v>
       </c>
       <c r="C123" t="str">
         <v/>
       </c>
       <c r="D123" t="str">
-        <v>32674</v>
+        <v>31003</v>
       </c>
       <c r="E123" t="str">
-        <v>4996</v>
+        <v>279</v>
       </c>
       <c r="F123" t="str">
         <v>Por peso</v>
@@ -2861,19 +2861,19 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>632568</v>
+        <v>631012</v>
       </c>
       <c r="B124" t="str">
-        <v>MORTAD. JAMONADA WINTER KG</v>
+        <v>LONGANIZA KG SUPER</v>
       </c>
       <c r="C124" t="str">
         <v/>
       </c>
       <c r="D124" t="str">
-        <v>32568</v>
+        <v>31012</v>
       </c>
       <c r="E124" t="str">
-        <v>6196</v>
+        <v>3116</v>
       </c>
       <c r="F124" t="str">
         <v>Por peso</v>
@@ -2881,19 +2881,19 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>631003</v>
+        <v>631143</v>
       </c>
       <c r="B125" t="str">
-        <v>PATE DE PAVO SOPRAVAL 125.</v>
+        <v>LONGANIZA CHILLAN AHUMADA KILO</v>
       </c>
       <c r="C125" t="str">
         <v/>
       </c>
       <c r="D125" t="str">
-        <v>31003</v>
+        <v>31143</v>
       </c>
       <c r="E125" t="str">
-        <v>279</v>
+        <v>10996</v>
       </c>
       <c r="F125" t="str">
         <v>Por peso</v>
@@ -2901,19 +2901,19 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>631012</v>
+        <v>631265</v>
       </c>
       <c r="B126" t="str">
-        <v>LONGANIZA KG SUPER</v>
+        <v>CHORIZO LA CRIANZA GRANEL KG.</v>
       </c>
       <c r="C126" t="str">
         <v/>
       </c>
       <c r="D126" t="str">
-        <v>31012</v>
+        <v>31265</v>
       </c>
       <c r="E126" t="str">
-        <v>3116</v>
+        <v>3516</v>
       </c>
       <c r="F126" t="str">
         <v>Por peso</v>
@@ -2921,19 +2921,19 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>631143</v>
+        <v>632633</v>
       </c>
       <c r="B127" t="str">
-        <v>LONGANIZA CHILLAN AHUMADA KILO</v>
+        <v>SALCHICHON CERV. ARUNA ARTESANAL KG</v>
       </c>
       <c r="C127" t="str">
         <v/>
       </c>
       <c r="D127" t="str">
-        <v>31143</v>
+        <v>32633</v>
       </c>
       <c r="E127" t="str">
-        <v>10996</v>
+        <v>3560</v>
       </c>
       <c r="F127" t="str">
         <v>Por peso</v>
@@ -2941,19 +2941,19 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>631265</v>
+        <v>632644</v>
       </c>
       <c r="B128" t="str">
-        <v>CHORIZO LA CRIANZA GRANEL KG.</v>
+        <v>CERVECIN VON UNGER</v>
       </c>
       <c r="C128" t="str">
         <v/>
       </c>
       <c r="D128" t="str">
-        <v>31265</v>
+        <v>32644</v>
       </c>
       <c r="E128" t="str">
-        <v>3516</v>
+        <v>2760</v>
       </c>
       <c r="F128" t="str">
         <v>Por peso</v>
@@ -2961,19 +2961,19 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>632633</v>
+        <v>632618</v>
       </c>
       <c r="B129" t="str">
-        <v>SALCHICHON CERV. ARUNA ARTESANAL KG</v>
+        <v>ARROLLADO LOMO CHILLAN KG</v>
       </c>
       <c r="C129" t="str">
         <v/>
       </c>
       <c r="D129" t="str">
-        <v>32633</v>
+        <v>32618</v>
       </c>
       <c r="E129" t="str">
-        <v>3560</v>
+        <v>11996</v>
       </c>
       <c r="F129" t="str">
         <v>Por peso</v>
@@ -2981,19 +2981,19 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>632644</v>
+        <v>633128</v>
       </c>
       <c r="B130" t="str">
-        <v>CERVECIN VON UNGER</v>
+        <v>CHORIZO PARRILLERO ROJO C CATALANA KG</v>
       </c>
       <c r="C130" t="str">
         <v/>
       </c>
       <c r="D130" t="str">
-        <v>32644</v>
+        <v>33128</v>
       </c>
       <c r="E130" t="str">
-        <v>2760</v>
+        <v>1836</v>
       </c>
       <c r="F130" t="str">
         <v>Por peso</v>
@@ -3001,19 +3001,19 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>632618</v>
+        <v>631375</v>
       </c>
       <c r="B131" t="str">
-        <v>ARROLLADO LOMO CHILLAN KG</v>
+        <v>MORTAD. ALEMANA FRANK 4911</v>
       </c>
       <c r="C131" t="str">
         <v/>
       </c>
       <c r="D131" t="str">
-        <v>32618</v>
+        <v>31375</v>
       </c>
       <c r="E131" t="str">
-        <v>11996</v>
+        <v>1796</v>
       </c>
       <c r="F131" t="str">
         <v>Por peso</v>
@@ -3021,19 +3021,19 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>633128</v>
+        <v>631351</v>
       </c>
       <c r="B132" t="str">
-        <v>CHORIZO PARRILLERO ROJO C CATALANA KG</v>
+        <v>JAMONADA MONTINA KG 5371AF</v>
       </c>
       <c r="C132" t="str">
         <v/>
       </c>
       <c r="D132" t="str">
-        <v>33128</v>
+        <v>31351</v>
       </c>
       <c r="E132" t="str">
-        <v>1836</v>
+        <v>5996</v>
       </c>
       <c r="F132" t="str">
         <v>Por peso</v>
@@ -3041,19 +3041,19 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>631375</v>
+        <v>631538</v>
       </c>
       <c r="B133" t="str">
-        <v>MORTAD. ALEMANA FRANK 4911</v>
+        <v>JAMONADA PAVO BALANCE KG PF</v>
       </c>
       <c r="C133" t="str">
         <v/>
       </c>
       <c r="D133" t="str">
-        <v>31375</v>
+        <v>31538</v>
       </c>
       <c r="E133" t="str">
-        <v>1796</v>
+        <v>10196</v>
       </c>
       <c r="F133" t="str">
         <v>Por peso</v>
@@ -3061,19 +3061,19 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>631351</v>
+        <v>631536</v>
       </c>
       <c r="B134" t="str">
-        <v>JAMONADA MONTINA KG 5371AF</v>
+        <v>ARROLLADO LOMO A4 S/AJI KG.</v>
       </c>
       <c r="C134" t="str">
         <v/>
       </c>
       <c r="D134" t="str">
-        <v>31351</v>
+        <v>31536</v>
       </c>
       <c r="E134" t="str">
-        <v>5996</v>
+        <v>3356</v>
       </c>
       <c r="F134" t="str">
         <v>Por peso</v>
@@ -3081,19 +3081,19 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>631538</v>
+        <v>631496</v>
       </c>
       <c r="B135" t="str">
-        <v>JAMONADA PAVO BALANCE KG PF</v>
+        <v>JAMON SANDWICH JW PF KILO</v>
       </c>
       <c r="C135" t="str">
         <v/>
       </c>
       <c r="D135" t="str">
-        <v>31538</v>
+        <v>31496</v>
       </c>
       <c r="E135" t="str">
-        <v>10196</v>
+        <v>7996</v>
       </c>
       <c r="F135" t="str">
         <v>Por peso</v>
@@ -3101,19 +3101,19 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>631536</v>
+        <v>631488</v>
       </c>
       <c r="B136" t="str">
-        <v>ARROLLADO LOMO A4 S/AJI KG.</v>
+        <v>ARROLLADO LOMO AR PF KILO</v>
       </c>
       <c r="C136" t="str">
         <v/>
       </c>
       <c r="D136" t="str">
-        <v>31536</v>
+        <v>31488</v>
       </c>
       <c r="E136" t="str">
-        <v>3356</v>
+        <v>9596</v>
       </c>
       <c r="F136" t="str">
         <v>Por peso</v>
@@ -3121,19 +3121,19 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>631496</v>
+        <v>631121</v>
       </c>
       <c r="B137" t="str">
-        <v>JAMON SANDWICH JW PF KILO</v>
+        <v>JAMON PLANCHADO SJ KG</v>
       </c>
       <c r="C137" t="str">
         <v/>
       </c>
       <c r="D137" t="str">
-        <v>31496</v>
+        <v>31121</v>
       </c>
       <c r="E137" t="str">
-        <v>7996</v>
+        <v>9996</v>
       </c>
       <c r="F137" t="str">
         <v>Por peso</v>
@@ -3141,19 +3141,19 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>631488</v>
+        <v>631166</v>
       </c>
       <c r="B138" t="str">
-        <v>ARROLLADO LOMO AR PF KILO</v>
+        <v>JAMON PIERNA LP KG</v>
       </c>
       <c r="C138" t="str">
         <v/>
       </c>
       <c r="D138" t="str">
-        <v>31488</v>
+        <v>31166</v>
       </c>
       <c r="E138" t="str">
-        <v>9596</v>
+        <v>13996</v>
       </c>
       <c r="F138" t="str">
         <v>Por peso</v>
@@ -3161,19 +3161,19 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>631121</v>
+        <v>631090</v>
       </c>
       <c r="B139" t="str">
-        <v>JAMON PLANCHADO SJ KG</v>
+        <v>JAMON PIERNA AHUM.WINTER</v>
       </c>
       <c r="C139" t="str">
         <v/>
       </c>
       <c r="D139" t="str">
-        <v>31121</v>
+        <v>31090</v>
       </c>
       <c r="E139" t="str">
-        <v>9996</v>
+        <v>11996</v>
       </c>
       <c r="F139" t="str">
         <v>Por peso</v>
@@ -3181,16 +3181,16 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>631166</v>
+        <v>631006</v>
       </c>
       <c r="B140" t="str">
-        <v>JAMON PIERNA LP KG</v>
+        <v>JAMON PECHUGA PAVO ACARAM.ARIZTIA</v>
       </c>
       <c r="C140" t="str">
         <v/>
       </c>
       <c r="D140" t="str">
-        <v>31166</v>
+        <v>31006</v>
       </c>
       <c r="E140" t="str">
         <v>13996</v>
@@ -3201,19 +3201,19 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>631090</v>
+        <v>631421</v>
       </c>
       <c r="B141" t="str">
-        <v>JAMON PIERNA AHUM.WINTER</v>
+        <v>ARROLLADO HUASO LP KG</v>
       </c>
       <c r="C141" t="str">
         <v/>
       </c>
       <c r="D141" t="str">
-        <v>31090</v>
+        <v>31421</v>
       </c>
       <c r="E141" t="str">
-        <v>11996</v>
+        <v>13996</v>
       </c>
       <c r="F141" t="str">
         <v>Por peso</v>
@@ -3221,19 +3221,19 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>631006</v>
+        <v>631528</v>
       </c>
       <c r="B142" t="str">
-        <v>JAMON PECHUGA PAVO ACARAM.ARIZTIA</v>
+        <v>JAMON PAVO ACARAM. PF KG.</v>
       </c>
       <c r="C142" t="str">
         <v/>
       </c>
       <c r="D142" t="str">
-        <v>31006</v>
+        <v>31528</v>
       </c>
       <c r="E142" t="str">
-        <v>13996</v>
+        <v>11996</v>
       </c>
       <c r="F142" t="str">
         <v>Por peso</v>
@@ -3241,19 +3241,19 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>631421</v>
+        <v>631493</v>
       </c>
       <c r="B143" t="str">
-        <v>ARROLLADO HUASO LP KG</v>
+        <v>JAMON AHUMADO G1 JH PF KILO</v>
       </c>
       <c r="C143" t="str">
         <v/>
       </c>
       <c r="D143" t="str">
-        <v>31421</v>
+        <v>31493</v>
       </c>
       <c r="E143" t="str">
-        <v>13996</v>
+        <v>12396</v>
       </c>
       <c r="F143" t="str">
         <v>Por peso</v>
@@ -3261,19 +3261,19 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>631528</v>
+        <v>631361</v>
       </c>
       <c r="B144" t="str">
-        <v>JAMON PAVO ACARAM. PF KG.</v>
+        <v>ARROLLADO HUASO CON AJI LC KG</v>
       </c>
       <c r="C144" t="str">
         <v/>
       </c>
       <c r="D144" t="str">
-        <v>31528</v>
+        <v>31361</v>
       </c>
       <c r="E144" t="str">
-        <v>11996</v>
+        <v>9996</v>
       </c>
       <c r="F144" t="str">
         <v>Por peso</v>
@@ -3281,19 +3281,19 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>631493</v>
+        <v>631243</v>
       </c>
       <c r="B145" t="str">
-        <v>JAMON AHUMADO G1 JH PF KILO</v>
+        <v>COPPA C A WINTER KG</v>
       </c>
       <c r="C145" t="str">
         <v/>
       </c>
       <c r="D145" t="str">
-        <v>31493</v>
+        <v>31243</v>
       </c>
       <c r="E145" t="str">
-        <v>12396</v>
+        <v>6996</v>
       </c>
       <c r="F145" t="str">
         <v>Por peso</v>
@@ -3301,19 +3301,19 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>631361</v>
+        <v>631264</v>
       </c>
       <c r="B146" t="str">
-        <v>ARROLLADO HUASO CON AJI LC KG</v>
+        <v>SALCHICHON CERV. AHUMADO KG.</v>
       </c>
       <c r="C146" t="str">
         <v/>
       </c>
       <c r="D146" t="str">
-        <v>31361</v>
+        <v>31264</v>
       </c>
       <c r="E146" t="str">
-        <v>9996</v>
+        <v>2159</v>
       </c>
       <c r="F146" t="str">
         <v>Por peso</v>
@@ -3321,16 +3321,16 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>631243</v>
+        <v>631122</v>
       </c>
       <c r="B147" t="str">
-        <v>COPPA C A WINTER KG</v>
+        <v>SALCHICHON CERV. S.JORGE KG</v>
       </c>
       <c r="C147" t="str">
         <v/>
       </c>
       <c r="D147" t="str">
-        <v>31243</v>
+        <v>31122</v>
       </c>
       <c r="E147" t="str">
         <v>6996</v>
@@ -3341,19 +3341,19 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>631264</v>
+        <v>631016</v>
       </c>
       <c r="B148" t="str">
-        <v>SALCHICHON CERV. AHUMADO KG.</v>
+        <v>PECHUGA DE PAVO AHUMADAPF KG.</v>
       </c>
       <c r="C148" t="str">
         <v/>
       </c>
       <c r="D148" t="str">
-        <v>31264</v>
+        <v>31016</v>
       </c>
       <c r="E148" t="str">
-        <v>2159</v>
+        <v>14396</v>
       </c>
       <c r="F148" t="str">
         <v>Por peso</v>
@@ -3361,19 +3361,19 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>631122</v>
+        <v>631454</v>
       </c>
       <c r="B149" t="str">
-        <v>SALCHICHON CERV. S.JORGE KG</v>
+        <v>PECHUGA PAVO COC.ARIZTIA 40303BF</v>
       </c>
       <c r="C149" t="str">
         <v/>
       </c>
       <c r="D149" t="str">
-        <v>31122</v>
+        <v>31454</v>
       </c>
       <c r="E149" t="str">
-        <v>6996</v>
+        <v>13996</v>
       </c>
       <c r="F149" t="str">
         <v>Por peso</v>
@@ -3381,19 +3381,19 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>631016</v>
+        <v>631128</v>
       </c>
       <c r="B150" t="str">
-        <v>PECHUGA DE PAVO AHUMADAPF KG.</v>
+        <v>PECHUGA AHUMADA SOPRAVAL KG</v>
       </c>
       <c r="C150" t="str">
         <v/>
       </c>
       <c r="D150" t="str">
-        <v>31016</v>
+        <v>31128</v>
       </c>
       <c r="E150" t="str">
-        <v>14396</v>
+        <v>12996</v>
       </c>
       <c r="F150" t="str">
         <v>Por peso</v>
@@ -3401,19 +3401,19 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>631454</v>
+        <v>631464</v>
       </c>
       <c r="B151" t="str">
-        <v>PECHUGA PAVO COC.ARIZTIA 40303BF</v>
+        <v>PATA RELLENA SUPER KG</v>
       </c>
       <c r="C151" t="str">
         <v/>
       </c>
       <c r="D151" t="str">
-        <v>31454</v>
+        <v>31464</v>
       </c>
       <c r="E151" t="str">
-        <v>13996</v>
+        <v>1239</v>
       </c>
       <c r="F151" t="str">
         <v>Por peso</v>
@@ -3421,19 +3421,19 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>631128</v>
+        <v>631409</v>
       </c>
       <c r="B152" t="str">
-        <v>PECHUGA AHUMADA SOPRAVAL KG</v>
+        <v>PECHUGA AHUM. ARIZTIA 5160</v>
       </c>
       <c r="C152" t="str">
         <v/>
       </c>
       <c r="D152" t="str">
-        <v>31128</v>
+        <v>31409</v>
       </c>
       <c r="E152" t="str">
-        <v>12996</v>
+        <v>3996</v>
       </c>
       <c r="F152" t="str">
         <v>Por peso</v>
@@ -3441,19 +3441,19 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>631464</v>
+        <v>631500</v>
       </c>
       <c r="B153" t="str">
-        <v>PATA RELLENA SUPER KG</v>
+        <v>ARROLLADO ARTESANAL R.ABUELO KG</v>
       </c>
       <c r="C153" t="str">
         <v/>
       </c>
       <c r="D153" t="str">
-        <v>31464</v>
+        <v>31500</v>
       </c>
       <c r="E153" t="str">
-        <v>1239</v>
+        <v>11996</v>
       </c>
       <c r="F153" t="str">
         <v>Por peso</v>
@@ -3461,19 +3461,19 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>631409</v>
+        <v>631322</v>
       </c>
       <c r="B154" t="str">
-        <v>PECHUGA AHUM. ARIZTIA 5160</v>
+        <v>JAMON AVE COCIDA FR PF KG</v>
       </c>
       <c r="C154" t="str">
         <v/>
       </c>
       <c r="D154" t="str">
-        <v>31409</v>
+        <v>31322</v>
       </c>
       <c r="E154" t="str">
-        <v>3996</v>
+        <v>10996</v>
       </c>
       <c r="F154" t="str">
         <v>Por peso</v>
@@ -3481,19 +3481,19 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>631500</v>
+        <v>632722</v>
       </c>
       <c r="B155" t="str">
-        <v>ARROLLADO ARTESANAL R.ABUELO KG</v>
+        <v>PECHUGA DE PAVO COCIDA PF KG</v>
       </c>
       <c r="C155" t="str">
         <v/>
       </c>
       <c r="D155" t="str">
-        <v>31500</v>
+        <v>32722</v>
       </c>
       <c r="E155" t="str">
-        <v>11996</v>
+        <v>14396</v>
       </c>
       <c r="F155" t="str">
         <v>Por peso</v>
@@ -3501,99 +3501,99 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>631322</v>
+        <v>632648</v>
       </c>
       <c r="B156" t="str">
-        <v>JAMON AVE COCIDA FR PF KG</v>
+        <v>M. LISA ARUNA MAZO</v>
       </c>
       <c r="C156" t="str">
         <v/>
       </c>
       <c r="D156" t="str">
-        <v>31322</v>
+        <v>32648</v>
       </c>
       <c r="E156" t="str">
-        <v>10996</v>
+        <v>3890</v>
       </c>
       <c r="F156" t="str">
-        <v>Por peso</v>
+        <v>Por cantidad</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>632722</v>
+        <v>631099</v>
       </c>
       <c r="B157" t="str">
-        <v>PECHUGA DE PAVO COCIDA PF KG</v>
+        <v>PIZZA DE MARISCOS FAMILIAR</v>
       </c>
       <c r="C157" t="str">
         <v/>
       </c>
       <c r="D157" t="str">
-        <v>32722</v>
+        <v>31099</v>
       </c>
       <c r="E157" t="str">
-        <v>14396</v>
+        <v>2490</v>
       </c>
       <c r="F157" t="str">
-        <v>Por peso</v>
+        <v>Por cantidad</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>632648</v>
+        <v>632790</v>
       </c>
       <c r="B158" t="str">
-        <v>M. LISA ARUNA MAZO</v>
+        <v>LONGANIZA KG HACIENDA DE NUBLE</v>
       </c>
       <c r="C158" t="str">
         <v/>
       </c>
       <c r="D158" t="str">
-        <v>32648</v>
+        <v>32790</v>
       </c>
       <c r="E158" t="str">
-        <v>3890</v>
+        <v>2990</v>
       </c>
       <c r="F158" t="str">
-        <v>Por cantidad</v>
+        <v>Por peso</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>631099</v>
+        <v>632660</v>
       </c>
       <c r="B159" t="str">
-        <v>PIZZA DE MARISCOS FAMILIAR</v>
+        <v>SALAME AHUMADO CORTE PF 3F</v>
       </c>
       <c r="C159" t="str">
         <v/>
       </c>
       <c r="D159" t="str">
-        <v>31099</v>
+        <v>32660</v>
       </c>
       <c r="E159" t="str">
-        <v>2490</v>
+        <v>13996</v>
       </c>
       <c r="F159" t="str">
-        <v>Por cantidad</v>
+        <v>Por peso</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>632790</v>
+        <v>632661</v>
       </c>
       <c r="B160" t="str">
-        <v>LONGANIZA KG HACIENDA DE NUBLE</v>
+        <v>SALAME ITALIANO CORTPF 3E</v>
       </c>
       <c r="C160" t="str">
         <v/>
       </c>
       <c r="D160" t="str">
-        <v>32790</v>
+        <v>32661</v>
       </c>
       <c r="E160" t="str">
-        <v>2990</v>
+        <v>13996</v>
       </c>
       <c r="F160" t="str">
         <v>Por peso</v>
@@ -3601,16 +3601,16 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>632660</v>
+        <v>632659</v>
       </c>
       <c r="B161" t="str">
-        <v>SALAME AHUMADO CORTE PF 3F</v>
+        <v>JAMON ARTESANAL G1 RDA A9 KG</v>
       </c>
       <c r="C161" t="str">
         <v/>
       </c>
       <c r="D161" t="str">
-        <v>32660</v>
+        <v>32659</v>
       </c>
       <c r="E161" t="str">
         <v>13996</v>
@@ -3621,19 +3621,19 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>632661</v>
+        <v>631134</v>
       </c>
       <c r="B162" t="str">
-        <v>SALAME ITALIANO CORTPF 3E</v>
+        <v>PECHUGA ASADA POLLO SUPER KG</v>
       </c>
       <c r="C162" t="str">
         <v/>
       </c>
       <c r="D162" t="str">
-        <v>32661</v>
+        <v>31134</v>
       </c>
       <c r="E162" t="str">
-        <v>13996</v>
+        <v>10996</v>
       </c>
       <c r="F162" t="str">
         <v>Por peso</v>
@@ -3641,19 +3641,19 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>632659</v>
+        <v>632397</v>
       </c>
       <c r="B163" t="str">
-        <v>JAMON ARTESANAL G1 RDA A9 KG</v>
+        <v>ARROLLADO HUASO FASTD.(334)KG.</v>
       </c>
       <c r="C163" t="str">
         <v/>
       </c>
       <c r="D163" t="str">
-        <v>32659</v>
+        <v>32397</v>
       </c>
       <c r="E163" t="str">
-        <v>13996</v>
+        <v>2876</v>
       </c>
       <c r="F163" t="str">
         <v>Por peso</v>
@@ -3661,19 +3661,19 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>631134</v>
+        <v>631188</v>
       </c>
       <c r="B164" t="str">
-        <v>PECHUGA ASADA POLLO SUPER KG</v>
+        <v>PECHUGA PAVO ASADA ARIZTIA KG 40036BF</v>
       </c>
       <c r="C164" t="str">
         <v/>
       </c>
       <c r="D164" t="str">
-        <v>31134</v>
+        <v>31188</v>
       </c>
       <c r="E164" t="str">
-        <v>10996</v>
+        <v>13996</v>
       </c>
       <c r="F164" t="str">
         <v>Por peso</v>
@@ -3681,19 +3681,19 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>632397</v>
+        <v>631184</v>
       </c>
       <c r="B165" t="str">
-        <v>ARROLLADO HUASO FASTD.(334)KG.</v>
+        <v>PATA RELLENA CATALANA KG</v>
       </c>
       <c r="C165" t="str">
         <v/>
       </c>
       <c r="D165" t="str">
-        <v>32397</v>
+        <v>31184</v>
       </c>
       <c r="E165" t="str">
-        <v>2876</v>
+        <v>2996</v>
       </c>
       <c r="F165" t="str">
         <v>Por peso</v>
@@ -3701,19 +3701,19 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>631188</v>
+        <v>631594</v>
       </c>
       <c r="B166" t="str">
-        <v>PECHUGA PAVO ASADA ARIZTIA KG 40036BF</v>
+        <v>SALAME KIDS CATALANA KG</v>
       </c>
       <c r="C166" t="str">
         <v/>
       </c>
       <c r="D166" t="str">
-        <v>31188</v>
+        <v>31594</v>
       </c>
       <c r="E166" t="str">
-        <v>13996</v>
+        <v>3880</v>
       </c>
       <c r="F166" t="str">
         <v>Por peso</v>
@@ -3721,19 +3721,19 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>631184</v>
+        <v>631187</v>
       </c>
       <c r="B167" t="str">
-        <v>PATA RELLENA CATALANA KG</v>
+        <v>SALCHICHON CAMPING CATALANA KG</v>
       </c>
       <c r="C167" t="str">
         <v/>
       </c>
       <c r="D167" t="str">
-        <v>31184</v>
+        <v>31187</v>
       </c>
       <c r="E167" t="str">
-        <v>2996</v>
+        <v>1876</v>
       </c>
       <c r="F167" t="str">
         <v>Por peso</v>
@@ -3741,19 +3741,19 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>631594</v>
+        <v>631183</v>
       </c>
       <c r="B168" t="str">
-        <v>SALAME KIDS CATALANA KG</v>
+        <v>MILANESA CATALANA KG</v>
       </c>
       <c r="C168" t="str">
         <v/>
       </c>
       <c r="D168" t="str">
-        <v>31594</v>
+        <v>31183</v>
       </c>
       <c r="E168" t="str">
-        <v>3880</v>
+        <v>2796</v>
       </c>
       <c r="F168" t="str">
         <v>Por peso</v>
@@ -3761,19 +3761,19 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>631187</v>
+        <v>632456</v>
       </c>
       <c r="B169" t="str">
-        <v>SALCHICHON CAMPING CATALANA KG</v>
+        <v>LONGANIZA ARTESANAL KG ARUNA</v>
       </c>
       <c r="C169" t="str">
         <v/>
       </c>
       <c r="D169" t="str">
-        <v>31187</v>
+        <v>42456</v>
       </c>
       <c r="E169" t="str">
-        <v>1876</v>
+        <v>2490</v>
       </c>
       <c r="F169" t="str">
         <v>Por peso</v>
@@ -3781,19 +3781,19 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>631183</v>
+        <v>631427</v>
       </c>
       <c r="B170" t="str">
-        <v>MILANESA CATALANA KG</v>
+        <v>TOCINO MONTS KG</v>
       </c>
       <c r="C170" t="str">
         <v/>
       </c>
       <c r="D170" t="str">
-        <v>31183</v>
+        <v>31427</v>
       </c>
       <c r="E170" t="str">
-        <v>2796</v>
+        <v>10760</v>
       </c>
       <c r="F170" t="str">
         <v>Por peso</v>
@@ -3801,19 +3801,19 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>632456</v>
+        <v>631124</v>
       </c>
       <c r="B171" t="str">
-        <v>LONGANIZA ARTESANAL KG ARUNA</v>
+        <v>JAMON ARTESANAL G2 PF EB</v>
       </c>
       <c r="C171" t="str">
         <v/>
       </c>
       <c r="D171" t="str">
-        <v>42456</v>
+        <v>31124</v>
       </c>
       <c r="E171" t="str">
-        <v>2490</v>
+        <v>9996</v>
       </c>
       <c r="F171" t="str">
         <v>Por peso</v>
@@ -3821,19 +3821,19 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>631427</v>
+        <v>633229</v>
       </c>
       <c r="B172" t="str">
-        <v>TOCINO MONTS KG</v>
+        <v>ACEITUNA AZAPA SEGUNDA CUGAT</v>
       </c>
       <c r="C172" t="str">
         <v/>
       </c>
       <c r="D172" t="str">
-        <v>31427</v>
+        <v>33229</v>
       </c>
       <c r="E172" t="str">
-        <v>10760</v>
+        <v>2796</v>
       </c>
       <c r="F172" t="str">
         <v>Por peso</v>
@@ -3841,19 +3841,19 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>631124</v>
+        <v>631781</v>
       </c>
       <c r="B173" t="str">
-        <v>JAMON ARTESANAL G2 PF EB</v>
+        <v>ACEITUNA AZAPA KILO</v>
       </c>
       <c r="C173" t="str">
         <v/>
       </c>
       <c r="D173" t="str">
-        <v>31124</v>
+        <v>31781</v>
       </c>
       <c r="E173" t="str">
-        <v>9996</v>
+        <v>8396</v>
       </c>
       <c r="F173" t="str">
         <v>Por peso</v>
@@ -3861,19 +3861,19 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>633229</v>
+        <v>631786</v>
       </c>
       <c r="B174" t="str">
-        <v>ACEITUNA AZAPA SEGUNDA CUGAT</v>
+        <v>PICKLE KILO</v>
       </c>
       <c r="C174" t="str">
         <v/>
       </c>
       <c r="D174" t="str">
-        <v>33229</v>
+        <v>31786</v>
       </c>
       <c r="E174" t="str">
-        <v>2796</v>
+        <v>5396</v>
       </c>
       <c r="F174" t="str">
         <v>Por peso</v>
@@ -3881,19 +3881,19 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>631781</v>
+        <v>631787</v>
       </c>
       <c r="B175" t="str">
-        <v>ACEITUNA AZAPA KILO</v>
+        <v>SALSA AMERICANA KILO</v>
       </c>
       <c r="C175" t="str">
         <v/>
       </c>
       <c r="D175" t="str">
-        <v>31781</v>
+        <v>31787</v>
       </c>
       <c r="E175" t="str">
-        <v>8396</v>
+        <v>2996</v>
       </c>
       <c r="F175" t="str">
         <v>Por peso</v>
@@ -3901,19 +3901,19 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>631786</v>
+        <v>631784</v>
       </c>
       <c r="B176" t="str">
-        <v>PICKLE KILO</v>
+        <v>CEBOLLA EN ESCABECHE·</v>
       </c>
       <c r="C176" t="str">
         <v/>
       </c>
       <c r="D176" t="str">
-        <v>31786</v>
+        <v>31784</v>
       </c>
       <c r="E176" t="str">
-        <v>5396</v>
+        <v>5996</v>
       </c>
       <c r="F176" t="str">
         <v>Por peso</v>
@@ -3921,19 +3921,19 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>631787</v>
+        <v>631777</v>
       </c>
       <c r="B177" t="str">
-        <v>SALSA AMERICANA KILO</v>
+        <v>JAMON COLONIAL AHUMADO</v>
       </c>
       <c r="C177" t="str">
         <v/>
       </c>
       <c r="D177" t="str">
-        <v>31787</v>
+        <v>31777</v>
       </c>
       <c r="E177" t="str">
-        <v>2996</v>
+        <v>6760</v>
       </c>
       <c r="F177" t="str">
         <v>Por peso</v>
@@ -3941,19 +3941,19 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>631784</v>
+        <v>631775</v>
       </c>
       <c r="B178" t="str">
-        <v>CEBOLLA EN ESCABECHE·</v>
+        <v>LONGANIZA CHILENA KG BIELEFELDT</v>
       </c>
       <c r="C178" t="str">
         <v/>
       </c>
       <c r="D178" t="str">
-        <v>31784</v>
+        <v>31775</v>
       </c>
       <c r="E178" t="str">
-        <v>5996</v>
+        <v>2199</v>
       </c>
       <c r="F178" t="str">
         <v>Por peso</v>
@@ -3961,19 +3961,19 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>631777</v>
+        <v>631774</v>
       </c>
       <c r="B179" t="str">
-        <v>JAMON COLONIAL AHUMADO</v>
+        <v>LONGANIZA CASERA KG BIELEFELDT</v>
       </c>
       <c r="C179" t="str">
         <v/>
       </c>
       <c r="D179" t="str">
-        <v>31777</v>
+        <v>31774</v>
       </c>
       <c r="E179" t="str">
-        <v>6760</v>
+        <v>3199</v>
       </c>
       <c r="F179" t="str">
         <v>Por peso</v>
@@ -3981,19 +3981,19 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>631775</v>
+        <v>631773</v>
       </c>
       <c r="B180" t="str">
-        <v>LONGANIZA CHILENA KG BIELEFELDT</v>
+        <v>ARROLLADO BIELEFELDT</v>
       </c>
       <c r="C180" t="str">
         <v/>
       </c>
       <c r="D180" t="str">
-        <v>31775</v>
+        <v>31773</v>
       </c>
       <c r="E180" t="str">
-        <v>2199</v>
+        <v>4390</v>
       </c>
       <c r="F180" t="str">
         <v>Por peso</v>
@@ -4001,16 +4001,16 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>631774</v>
+        <v>631776</v>
       </c>
       <c r="B181" t="str">
-        <v>LONGANIZA CASERA KG BIELEFELDT</v>
+        <v>QUESO CHANCHO BIELEFELDT</v>
       </c>
       <c r="C181" t="str">
         <v/>
       </c>
       <c r="D181" t="str">
-        <v>31774</v>
+        <v>31776</v>
       </c>
       <c r="E181" t="str">
         <v>3199</v>
@@ -4021,19 +4021,19 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>631773</v>
+        <v>631689</v>
       </c>
       <c r="B182" t="str">
-        <v>ARROLLADO BIELEFELDT</v>
+        <v>QUESO DE CERDO PITRUFQUEN</v>
       </c>
       <c r="C182" t="str">
         <v/>
       </c>
       <c r="D182" t="str">
-        <v>31773</v>
+        <v>31689</v>
       </c>
       <c r="E182" t="str">
-        <v>4390</v>
+        <v>10196</v>
       </c>
       <c r="F182" t="str">
         <v>Por peso</v>
@@ -4041,19 +4041,19 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>631776</v>
+        <v>631686</v>
       </c>
       <c r="B183" t="str">
-        <v>QUESO CHANCHO BIELEFELDT</v>
+        <v>ARROLLADO HUASO PITRUFQUEN</v>
       </c>
       <c r="C183" t="str">
         <v/>
       </c>
       <c r="D183" t="str">
-        <v>31776</v>
+        <v>31686</v>
       </c>
       <c r="E183" t="str">
-        <v>3199</v>
+        <v>12996</v>
       </c>
       <c r="F183" t="str">
         <v>Por peso</v>
@@ -4061,19 +4061,19 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>631689</v>
+        <v>631687</v>
       </c>
       <c r="B184" t="str">
-        <v>QUESO DE CERDO PITRUFQUEN</v>
+        <v>LONGANIZA KG PITRUFQUEN</v>
       </c>
       <c r="C184" t="str">
         <v/>
       </c>
       <c r="D184" t="str">
-        <v>31689</v>
+        <v>31687</v>
       </c>
       <c r="E184" t="str">
-        <v>10196</v>
+        <v>9596</v>
       </c>
       <c r="F184" t="str">
         <v>Por peso</v>
@@ -4081,19 +4081,19 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>631686</v>
+        <v>631688</v>
       </c>
       <c r="B185" t="str">
-        <v>ARROLLADO HUASO PITRUFQUEN</v>
+        <v>PATE DE CERDO PITRUFQUEN</v>
       </c>
       <c r="C185" t="str">
         <v/>
       </c>
       <c r="D185" t="str">
-        <v>31686</v>
+        <v>31688</v>
       </c>
       <c r="E185" t="str">
-        <v>12996</v>
+        <v>9696</v>
       </c>
       <c r="F185" t="str">
         <v>Por peso</v>
@@ -4101,19 +4101,19 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>631687</v>
+        <v>633668</v>
       </c>
       <c r="B186" t="str">
-        <v>LONGANIZA KG PITRUFQUEN</v>
+        <v>JAMON PIERNA PAVO AHUM ARIZTIA KG</v>
       </c>
       <c r="C186" t="str">
         <v/>
       </c>
       <c r="D186" t="str">
-        <v>31687</v>
+        <v>33668</v>
       </c>
       <c r="E186" t="str">
-        <v>9596</v>
+        <v>11996</v>
       </c>
       <c r="F186" t="str">
         <v>Por peso</v>
@@ -4121,19 +4121,19 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>631688</v>
+        <v>633445</v>
       </c>
       <c r="B187" t="str">
-        <v>PATE DE CERDO PITRUFQUEN</v>
+        <v>ACEITUNA AZAPA PRIMERA CUGAT</v>
       </c>
       <c r="C187" t="str">
         <v/>
       </c>
       <c r="D187" t="str">
-        <v>31688</v>
+        <v>33445</v>
       </c>
       <c r="E187" t="str">
-        <v>9696</v>
+        <v>2996</v>
       </c>
       <c r="F187" t="str">
         <v>Por peso</v>
@@ -4141,19 +4141,19 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>633668</v>
+        <v>633660</v>
       </c>
       <c r="B188" t="str">
-        <v>JAMON PIERNA PAVO AHUM ARIZTIA KG</v>
+        <v>ACEITUNA CUGAT RELLENA ROCOTO</v>
       </c>
       <c r="C188" t="str">
         <v/>
       </c>
       <c r="D188" t="str">
-        <v>33668</v>
+        <v>33660</v>
       </c>
       <c r="E188" t="str">
-        <v>11996</v>
+        <v>3916</v>
       </c>
       <c r="F188" t="str">
         <v>Por peso</v>
@@ -4161,19 +4161,19 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>633445</v>
+        <v>633663</v>
       </c>
       <c r="B189" t="str">
-        <v>ACEITUNA AZAPA PRIMERA CUGAT</v>
+        <v>ACEITUNA CUGAT RELLENA ALMENDRA</v>
       </c>
       <c r="C189" t="str">
         <v/>
       </c>
       <c r="D189" t="str">
-        <v>33445</v>
+        <v>33663</v>
       </c>
       <c r="E189" t="str">
-        <v>2996</v>
+        <v>3960</v>
       </c>
       <c r="F189" t="str">
         <v>Por peso</v>
@@ -4181,19 +4181,19 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>633660</v>
+        <v>631879</v>
       </c>
       <c r="B190" t="str">
-        <v>ACEITUNA CUGAT RELLENA ROCOTO</v>
+        <v>ACEITUNA NEGRA 100/120 PRIMERA AMARGA</v>
       </c>
       <c r="C190" t="str">
         <v/>
       </c>
       <c r="D190" t="str">
-        <v>33660</v>
+        <v>31879</v>
       </c>
       <c r="E190" t="str">
-        <v>3916</v>
+        <v>4796</v>
       </c>
       <c r="F190" t="str">
         <v>Por peso</v>
@@ -4201,19 +4201,19 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>633663</v>
+        <v>631880</v>
       </c>
       <c r="B191" t="str">
-        <v>ACEITUNA CUGAT RELLENA ALMENDRA</v>
+        <v>ACEITUNA SEVILLANA 90/100 EXTRA GRANEL</v>
       </c>
       <c r="C191" t="str">
         <v/>
       </c>
       <c r="D191" t="str">
-        <v>33663</v>
+        <v>31880</v>
       </c>
       <c r="E191" t="str">
-        <v>3960</v>
+        <v>3996</v>
       </c>
       <c r="F191" t="str">
         <v>Por peso</v>
@@ -4221,19 +4221,19 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>631879</v>
+        <v>631897</v>
       </c>
       <c r="B192" t="str">
-        <v>ACEITUNA NEGRA 100/120 PRIMERA AMARGA</v>
+        <v>LONGANIZA CASERA KG SAN FELIPE</v>
       </c>
       <c r="C192" t="str">
         <v/>
       </c>
       <c r="D192" t="str">
-        <v>31879</v>
+        <v>31897</v>
       </c>
       <c r="E192" t="str">
-        <v>4796</v>
+        <v>3596</v>
       </c>
       <c r="F192" t="str">
         <v>Por peso</v>
@@ -4241,19 +4241,19 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>631880</v>
+        <v>631587</v>
       </c>
       <c r="B193" t="str">
-        <v>ACEITUNA SEVILLANA 90/100 EXTRA GRANEL</v>
+        <v>CHORIZO ESPECIAL SAN FELIPE KG</v>
       </c>
       <c r="C193" t="str">
         <v/>
       </c>
       <c r="D193" t="str">
-        <v>31880</v>
+        <v>31587</v>
       </c>
       <c r="E193" t="str">
-        <v>3996</v>
+        <v>3596</v>
       </c>
       <c r="F193" t="str">
         <v>Por peso</v>
@@ -4261,19 +4261,19 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>631897</v>
+        <v>631568</v>
       </c>
       <c r="B194" t="str">
-        <v>LONGANIZA CASERA KG SAN FELIPE</v>
+        <v>QUESO CABEZA WINTER KG</v>
       </c>
       <c r="C194" t="str">
         <v/>
       </c>
       <c r="D194" t="str">
-        <v>31897</v>
+        <v>31568</v>
       </c>
       <c r="E194" t="str">
-        <v>3596</v>
+        <v>6196</v>
       </c>
       <c r="F194" t="str">
         <v>Por peso</v>
@@ -4281,19 +4281,19 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>631587</v>
+        <v>631635</v>
       </c>
       <c r="B195" t="str">
-        <v>CHORIZO ESPECIAL SAN FELIPE KG</v>
+        <v>PATE CERDO HICAR KG SN FELIPE</v>
       </c>
       <c r="C195" t="str">
         <v/>
       </c>
       <c r="D195" t="str">
-        <v>31587</v>
+        <v>31635</v>
       </c>
       <c r="E195" t="str">
-        <v>3596</v>
+        <v>3996</v>
       </c>
       <c r="F195" t="str">
         <v>Por peso</v>
@@ -4301,19 +4301,19 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>631568</v>
+        <v>631898</v>
       </c>
       <c r="B196" t="str">
-        <v>QUESO CABEZA WINTER KG</v>
+        <v>AJI ORO KILO LAS LOMAS</v>
       </c>
       <c r="C196" t="str">
         <v/>
       </c>
       <c r="D196" t="str">
-        <v>31568</v>
+        <v>31898</v>
       </c>
       <c r="E196" t="str">
-        <v>6196</v>
+        <v>4360</v>
       </c>
       <c r="F196" t="str">
         <v>Por peso</v>
@@ -4321,19 +4321,19 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>631635</v>
+        <v>631896</v>
       </c>
       <c r="B197" t="str">
-        <v>PATE CERDO HICAR KG SN FELIPE</v>
+        <v>ACEITUNA HUASCO SEGUNDA</v>
       </c>
       <c r="C197" t="str">
         <v/>
       </c>
       <c r="D197" t="str">
-        <v>31635</v>
+        <v>31896</v>
       </c>
       <c r="E197" t="str">
-        <v>3996</v>
+        <v>3596</v>
       </c>
       <c r="F197" t="str">
         <v>Por peso</v>
@@ -4341,19 +4341,19 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>631898</v>
+        <v>631895</v>
       </c>
       <c r="B198" t="str">
-        <v>AJI ORO KILO LAS LOMAS</v>
+        <v>ACEITUNA NEGRA 90/100 EXTRA AMARGA</v>
       </c>
       <c r="C198" t="str">
         <v/>
       </c>
       <c r="D198" t="str">
-        <v>31898</v>
+        <v>31895</v>
       </c>
       <c r="E198" t="str">
-        <v>4360</v>
+        <v>3996</v>
       </c>
       <c r="F198" t="str">
         <v>Por peso</v>
@@ -4361,19 +4361,19 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>631896</v>
+        <v>631894</v>
       </c>
       <c r="B199" t="str">
-        <v>ACEITUNA HUASCO SEGUNDA</v>
+        <v>PEPINO DILL CORNICHON KILOS LAS LOMAS</v>
       </c>
       <c r="C199" t="str">
         <v/>
       </c>
       <c r="D199" t="str">
-        <v>31896</v>
+        <v>31894</v>
       </c>
       <c r="E199" t="str">
-        <v>3596</v>
+        <v>5596</v>
       </c>
       <c r="F199" t="str">
         <v>Por peso</v>
@@ -4381,19 +4381,19 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>631895</v>
+        <v>631893</v>
       </c>
       <c r="B200" t="str">
-        <v>ACEITUNA NEGRA 90/100 EXTRA AMARGA</v>
+        <v>PEPINO DILL MEDIANO KILO LAS LOMAS</v>
       </c>
       <c r="C200" t="str">
         <v/>
       </c>
       <c r="D200" t="str">
-        <v>31895</v>
+        <v>31893</v>
       </c>
       <c r="E200" t="str">
-        <v>3996</v>
+        <v>5160</v>
       </c>
       <c r="F200" t="str">
         <v>Por peso</v>
@@ -4401,19 +4401,19 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>631894</v>
+        <v>631892</v>
       </c>
       <c r="B201" t="str">
-        <v>PEPINO DILL CORNICHON KILOS LAS LOMAS</v>
+        <v>PICKLES FINO KILO LAS LOMAS</v>
       </c>
       <c r="C201" t="str">
         <v/>
       </c>
       <c r="D201" t="str">
-        <v>31894</v>
+        <v>31892</v>
       </c>
       <c r="E201" t="str">
-        <v>5596</v>
+        <v>3160</v>
       </c>
       <c r="F201" t="str">
         <v>Por peso</v>
@@ -4421,19 +4421,19 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>631893</v>
+        <v>631267</v>
       </c>
       <c r="B202" t="str">
-        <v>PEPINO DILL MEDIANO KILO LAS LOMAS</v>
+        <v>LONGANIZA KG SCHWENCKE</v>
       </c>
       <c r="C202" t="str">
         <v/>
       </c>
       <c r="D202" t="str">
-        <v>31893</v>
+        <v>31267</v>
       </c>
       <c r="E202" t="str">
-        <v>5160</v>
+        <v>10396</v>
       </c>
       <c r="F202" t="str">
         <v>Por peso</v>
@@ -4441,19 +4441,19 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>631892</v>
+        <v>631266</v>
       </c>
       <c r="B203" t="str">
-        <v>PICKLES FINO KILO LAS LOMAS</v>
+        <v>LONGANIZA ESPECIAL KG DON MATIAS</v>
       </c>
       <c r="C203" t="str">
         <v/>
       </c>
       <c r="D203" t="str">
-        <v>31892</v>
+        <v>31266</v>
       </c>
       <c r="E203" t="str">
-        <v>3160</v>
+        <v>8396</v>
       </c>
       <c r="F203" t="str">
         <v>Por peso</v>
@@ -4461,19 +4461,19 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>631267</v>
+        <v>631269</v>
       </c>
       <c r="B204" t="str">
-        <v>LONGANIZA KG SCHWENCKE</v>
+        <v>QUESO CABEZA KG SCHWENCKE</v>
       </c>
       <c r="C204" t="str">
         <v/>
       </c>
       <c r="D204" t="str">
-        <v>31267</v>
+        <v>31269</v>
       </c>
       <c r="E204" t="str">
-        <v>10396</v>
+        <v>11596</v>
       </c>
       <c r="F204" t="str">
         <v>Por peso</v>
@@ -4481,19 +4481,19 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>631266</v>
+        <v>631274</v>
       </c>
       <c r="B205" t="str">
-        <v>LONGANIZA ESPECIAL KG DON MATIAS</v>
+        <v>MORTAD. LISA SCHWENCKE KG</v>
       </c>
       <c r="C205" t="str">
         <v/>
       </c>
       <c r="D205" t="str">
-        <v>31266</v>
+        <v>31274</v>
       </c>
       <c r="E205" t="str">
-        <v>8396</v>
+        <v>9196</v>
       </c>
       <c r="F205" t="str">
         <v>Por peso</v>
@@ -4501,19 +4501,19 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>631269</v>
+        <v>631072</v>
       </c>
       <c r="B206" t="str">
-        <v>QUESO CABEZA KG SCHWENCKE</v>
+        <v>MORTAD. JAMONADA SCHWENCKE KG</v>
       </c>
       <c r="C206" t="str">
         <v/>
       </c>
       <c r="D206" t="str">
-        <v>31269</v>
+        <v>31072</v>
       </c>
       <c r="E206" t="str">
-        <v>11596</v>
+        <v>9996</v>
       </c>
       <c r="F206" t="str">
         <v>Por peso</v>
@@ -4521,19 +4521,19 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>631274</v>
+        <v>631301</v>
       </c>
       <c r="B207" t="str">
-        <v>MORTAD. LISA SCHWENCKE KG</v>
+        <v>MORTAD. LISA PACEL KG</v>
       </c>
       <c r="C207" t="str">
         <v/>
       </c>
       <c r="D207" t="str">
-        <v>31274</v>
+        <v>31301</v>
       </c>
       <c r="E207" t="str">
-        <v>9196</v>
+        <v>10996</v>
       </c>
       <c r="F207" t="str">
         <v>Por peso</v>
@@ -4541,19 +4541,19 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>631072</v>
+        <v>631302</v>
       </c>
       <c r="B208" t="str">
-        <v>MORTAD. JAMONADA SCHWENCKE KG</v>
+        <v>MORTAD. JAMONADA PACEL KG</v>
       </c>
       <c r="C208" t="str">
         <v/>
       </c>
       <c r="D208" t="str">
-        <v>31072</v>
+        <v>31302</v>
       </c>
       <c r="E208" t="str">
-        <v>9996</v>
+        <v>11996</v>
       </c>
       <c r="F208" t="str">
         <v>Por peso</v>
@@ -4561,16 +4561,16 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>631301</v>
+        <v>631303</v>
       </c>
       <c r="B209" t="str">
-        <v>MORTAD. LISA PACEL KG</v>
+        <v>MORTAD. ALEMANA PACEL KG.</v>
       </c>
       <c r="C209" t="str">
         <v/>
       </c>
       <c r="D209" t="str">
-        <v>31301</v>
+        <v>31303</v>
       </c>
       <c r="E209" t="str">
         <v>10996</v>
@@ -4581,19 +4581,19 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>631302</v>
+        <v>631306</v>
       </c>
       <c r="B210" t="str">
-        <v>MORTAD. JAMONADA PACEL KG</v>
+        <v>LONGANIZA ARTESANAL PACEL KG</v>
       </c>
       <c r="C210" t="str">
         <v/>
       </c>
       <c r="D210" t="str">
-        <v>31302</v>
+        <v>31306</v>
       </c>
       <c r="E210" t="str">
-        <v>11996</v>
+        <v>12996</v>
       </c>
       <c r="F210" t="str">
         <v>Por peso</v>
@@ -4601,19 +4601,19 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>631303</v>
+        <v>631307</v>
       </c>
       <c r="B211" t="str">
-        <v>MORTAD. ALEMANA PACEL KG.</v>
+        <v>PRIETA PACEL KG</v>
       </c>
       <c r="C211" t="str">
         <v/>
       </c>
       <c r="D211" t="str">
-        <v>31303</v>
+        <v>31307</v>
       </c>
       <c r="E211" t="str">
-        <v>10996</v>
+        <v>9996</v>
       </c>
       <c r="F211" t="str">
         <v>Por peso</v>
@@ -4621,19 +4621,19 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>631306</v>
+        <v>631308</v>
       </c>
       <c r="B212" t="str">
-        <v>LONGANIZA ARTESANAL PACEL KG</v>
+        <v>ARROLLADO HUASO PACEL KG.</v>
       </c>
       <c r="C212" t="str">
         <v/>
       </c>
       <c r="D212" t="str">
-        <v>31306</v>
+        <v>31308</v>
       </c>
       <c r="E212" t="str">
-        <v>12996</v>
+        <v>14996</v>
       </c>
       <c r="F212" t="str">
         <v>Por peso</v>
@@ -4641,19 +4641,19 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>631307</v>
+        <v>632890</v>
       </c>
       <c r="B213" t="str">
-        <v>PRIETA PACEL KG</v>
+        <v>JAMON COLONIAL G1 PF KG</v>
       </c>
       <c r="C213" t="str">
         <v/>
       </c>
       <c r="D213" t="str">
-        <v>31307</v>
+        <v>32890</v>
       </c>
       <c r="E213" t="str">
-        <v>9996</v>
+        <v>11996</v>
       </c>
       <c r="F213" t="str">
         <v>Por peso</v>
@@ -4661,19 +4661,19 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>631308</v>
+        <v>631990</v>
       </c>
       <c r="B214" t="str">
-        <v>ARROLLADO HUASO PACEL KG.</v>
+        <v>ACEITUNA AZAPA SUPER·90-100 KG</v>
       </c>
       <c r="C214" t="str">
         <v/>
       </c>
       <c r="D214" t="str">
-        <v>31308</v>
+        <v>31990</v>
       </c>
       <c r="E214" t="str">
-        <v>14996</v>
+        <v>6396</v>
       </c>
       <c r="F214" t="str">
         <v>Por peso</v>
@@ -4681,19 +4681,19 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>632890</v>
+        <v>631904</v>
       </c>
       <c r="B215" t="str">
-        <v>JAMON COLONIAL G1 PF KG</v>
+        <v>COSTILLAR AHUMADO PACEL KG</v>
       </c>
       <c r="C215" t="str">
         <v/>
       </c>
       <c r="D215" t="str">
-        <v>32890</v>
+        <v>31904</v>
       </c>
       <c r="E215" t="str">
-        <v>11996</v>
+        <v>16996</v>
       </c>
       <c r="F215" t="str">
         <v>Por peso</v>
@@ -4701,19 +4701,19 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>631990</v>
+        <v>631340</v>
       </c>
       <c r="B216" t="str">
-        <v>ACEITUNA AZAPA SUPER·90-100 KG</v>
+        <v>PICKLE ESPECIAL FINO KG. SOLIS</v>
       </c>
       <c r="C216" t="str">
         <v/>
       </c>
       <c r="D216" t="str">
-        <v>31990</v>
+        <v>31340</v>
       </c>
       <c r="E216" t="str">
-        <v>6396</v>
+        <v>4396</v>
       </c>
       <c r="F216" t="str">
         <v>Por peso</v>
@@ -4721,19 +4721,19 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>631904</v>
+        <v>631341</v>
       </c>
       <c r="B217" t="str">
-        <v>COSTILLAR AHUMADO PACEL KG</v>
+        <v>CEBOLLA ESCABECHE KG. SOLIS</v>
       </c>
       <c r="C217" t="str">
         <v/>
       </c>
       <c r="D217" t="str">
-        <v>31904</v>
+        <v>31341</v>
       </c>
       <c r="E217" t="str">
-        <v>16996</v>
+        <v>3996</v>
       </c>
       <c r="F217" t="str">
         <v>Por peso</v>
@@ -4741,19 +4741,19 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>631340</v>
+        <v>631342</v>
       </c>
       <c r="B218" t="str">
-        <v>PICKLE ESPECIAL FINO KG. SOLIS</v>
+        <v>CEBOLLA PERLA KG. SOLIS</v>
       </c>
       <c r="C218" t="str">
         <v/>
       </c>
       <c r="D218" t="str">
-        <v>31340</v>
+        <v>31342</v>
       </c>
       <c r="E218" t="str">
-        <v>4396</v>
+        <v>4690</v>
       </c>
       <c r="F218" t="str">
         <v>Por peso</v>
@@ -4761,19 +4761,19 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>631341</v>
+        <v>631343</v>
       </c>
       <c r="B219" t="str">
-        <v>CEBOLLA ESCABECHE KG. SOLIS</v>
+        <v>AJI ORO KG. SOLIS</v>
       </c>
       <c r="C219" t="str">
         <v/>
       </c>
       <c r="D219" t="str">
-        <v>31341</v>
+        <v>31343</v>
       </c>
       <c r="E219" t="str">
-        <v>3996</v>
+        <v>4396</v>
       </c>
       <c r="F219" t="str">
         <v>Por peso</v>
@@ -4781,19 +4781,19 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>631342</v>
+        <v>631344</v>
       </c>
       <c r="B220" t="str">
-        <v>CEBOLLA PERLA KG. SOLIS</v>
+        <v>PEPINILLO DILL KG. SOLIS</v>
       </c>
       <c r="C220" t="str">
         <v/>
       </c>
       <c r="D220" t="str">
-        <v>31342</v>
+        <v>31344</v>
       </c>
       <c r="E220" t="str">
-        <v>4690</v>
+        <v>4696</v>
       </c>
       <c r="F220" t="str">
         <v>Por peso</v>
@@ -4801,19 +4801,19 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>631343</v>
+        <v>631346</v>
       </c>
       <c r="B221" t="str">
-        <v>AJI ORO KG. SOLIS</v>
+        <v>PEPINO FINO CHICO KG SOLIS</v>
       </c>
       <c r="C221" t="str">
         <v/>
       </c>
       <c r="D221" t="str">
-        <v>31343</v>
+        <v>31346</v>
       </c>
       <c r="E221" t="str">
-        <v>4396</v>
+        <v>4696</v>
       </c>
       <c r="F221" t="str">
         <v>Por peso</v>
@@ -4821,19 +4821,19 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>631344</v>
+        <v>631350</v>
       </c>
       <c r="B222" t="str">
-        <v>PEPINILLO DILL KG. SOLIS</v>
+        <v>AMERICANAKG. SOLIS</v>
       </c>
       <c r="C222" t="str">
         <v/>
       </c>
       <c r="D222" t="str">
-        <v>31344</v>
+        <v>31350</v>
       </c>
       <c r="E222" t="str">
-        <v>4696</v>
+        <v>2996</v>
       </c>
       <c r="F222" t="str">
         <v>Por peso</v>
@@ -4841,19 +4841,19 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>631346</v>
+        <v>631339</v>
       </c>
       <c r="B223" t="str">
-        <v>PEPINO FINO CHICO KG SOLIS</v>
+        <v>ACEITUNA AZAPA EXTRA KG SOLIS</v>
       </c>
       <c r="C223" t="str">
         <v/>
       </c>
       <c r="D223" t="str">
-        <v>31346</v>
+        <v>31339</v>
       </c>
       <c r="E223" t="str">
-        <v>4696</v>
+        <v>9396</v>
       </c>
       <c r="F223" t="str">
         <v>Por peso</v>
@@ -4861,19 +4861,19 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>631350</v>
+        <v>631499</v>
       </c>
       <c r="B224" t="str">
-        <v>AMERICANAKG. SOLIS</v>
+        <v>JAMON GLACE G2 C9 PF KG</v>
       </c>
       <c r="C224" t="str">
         <v/>
       </c>
       <c r="D224" t="str">
-        <v>31350</v>
+        <v>31499</v>
       </c>
       <c r="E224" t="str">
-        <v>2996</v>
+        <v>9996</v>
       </c>
       <c r="F224" t="str">
         <v>Por peso</v>
@@ -4881,19 +4881,19 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>631339</v>
+        <v>634515</v>
       </c>
       <c r="B225" t="str">
-        <v>ACEITUNA AZAPA EXTRA KG SOLIS</v>
+        <v>SALAME KG PREFERIDA</v>
       </c>
       <c r="C225" t="str">
         <v/>
       </c>
       <c r="D225" t="str">
-        <v>31339</v>
+        <v>34515</v>
       </c>
       <c r="E225" t="str">
-        <v>9396</v>
+        <v>15996</v>
       </c>
       <c r="F225" t="str">
         <v>Por peso</v>
@@ -4901,19 +4901,19 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>631499</v>
+        <v>633096</v>
       </c>
       <c r="B226" t="str">
-        <v>JAMON GLACE G2 C9 PF KG</v>
+        <v>PECHUGA POLLO COCIDA SAN JORGE KG</v>
       </c>
       <c r="C226" t="str">
         <v/>
       </c>
       <c r="D226" t="str">
-        <v>31499</v>
+        <v>33096</v>
       </c>
       <c r="E226" t="str">
-        <v>9996</v>
+        <v>10996</v>
       </c>
       <c r="F226" t="str">
         <v>Por peso</v>
@@ -4921,19 +4921,19 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>634515</v>
+        <v>633403</v>
       </c>
       <c r="B227" t="str">
-        <v>SALAME KG PREFERIDA</v>
+        <v>ACEITUNA SEVILLANA CUGAT KILO</v>
       </c>
       <c r="C227" t="str">
         <v/>
       </c>
       <c r="D227" t="str">
-        <v>34515</v>
+        <v>33403</v>
       </c>
       <c r="E227" t="str">
-        <v>15996</v>
+        <v>2996</v>
       </c>
       <c r="F227" t="str">
         <v>Por peso</v>
@@ -4941,19 +4941,19 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>633096</v>
+        <v>635072</v>
       </c>
       <c r="B228" t="str">
-        <v>PECHUGA POLLO COCIDA SAN JORGE KG</v>
+        <v>COSTILLAR AHUMADO KILO BRAUNAU</v>
       </c>
       <c r="C228" t="str">
         <v/>
       </c>
       <c r="D228" t="str">
-        <v>33096</v>
+        <v>35072</v>
       </c>
       <c r="E228" t="str">
-        <v>10996</v>
+        <v>15996</v>
       </c>
       <c r="F228" t="str">
         <v>Por peso</v>
@@ -4961,19 +4961,19 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>633403</v>
+        <v>635074</v>
       </c>
       <c r="B229" t="str">
-        <v>ACEITUNA SEVILLANA CUGAT KILO</v>
+        <v>LONGANIZA KG BRAUNAU</v>
       </c>
       <c r="C229" t="str">
         <v/>
       </c>
       <c r="D229" t="str">
-        <v>33403</v>
+        <v>35074</v>
       </c>
       <c r="E229" t="str">
-        <v>2996</v>
+        <v>14796</v>
       </c>
       <c r="F229" t="str">
         <v>Por peso</v>
@@ -4981,19 +4981,19 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>635072</v>
+        <v>635077</v>
       </c>
       <c r="B230" t="str">
-        <v>COSTILLAR AHUMADO KILO BRAUNAU</v>
+        <v>PATE FINAS HIERBAS BRAUNAU</v>
       </c>
       <c r="C230" t="str">
         <v/>
       </c>
       <c r="D230" t="str">
-        <v>35072</v>
+        <v>35077</v>
       </c>
       <c r="E230" t="str">
-        <v>15996</v>
+        <v>9960</v>
       </c>
       <c r="F230" t="str">
         <v>Por peso</v>
@@ -5001,19 +5001,19 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>635074</v>
+        <v>635079</v>
       </c>
       <c r="B231" t="str">
-        <v>LONGANIZA KG BRAUNAU</v>
+        <v>QUESO CABEZA KG BRAUNAU</v>
       </c>
       <c r="C231" t="str">
         <v/>
       </c>
       <c r="D231" t="str">
-        <v>35074</v>
+        <v>35079</v>
       </c>
       <c r="E231" t="str">
-        <v>14796</v>
+        <v>11196</v>
       </c>
       <c r="F231" t="str">
         <v>Por peso</v>
@@ -5021,19 +5021,19 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>635077</v>
+        <v>635080</v>
       </c>
       <c r="B232" t="str">
-        <v>PATE FINAS HIERBAS BRAUNAU</v>
+        <v>QUESO SANGRE BRAUNAU KG</v>
       </c>
       <c r="C232" t="str">
         <v/>
       </c>
       <c r="D232" t="str">
-        <v>35077</v>
+        <v>35080</v>
       </c>
       <c r="E232" t="str">
-        <v>9960</v>
+        <v>10886</v>
       </c>
       <c r="F232" t="str">
         <v>Por peso</v>
@@ -5041,19 +5041,19 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>635079</v>
+        <v>635541</v>
       </c>
       <c r="B233" t="str">
-        <v>QUESO CABEZA KG BRAUNAU</v>
+        <v>JAMON COLONIAL SUPER CERDO KG</v>
       </c>
       <c r="C233" t="str">
         <v/>
       </c>
       <c r="D233" t="str">
-        <v>35079</v>
+        <v>35541</v>
       </c>
       <c r="E233" t="str">
-        <v>11196</v>
+        <v>8396</v>
       </c>
       <c r="F233" t="str">
         <v>Por peso</v>
@@ -5061,19 +5061,19 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>635080</v>
+        <v>635542</v>
       </c>
       <c r="B234" t="str">
-        <v>QUESO SANGRE BRAUNAU KG</v>
+        <v>JAMON ACARAMELA SUPER CERDO KG</v>
       </c>
       <c r="C234" t="str">
         <v/>
       </c>
       <c r="D234" t="str">
-        <v>35080</v>
+        <v>35542</v>
       </c>
       <c r="E234" t="str">
-        <v>10886</v>
+        <v>8796</v>
       </c>
       <c r="F234" t="str">
         <v>Por peso</v>
@@ -5081,19 +5081,19 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>635541</v>
+        <v>634571</v>
       </c>
       <c r="B235" t="str">
-        <v>JAMON COLONIAL SUPER CERDO KG</v>
+        <v>ACEITUNA SEVILLANA ECONOMICA KG SOLIS</v>
       </c>
       <c r="C235" t="str">
         <v/>
       </c>
       <c r="D235" t="str">
-        <v>35541</v>
+        <v>34571</v>
       </c>
       <c r="E235" t="str">
-        <v>8396</v>
+        <v>6196</v>
       </c>
       <c r="F235" t="str">
         <v>Por peso</v>
@@ -5101,19 +5101,19 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>635542</v>
+        <v>631780</v>
       </c>
       <c r="B236" t="str">
-        <v>JAMON ACARAMELA SUPER CERDO KG</v>
+        <v>LONGANIZA ARTESANAL KG MOLINO VIEJO</v>
       </c>
       <c r="C236" t="str">
         <v/>
       </c>
       <c r="D236" t="str">
-        <v>35542</v>
+        <v>31780</v>
       </c>
       <c r="E236" t="str">
-        <v>8796</v>
+        <v>10360</v>
       </c>
       <c r="F236" t="str">
         <v>Por peso</v>
@@ -5121,19 +5121,19 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>634571</v>
+        <v>635550</v>
       </c>
       <c r="B237" t="str">
-        <v>ACEITUNA SEVILLANA ECONOMICA KG SOLIS</v>
+        <v>CEBOLLA ESCABECHE KILO LAS LOMAS</v>
       </c>
       <c r="C237" t="str">
         <v/>
       </c>
       <c r="D237" t="str">
-        <v>34571</v>
+        <v>35550</v>
       </c>
       <c r="E237" t="str">
-        <v>6196</v>
+        <v>3596</v>
       </c>
       <c r="F237" t="str">
         <v>Por peso</v>
@@ -5141,19 +5141,19 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>631780</v>
+        <v>635551</v>
       </c>
       <c r="B238" t="str">
-        <v>LONGANIZA ARTESANAL KG MOLINO VIEJO</v>
+        <v>CHUCRUT KILO LAS LOMAS</v>
       </c>
       <c r="C238" t="str">
         <v/>
       </c>
       <c r="D238" t="str">
-        <v>31780</v>
+        <v>35551</v>
       </c>
       <c r="E238" t="str">
-        <v>10360</v>
+        <v>2996</v>
       </c>
       <c r="F238" t="str">
         <v>Por peso</v>
@@ -5161,19 +5161,19 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>635550</v>
+        <v>635552</v>
       </c>
       <c r="B239" t="str">
-        <v>CEBOLLA ESCABECHE KILO LAS LOMAS</v>
+        <v>SALSA AMERICANA KILO LAS LOMAS</v>
       </c>
       <c r="C239" t="str">
         <v/>
       </c>
       <c r="D239" t="str">
-        <v>35550</v>
+        <v>35552</v>
       </c>
       <c r="E239" t="str">
-        <v>3596</v>
+        <v>3160</v>
       </c>
       <c r="F239" t="str">
         <v>Por peso</v>
@@ -5181,19 +5181,19 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>635551</v>
+        <v>634541</v>
       </c>
       <c r="B240" t="str">
-        <v>CHUCRUT KILO LAS LOMAS</v>
+        <v>MORTAD. JAMONADA CENTENARIO LP KG</v>
       </c>
       <c r="C240" t="str">
         <v/>
       </c>
       <c r="D240" t="str">
-        <v>35551</v>
+        <v>34541</v>
       </c>
       <c r="E240" t="str">
-        <v>2996</v>
+        <v>9196</v>
       </c>
       <c r="F240" t="str">
         <v>Por peso</v>
@@ -5201,19 +5201,19 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>635552</v>
+        <v>633099</v>
       </c>
       <c r="B241" t="str">
-        <v>SALSA AMERICANA KILO LAS LOMAS</v>
+        <v>LONGANIZA CASERA KG CASTILLA</v>
       </c>
       <c r="C241" t="str">
         <v/>
       </c>
       <c r="D241" t="str">
-        <v>35552</v>
+        <v>33099</v>
       </c>
       <c r="E241" t="str">
-        <v>3160</v>
+        <v>8596</v>
       </c>
       <c r="F241" t="str">
         <v>Por peso</v>
@@ -5221,19 +5221,19 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>634541</v>
+        <v>633098</v>
       </c>
       <c r="B242" t="str">
-        <v>MORTAD. JAMONADA CENTENARIO LP KG</v>
+        <v>ARROLLADO HUASO CASTILLA KILO</v>
       </c>
       <c r="C242" t="str">
         <v/>
       </c>
       <c r="D242" t="str">
-        <v>34541</v>
+        <v>33098</v>
       </c>
       <c r="E242" t="str">
-        <v>9196</v>
+        <v>9996</v>
       </c>
       <c r="F242" t="str">
         <v>Por peso</v>
@@ -5241,19 +5241,19 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>633099</v>
+        <v>633103</v>
       </c>
       <c r="B243" t="str">
-        <v>LONGANIZA CASERA KG CASTILLA</v>
+        <v>ARROLLADOCAJI CASTILLA KILO</v>
       </c>
       <c r="C243" t="str">
         <v/>
       </c>
       <c r="D243" t="str">
-        <v>33099</v>
+        <v>33103</v>
       </c>
       <c r="E243" t="str">
-        <v>8596</v>
+        <v>9996</v>
       </c>
       <c r="F243" t="str">
         <v>Por peso</v>
@@ -5261,16 +5261,16 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>633098</v>
+        <v>633104</v>
       </c>
       <c r="B244" t="str">
-        <v>ARROLLADO HUASO CASTILLA KILO</v>
+        <v>QUESO CABEZA KG CASTILLA</v>
       </c>
       <c r="C244" t="str">
         <v/>
       </c>
       <c r="D244" t="str">
-        <v>33098</v>
+        <v>33104</v>
       </c>
       <c r="E244" t="str">
         <v>9996</v>
@@ -5281,19 +5281,19 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>633103</v>
+        <v>633330</v>
       </c>
       <c r="B245" t="str">
-        <v>ARROLLADOCAJI CASTILLA KILO</v>
+        <v>COSTILLAR CERDO AHUMADO CASTILLA KILO</v>
       </c>
       <c r="C245" t="str">
         <v/>
       </c>
       <c r="D245" t="str">
-        <v>33103</v>
+        <v>33330</v>
       </c>
       <c r="E245" t="str">
-        <v>9996</v>
+        <v>14796</v>
       </c>
       <c r="F245" t="str">
         <v>Por peso</v>
@@ -5301,19 +5301,19 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>633104</v>
+        <v>634292</v>
       </c>
       <c r="B246" t="str">
-        <v>QUESO CABEZA KG CASTILLA</v>
+        <v>PEPINO COCKTAIL HP KILO</v>
       </c>
       <c r="C246" t="str">
         <v/>
       </c>
       <c r="D246" t="str">
-        <v>33104</v>
+        <v>34292</v>
       </c>
       <c r="E246" t="str">
-        <v>9996</v>
+        <v>4996</v>
       </c>
       <c r="F246" t="str">
         <v>Por peso</v>
@@ -5321,19 +5321,19 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>633330</v>
+        <v>638989</v>
       </c>
       <c r="B247" t="str">
-        <v>COSTILLAR CERDO AHUMADO CASTILLA KILO</v>
+        <v>QUESO DE CABEZA DON RODRIGO</v>
       </c>
       <c r="C247" t="str">
         <v/>
       </c>
       <c r="D247" t="str">
-        <v>33330</v>
+        <v>38989</v>
       </c>
       <c r="E247" t="str">
-        <v>14796</v>
+        <v>5996</v>
       </c>
       <c r="F247" t="str">
         <v>Por peso</v>
@@ -5341,19 +5341,19 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>634292</v>
+        <v>638485</v>
       </c>
       <c r="B248" t="str">
-        <v>PEPINO COCKTAIL HP KILO</v>
+        <v>ARROLLADO DE LOMO SIN AJI DON RODRIGO</v>
       </c>
       <c r="C248" t="str">
         <v/>
       </c>
       <c r="D248" t="str">
-        <v>34292</v>
+        <v>38485</v>
       </c>
       <c r="E248" t="str">
-        <v>4996</v>
+        <v>8996</v>
       </c>
       <c r="F248" t="str">
         <v>Por peso</v>
@@ -5361,16 +5361,16 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>638989</v>
+        <v>638486</v>
       </c>
       <c r="B249" t="str">
-        <v>QUESO DE CABEZA DON RODRIGO</v>
+        <v>QUESO CABEZA CHILENO PORCIONADO DON RODRIGO</v>
       </c>
       <c r="C249" t="str">
         <v/>
       </c>
       <c r="D249" t="str">
-        <v>38989</v>
+        <v>38486</v>
       </c>
       <c r="E249" t="str">
         <v>5996</v>
@@ -5381,19 +5381,19 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>638485</v>
+        <v>634801</v>
       </c>
       <c r="B250" t="str">
-        <v>ARROLLADO DE LOMO SIN AJI DON RODRIGO</v>
+        <v>LONGANIZA BLANCA DON RODRIGO</v>
       </c>
       <c r="C250" t="str">
         <v/>
       </c>
       <c r="D250" t="str">
-        <v>38485</v>
+        <v>34801</v>
       </c>
       <c r="E250" t="str">
-        <v>8996</v>
+        <v>4390</v>
       </c>
       <c r="F250" t="str">
         <v>Por peso</v>
@@ -5401,16 +5401,16 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>638486</v>
+        <v>634802</v>
       </c>
       <c r="B251" t="str">
-        <v>QUESO CABEZA CHILENO PORCIONADO DON RODRIGO</v>
+        <v>QUESO CABEZA PORCIONADO DON RODRIGO</v>
       </c>
       <c r="C251" t="str">
         <v/>
       </c>
       <c r="D251" t="str">
-        <v>38486</v>
+        <v>34802</v>
       </c>
       <c r="E251" t="str">
         <v>5996</v>
@@ -5421,19 +5421,19 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>634801</v>
+        <v>636421</v>
       </c>
       <c r="B252" t="str">
-        <v>LONGANIZA BLANCA DON RODRIGO</v>
+        <v>LONGANIZA BELEN KG</v>
       </c>
       <c r="C252" t="str">
         <v/>
       </c>
       <c r="D252" t="str">
-        <v>34801</v>
+        <v>36421</v>
       </c>
       <c r="E252" t="str">
-        <v>4390</v>
+        <v>7196</v>
       </c>
       <c r="F252" t="str">
         <v>Por peso</v>
@@ -5441,19 +5441,19 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>634802</v>
+        <v>636422</v>
       </c>
       <c r="B253" t="str">
-        <v>QUESO CABEZA PORCIONADO DON RODRIGO</v>
+        <v>LONGANIZA BELEN MERKEN KG</v>
       </c>
       <c r="C253" t="str">
         <v/>
       </c>
       <c r="D253" t="str">
-        <v>34802</v>
+        <v>36422</v>
       </c>
       <c r="E253" t="str">
-        <v>5996</v>
+        <v>7996</v>
       </c>
       <c r="F253" t="str">
         <v>Por peso</v>
@@ -5461,19 +5461,19 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>636421</v>
+        <v>636423</v>
       </c>
       <c r="B254" t="str">
-        <v>LONGANIZA BELEN KG</v>
+        <v>ARROLLADO BELEN KG</v>
       </c>
       <c r="C254" t="str">
         <v/>
       </c>
       <c r="D254" t="str">
-        <v>36421</v>
+        <v>36423</v>
       </c>
       <c r="E254" t="str">
-        <v>7196</v>
+        <v>9196</v>
       </c>
       <c r="F254" t="str">
         <v>Por peso</v>
@@ -5481,19 +5481,19 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>636422</v>
+        <v>636424</v>
       </c>
       <c r="B255" t="str">
-        <v>LONGANIZA BELEN MERKEN KG</v>
+        <v>AROLLADO BELEN MERKEN KG</v>
       </c>
       <c r="C255" t="str">
         <v/>
       </c>
       <c r="D255" t="str">
-        <v>36422</v>
+        <v>36424</v>
       </c>
       <c r="E255" t="str">
-        <v>7996</v>
+        <v>9396</v>
       </c>
       <c r="F255" t="str">
         <v>Por peso</v>
@@ -5501,19 +5501,19 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>636423</v>
+        <v>636425</v>
       </c>
       <c r="B256" t="str">
-        <v>ARROLLADO BELEN KG</v>
+        <v>QUESO CERDO BELEN KG</v>
       </c>
       <c r="C256" t="str">
         <v/>
       </c>
       <c r="D256" t="str">
-        <v>36423</v>
+        <v>36425</v>
       </c>
       <c r="E256" t="str">
-        <v>9196</v>
+        <v>5996</v>
       </c>
       <c r="F256" t="str">
         <v>Por peso</v>
@@ -5521,19 +5521,19 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>636424</v>
+        <v>636000</v>
       </c>
       <c r="B257" t="str">
-        <v>AROLLADO BELEN MERKEN KG</v>
+        <v>PICKLE PORTAL DEL SUR KG</v>
       </c>
       <c r="C257" t="str">
         <v/>
       </c>
       <c r="D257" t="str">
-        <v>36424</v>
+        <v>36000</v>
       </c>
       <c r="E257" t="str">
-        <v>9396</v>
+        <v>3490</v>
       </c>
       <c r="F257" t="str">
         <v>Por peso</v>
@@ -5541,19 +5541,19 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>636425</v>
+        <v>636001</v>
       </c>
       <c r="B258" t="str">
-        <v>QUESO CERDO BELEN KG</v>
+        <v>AJI ORO PORTAL DEL SUR KG</v>
       </c>
       <c r="C258" t="str">
         <v/>
       </c>
       <c r="D258" t="str">
-        <v>36425</v>
+        <v>36001</v>
       </c>
       <c r="E258" t="str">
-        <v>5996</v>
+        <v>3890</v>
       </c>
       <c r="F258" t="str">
         <v>Por peso</v>
@@ -5561,19 +5561,19 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>636000</v>
+        <v>636002</v>
       </c>
       <c r="B259" t="str">
-        <v>PICKLE PORTAL DEL SUR KG</v>
+        <v>CEBOLLA PERLA PORTAL DEL SUR KG</v>
       </c>
       <c r="C259" t="str">
         <v/>
       </c>
       <c r="D259" t="str">
-        <v>36000</v>
+        <v>36002</v>
       </c>
       <c r="E259" t="str">
-        <v>3490</v>
+        <v>4990</v>
       </c>
       <c r="F259" t="str">
         <v>Por peso</v>
@@ -5581,19 +5581,19 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>636001</v>
+        <v>636003</v>
       </c>
       <c r="B260" t="str">
-        <v>AJI ORO PORTAL DEL SUR KG</v>
+        <v>PEPINILLO PORTAL DEL SUR KG</v>
       </c>
       <c r="C260" t="str">
         <v/>
       </c>
       <c r="D260" t="str">
-        <v>36001</v>
+        <v>36003</v>
       </c>
       <c r="E260" t="str">
-        <v>3890</v>
+        <v>4698</v>
       </c>
       <c r="F260" t="str">
         <v>Por peso</v>
@@ -5601,19 +5601,19 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>636002</v>
+        <v>636004</v>
       </c>
       <c r="B261" t="str">
-        <v>CEBOLLA PERLA PORTAL DEL SUR KG</v>
+        <v>CHUCRUT PORTAL DEL SUR KG</v>
       </c>
       <c r="C261" t="str">
         <v/>
       </c>
       <c r="D261" t="str">
-        <v>36002</v>
+        <v>36004</v>
       </c>
       <c r="E261" t="str">
-        <v>4990</v>
+        <v>3290</v>
       </c>
       <c r="F261" t="str">
         <v>Por peso</v>
@@ -5621,19 +5621,19 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>636003</v>
+        <v>636005</v>
       </c>
       <c r="B262" t="str">
-        <v>PEPINILLO PORTAL DEL SUR KG</v>
+        <v>SALSA AMERICANA PORTAL DEL SUR KG</v>
       </c>
       <c r="C262" t="str">
         <v/>
       </c>
       <c r="D262" t="str">
-        <v>36003</v>
+        <v>36005</v>
       </c>
       <c r="E262" t="str">
-        <v>4698</v>
+        <v>2990</v>
       </c>
       <c r="F262" t="str">
         <v>Por peso</v>
@@ -5641,16 +5641,16 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>636004</v>
+        <v>636006</v>
       </c>
       <c r="B263" t="str">
-        <v>CHUCRUT PORTAL DEL SUR KG</v>
+        <v>ACEITUNA CHICA PORTAL DEL SUR KG</v>
       </c>
       <c r="C263" t="str">
         <v/>
       </c>
       <c r="D263" t="str">
-        <v>36004</v>
+        <v>36006</v>
       </c>
       <c r="E263" t="str">
         <v>3290</v>
@@ -5661,19 +5661,19 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>636005</v>
+        <v>636007</v>
       </c>
       <c r="B264" t="str">
-        <v>SALSA AMERICANA PORTAL DEL SUR KG</v>
+        <v>ACEITUNA AZAPA PORTAL DEL SUR KG</v>
       </c>
       <c r="C264" t="str">
         <v/>
       </c>
       <c r="D264" t="str">
-        <v>36005</v>
+        <v>36007</v>
       </c>
       <c r="E264" t="str">
-        <v>2990</v>
+        <v>4990</v>
       </c>
       <c r="F264" t="str">
         <v>Por peso</v>
@@ -5681,19 +5681,19 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>636006</v>
+        <v>631178</v>
       </c>
       <c r="B265" t="str">
-        <v>ACEITUNA CHICA PORTAL DEL SUR KG</v>
+        <v>LONGANIZA CORDILLERA GRANEL KG</v>
       </c>
       <c r="C265" t="str">
         <v/>
       </c>
       <c r="D265" t="str">
-        <v>36006</v>
+        <v>31178</v>
       </c>
       <c r="E265" t="str">
-        <v>3290</v>
+        <v>6996</v>
       </c>
       <c r="F265" t="str">
         <v>Por peso</v>
@@ -5701,19 +5701,19 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>636007</v>
+        <v>631586</v>
       </c>
       <c r="B266" t="str">
-        <v>ACEITUNA AZAPA PORTAL DEL SUR KG</v>
+        <v>PRIETAS CORDILLERA GRANEL KG</v>
       </c>
       <c r="C266" t="str">
         <v/>
       </c>
       <c r="D266" t="str">
-        <v>36007</v>
+        <v>31586</v>
       </c>
       <c r="E266" t="str">
-        <v>4990</v>
+        <v>4596</v>
       </c>
       <c r="F266" t="str">
         <v>Por peso</v>
@@ -5721,19 +5721,19 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>631178</v>
+        <v>631699</v>
       </c>
       <c r="B267" t="str">
-        <v>LONGANIZA CORDILLERA GRANEL KG</v>
+        <v>ARROLLADO CORDILLERA GRANEL KG</v>
       </c>
       <c r="C267" t="str">
         <v/>
       </c>
       <c r="D267" t="str">
-        <v>31178</v>
+        <v>31699</v>
       </c>
       <c r="E267" t="str">
-        <v>6996</v>
+        <v>7396</v>
       </c>
       <c r="F267" t="str">
         <v>Por peso</v>
@@ -5741,19 +5741,19 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>631586</v>
+        <v>631583</v>
       </c>
       <c r="B268" t="str">
-        <v>PRIETAS CORDILLERA GRANEL KG</v>
+        <v>QUESO CABEZA GRANEL KG</v>
       </c>
       <c r="C268" t="str">
         <v/>
       </c>
       <c r="D268" t="str">
-        <v>31586</v>
+        <v>31583</v>
       </c>
       <c r="E268" t="str">
-        <v>4596</v>
+        <v>5196</v>
       </c>
       <c r="F268" t="str">
         <v>Por peso</v>
@@ -5761,19 +5761,19 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>631699</v>
+        <v>631258</v>
       </c>
       <c r="B269" t="str">
-        <v>ARROLLADO CORDILLERA GRANEL KG</v>
+        <v>JAMON PIERNA ARTESANAL DON RODRIGO</v>
       </c>
       <c r="C269" t="str">
         <v/>
       </c>
       <c r="D269" t="str">
-        <v>31699</v>
+        <v>31258</v>
       </c>
       <c r="E269" t="str">
-        <v>7396</v>
+        <v>11996</v>
       </c>
       <c r="F269" t="str">
         <v>Por peso</v>
@@ -5781,19 +5781,19 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>631583</v>
+        <v>631479</v>
       </c>
       <c r="B270" t="str">
-        <v>QUESO CABEZA GRANEL KG</v>
+        <v>ARROLLADO CHILENO PORCIONADO DON RODRIGO</v>
       </c>
       <c r="C270" t="str">
         <v/>
       </c>
       <c r="D270" t="str">
-        <v>31583</v>
+        <v>31479</v>
       </c>
       <c r="E270" t="str">
-        <v>5196</v>
+        <v>8990</v>
       </c>
       <c r="F270" t="str">
         <v>Por peso</v>
@@ -5801,19 +5801,19 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>631258</v>
+        <v>631965</v>
       </c>
       <c r="B271" t="str">
-        <v>JAMON PIERNA ARTESANAL DON RODRIGO</v>
+        <v>JAMON PIERNA ARTESANAL WINTER KG</v>
       </c>
       <c r="C271" t="str">
         <v/>
       </c>
       <c r="D271" t="str">
-        <v>31258</v>
+        <v>31965</v>
       </c>
       <c r="E271" t="str">
-        <v>11996</v>
+        <v>9996</v>
       </c>
       <c r="F271" t="str">
         <v>Por peso</v>
@@ -5821,19 +5821,19 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>631479</v>
+        <v>636518</v>
       </c>
       <c r="B272" t="str">
-        <v>ARROLLADO CHILENO PORCIONADO DON RODRIGO</v>
+        <v>LONGANIZA DON CARLOS KG</v>
       </c>
       <c r="C272" t="str">
         <v/>
       </c>
       <c r="D272" t="str">
-        <v>31479</v>
+        <v>36518</v>
       </c>
       <c r="E272" t="str">
-        <v>8990</v>
+        <v>4796</v>
       </c>
       <c r="F272" t="str">
         <v>Por peso</v>
@@ -5841,19 +5841,19 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>631965</v>
+        <v>639134</v>
       </c>
       <c r="B273" t="str">
-        <v>JAMON PIERNA ARTESANAL WINTER KG</v>
+        <v>ARROLLADO LOMO CON AJI DON CARLOS KG</v>
       </c>
       <c r="C273" t="str">
         <v/>
       </c>
       <c r="D273" t="str">
-        <v>31965</v>
+        <v>39134</v>
       </c>
       <c r="E273" t="str">
-        <v>9996</v>
+        <v>6396</v>
       </c>
       <c r="F273" t="str">
         <v>Por peso</v>
@@ -5861,16 +5861,16 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>636518</v>
+        <v>636173</v>
       </c>
       <c r="B274" t="str">
-        <v>LONGANIZA DON CARLOS KG</v>
+        <v>PRIETAS DON CARLOS KG</v>
       </c>
       <c r="C274" t="str">
         <v/>
       </c>
       <c r="D274" t="str">
-        <v>36518</v>
+        <v>36173</v>
       </c>
       <c r="E274" t="str">
         <v>4796</v>
@@ -5881,19 +5881,19 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>639134</v>
+        <v>636913</v>
       </c>
       <c r="B275" t="str">
-        <v>ARROLLADO LOMO CON AJI DON CARLOS KG</v>
+        <v>COSTILLAR AHUMADO DON CARLOS KG</v>
       </c>
       <c r="C275" t="str">
         <v/>
       </c>
       <c r="D275" t="str">
-        <v>39134</v>
+        <v>36913</v>
       </c>
       <c r="E275" t="str">
-        <v>6396</v>
+        <v>7596</v>
       </c>
       <c r="F275" t="str">
         <v>Por peso</v>
@@ -5901,19 +5901,19 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>636173</v>
+        <v>636942</v>
       </c>
       <c r="B276" t="str">
-        <v>PRIETAS DON CARLOS KG</v>
+        <v>PERNIL COCIDO MANO DON CARLOS.KG</v>
       </c>
       <c r="C276" t="str">
         <v/>
       </c>
       <c r="D276" t="str">
-        <v>36173</v>
+        <v>36942</v>
       </c>
       <c r="E276" t="str">
-        <v>4796</v>
+        <v>4996</v>
       </c>
       <c r="F276" t="str">
         <v>Por peso</v>
@@ -5921,19 +5921,19 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>636913</v>
+        <v>636981</v>
       </c>
       <c r="B277" t="str">
-        <v>COSTILLAR AHUMADO DON CARLOS KG</v>
+        <v>QUESO CABEZA DON CARLOS KG</v>
       </c>
       <c r="C277" t="str">
         <v/>
       </c>
       <c r="D277" t="str">
-        <v>36913</v>
+        <v>36981</v>
       </c>
       <c r="E277" t="str">
-        <v>7596</v>
+        <v>4796</v>
       </c>
       <c r="F277" t="str">
         <v>Por peso</v>
@@ -5941,19 +5941,19 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>636942</v>
+        <v>631003</v>
       </c>
       <c r="B278" t="str">
-        <v>PERNIL COCIDO MANO DON CARLOS.KG</v>
+        <v>LONGANIZA PARRILLERA CHILLAN KG</v>
       </c>
       <c r="C278" t="str">
         <v/>
       </c>
       <c r="D278" t="str">
-        <v>36942</v>
+        <v>31003</v>
       </c>
       <c r="E278" t="str">
-        <v>4996</v>
+        <v>10996</v>
       </c>
       <c r="F278" t="str">
         <v>Por peso</v>
@@ -5961,19 +5961,19 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>636981</v>
+        <v>638990</v>
       </c>
       <c r="B279" t="str">
-        <v>QUESO CABEZA DON CARLOS KG</v>
+        <v>ARROLLADO HUASO CHILLAN KG</v>
       </c>
       <c r="C279" t="str">
         <v/>
       </c>
       <c r="D279" t="str">
-        <v>36981</v>
+        <v>38990</v>
       </c>
       <c r="E279" t="str">
-        <v>4796</v>
+        <v>13996</v>
       </c>
       <c r="F279" t="str">
         <v>Por peso</v>
@@ -5981,19 +5981,19 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>631003</v>
+        <v>639000</v>
       </c>
       <c r="B280" t="str">
-        <v>LONGANIZA PARRILLERA CHILLAN KG</v>
+        <v>PERNIL COCIDO SIN HUESO</v>
       </c>
       <c r="C280" t="str">
         <v/>
       </c>
       <c r="D280" t="str">
-        <v>31003</v>
+        <v>39000</v>
       </c>
       <c r="E280" t="str">
-        <v>10996</v>
+        <v>11996</v>
       </c>
       <c r="F280" t="str">
         <v>Por peso</v>
@@ -6001,19 +6001,19 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>638990</v>
+        <v>639010</v>
       </c>
       <c r="B281" t="str">
-        <v>ARROLLADO HUASO CHILLAN KG</v>
+        <v>QUESO DE CABEZA CHILLAN KG</v>
       </c>
       <c r="C281" t="str">
         <v/>
       </c>
       <c r="D281" t="str">
-        <v>38990</v>
+        <v>39010</v>
       </c>
       <c r="E281" t="str">
-        <v>13996</v>
+        <v>10996</v>
       </c>
       <c r="F281" t="str">
         <v>Por peso</v>
@@ -6021,19 +6021,19 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>639000</v>
+        <v>631074</v>
       </c>
       <c r="B282" t="str">
-        <v>PERNIL COCIDO SIN HUESO</v>
+        <v>LONGANICILLA DON RODRIGO VACIO KG</v>
       </c>
       <c r="C282" t="str">
         <v/>
       </c>
       <c r="D282" t="str">
-        <v>39000</v>
+        <v>31074</v>
       </c>
       <c r="E282" t="str">
-        <v>11996</v>
+        <v>6996</v>
       </c>
       <c r="F282" t="str">
         <v>Por peso</v>
@@ -6041,19 +6041,19 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>639010</v>
+        <v>631078</v>
       </c>
       <c r="B283" t="str">
-        <v>QUESO DE CABEZA CHILLAN KG</v>
+        <v>JAMON CENTENARIO COLONIAL LP</v>
       </c>
       <c r="C283" t="str">
         <v/>
       </c>
       <c r="D283" t="str">
-        <v>39010</v>
+        <v>31078</v>
       </c>
       <c r="E283" t="str">
-        <v>10996</v>
+        <v>11996</v>
       </c>
       <c r="F283" t="str">
         <v>Por peso</v>
@@ -6061,19 +6061,19 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>631074</v>
+        <v>631080</v>
       </c>
       <c r="B284" t="str">
-        <v>LONGANICILLA DON RODRIGO VACIO KG</v>
+        <v>QUESO CABEZA CPIMENTON KG DON RODRIGO</v>
       </c>
       <c r="C284" t="str">
         <v/>
       </c>
       <c r="D284" t="str">
-        <v>31074</v>
+        <v>31080</v>
       </c>
       <c r="E284" t="str">
-        <v>6996</v>
+        <v>5996</v>
       </c>
       <c r="F284" t="str">
         <v>Por peso</v>
@@ -6081,19 +6081,19 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>631078</v>
+        <v>631084</v>
       </c>
       <c r="B285" t="str">
-        <v>JAMON CENTENARIO COLONIAL LP</v>
+        <v>JAMON ACARAMELADO DON RODRIGO KG</v>
       </c>
       <c r="C285" t="str">
         <v/>
       </c>
       <c r="D285" t="str">
-        <v>31078</v>
+        <v>31084</v>
       </c>
       <c r="E285" t="str">
-        <v>11996</v>
+        <v>8996</v>
       </c>
       <c r="F285" t="str">
         <v>Por peso</v>
@@ -6101,19 +6101,19 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>631080</v>
+        <v>631087</v>
       </c>
       <c r="B286" t="str">
-        <v>QUESO CABEZA CPIMENTON KG DON RODRIGO</v>
+        <v>ARROLLADO CON CUERO FANDA KG</v>
       </c>
       <c r="C286" t="str">
         <v/>
       </c>
       <c r="D286" t="str">
-        <v>31080</v>
+        <v>31087</v>
       </c>
       <c r="E286" t="str">
-        <v>5996</v>
+        <v>8796</v>
       </c>
       <c r="F286" t="str">
         <v>Por peso</v>
@@ -6121,19 +6121,19 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>631084</v>
+        <v>631088</v>
       </c>
       <c r="B287" t="str">
-        <v>JAMON ACARAMELADO DON RODRIGO KG</v>
+        <v>SALCHICHON CERVECERO RDA KG</v>
       </c>
       <c r="C287" t="str">
         <v/>
       </c>
       <c r="D287" t="str">
-        <v>31084</v>
+        <v>31088</v>
       </c>
       <c r="E287" t="str">
-        <v>8996</v>
+        <v>9596</v>
       </c>
       <c r="F287" t="str">
         <v>Por peso</v>
@@ -6141,19 +6141,19 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>631087</v>
+        <v>631089</v>
       </c>
       <c r="B288" t="str">
-        <v>ARROLLADO CON CUERO FANDA KG</v>
+        <v>JAMONADA DE PAVO RDA 3KG</v>
       </c>
       <c r="C288" t="str">
         <v/>
       </c>
       <c r="D288" t="str">
-        <v>31087</v>
+        <v>31089</v>
       </c>
       <c r="E288" t="str">
-        <v>8796</v>
+        <v>14196</v>
       </c>
       <c r="F288" t="str">
         <v>Por peso</v>
@@ -6161,19 +6161,19 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>631088</v>
+        <v>631091</v>
       </c>
       <c r="B289" t="str">
-        <v>SALCHICHON CERVECERO RDA KG</v>
+        <v>JAMONADA DE POLLO RDA 3KG</v>
       </c>
       <c r="C289" t="str">
         <v/>
       </c>
       <c r="D289" t="str">
-        <v>31088</v>
+        <v>31091</v>
       </c>
       <c r="E289" t="str">
-        <v>9596</v>
+        <v>11996</v>
       </c>
       <c r="F289" t="str">
         <v>Por peso</v>
@@ -6181,19 +6181,19 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>631089</v>
+        <v>631092</v>
       </c>
       <c r="B290" t="str">
-        <v>JAMONADA DE PAVO RDA 3KG</v>
+        <v>JAMON PIERNA SANDWICH RDA KG</v>
       </c>
       <c r="C290" t="str">
         <v/>
       </c>
       <c r="D290" t="str">
-        <v>31089</v>
+        <v>31092</v>
       </c>
       <c r="E290" t="str">
-        <v>14196</v>
+        <v>10996</v>
       </c>
       <c r="F290" t="str">
         <v>Por peso</v>
@@ -6201,19 +6201,19 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>631091</v>
+        <v>631093</v>
       </c>
       <c r="B291" t="str">
-        <v>JAMONADA DE POLLO RDA 3KG</v>
+        <v>TOCINO HUMADO PF KG</v>
       </c>
       <c r="C291" t="str">
         <v/>
       </c>
       <c r="D291" t="str">
-        <v>31091</v>
+        <v>31093</v>
       </c>
       <c r="E291" t="str">
-        <v>11996</v>
+        <v>17996</v>
       </c>
       <c r="F291" t="str">
         <v>Por peso</v>
@@ -6221,19 +6221,19 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>631092</v>
+        <v>631096</v>
       </c>
       <c r="B292" t="str">
-        <v>JAMON PIERNA SANDWICH RDA KG</v>
+        <v>PEPPERONI PF KG</v>
       </c>
       <c r="C292" t="str">
         <v/>
       </c>
       <c r="D292" t="str">
-        <v>31092</v>
+        <v>31096</v>
       </c>
       <c r="E292" t="str">
-        <v>10996</v>
+        <v>14996</v>
       </c>
       <c r="F292" t="str">
         <v>Por peso</v>
@@ -6241,19 +6241,19 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>631093</v>
+        <v>638765</v>
       </c>
       <c r="B293" t="str">
-        <v>TOCINO HUMADO PF KG</v>
+        <v>BUTIFARRA DON RODRIGO</v>
       </c>
       <c r="C293" t="str">
         <v/>
       </c>
       <c r="D293" t="str">
-        <v>31093</v>
+        <v>38765</v>
       </c>
       <c r="E293" t="str">
-        <v>17996</v>
+        <v>4396</v>
       </c>
       <c r="F293" t="str">
         <v>Por peso</v>
@@ -6261,19 +6261,19 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>631096</v>
+        <v>636789</v>
       </c>
       <c r="B294" t="str">
-        <v>PEPPERONI PF KG</v>
+        <v>JAMON FIAMBRE DON RODRIGO</v>
       </c>
       <c r="C294" t="str">
         <v/>
       </c>
       <c r="D294" t="str">
-        <v>31096</v>
+        <v>36789</v>
       </c>
       <c r="E294" t="str">
-        <v>14996</v>
+        <v>4996</v>
       </c>
       <c r="F294" t="str">
         <v>Por peso</v>
@@ -6281,16 +6281,16 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>638765</v>
+        <v>630910</v>
       </c>
       <c r="B295" t="str">
-        <v>BUTIFARRA DON RODRIGO</v>
+        <v>MORTADELA DON RODRIGO</v>
       </c>
       <c r="C295" t="str">
         <v/>
       </c>
       <c r="D295" t="str">
-        <v>38765</v>
+        <v>30910</v>
       </c>
       <c r="E295" t="str">
         <v>4396</v>
@@ -6301,19 +6301,19 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>636789</v>
+        <v>632936</v>
       </c>
       <c r="B296" t="str">
-        <v>JAMON FIAMBRE DON RODRIGO</v>
+        <v>PECHUGA DE POLLO ACARAMELADO SJ KG</v>
       </c>
       <c r="C296" t="str">
         <v/>
       </c>
       <c r="D296" t="str">
-        <v>36789</v>
+        <v>32936</v>
       </c>
       <c r="E296" t="str">
-        <v>4996</v>
+        <v>10996</v>
       </c>
       <c r="F296" t="str">
         <v>Por peso</v>
@@ -6321,19 +6321,19 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>630910</v>
+        <v>636265</v>
       </c>
       <c r="B297" t="str">
-        <v>MORTADELA DON RODRIGO</v>
+        <v>JAMON COCIDO SADIA KG</v>
       </c>
       <c r="C297" t="str">
         <v/>
       </c>
       <c r="D297" t="str">
-        <v>30910</v>
+        <v>36265</v>
       </c>
       <c r="E297" t="str">
-        <v>4396</v>
+        <v>7996</v>
       </c>
       <c r="F297" t="str">
         <v>Por peso</v>
@@ -6341,19 +6341,19 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>632936</v>
+        <v>636492</v>
       </c>
       <c r="B298" t="str">
-        <v>PECHUGA DE POLLO ACARAMELADO SJ KG</v>
+        <v>JAMON COLONIAL WINTER KG</v>
       </c>
       <c r="C298" t="str">
         <v/>
       </c>
       <c r="D298" t="str">
-        <v>32936</v>
+        <v>36492</v>
       </c>
       <c r="E298" t="str">
-        <v>10996</v>
+        <v>11996</v>
       </c>
       <c r="F298" t="str">
         <v>Por peso</v>
@@ -6361,19 +6361,19 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>636265</v>
+        <v>634525</v>
       </c>
       <c r="B299" t="str">
-        <v>JAMON COCIDO SADIA KG</v>
+        <v>JAMON PLANCHADO SUPER KG</v>
       </c>
       <c r="C299" t="str">
         <v/>
       </c>
       <c r="D299" t="str">
-        <v>36265</v>
+        <v>34525</v>
       </c>
       <c r="E299" t="str">
-        <v>7996</v>
+        <v>8396</v>
       </c>
       <c r="F299" t="str">
         <v>Por peso</v>
@@ -6381,19 +6381,19 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>636492</v>
+        <v>632323</v>
       </c>
       <c r="B300" t="str">
-        <v>JAMON COLONIAL WINTER KG</v>
+        <v>ARROLLADO DE LOMO CON AJI DON RODRIGO</v>
       </c>
       <c r="C300" t="str">
         <v/>
       </c>
       <c r="D300" t="str">
-        <v>36492</v>
+        <v>32323</v>
       </c>
       <c r="E300" t="str">
-        <v>11996</v>
+        <v>8996</v>
       </c>
       <c r="F300" t="str">
         <v>Por peso</v>
@@ -6401,19 +6401,19 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>634525</v>
+        <v>634056</v>
       </c>
       <c r="B301" t="str">
-        <v>JAMON PLANCHADO SUPER KG</v>
+        <v>QUESO DE CABEZA DLEON KG</v>
       </c>
       <c r="C301" t="str">
         <v/>
       </c>
       <c r="D301" t="str">
-        <v>34525</v>
+        <v>34056</v>
       </c>
       <c r="E301" t="str">
-        <v>8396</v>
+        <v>10796</v>
       </c>
       <c r="F301" t="str">
         <v>Por peso</v>
@@ -6421,19 +6421,19 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>632323</v>
+        <v>634055</v>
       </c>
       <c r="B302" t="str">
-        <v>ARROLLADO DE LOMO CON AJI DON RODRIGO</v>
+        <v>SALCHICHON CERVEZA AHUM. DLEON KG</v>
       </c>
       <c r="C302" t="str">
         <v/>
       </c>
       <c r="D302" t="str">
-        <v>32323</v>
+        <v>34055</v>
       </c>
       <c r="E302" t="str">
-        <v>8996</v>
+        <v>12996</v>
       </c>
       <c r="F302" t="str">
         <v>Por peso</v>
@@ -6441,19 +6441,19 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>634056</v>
+        <v>634054</v>
       </c>
       <c r="B303" t="str">
-        <v>QUESO DE CABEZA DLEON KG</v>
+        <v>JAMON COLONIAL DLEON KG</v>
       </c>
       <c r="C303" t="str">
         <v/>
       </c>
       <c r="D303" t="str">
-        <v>34056</v>
+        <v>34054</v>
       </c>
       <c r="E303" t="str">
-        <v>10796</v>
+        <v>15960</v>
       </c>
       <c r="F303" t="str">
         <v>Por peso</v>
@@ -6461,19 +6461,19 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>634055</v>
+        <v>634052</v>
       </c>
       <c r="B304" t="str">
-        <v>SALCHICHON CERVEZA AHUM. DLEON KG</v>
+        <v>JAMON PIERNA PLANCHADO DLEON KG</v>
       </c>
       <c r="C304" t="str">
         <v/>
       </c>
       <c r="D304" t="str">
-        <v>34055</v>
+        <v>34052</v>
       </c>
       <c r="E304" t="str">
-        <v>12996</v>
+        <v>16990</v>
       </c>
       <c r="F304" t="str">
         <v>Por peso</v>
@@ -6481,19 +6481,19 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>634054</v>
+        <v>634025</v>
       </c>
       <c r="B305" t="str">
-        <v>JAMON COLONIAL DLEON KG</v>
+        <v>AROLLADO DE HUASO CON AJI DLEON KG</v>
       </c>
       <c r="C305" t="str">
         <v/>
       </c>
       <c r="D305" t="str">
-        <v>34054</v>
+        <v>34025</v>
       </c>
       <c r="E305" t="str">
-        <v>15960</v>
+        <v>13996</v>
       </c>
       <c r="F305" t="str">
         <v>Por peso</v>
@@ -6501,19 +6501,19 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>634052</v>
+        <v>634016</v>
       </c>
       <c r="B306" t="str">
-        <v>JAMON PIERNA PLANCHADO DLEON KG</v>
+        <v>LONGANIZA AHUMADA ESPECIAL DLEON KG</v>
       </c>
       <c r="C306" t="str">
         <v/>
       </c>
       <c r="D306" t="str">
-        <v>34052</v>
+        <v>34016</v>
       </c>
       <c r="E306" t="str">
-        <v>16990</v>
+        <v>10990</v>
       </c>
       <c r="F306" t="str">
         <v>Por peso</v>
@@ -6521,19 +6521,19 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>634025</v>
+        <v>634015</v>
       </c>
       <c r="B307" t="str">
-        <v>AROLLADO DE HUASO CON AJI DLEON KG</v>
+        <v>LONGANIZA RECETADE FAMILIADLEON KG</v>
       </c>
       <c r="C307" t="str">
         <v/>
       </c>
       <c r="D307" t="str">
-        <v>34025</v>
+        <v>34015</v>
       </c>
       <c r="E307" t="str">
-        <v>13996</v>
+        <v>11990</v>
       </c>
       <c r="F307" t="str">
         <v>Por peso</v>
@@ -6541,19 +6541,19 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>634016</v>
+        <v>631362</v>
       </c>
       <c r="B308" t="str">
-        <v>LONGANIZA AHUMADA ESPECIAL DLEON KG</v>
+        <v>MORTAD. JAMONADA KG LC</v>
       </c>
       <c r="C308" t="str">
         <v/>
       </c>
       <c r="D308" t="str">
-        <v>34016</v>
+        <v>31362</v>
       </c>
       <c r="E308" t="str">
-        <v>10990</v>
+        <v>8396</v>
       </c>
       <c r="F308" t="str">
         <v>Por peso</v>
@@ -6561,19 +6561,19 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>634015</v>
+        <v>631390</v>
       </c>
       <c r="B309" t="str">
-        <v>LONGANIZA RECETADE FAMILIADLEON KG</v>
+        <v>JAMON SANDWICH PREFERIDA KG</v>
       </c>
       <c r="C309" t="str">
         <v/>
       </c>
       <c r="D309" t="str">
-        <v>34015</v>
+        <v>31390</v>
       </c>
       <c r="E309" t="str">
-        <v>11990</v>
+        <v>9996</v>
       </c>
       <c r="F309" t="str">
         <v>Por peso</v>
@@ -6581,19 +6581,19 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>631362</v>
+        <v>631360</v>
       </c>
       <c r="B310" t="str">
-        <v>MORTAD. JAMONADA KG LC</v>
+        <v>AROLLADO LOMO CON AJI LCKG</v>
       </c>
       <c r="C310" t="str">
         <v/>
       </c>
       <c r="D310" t="str">
-        <v>31362</v>
+        <v>31360</v>
       </c>
       <c r="E310" t="str">
-        <v>8396</v>
+        <v>8996</v>
       </c>
       <c r="F310" t="str">
         <v>Por peso</v>
@@ -6601,19 +6601,19 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>631390</v>
+        <v>634715</v>
       </c>
       <c r="B311" t="str">
-        <v>JAMON SANDWICH PREFERIDA KG</v>
+        <v>JAMON PLANCHADO G1 E. ALEMAN EMPORIO ALEMAN</v>
       </c>
       <c r="C311" t="str">
         <v/>
       </c>
       <c r="D311" t="str">
-        <v>31390</v>
+        <v>34715</v>
       </c>
       <c r="E311" t="str">
-        <v>9996</v>
+        <v>16996</v>
       </c>
       <c r="F311" t="str">
         <v>Por peso</v>
@@ -6621,19 +6621,19 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>631360</v>
+        <v>631312</v>
       </c>
       <c r="B312" t="str">
-        <v>AROLLADO LOMO CON AJI LCKG</v>
+        <v>JAMON PIERNA G1 E. ALEMAN EMPORIO ALEMAN</v>
       </c>
       <c r="C312" t="str">
         <v/>
       </c>
       <c r="D312" t="str">
-        <v>31360</v>
+        <v>31312</v>
       </c>
       <c r="E312" t="str">
-        <v>8996</v>
+        <v>16996</v>
       </c>
       <c r="F312" t="str">
         <v>Por peso</v>
@@ -6641,19 +6641,19 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>634715</v>
+        <v>639562</v>
       </c>
       <c r="B313" t="str">
-        <v>JAMON PLANCHADO G1 E. ALEMAN EMPORIO ALEMAN</v>
+        <v>ARROLLADO CAMP. C AJI KG E.ALEMAN</v>
       </c>
       <c r="C313" t="str">
         <v/>
       </c>
       <c r="D313" t="str">
-        <v>34715</v>
+        <v>39562</v>
       </c>
       <c r="E313" t="str">
-        <v>16996</v>
+        <v>12996</v>
       </c>
       <c r="F313" t="str">
         <v>Por peso</v>
@@ -6661,19 +6661,19 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>631312</v>
+        <v>639563</v>
       </c>
       <c r="B314" t="str">
-        <v>JAMON PIERNA G1 E. ALEMAN EMPORIO ALEMAN</v>
+        <v>ARROLLADO ART. S AJI KG E.ALEMAN</v>
       </c>
       <c r="C314" t="str">
         <v/>
       </c>
       <c r="D314" t="str">
-        <v>31312</v>
+        <v>39563</v>
       </c>
       <c r="E314" t="str">
-        <v>16996</v>
+        <v>12996</v>
       </c>
       <c r="F314" t="str">
         <v>Por peso</v>
@@ -6681,19 +6681,19 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>639562</v>
+        <v>630200</v>
       </c>
       <c r="B315" t="str">
-        <v>ARROLLADO CAMP. C AJI KG E.ALEMAN</v>
+        <v>LONGANIZA AHUMADA KG E.ALEMAN</v>
       </c>
       <c r="C315" t="str">
         <v/>
       </c>
       <c r="D315" t="str">
-        <v>39562</v>
+        <v>30200</v>
       </c>
       <c r="E315" t="str">
-        <v>12996</v>
+        <v>11996</v>
       </c>
       <c r="F315" t="str">
         <v>Por peso</v>
@@ -6701,19 +6701,19 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>639563</v>
+        <v>634225</v>
       </c>
       <c r="B316" t="str">
-        <v>ARROLLADO ART. S AJI KG E.ALEMAN</v>
+        <v>ACEITUNA AZAPA NEGRA VALLE CHILE KG</v>
       </c>
       <c r="C316" t="str">
         <v/>
       </c>
       <c r="D316" t="str">
-        <v>39563</v>
+        <v>34225</v>
       </c>
       <c r="E316" t="str">
-        <v>12996</v>
+        <v>8596</v>
       </c>
       <c r="F316" t="str">
         <v>Por peso</v>
@@ -6721,19 +6721,19 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>630200</v>
+        <v>634226</v>
       </c>
       <c r="B317" t="str">
-        <v>LONGANIZA AHUMADA KG E.ALEMAN</v>
+        <v>ACEITUNA SEVILLANA VERDE VALLE CHILE KG</v>
       </c>
       <c r="C317" t="str">
         <v/>
       </c>
       <c r="D317" t="str">
-        <v>30200</v>
+        <v>34226</v>
       </c>
       <c r="E317" t="str">
-        <v>11996</v>
+        <v>8596</v>
       </c>
       <c r="F317" t="str">
         <v>Por peso</v>
@@ -6741,19 +6741,19 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>634225</v>
+        <v>634227</v>
       </c>
       <c r="B318" t="str">
-        <v>ACEITUNA AZAPA NEGRA VALLE CHILE KG</v>
+        <v>ACEITUNA RELLENA MORRON VALLE CHILE KG</v>
       </c>
       <c r="C318" t="str">
         <v/>
       </c>
       <c r="D318" t="str">
-        <v>34225</v>
+        <v>34227</v>
       </c>
       <c r="E318" t="str">
-        <v>8596</v>
+        <v>8996</v>
       </c>
       <c r="F318" t="str">
         <v>Por peso</v>
@@ -6761,19 +6761,19 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>634226</v>
+        <v>634228</v>
       </c>
       <c r="B319" t="str">
-        <v>ACEITUNA SEVILLANA VERDE VALLE CHILE KG</v>
+        <v>SALSA AMERICANA VALLE CHILE KG</v>
       </c>
       <c r="C319" t="str">
         <v/>
       </c>
       <c r="D319" t="str">
-        <v>34226</v>
+        <v>34228</v>
       </c>
       <c r="E319" t="str">
-        <v>8596</v>
+        <v>3196</v>
       </c>
       <c r="F319" t="str">
         <v>Por peso</v>
@@ -6781,19 +6781,19 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>634227</v>
+        <v>634229</v>
       </c>
       <c r="B320" t="str">
-        <v>ACEITUNA RELLENA MORRON VALLE CHILE KG</v>
+        <v>CHUCRUT VALLE CHILE KG</v>
       </c>
       <c r="C320" t="str">
         <v/>
       </c>
       <c r="D320" t="str">
-        <v>34227</v>
+        <v>34229</v>
       </c>
       <c r="E320" t="str">
-        <v>8996</v>
+        <v>3596</v>
       </c>
       <c r="F320" t="str">
         <v>Por peso</v>
@@ -6801,19 +6801,19 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>634228</v>
+        <v>634230</v>
       </c>
       <c r="B321" t="str">
-        <v>SALSA AMERICANA VALLE CHILE KG</v>
+        <v>AJI ORO ESCABECHEVALLE CHILE KG</v>
       </c>
       <c r="C321" t="str">
         <v/>
       </c>
       <c r="D321" t="str">
-        <v>34228</v>
+        <v>34230</v>
       </c>
       <c r="E321" t="str">
-        <v>3196</v>
+        <v>4396</v>
       </c>
       <c r="F321" t="str">
         <v>Por peso</v>
@@ -6821,19 +6821,19 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>634229</v>
+        <v>634231</v>
       </c>
       <c r="B322" t="str">
-        <v>CHUCRUT VALLE CHILE KG</v>
+        <v>CEBOLLA PERLA VALLE CHILE KG</v>
       </c>
       <c r="C322" t="str">
         <v/>
       </c>
       <c r="D322" t="str">
-        <v>34229</v>
+        <v>34231</v>
       </c>
       <c r="E322" t="str">
-        <v>3596</v>
+        <v>5396</v>
       </c>
       <c r="F322" t="str">
         <v>Por peso</v>
@@ -6841,16 +6841,16 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>634230</v>
+        <v>634232</v>
       </c>
       <c r="B323" t="str">
-        <v>AJI ORO ESCABECHEVALLE CHILE KG</v>
+        <v>PICKLE ESPECIAL FINO VALLE CHILE KG</v>
       </c>
       <c r="C323" t="str">
         <v/>
       </c>
       <c r="D323" t="str">
-        <v>34230</v>
+        <v>34232</v>
       </c>
       <c r="E323" t="str">
         <v>4396</v>
@@ -6861,19 +6861,19 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>634231</v>
+        <v>634233</v>
       </c>
       <c r="B324" t="str">
-        <v>CEBOLLA PERLA VALLE CHILE KG</v>
+        <v>PEPINILLO FINO VALLE CHILE KG</v>
       </c>
       <c r="C324" t="str">
         <v/>
       </c>
       <c r="D324" t="str">
-        <v>34231</v>
+        <v>34233</v>
       </c>
       <c r="E324" t="str">
-        <v>5396</v>
+        <v>6196</v>
       </c>
       <c r="F324" t="str">
         <v>Por peso</v>
@@ -6881,19 +6881,19 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>634232</v>
+        <v>634234</v>
       </c>
       <c r="B325" t="str">
-        <v>PICKLE ESPECIAL FINO VALLE CHILE KG</v>
+        <v>PEPINILLO DILL VALLE CHILE KG</v>
       </c>
       <c r="C325" t="str">
         <v/>
       </c>
       <c r="D325" t="str">
-        <v>34232</v>
+        <v>34234</v>
       </c>
       <c r="E325" t="str">
-        <v>4396</v>
+        <v>6796</v>
       </c>
       <c r="F325" t="str">
         <v>Por peso</v>
@@ -6901,19 +6901,19 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>634233</v>
+        <v>631120</v>
       </c>
       <c r="B326" t="str">
-        <v>PEPINILLO FINO VALLE CHILE KG</v>
+        <v>TOCINO LP KG</v>
       </c>
       <c r="C326" t="str">
         <v/>
       </c>
       <c r="D326" t="str">
-        <v>34233</v>
+        <v>31120</v>
       </c>
       <c r="E326" t="str">
-        <v>6196</v>
+        <v>14996</v>
       </c>
       <c r="F326" t="str">
         <v>Por peso</v>
@@ -6921,19 +6921,19 @@
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>634234</v>
+        <v>632295</v>
       </c>
       <c r="B327" t="str">
-        <v>PEPINILLO DILL VALLE CHILE KG</v>
+        <v>MORTAD. LISA WINTER KG</v>
       </c>
       <c r="C327" t="str">
         <v/>
       </c>
       <c r="D327" t="str">
-        <v>34234</v>
+        <v>32295</v>
       </c>
       <c r="E327" t="str">
-        <v>6796</v>
+        <v>4396</v>
       </c>
       <c r="F327" t="str">
         <v>Por peso</v>
@@ -6941,19 +6941,19 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>631120</v>
+        <v>632870</v>
       </c>
       <c r="B328" t="str">
-        <v>TOCINO LP KG</v>
+        <v>PECHUGA POLLO COCIDA LP KG</v>
       </c>
       <c r="C328" t="str">
         <v/>
       </c>
       <c r="D328" t="str">
-        <v>31120</v>
+        <v>32870</v>
       </c>
       <c r="E328" t="str">
-        <v>14996</v>
+        <v>13996</v>
       </c>
       <c r="F328" t="str">
         <v>Por peso</v>
@@ -6961,19 +6961,19 @@
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>632295</v>
+        <v>632871</v>
       </c>
       <c r="B329" t="str">
-        <v>MORTAD. LISA WINTER KG</v>
+        <v>PECHUGA POLLO ACARAMELADO LP KG</v>
       </c>
       <c r="C329" t="str">
         <v/>
       </c>
       <c r="D329" t="str">
-        <v>32295</v>
+        <v>32871</v>
       </c>
       <c r="E329" t="str">
-        <v>4396</v>
+        <v>13996</v>
       </c>
       <c r="F329" t="str">
         <v>Por peso</v>
@@ -6981,19 +6981,19 @@
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>632870</v>
+        <v>632872</v>
       </c>
       <c r="B330" t="str">
-        <v>PECHUGA POLLO COCIDA LP KG</v>
+        <v>QUESO CABEZA LP KG</v>
       </c>
       <c r="C330" t="str">
         <v/>
       </c>
       <c r="D330" t="str">
-        <v>32870</v>
+        <v>32872</v>
       </c>
       <c r="E330" t="str">
-        <v>13996</v>
+        <v>9996</v>
       </c>
       <c r="F330" t="str">
         <v>Por peso</v>
@@ -7001,19 +7001,19 @@
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>632871</v>
+        <v>633080</v>
       </c>
       <c r="B331" t="str">
-        <v>PECHUGA POLLO ACARAMELADO LP KG</v>
+        <v>QUESO ROQUEFORT LOS FUNDOS</v>
       </c>
       <c r="C331" t="str">
         <v/>
       </c>
       <c r="D331" t="str">
-        <v>32871</v>
+        <v>33080</v>
       </c>
       <c r="E331" t="str">
-        <v>13996</v>
+        <v>6679</v>
       </c>
       <c r="F331" t="str">
         <v>Por peso</v>
@@ -7021,19 +7021,19 @@
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>632872</v>
+        <v>633030</v>
       </c>
       <c r="B332" t="str">
-        <v>QUESO CABEZA LP KG</v>
+        <v>QUESO CABRA KILO</v>
       </c>
       <c r="C332" t="str">
         <v/>
       </c>
       <c r="D332" t="str">
-        <v>32872</v>
+        <v>33030</v>
       </c>
       <c r="E332" t="str">
-        <v>9996</v>
+        <v>3196</v>
       </c>
       <c r="F332" t="str">
         <v>Por peso</v>
@@ -7041,19 +7041,19 @@
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>633080</v>
+        <v>633440</v>
       </c>
       <c r="B333" t="str">
-        <v>QUESO ROQUEFORT LOS FUNDOS</v>
+        <v>QUESO EDAM QUILLAYES 330 GRS</v>
       </c>
       <c r="C333" t="str">
         <v/>
       </c>
       <c r="D333" t="str">
-        <v>33080</v>
+        <v>33440</v>
       </c>
       <c r="E333" t="str">
-        <v>6679</v>
+        <v>8990</v>
       </c>
       <c r="F333" t="str">
         <v>Por peso</v>
@@ -7061,19 +7061,19 @@
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>633030</v>
+        <v>633480</v>
       </c>
       <c r="B334" t="str">
-        <v>QUESO CABRA KILO</v>
+        <v>QUESO AJI QUILLAYES 330 GRS</v>
       </c>
       <c r="C334" t="str">
         <v/>
       </c>
       <c r="D334" t="str">
-        <v>33030</v>
+        <v>33480</v>
       </c>
       <c r="E334" t="str">
-        <v>3196</v>
+        <v>7590</v>
       </c>
       <c r="F334" t="str">
         <v>Por peso</v>
@@ -7081,19 +7081,19 @@
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>633440</v>
+        <v>633446</v>
       </c>
       <c r="B335" t="str">
-        <v>QUESO EDAM QUILLAYES 330 GRS</v>
+        <v>QUESO PIMIENTA QUILLAYES 330 GRS</v>
       </c>
       <c r="C335" t="str">
         <v/>
       </c>
       <c r="D335" t="str">
-        <v>33440</v>
+        <v>33446</v>
       </c>
       <c r="E335" t="str">
-        <v>8990</v>
+        <v>7890</v>
       </c>
       <c r="F335" t="str">
         <v>Por peso</v>
@@ -7101,19 +7101,19 @@
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>633480</v>
+        <v>633035</v>
       </c>
       <c r="B336" t="str">
-        <v>QUESO AJI QUILLAYES 330 GRS</v>
+        <v>QUESO FRESCO CHACRA LOS FUNDOS</v>
       </c>
       <c r="C336" t="str">
         <v/>
       </c>
       <c r="D336" t="str">
-        <v>33480</v>
+        <v>33035</v>
       </c>
       <c r="E336" t="str">
-        <v>7590</v>
+        <v>1990</v>
       </c>
       <c r="F336" t="str">
         <v>Por peso</v>
@@ -7121,19 +7121,19 @@
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>633446</v>
+        <v>633217</v>
       </c>
       <c r="B337" t="str">
-        <v>QUESO PIMIENTA QUILLAYES 330 GRS</v>
+        <v>QUESO EL ROBLE CHANCO LAM. KG. 8KLCAJA</v>
       </c>
       <c r="C337" t="str">
         <v/>
       </c>
       <c r="D337" t="str">
-        <v>33446</v>
+        <v>33217</v>
       </c>
       <c r="E337" t="str">
-        <v>7890</v>
+        <v>14760</v>
       </c>
       <c r="F337" t="str">
         <v>Por peso</v>
@@ -7141,19 +7141,19 @@
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>633035</v>
+        <v>633220</v>
       </c>
       <c r="B338" t="str">
-        <v>QUESO FRESCO CHACRA LOS FUNDOS</v>
+        <v>QUESO LOS TILOS CABRA KG</v>
       </c>
       <c r="C338" t="str">
         <v/>
       </c>
       <c r="D338" t="str">
-        <v>33035</v>
+        <v>33220</v>
       </c>
       <c r="E338" t="str">
-        <v>1990</v>
+        <v>26990</v>
       </c>
       <c r="F338" t="str">
         <v>Por peso</v>
@@ -7161,19 +7161,19 @@
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>633217</v>
+        <v>633336</v>
       </c>
       <c r="B339" t="str">
-        <v>QUESO EL ROBLE CHANCO LAM. KG. 8KLCAJA</v>
+        <v>QUESO MANTECOSO SAN IGNACIO KG</v>
       </c>
       <c r="C339" t="str">
         <v/>
       </c>
       <c r="D339" t="str">
-        <v>33217</v>
+        <v>33336</v>
       </c>
       <c r="E339" t="str">
-        <v>14760</v>
+        <v>13160</v>
       </c>
       <c r="F339" t="str">
         <v>Por peso</v>
@@ -7181,19 +7181,19 @@
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>633220</v>
+        <v>632620</v>
       </c>
       <c r="B340" t="str">
-        <v>QUESO LOS TILOS CABRA KG</v>
+        <v>QUESO LOS TILOS MANTECOSOKG</v>
       </c>
       <c r="C340" t="str">
         <v/>
       </c>
       <c r="D340" t="str">
-        <v>33220</v>
+        <v>32620</v>
       </c>
       <c r="E340" t="str">
-        <v>26990</v>
+        <v>13160</v>
       </c>
       <c r="F340" t="str">
         <v>Por peso</v>
@@ -7201,19 +7201,19 @@
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>633336</v>
+        <v>633002</v>
       </c>
       <c r="B341" t="str">
-        <v>QUESO MANTECOSO SAN IGNACIO KG</v>
+        <v>QUESO LAMIN.CHANCO LOS ALERCES</v>
       </c>
       <c r="C341" t="str">
         <v/>
       </c>
       <c r="D341" t="str">
-        <v>33336</v>
+        <v>33002</v>
       </c>
       <c r="E341" t="str">
-        <v>13160</v>
+        <v>4799</v>
       </c>
       <c r="F341" t="str">
         <v>Por peso</v>
@@ -7221,19 +7221,19 @@
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>632620</v>
+        <v>633421</v>
       </c>
       <c r="B342" t="str">
-        <v>QUESO LOS TILOS MANTECOSOKG</v>
+        <v>QUESO GAUDA TROZO FRUTILLAR</v>
       </c>
       <c r="C342" t="str">
         <v/>
       </c>
       <c r="D342" t="str">
-        <v>32620</v>
+        <v>33421</v>
       </c>
       <c r="E342" t="str">
-        <v>13160</v>
+        <v>3076</v>
       </c>
       <c r="F342" t="str">
         <v>Por peso</v>
@@ -7241,19 +7241,19 @@
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>633002</v>
+        <v>633419</v>
       </c>
       <c r="B343" t="str">
-        <v>QUESO LAMIN.CHANCO LOS ALERCES</v>
+        <v>QUESO GAUDA TROZO.8K.MULPULMO</v>
       </c>
       <c r="C343" t="str">
         <v/>
       </c>
       <c r="D343" t="str">
-        <v>33002</v>
+        <v>33419</v>
       </c>
       <c r="E343" t="str">
-        <v>4799</v>
+        <v>3996</v>
       </c>
       <c r="F343" t="str">
         <v>Por peso</v>
@@ -7261,19 +7261,19 @@
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>633421</v>
+        <v>633121</v>
       </c>
       <c r="B344" t="str">
-        <v>QUESO GAUDA TROZO FRUTILLAR</v>
+        <v>QUESO GAUDA LOS FUNDOS</v>
       </c>
       <c r="C344" t="str">
         <v/>
       </c>
       <c r="D344" t="str">
-        <v>33421</v>
+        <v>33121</v>
       </c>
       <c r="E344" t="str">
-        <v>3076</v>
+        <v>2469</v>
       </c>
       <c r="F344" t="str">
         <v>Por peso</v>
@@ -7281,19 +7281,19 @@
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>633419</v>
+        <v>633125</v>
       </c>
       <c r="B345" t="str">
-        <v>QUESO GAUDA TROZO.8K.MULPULMO</v>
+        <v>QUESO GAUDA DOS CASTAnOS</v>
       </c>
       <c r="C345" t="str">
         <v/>
       </c>
       <c r="D345" t="str">
-        <v>33419</v>
+        <v>33125</v>
       </c>
       <c r="E345" t="str">
-        <v>3996</v>
+        <v>2620</v>
       </c>
       <c r="F345" t="str">
         <v>Por peso</v>
@@ -7301,19 +7301,19 @@
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>633121</v>
+        <v>633415</v>
       </c>
       <c r="B346" t="str">
-        <v>QUESO GAUDA LOS FUNDOS</v>
+        <v>QUESO GAUDA BARRA 2 KGS PF.UU</v>
       </c>
       <c r="C346" t="str">
         <v/>
       </c>
       <c r="D346" t="str">
-        <v>33121</v>
+        <v>33415</v>
       </c>
       <c r="E346" t="str">
-        <v>2469</v>
+        <v>2436</v>
       </c>
       <c r="F346" t="str">
         <v>Por peso</v>
@@ -7321,19 +7321,19 @@
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>633125</v>
+        <v>633397</v>
       </c>
       <c r="B347" t="str">
-        <v>QUESO GAUDA DOS CASTAnOS</v>
+        <v>QUESO CHANCO TUNCA TROZO</v>
       </c>
       <c r="C347" t="str">
         <v/>
       </c>
       <c r="D347" t="str">
-        <v>33125</v>
+        <v>33397</v>
       </c>
       <c r="E347" t="str">
-        <v>2620</v>
+        <v>3596</v>
       </c>
       <c r="F347" t="str">
         <v>Por peso</v>
@@ -7341,19 +7341,19 @@
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>633415</v>
+        <v>633126</v>
       </c>
       <c r="B348" t="str">
-        <v>QUESO GAUDA BARRA 2 KGS PF.UU</v>
+        <v>QUESO CHANCO DOS CASTAnOS</v>
       </c>
       <c r="C348" t="str">
         <v/>
       </c>
       <c r="D348" t="str">
-        <v>33415</v>
+        <v>33126</v>
       </c>
       <c r="E348" t="str">
-        <v>2436</v>
+        <v>3097</v>
       </c>
       <c r="F348" t="str">
         <v>Por peso</v>
@@ -7361,19 +7361,19 @@
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>633397</v>
+        <v>633420</v>
       </c>
       <c r="B349" t="str">
-        <v>QUESO CHANCO TUNCA TROZO</v>
+        <v>QUESO CHANCO EL SALVADOR LAMIN</v>
       </c>
       <c r="C349" t="str">
         <v/>
       </c>
       <c r="D349" t="str">
-        <v>33397</v>
+        <v>33420</v>
       </c>
       <c r="E349" t="str">
-        <v>3596</v>
+        <v>4956</v>
       </c>
       <c r="F349" t="str">
         <v>Por peso</v>
@@ -7381,19 +7381,19 @@
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>633126</v>
+        <v>633187</v>
       </c>
       <c r="B350" t="str">
-        <v>QUESO CHANCO DOS CASTAnOS</v>
+        <v>QUESO ROCKEFORT TR. VACIO OCTAY</v>
       </c>
       <c r="C350" t="str">
         <v/>
       </c>
       <c r="D350" t="str">
-        <v>33126</v>
+        <v>33187</v>
       </c>
       <c r="E350" t="str">
-        <v>3097</v>
+        <v>10370</v>
       </c>
       <c r="F350" t="str">
         <v>Por peso</v>
@@ -7401,19 +7401,19 @@
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>633420</v>
+        <v>633180</v>
       </c>
       <c r="B351" t="str">
-        <v>QUESO CHANCO EL SALVADOR LAMIN</v>
+        <v>QUESO ALPINO KL OCTAY</v>
       </c>
       <c r="C351" t="str">
         <v/>
       </c>
       <c r="D351" t="str">
-        <v>33420</v>
+        <v>33180</v>
       </c>
       <c r="E351" t="str">
-        <v>4956</v>
+        <v>7990</v>
       </c>
       <c r="F351" t="str">
         <v>Por peso</v>
@@ -7421,19 +7421,19 @@
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>633187</v>
+        <v>633179</v>
       </c>
       <c r="B352" t="str">
-        <v>QUESO ROCKEFORT TR. VACIO OCTAY</v>
+        <v>QUESO EDAM KL OCTAY</v>
       </c>
       <c r="C352" t="str">
         <v/>
       </c>
       <c r="D352" t="str">
-        <v>33187</v>
+        <v>33179</v>
       </c>
       <c r="E352" t="str">
-        <v>10370</v>
+        <v>7990</v>
       </c>
       <c r="F352" t="str">
         <v>Por peso</v>
@@ -7441,16 +7441,16 @@
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>633180</v>
+        <v>633118</v>
       </c>
       <c r="B353" t="str">
-        <v>QUESO ALPINO KL OCTAY</v>
+        <v>QUESO TILSITER KL OCTAY</v>
       </c>
       <c r="C353" t="str">
         <v/>
       </c>
       <c r="D353" t="str">
-        <v>33180</v>
+        <v>33118</v>
       </c>
       <c r="E353" t="str">
         <v>7990</v>
@@ -7461,19 +7461,19 @@
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>633179</v>
+        <v>633011</v>
       </c>
       <c r="B354" t="str">
-        <v>QUESO EDAM KL OCTAY</v>
+        <v>QUESO MANT. RIO CRUCES VALDIVIA PIEZAKG</v>
       </c>
       <c r="C354" t="str">
         <v/>
       </c>
       <c r="D354" t="str">
-        <v>33179</v>
+        <v>33011</v>
       </c>
       <c r="E354" t="str">
-        <v>7990</v>
+        <v>13160</v>
       </c>
       <c r="F354" t="str">
         <v>Por peso</v>
@@ -7481,19 +7481,19 @@
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>633118</v>
+        <v>633507</v>
       </c>
       <c r="B355" t="str">
-        <v>QUESO TILSITER KL OCTAY</v>
+        <v>QUESO CHANCO TUNCA LAMINADO</v>
       </c>
       <c r="C355" t="str">
         <v/>
       </c>
       <c r="D355" t="str">
-        <v>33118</v>
+        <v>33507</v>
       </c>
       <c r="E355" t="str">
-        <v>7990</v>
+        <v>5196</v>
       </c>
       <c r="F355" t="str">
         <v>Por peso</v>
@@ -7501,19 +7501,19 @@
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>633011</v>
+        <v>633225</v>
       </c>
       <c r="B356" t="str">
-        <v>QUESO MANT. RIO CRUCES VALDIVIA PIEZAKG</v>
+        <v>QUESO CON OREGANO QUILLAYES 330 GRS</v>
       </c>
       <c r="C356" t="str">
         <v/>
       </c>
       <c r="D356" t="str">
-        <v>33011</v>
+        <v>33225</v>
       </c>
       <c r="E356" t="str">
-        <v>13160</v>
+        <v>8990</v>
       </c>
       <c r="F356" t="str">
         <v>Por peso</v>
@@ -7521,19 +7521,19 @@
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>633507</v>
+        <v>636310</v>
       </c>
       <c r="B357" t="str">
-        <v>QUESO CHANCO TUNCA LAMINADO</v>
+        <v>QUESO CHANCO BARRA 4KG</v>
       </c>
       <c r="C357" t="str">
         <v/>
       </c>
       <c r="D357" t="str">
-        <v>33507</v>
+        <v>36310</v>
       </c>
       <c r="E357" t="str">
-        <v>5196</v>
+        <v>11960</v>
       </c>
       <c r="F357" t="str">
         <v>Por peso</v>
@@ -7541,19 +7541,19 @@
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>633225</v>
+        <v>631682</v>
       </c>
       <c r="B358" t="str">
-        <v>QUESO CON OREGANO QUILLAYES 330 GRS</v>
+        <v>PICADILLO GAUDA+SALAME PF</v>
       </c>
       <c r="C358" t="str">
         <v/>
       </c>
       <c r="D358" t="str">
-        <v>33225</v>
+        <v>31682</v>
       </c>
       <c r="E358" t="str">
-        <v>8990</v>
+        <v>1990</v>
       </c>
       <c r="F358" t="str">
         <v>Por peso</v>
@@ -7561,19 +7561,19 @@
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>636310</v>
+        <v>633345</v>
       </c>
       <c r="B359" t="str">
-        <v>QUESO CHANCO BARRA 4KG</v>
+        <v>QUESO MANT. SAN PEDRO KG</v>
       </c>
       <c r="C359" t="str">
         <v/>
       </c>
       <c r="D359" t="str">
-        <v>36310</v>
+        <v>33345</v>
       </c>
       <c r="E359" t="str">
-        <v>11960</v>
+        <v>13160</v>
       </c>
       <c r="F359" t="str">
         <v>Por peso</v>
@@ -7581,19 +7581,19 @@
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>631682</v>
+        <v>634567</v>
       </c>
       <c r="B360" t="str">
-        <v>PICADILLO GAUDA+SALAME PF</v>
+        <v>QUESO CHANCO LA TURBINA</v>
       </c>
       <c r="C360" t="str">
         <v/>
       </c>
       <c r="D360" t="str">
-        <v>31682</v>
+        <v>34567</v>
       </c>
       <c r="E360" t="str">
-        <v>1990</v>
+        <v>5596</v>
       </c>
       <c r="F360" t="str">
         <v>Por peso</v>
@@ -7601,19 +7601,19 @@
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>633345</v>
+        <v>633167</v>
       </c>
       <c r="B361" t="str">
-        <v>QUESO MANT. SAN PEDRO KG</v>
+        <v>QUESO FRESCO CHACRA CUÑIHUE</v>
       </c>
       <c r="C361" t="str">
         <v/>
       </c>
       <c r="D361" t="str">
-        <v>33345</v>
+        <v>33167</v>
       </c>
       <c r="E361" t="str">
-        <v>13160</v>
+        <v>4396</v>
       </c>
       <c r="F361" t="str">
         <v>Por peso</v>
@@ -7621,19 +7621,19 @@
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>634567</v>
+        <v>635862</v>
       </c>
       <c r="B362" t="str">
-        <v>QUESO CHANCO LA TURBINA</v>
+        <v>QUESO MANTECOSO CUNIHUE</v>
       </c>
       <c r="C362" t="str">
         <v/>
       </c>
       <c r="D362" t="str">
-        <v>34567</v>
+        <v>35862</v>
       </c>
       <c r="E362" t="str">
-        <v>5596</v>
+        <v>12360</v>
       </c>
       <c r="F362" t="str">
         <v>Por peso</v>
@@ -7641,19 +7641,19 @@
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>633167</v>
+        <v>633466</v>
       </c>
       <c r="B363" t="str">
-        <v>QUESO FRESCO CHACRA CUÑIHUE</v>
+        <v>QUESO MANTECOSO SAN SEBASTIAN</v>
       </c>
       <c r="C363" t="str">
         <v/>
       </c>
       <c r="D363" t="str">
-        <v>33167</v>
+        <v>33466</v>
       </c>
       <c r="E363" t="str">
-        <v>4396</v>
+        <v>5396</v>
       </c>
       <c r="F363" t="str">
         <v>Por peso</v>
@@ -7661,19 +7661,19 @@
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>635862</v>
+        <v>633467</v>
       </c>
       <c r="B364" t="str">
-        <v>QUESO MANTECOSO CUNIHUE</v>
+        <v>QUESO CHANCO PUYEHUE</v>
       </c>
       <c r="C364" t="str">
         <v/>
       </c>
       <c r="D364" t="str">
-        <v>35862</v>
+        <v>33467</v>
       </c>
       <c r="E364" t="str">
-        <v>12360</v>
+        <v>5160</v>
       </c>
       <c r="F364" t="str">
         <v>Por peso</v>
@@ -7681,19 +7681,19 @@
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>633466</v>
+        <v>633468</v>
       </c>
       <c r="B365" t="str">
-        <v>QUESO MANTECOSO SAN SEBASTIAN</v>
+        <v>QUESO CHANCO LAMINADO PUYEHUE.</v>
       </c>
       <c r="C365" t="str">
         <v/>
       </c>
       <c r="D365" t="str">
-        <v>33466</v>
+        <v>33468</v>
       </c>
       <c r="E365" t="str">
-        <v>5396</v>
+        <v>4396</v>
       </c>
       <c r="F365" t="str">
         <v>Por peso</v>
@@ -7701,19 +7701,19 @@
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>633467</v>
+        <v>633470</v>
       </c>
       <c r="B366" t="str">
-        <v>QUESO CHANCO PUYEHUE</v>
+        <v>QUESO GAUDA PUYEHUE</v>
       </c>
       <c r="C366" t="str">
         <v/>
       </c>
       <c r="D366" t="str">
-        <v>33467</v>
+        <v>33470</v>
       </c>
       <c r="E366" t="str">
-        <v>5160</v>
+        <v>3960</v>
       </c>
       <c r="F366" t="str">
         <v>Por peso</v>
@@ -7721,19 +7721,19 @@
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>633468</v>
+        <v>633471</v>
       </c>
       <c r="B367" t="str">
-        <v>QUESO CHANCO LAMINADO PUYEHUE.</v>
+        <v>QUESO GAUDA LAMINADO PUYEHUE</v>
       </c>
       <c r="C367" t="str">
         <v/>
       </c>
       <c r="D367" t="str">
-        <v>33468</v>
+        <v>33471</v>
       </c>
       <c r="E367" t="str">
-        <v>4396</v>
+        <v>3960</v>
       </c>
       <c r="F367" t="str">
         <v>Por peso</v>
@@ -7741,19 +7741,19 @@
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>633470</v>
+        <v>633255</v>
       </c>
       <c r="B368" t="str">
-        <v>QUESO GAUDA PUYEHUE</v>
+        <v>QUESO CHANCO BOLA PTO OCTAY KG</v>
       </c>
       <c r="C368" t="str">
         <v/>
       </c>
       <c r="D368" t="str">
-        <v>33470</v>
+        <v>33255</v>
       </c>
       <c r="E368" t="str">
-        <v>3960</v>
+        <v>6396</v>
       </c>
       <c r="F368" t="str">
         <v>Por peso</v>
@@ -7761,19 +7761,19 @@
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>633471</v>
+        <v>633254</v>
       </c>
       <c r="B369" t="str">
-        <v>QUESO GAUDA LAMINADO PUYEHUE</v>
+        <v>QUESO GAUDA PUERTO VARAS</v>
       </c>
       <c r="C369" t="str">
         <v/>
       </c>
       <c r="D369" t="str">
-        <v>33471</v>
+        <v>33254</v>
       </c>
       <c r="E369" t="str">
-        <v>3960</v>
+        <v>5196</v>
       </c>
       <c r="F369" t="str">
         <v>Por peso</v>
@@ -7781,19 +7781,19 @@
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>633255</v>
+        <v>633366</v>
       </c>
       <c r="B370" t="str">
-        <v>QUESO CHANCO BOLA PTO OCTAY KG</v>
+        <v>DESPUNTE QUESOS</v>
       </c>
       <c r="C370" t="str">
         <v/>
       </c>
       <c r="D370" t="str">
-        <v>33255</v>
+        <v>33366</v>
       </c>
       <c r="E370" t="str">
-        <v>6396</v>
+        <v>4796</v>
       </c>
       <c r="F370" t="str">
         <v>Por peso</v>
@@ -7801,19 +7801,19 @@
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>633254</v>
+        <v>633661</v>
       </c>
       <c r="B371" t="str">
-        <v>QUESO GAUDA PUERTO VARAS</v>
+        <v>QUESO MANTECOSO BIOLECHE</v>
       </c>
       <c r="C371" t="str">
         <v/>
       </c>
       <c r="D371" t="str">
-        <v>33254</v>
+        <v>33661</v>
       </c>
       <c r="E371" t="str">
-        <v>5196</v>
+        <v>7996</v>
       </c>
       <c r="F371" t="str">
         <v>Por peso</v>
@@ -7821,19 +7821,19 @@
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>633366</v>
+        <v>637700</v>
       </c>
       <c r="B372" t="str">
-        <v>DESPUNTE QUESOS</v>
+        <v>QUESO MANTECOSO LONGAVI</v>
       </c>
       <c r="C372" t="str">
         <v/>
       </c>
       <c r="D372" t="str">
-        <v>33366</v>
+        <v>37700</v>
       </c>
       <c r="E372" t="str">
-        <v>4796</v>
+        <v>6596</v>
       </c>
       <c r="F372" t="str">
         <v>Por peso</v>
@@ -7841,19 +7841,19 @@
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>633661</v>
+        <v>632827</v>
       </c>
       <c r="B373" t="str">
-        <v>QUESO MANTECOSO BIOLECHE</v>
+        <v>QUESO GAUDA KG MOLINO VIEJO</v>
       </c>
       <c r="C373" t="str">
         <v/>
       </c>
       <c r="D373" t="str">
-        <v>33661</v>
+        <v>32827</v>
       </c>
       <c r="E373" t="str">
-        <v>7996</v>
+        <v>10360</v>
       </c>
       <c r="F373" t="str">
         <v>Por peso</v>
@@ -7861,19 +7861,19 @@
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>637700</v>
+        <v>633090</v>
       </c>
       <c r="B374" t="str">
-        <v>QUESO MANTECOSO LONGAVI</v>
+        <v>QUESO CHANCO MOLINO VIEJO KG</v>
       </c>
       <c r="C374" t="str">
         <v/>
       </c>
       <c r="D374" t="str">
-        <v>37700</v>
+        <v>33090</v>
       </c>
       <c r="E374" t="str">
-        <v>6596</v>
+        <v>10360</v>
       </c>
       <c r="F374" t="str">
         <v>Por peso</v>
@@ -7881,19 +7881,19 @@
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>632827</v>
+        <v>633105</v>
       </c>
       <c r="B375" t="str">
-        <v>QUESO GAUDA KG MOLINO VIEJO</v>
+        <v>QUESO MANTECOSO LAM. RAFULCO KG</v>
       </c>
       <c r="C375" t="str">
         <v/>
       </c>
       <c r="D375" t="str">
-        <v>32827</v>
+        <v>33105</v>
       </c>
       <c r="E375" t="str">
-        <v>10360</v>
+        <v>9560</v>
       </c>
       <c r="F375" t="str">
         <v>Por peso</v>
@@ -7901,16 +7901,16 @@
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>633090</v>
+        <v>633092</v>
       </c>
       <c r="B376" t="str">
-        <v>QUESO CHANCO MOLINO VIEJO KG</v>
+        <v>QUESO MANTECOSO SC KG. MOLINO VIEJO</v>
       </c>
       <c r="C376" t="str">
         <v/>
       </c>
       <c r="D376" t="str">
-        <v>33090</v>
+        <v>33092</v>
       </c>
       <c r="E376" t="str">
         <v>10360</v>
@@ -7921,19 +7921,19 @@
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>633105</v>
+        <v>633199</v>
       </c>
       <c r="B377" t="str">
-        <v>QUESO MANTECOSO LAM. RAFULCO KG</v>
+        <v>QUESO GAUDA PROV CHI· KG</v>
       </c>
       <c r="C377" t="str">
         <v/>
       </c>
       <c r="D377" t="str">
-        <v>33105</v>
+        <v>33199</v>
       </c>
       <c r="E377" t="str">
-        <v>9560</v>
+        <v>3996</v>
       </c>
       <c r="F377" t="str">
         <v>Por peso</v>
@@ -7941,19 +7941,19 @@
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>633092</v>
+        <v>633298</v>
       </c>
       <c r="B378" t="str">
-        <v>QUESO MANTECOSO SC KG. MOLINO VIEJO</v>
+        <v>QUESO GAUDA PROV CHILCO LAMINADO</v>
       </c>
       <c r="C378" t="str">
         <v/>
       </c>
       <c r="D378" t="str">
-        <v>33092</v>
+        <v>33298</v>
       </c>
       <c r="E378" t="str">
-        <v>10360</v>
+        <v>3996</v>
       </c>
       <c r="F378" t="str">
         <v>Por peso</v>
@@ -7961,19 +7961,19 @@
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>633199</v>
+        <v>632121</v>
       </c>
       <c r="B379" t="str">
-        <v>QUESO GAUDA PROV CHI· KG</v>
+        <v>QUESO CHANCO LAS AGUILAS KILO</v>
       </c>
       <c r="C379" t="str">
         <v/>
       </c>
       <c r="D379" t="str">
-        <v>33199</v>
+        <v>32121</v>
       </c>
       <c r="E379" t="str">
-        <v>3996</v>
+        <v>12360</v>
       </c>
       <c r="F379" t="str">
         <v>Por peso</v>
@@ -7981,19 +7981,19 @@
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>633298</v>
+        <v>632222</v>
       </c>
       <c r="B380" t="str">
-        <v>QUESO GAUDA PROV CHILCO LAMINADO</v>
+        <v>QUESO GAUDA SURLAT LAMINADO KG</v>
       </c>
       <c r="C380" t="str">
         <v/>
       </c>
       <c r="D380" t="str">
-        <v>33298</v>
+        <v>32222</v>
       </c>
       <c r="E380" t="str">
-        <v>3996</v>
+        <v>11560</v>
       </c>
       <c r="F380" t="str">
         <v>Por peso</v>
@@ -8001,19 +8001,19 @@
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>632121</v>
+        <v>633005</v>
       </c>
       <c r="B381" t="str">
-        <v>QUESO CHANCO LAS AGUILAS KILO</v>
+        <v>QUESO GAUDA CALO PIEZA 3KG</v>
       </c>
       <c r="C381" t="str">
         <v/>
       </c>
       <c r="D381" t="str">
-        <v>32121</v>
+        <v>33005</v>
       </c>
       <c r="E381" t="str">
-        <v>12360</v>
+        <v>10996</v>
       </c>
       <c r="F381" t="str">
         <v>Por peso</v>
@@ -8021,19 +8021,19 @@
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>632222</v>
+        <v>633620</v>
       </c>
       <c r="B382" t="str">
-        <v>QUESO GAUDA SURLAT LAMINADO KG</v>
+        <v>QUESO MANT. PIEZA LONGAVI KG</v>
       </c>
       <c r="C382" t="str">
         <v/>
       </c>
       <c r="D382" t="str">
-        <v>32222</v>
+        <v>33620</v>
       </c>
       <c r="E382" t="str">
-        <v>11560</v>
+        <v>12760</v>
       </c>
       <c r="F382" t="str">
         <v>Por peso</v>
@@ -8041,19 +8041,19 @@
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>633005</v>
+        <v>633621</v>
       </c>
       <c r="B383" t="str">
-        <v>QUESO GAUDA CALO PIEZA 3KG</v>
+        <v>QUESO CABRADISLAC</v>
       </c>
       <c r="C383" t="str">
         <v/>
       </c>
       <c r="D383" t="str">
-        <v>33005</v>
+        <v>33621</v>
       </c>
       <c r="E383" t="str">
-        <v>10996</v>
+        <v>28990</v>
       </c>
       <c r="F383" t="str">
         <v>Por peso</v>
@@ -8061,19 +8061,19 @@
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>633620</v>
+        <v>633249</v>
       </c>
       <c r="B384" t="str">
-        <v>QUESO MANT. PIEZA LONGAVI KG</v>
+        <v>QUESO BRIE COEUR DE LION PIEZA</v>
       </c>
       <c r="C384" t="str">
         <v/>
       </c>
       <c r="D384" t="str">
-        <v>33620</v>
+        <v>33249</v>
       </c>
       <c r="E384" t="str">
-        <v>12760</v>
+        <v>59990</v>
       </c>
       <c r="F384" t="str">
         <v>Por peso</v>
@@ -8081,19 +8081,19 @@
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>633621</v>
+        <v>633581</v>
       </c>
       <c r="B385" t="str">
-        <v>QUESO CABRADISLAC</v>
+        <v>QUESO GOUDA SURLAT BARRA 3.55 KG</v>
       </c>
       <c r="C385" t="str">
         <v/>
       </c>
       <c r="D385" t="str">
-        <v>33621</v>
+        <v>33581</v>
       </c>
       <c r="E385" t="str">
-        <v>28990</v>
+        <v>7960</v>
       </c>
       <c r="F385" t="str">
         <v>Por peso</v>
@@ -8101,19 +8101,19 @@
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>633249</v>
+        <v>633834</v>
       </c>
       <c r="B386" t="str">
-        <v>QUESO BRIE COEUR DE LION PIEZA</v>
+        <v>QUESO CHANCO LAMINADO QUILLAYES KG</v>
       </c>
       <c r="C386" t="str">
         <v/>
       </c>
       <c r="D386" t="str">
-        <v>33249</v>
+        <v>33834</v>
       </c>
       <c r="E386" t="str">
-        <v>59990</v>
+        <v>11990</v>
       </c>
       <c r="F386" t="str">
         <v>Por peso</v>
@@ -8121,19 +8121,19 @@
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>633581</v>
+        <v>633981</v>
       </c>
       <c r="B387" t="str">
-        <v>QUESO GOUDA SURLAT BARRA 3.55 KG</v>
+        <v>QUESO GAUDA QUILLAYES LAMINADO GRANEL KG</v>
       </c>
       <c r="C387" t="str">
         <v/>
       </c>
       <c r="D387" t="str">
-        <v>33581</v>
+        <v>33981</v>
       </c>
       <c r="E387" t="str">
-        <v>7960</v>
+        <v>13160</v>
       </c>
       <c r="F387" t="str">
         <v>Por peso</v>
@@ -8141,19 +8141,19 @@
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>633834</v>
+        <v>634035</v>
       </c>
       <c r="B388" t="str">
-        <v>QUESO CHANCO LAMINADO QUILLAYES KG</v>
+        <v>QUESO RALLADO GRANEL</v>
       </c>
       <c r="C388" t="str">
         <v/>
       </c>
       <c r="D388" t="str">
-        <v>33834</v>
+        <v>34035</v>
       </c>
       <c r="E388" t="str">
-        <v>11990</v>
+        <v>4990</v>
       </c>
       <c r="F388" t="str">
         <v>Por peso</v>
@@ -8161,19 +8161,19 @@
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>633981</v>
+        <v>636291</v>
       </c>
       <c r="B389" t="str">
-        <v>QUESO GAUDA QUILLAYES LAMINADO GRANEL KG</v>
+        <v>QUESO MANTECOSO LAM QUILQUE 3.4 KG</v>
       </c>
       <c r="C389" t="str">
         <v/>
       </c>
       <c r="D389" t="str">
-        <v>33981</v>
+        <v>36291</v>
       </c>
       <c r="E389" t="str">
-        <v>13160</v>
+        <v>12990</v>
       </c>
       <c r="F389" t="str">
         <v>Por peso</v>
@@ -8181,19 +8181,19 @@
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>634035</v>
+        <v>633150</v>
       </c>
       <c r="B390" t="str">
-        <v>QUESO RALLADO GRANEL</v>
+        <v>QUESO LAS PARCELAS DE VALDIVIA LAM 2.5KG</v>
       </c>
       <c r="C390" t="str">
         <v/>
       </c>
       <c r="D390" t="str">
-        <v>34035</v>
+        <v>33150</v>
       </c>
       <c r="E390" t="str">
-        <v>4990</v>
+        <v>17560</v>
       </c>
       <c r="F390" t="str">
         <v>Por peso</v>
@@ -8201,19 +8201,19 @@
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>636291</v>
+        <v>633015</v>
       </c>
       <c r="B391" t="str">
-        <v>QUESO MANTECOSO LAM QUILQUE 3.4 KG</v>
+        <v>QUESO MANTECOSO LA VAQUITA BOLSA</v>
       </c>
       <c r="C391" t="str">
         <v/>
       </c>
       <c r="D391" t="str">
-        <v>36291</v>
+        <v>33015</v>
       </c>
       <c r="E391" t="str">
-        <v>12990</v>
+        <v>10360</v>
       </c>
       <c r="F391" t="str">
         <v>Por peso</v>
@@ -8221,19 +8221,19 @@
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>633150</v>
+        <v>631053</v>
       </c>
       <c r="B392" t="str">
-        <v>QUESO LAS PARCELAS DE VALDIVIA LAM 2.5KG</v>
+        <v>QUESO MANT. PRADERAS DEL SURE O KG</v>
       </c>
       <c r="C392" t="str">
         <v/>
       </c>
       <c r="D392" t="str">
-        <v>33150</v>
+        <v>31053</v>
       </c>
       <c r="E392" t="str">
-        <v>17560</v>
+        <v>13990</v>
       </c>
       <c r="F392" t="str">
         <v>Por peso</v>
@@ -8241,16 +8241,16 @@
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>633015</v>
+        <v>631075</v>
       </c>
       <c r="B393" t="str">
-        <v>QUESO MANTECOSO LA VAQUITA BOLSA</v>
+        <v>QUESO GAUDA BARRA ARG FRUTILLAR KG</v>
       </c>
       <c r="C393" t="str">
         <v/>
       </c>
       <c r="D393" t="str">
-        <v>33015</v>
+        <v>31075</v>
       </c>
       <c r="E393" t="str">
         <v>10360</v>
@@ -8261,19 +8261,19 @@
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>631053</v>
+        <v>631082</v>
       </c>
       <c r="B394" t="str">
-        <v>QUESO MANT. PRADERAS DEL SURE O KG</v>
+        <v>QUESO GAUDA HOLANDES KG</v>
       </c>
       <c r="C394" t="str">
         <v/>
       </c>
       <c r="D394" t="str">
-        <v>31053</v>
+        <v>31082</v>
       </c>
       <c r="E394" t="str">
-        <v>13990</v>
+        <v>9160</v>
       </c>
       <c r="F394" t="str">
         <v>Por peso</v>
@@ -8281,19 +8281,19 @@
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>631075</v>
+        <v>631083</v>
       </c>
       <c r="B395" t="str">
-        <v>QUESO GAUDA BARRA ARG FRUTILLAR KG</v>
+        <v>QUESO LLANERO MAD KG - PIEZA 5 KL</v>
       </c>
       <c r="C395" t="str">
         <v/>
       </c>
       <c r="D395" t="str">
-        <v>31075</v>
+        <v>31083</v>
       </c>
       <c r="E395" t="str">
-        <v>10360</v>
+        <v>15960</v>
       </c>
       <c r="F395" t="str">
         <v>Por peso</v>
@@ -8301,19 +8301,19 @@
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>631083</v>
+        <v>632369</v>
       </c>
       <c r="B396" t="str">
-        <v>QUESO LLANERO MAD KG - PIEZA 5 KL</v>
+        <v>QUESO GAUDA BARRA ROJA LA VAQUITA KG</v>
       </c>
       <c r="C396" t="str">
         <v/>
       </c>
       <c r="D396" t="str">
-        <v>31083</v>
+        <v>32369</v>
       </c>
       <c r="E396" t="str">
-        <v>15960</v>
+        <v>9160</v>
       </c>
       <c r="F396" t="str">
         <v>Por peso</v>
@@ -8321,19 +8321,19 @@
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>632369</v>
+        <v>633310</v>
       </c>
       <c r="B397" t="str">
-        <v>QUESO GAUDA BARRA ROJA LA VAQUITA KG</v>
+        <v>QUESO EDAM HOLANDES GALLERY KG</v>
       </c>
       <c r="C397" t="str">
         <v/>
       </c>
       <c r="D397" t="str">
-        <v>32369</v>
+        <v>33310</v>
       </c>
       <c r="E397" t="str">
-        <v>9160</v>
+        <v>9960</v>
       </c>
       <c r="F397" t="str">
         <v>Por peso</v>
@@ -8341,19 +8341,19 @@
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>633310</v>
+        <v>633313</v>
       </c>
       <c r="B398" t="str">
-        <v>QUESO EDAM HOLANDES GALLERY KG</v>
+        <v>QUESO CABRA HOLANDES GALLERY KG</v>
       </c>
       <c r="C398" t="str">
         <v/>
       </c>
       <c r="D398" t="str">
-        <v>33310</v>
+        <v>33313</v>
       </c>
       <c r="E398" t="str">
-        <v>9960</v>
+        <v>15960</v>
       </c>
       <c r="F398" t="str">
         <v>Por peso</v>
@@ -8361,19 +8361,19 @@
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>633313</v>
+        <v>636230</v>
       </c>
       <c r="B399" t="str">
-        <v>QUESO CABRA HOLANDES GALLERY KG</v>
+        <v>QUESO RODDA LAM.SOPROLE 2.2KG</v>
       </c>
       <c r="C399" t="str">
         <v/>
       </c>
       <c r="D399" t="str">
-        <v>33313</v>
+        <v>36230</v>
       </c>
       <c r="E399" t="str">
-        <v>15960</v>
+        <v>11990</v>
       </c>
       <c r="F399" t="str">
         <v>Por peso</v>
@@ -8381,19 +8381,19 @@
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>636230</v>
+        <v>634145</v>
       </c>
       <c r="B400" t="str">
-        <v>QUESO RODDA LAM.SOPROLE 2.2KG</v>
+        <v>QUESO MANT. FUNDO DE SURE O KG</v>
       </c>
       <c r="C400" t="str">
         <v/>
       </c>
       <c r="D400" t="str">
-        <v>36230</v>
+        <v>34145</v>
       </c>
       <c r="E400" t="str">
-        <v>11990</v>
+        <v>12990</v>
       </c>
       <c r="F400" t="str">
         <v>Por peso</v>
@@ -8401,19 +8401,19 @@
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>634145</v>
+        <v>633211</v>
       </c>
       <c r="B401" t="str">
-        <v>QUESO MANT. FUNDO DE SURE O KG</v>
+        <v>QUESO EDAM ASTURIANA KG</v>
       </c>
       <c r="C401" t="str">
         <v/>
       </c>
       <c r="D401" t="str">
-        <v>34145</v>
+        <v>33211</v>
       </c>
       <c r="E401" t="str">
-        <v>12990</v>
+        <v>9560</v>
       </c>
       <c r="F401" t="str">
         <v>Por peso</v>

--- a/MaestraPLU_Rotiseria.xlsx
+++ b/MaestraPLU_Rotiseria.xlsx
@@ -1061,19 +1061,19 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>633119</v>
+        <v>633211</v>
       </c>
       <c r="B34" t="str">
-        <v>ACEITUNA S/AMARGO 100/120 BOLSA</v>
+        <v>QUESO EDAM ASTURIANA KG</v>
       </c>
       <c r="C34" t="str">
         <v/>
       </c>
       <c r="D34" t="str">
-        <v>33119</v>
+        <v>33211</v>
       </c>
       <c r="E34" t="str">
-        <v>3996</v>
+        <v>7160</v>
       </c>
       <c r="F34" t="str">
         <v>Por peso</v>
@@ -1081,19 +1081,19 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>631085</v>
+        <v>633119</v>
       </c>
       <c r="B35" t="str">
-        <v>AJI EN ESCABECHE</v>
+        <v>ACEITUNA S/AMARGO 100/120 BOLSA</v>
       </c>
       <c r="C35" t="str">
         <v/>
       </c>
       <c r="D35" t="str">
-        <v>41085</v>
+        <v>33119</v>
       </c>
       <c r="E35" t="str">
-        <v>1390</v>
+        <v>3996</v>
       </c>
       <c r="F35" t="str">
         <v>Por peso</v>
@@ -1101,19 +1101,19 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>632698</v>
+        <v>631085</v>
       </c>
       <c r="B36" t="str">
-        <v>MORTAD. ALEMANA ARUNA ARTESANAL</v>
+        <v>AJI EN ESCABECHE</v>
       </c>
       <c r="C36" t="str">
         <v/>
       </c>
       <c r="D36" t="str">
-        <v>32698</v>
+        <v>41085</v>
       </c>
       <c r="E36" t="str">
-        <v>1996</v>
+        <v>1390</v>
       </c>
       <c r="F36" t="str">
         <v>Por peso</v>
@@ -1121,19 +1121,19 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>632680</v>
+        <v>632698</v>
       </c>
       <c r="B37" t="str">
-        <v>MORTAD. LISA ARUNA ARTESANAL</v>
+        <v>MORTAD. ALEMANA ARUNA ARTESANAL</v>
       </c>
       <c r="C37" t="str">
         <v/>
       </c>
       <c r="D37" t="str">
-        <v>32680</v>
+        <v>32698</v>
       </c>
       <c r="E37" t="str">
-        <v>1196</v>
+        <v>1996</v>
       </c>
       <c r="F37" t="str">
         <v>Por peso</v>
@@ -1141,59 +1141,59 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>632652</v>
+        <v>632680</v>
       </c>
       <c r="B38" t="str">
-        <v>SALCHICHON CERV. ARUNA ARTESANAL</v>
+        <v>MORTAD. LISA ARUNA ARTESANAL</v>
       </c>
       <c r="C38" t="str">
         <v/>
       </c>
       <c r="D38" t="str">
-        <v>32652</v>
+        <v>32680</v>
       </c>
       <c r="E38" t="str">
-        <v>3290</v>
+        <v>1196</v>
       </c>
       <c r="F38" t="str">
-        <v>Por cantidad</v>
+        <v>Por peso</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>632158</v>
+        <v>632652</v>
       </c>
       <c r="B39" t="str">
-        <v>PICKLE GRANEL KG. SEVILLANA</v>
+        <v>SALCHICHON CERV. ARUNA ARTESANAL</v>
       </c>
       <c r="C39" t="str">
         <v/>
       </c>
       <c r="D39" t="str">
-        <v>32158</v>
+        <v>32652</v>
       </c>
       <c r="E39" t="str">
-        <v>1476</v>
+        <v>3290</v>
       </c>
       <c r="F39" t="str">
-        <v>Por peso</v>
+        <v>Por cantidad</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>632161</v>
+        <v>632158</v>
       </c>
       <c r="B40" t="str">
-        <v>AMERICANA GRANEL</v>
+        <v>PICKLE GRANEL KG. SEVILLANA</v>
       </c>
       <c r="C40" t="str">
         <v/>
       </c>
       <c r="D40" t="str">
-        <v>32161</v>
+        <v>32158</v>
       </c>
       <c r="E40" t="str">
-        <v>1490</v>
+        <v>1476</v>
       </c>
       <c r="F40" t="str">
         <v>Por peso</v>
@@ -1201,19 +1201,19 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>632163</v>
+        <v>632161</v>
       </c>
       <c r="B41" t="str">
-        <v>ACEITUNA SEVILLANA KG SOLIS</v>
+        <v>AMERICANA GRANEL</v>
       </c>
       <c r="C41" t="str">
         <v/>
       </c>
       <c r="D41" t="str">
-        <v>32163</v>
+        <v>32161</v>
       </c>
       <c r="E41" t="str">
-        <v>9396</v>
+        <v>1490</v>
       </c>
       <c r="F41" t="str">
         <v>Por peso</v>
@@ -1221,19 +1221,19 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>632008</v>
+        <v>632163</v>
       </c>
       <c r="B42" t="str">
-        <v>ACEITUNAS EXTRA AZAPA KG.</v>
+        <v>ACEITUNA SEVILLANA KG SOLIS</v>
       </c>
       <c r="C42" t="str">
         <v/>
       </c>
       <c r="D42" t="str">
-        <v>32008</v>
+        <v>32163</v>
       </c>
       <c r="E42" t="str">
-        <v>2396</v>
+        <v>9396</v>
       </c>
       <c r="F42" t="str">
         <v>Por peso</v>
@@ -1241,19 +1241,19 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>632525</v>
+        <v>632008</v>
       </c>
       <c r="B43" t="str">
-        <v>ACEITUNA AZAPA BANQUETE</v>
+        <v>ACEITUNAS EXTRA AZAPA KG.</v>
       </c>
       <c r="C43" t="str">
         <v/>
       </c>
       <c r="D43" t="str">
-        <v>32525</v>
+        <v>32008</v>
       </c>
       <c r="E43" t="str">
-        <v>3765</v>
+        <v>2396</v>
       </c>
       <c r="F43" t="str">
         <v>Por peso</v>
@@ -1261,19 +1261,19 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>632518</v>
+        <v>632525</v>
       </c>
       <c r="B44" t="str">
-        <v>ACEITUNAS SEVILLANA COCKTEIL KL</v>
+        <v>ACEITUNA AZAPA BANQUETE</v>
       </c>
       <c r="C44" t="str">
         <v/>
       </c>
       <c r="D44" t="str">
-        <v>32518</v>
+        <v>32525</v>
       </c>
       <c r="E44" t="str">
-        <v>2169</v>
+        <v>3765</v>
       </c>
       <c r="F44" t="str">
         <v>Por peso</v>
@@ -1281,19 +1281,19 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>632576</v>
+        <v>632518</v>
       </c>
       <c r="B45" t="str">
-        <v>ACEITUNA DESHUESADA NEGRA KG</v>
+        <v>ACEITUNAS SEVILLANA COCKTEIL KL</v>
       </c>
       <c r="C45" t="str">
         <v/>
       </c>
       <c r="D45" t="str">
-        <v>32576</v>
+        <v>32518</v>
       </c>
       <c r="E45" t="str">
-        <v>3596</v>
+        <v>2169</v>
       </c>
       <c r="F45" t="str">
         <v>Por peso</v>
@@ -1301,19 +1301,19 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>634454</v>
+        <v>632576</v>
       </c>
       <c r="B46" t="str">
-        <v>CEBOLLA PERLA GRANEL KG SOL</v>
+        <v>ACEITUNA DESHUESADA NEGRA KG</v>
       </c>
       <c r="C46" t="str">
         <v/>
       </c>
       <c r="D46" t="str">
-        <v>34454</v>
+        <v>32576</v>
       </c>
       <c r="E46" t="str">
-        <v>2229</v>
+        <v>3596</v>
       </c>
       <c r="F46" t="str">
         <v>Por peso</v>
@@ -1321,19 +1321,19 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>631253</v>
+        <v>634454</v>
       </c>
       <c r="B47" t="str">
-        <v>AJI ORO GRANEL SOL KG</v>
+        <v>CEBOLLA PERLA GRANEL KG SOL</v>
       </c>
       <c r="C47" t="str">
         <v/>
       </c>
       <c r="D47" t="str">
-        <v>31253</v>
+        <v>34454</v>
       </c>
       <c r="E47" t="str">
-        <v>1290</v>
+        <v>2229</v>
       </c>
       <c r="F47" t="str">
         <v>Por peso</v>
@@ -1341,19 +1341,19 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>632151</v>
+        <v>631253</v>
       </c>
       <c r="B48" t="str">
-        <v>ACEITUNA VERDE GRANEL</v>
+        <v>AJI ORO GRANEL SOL KG</v>
       </c>
       <c r="C48" t="str">
         <v/>
       </c>
       <c r="D48" t="str">
-        <v>32151</v>
+        <v>31253</v>
       </c>
       <c r="E48" t="str">
-        <v>2596</v>
+        <v>1290</v>
       </c>
       <c r="F48" t="str">
         <v>Por peso</v>
@@ -1361,19 +1361,19 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>632516</v>
+        <v>632151</v>
       </c>
       <c r="B49" t="str">
-        <v>PICKLE KG</v>
+        <v>ACEITUNA VERDE GRANEL</v>
       </c>
       <c r="C49" t="str">
         <v/>
       </c>
       <c r="D49" t="str">
-        <v>32516</v>
+        <v>32151</v>
       </c>
       <c r="E49" t="str">
-        <v>990</v>
+        <v>2596</v>
       </c>
       <c r="F49" t="str">
         <v>Por peso</v>
@@ -1381,19 +1381,19 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>632513</v>
+        <v>632516</v>
       </c>
       <c r="B50" t="str">
-        <v>ACEITUNA P/PINCHANGA KG</v>
+        <v>PICKLE KG</v>
       </c>
       <c r="C50" t="str">
         <v/>
       </c>
       <c r="D50" t="str">
-        <v>32513</v>
+        <v>32516</v>
       </c>
       <c r="E50" t="str">
-        <v>1190</v>
+        <v>990</v>
       </c>
       <c r="F50" t="str">
         <v>Por peso</v>
@@ -1401,19 +1401,19 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>632103</v>
+        <v>632513</v>
       </c>
       <c r="B51" t="str">
-        <v>LONGANIZA VON UNGER 4 UNI</v>
+        <v>ACEITUNA P/PINCHANGA KG</v>
       </c>
       <c r="C51" t="str">
         <v/>
       </c>
       <c r="D51" t="str">
-        <v>32103</v>
+        <v>32513</v>
       </c>
       <c r="E51" t="str">
-        <v>1990</v>
+        <v>1190</v>
       </c>
       <c r="F51" t="str">
         <v>Por peso</v>
@@ -1421,19 +1421,19 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>632451</v>
+        <v>632103</v>
       </c>
       <c r="B52" t="str">
-        <v>MORTAD.AVE PIMENTON ARUNA</v>
+        <v>LONGANIZA VON UNGER 4 UNI</v>
       </c>
       <c r="C52" t="str">
         <v/>
       </c>
       <c r="D52" t="str">
-        <v>32451</v>
+        <v>32103</v>
       </c>
       <c r="E52" t="str">
-        <v>1596</v>
+        <v>1990</v>
       </c>
       <c r="F52" t="str">
         <v>Por peso</v>
@@ -1441,19 +1441,19 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>631728</v>
+        <v>632451</v>
       </c>
       <c r="B53" t="str">
-        <v>MALAYA DE VACUNO ARUNA ART.</v>
+        <v>MORTAD.AVE PIMENTON ARUNA</v>
       </c>
       <c r="C53" t="str">
         <v/>
       </c>
       <c r="D53" t="str">
-        <v>31728</v>
+        <v>32451</v>
       </c>
       <c r="E53" t="str">
-        <v>3696</v>
+        <v>1596</v>
       </c>
       <c r="F53" t="str">
         <v>Por peso</v>
@@ -1461,19 +1461,19 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>632421</v>
+        <v>631728</v>
       </c>
       <c r="B54" t="str">
-        <v>ARROLLADO HUASITO VON UNGER KG</v>
+        <v>MALAYA DE VACUNO ARUNA ART.</v>
       </c>
       <c r="C54" t="str">
         <v/>
       </c>
       <c r="D54" t="str">
-        <v>32421</v>
+        <v>31728</v>
       </c>
       <c r="E54" t="str">
-        <v>4196</v>
+        <v>3696</v>
       </c>
       <c r="F54" t="str">
         <v>Por peso</v>
@@ -1481,19 +1481,19 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>632703</v>
+        <v>632421</v>
       </c>
       <c r="B55" t="str">
-        <v>ARROLLADO DE COPA ARUNA ARTESANAL</v>
+        <v>ARROLLADO HUASITO VON UNGER KG</v>
       </c>
       <c r="C55" t="str">
         <v/>
       </c>
       <c r="D55" t="str">
-        <v>32703</v>
+        <v>32421</v>
       </c>
       <c r="E55" t="str">
-        <v>1990</v>
+        <v>4196</v>
       </c>
       <c r="F55" t="str">
         <v>Por peso</v>
@@ -1501,19 +1501,19 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>632658</v>
+        <v>632703</v>
       </c>
       <c r="B56" t="str">
-        <v>GORDAS ARTESANAL KG ARUNA</v>
+        <v>ARROLLADO DE COPA ARUNA ARTESANAL</v>
       </c>
       <c r="C56" t="str">
         <v/>
       </c>
       <c r="D56" t="str">
-        <v>32658</v>
+        <v>32703</v>
       </c>
       <c r="E56" t="str">
-        <v>1890</v>
+        <v>1990</v>
       </c>
       <c r="F56" t="str">
         <v>Por peso</v>
@@ -1521,16 +1521,16 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>631027</v>
+        <v>632658</v>
       </c>
       <c r="B57" t="str">
-        <v>PERNIL ARUNA ARTESANAL</v>
+        <v>GORDAS ARTESANAL KG ARUNA</v>
       </c>
       <c r="C57" t="str">
         <v/>
       </c>
       <c r="D57" t="str">
-        <v>31027</v>
+        <v>32658</v>
       </c>
       <c r="E57" t="str">
         <v>1890</v>
@@ -1541,19 +1541,19 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>632153</v>
+        <v>631027</v>
       </c>
       <c r="B58" t="str">
-        <v>PRIETA KG PAULINA</v>
+        <v>PERNIL ARUNA ARTESANAL</v>
       </c>
       <c r="C58" t="str">
         <v/>
       </c>
       <c r="D58" t="str">
-        <v>32153</v>
+        <v>31027</v>
       </c>
       <c r="E58" t="str">
-        <v>2716</v>
+        <v>1890</v>
       </c>
       <c r="F58" t="str">
         <v>Por peso</v>
@@ -1561,19 +1561,19 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>632191</v>
+        <v>632153</v>
       </c>
       <c r="B59" t="str">
-        <v>LONGANIZA KG PAULINA</v>
+        <v>PRIETA KG PAULINA</v>
       </c>
       <c r="C59" t="str">
         <v/>
       </c>
       <c r="D59" t="str">
-        <v>32191</v>
+        <v>32153</v>
       </c>
       <c r="E59" t="str">
-        <v>1916</v>
+        <v>2716</v>
       </c>
       <c r="F59" t="str">
         <v>Por peso</v>
@@ -1581,19 +1581,19 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>632537</v>
+        <v>632191</v>
       </c>
       <c r="B60" t="str">
-        <v>LONGANIZA FASTDELI (317) KG.</v>
+        <v>LONGANIZA KG PAULINA</v>
       </c>
       <c r="C60" t="str">
         <v/>
       </c>
       <c r="D60" t="str">
-        <v>32537</v>
+        <v>32191</v>
       </c>
       <c r="E60" t="str">
-        <v>1676</v>
+        <v>1916</v>
       </c>
       <c r="F60" t="str">
         <v>Por peso</v>
@@ -1601,19 +1601,19 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>632033</v>
+        <v>632537</v>
       </c>
       <c r="B61" t="str">
-        <v>CHORIZO PARRILLERO SUPER</v>
+        <v>LONGANIZA FASTDELI (317) KG.</v>
       </c>
       <c r="C61" t="str">
         <v/>
       </c>
       <c r="D61" t="str">
-        <v>32033</v>
+        <v>32537</v>
       </c>
       <c r="E61" t="str">
-        <v>3116</v>
+        <v>1676</v>
       </c>
       <c r="F61" t="str">
         <v>Por peso</v>
@@ -1621,19 +1621,19 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>632329</v>
+        <v>632033</v>
       </c>
       <c r="B62" t="str">
-        <v>CHORIZO VALDIVIA KILO</v>
+        <v>CHORIZO PARRILLERO SUPER</v>
       </c>
       <c r="C62" t="str">
         <v/>
       </c>
       <c r="D62" t="str">
-        <v>32329</v>
+        <v>32033</v>
       </c>
       <c r="E62" t="str">
-        <v>2990</v>
+        <v>3116</v>
       </c>
       <c r="F62" t="str">
         <v>Por peso</v>
@@ -1641,19 +1641,19 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>632538</v>
+        <v>632329</v>
       </c>
       <c r="B63" t="str">
-        <v>CHORIZO FASTDELI (319) KG.</v>
+        <v>CHORIZO VALDIVIA KILO</v>
       </c>
       <c r="C63" t="str">
         <v/>
       </c>
       <c r="D63" t="str">
-        <v>32538</v>
+        <v>32329</v>
       </c>
       <c r="E63" t="str">
-        <v>2396</v>
+        <v>2990</v>
       </c>
       <c r="F63" t="str">
         <v>Por peso</v>
@@ -1661,19 +1661,19 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>631900</v>
+        <v>632538</v>
       </c>
       <c r="B64" t="str">
-        <v>CHORIZO RECETA ALEMANA 5 UNID.</v>
+        <v>CHORIZO FASTDELI (319) KG.</v>
       </c>
       <c r="C64" t="str">
         <v/>
       </c>
       <c r="D64" t="str">
-        <v>01900</v>
+        <v>32538</v>
       </c>
       <c r="E64" t="str">
-        <v>1590</v>
+        <v>2396</v>
       </c>
       <c r="F64" t="str">
         <v>Por peso</v>
@@ -1681,19 +1681,19 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>632093</v>
+        <v>631900</v>
       </c>
       <c r="B65" t="str">
-        <v>MORTAD. JAMONADA POLLO SUPER KG</v>
+        <v>CHORIZO RECETA ALEMANA 5 UNID.</v>
       </c>
       <c r="C65" t="str">
         <v/>
       </c>
       <c r="D65" t="str">
-        <v>32093</v>
+        <v>01900</v>
       </c>
       <c r="E65" t="str">
-        <v>7596</v>
+        <v>1590</v>
       </c>
       <c r="F65" t="str">
         <v>Por peso</v>
@@ -1701,19 +1701,19 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>632539</v>
+        <v>632093</v>
       </c>
       <c r="B66" t="str">
-        <v>MORT. JAMONADA FASTD.(331)KG</v>
+        <v>MORTAD. JAMONADA POLLO SUPER KG</v>
       </c>
       <c r="C66" t="str">
         <v/>
       </c>
       <c r="D66" t="str">
-        <v>32539</v>
+        <v>32093</v>
       </c>
       <c r="E66" t="str">
-        <v>1940</v>
+        <v>7596</v>
       </c>
       <c r="F66" t="str">
         <v>Por peso</v>
@@ -1721,19 +1721,19 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>632088</v>
+        <v>632539</v>
       </c>
       <c r="B67" t="str">
-        <v>MORTAD. FINA PF</v>
+        <v>MORT. JAMONADA FASTD.(331)KG</v>
       </c>
       <c r="C67" t="str">
         <v/>
       </c>
       <c r="D67" t="str">
-        <v>32088</v>
+        <v>32539</v>
       </c>
       <c r="E67" t="str">
-        <v>4996</v>
+        <v>1940</v>
       </c>
       <c r="F67" t="str">
         <v>Por peso</v>
@@ -1741,19 +1741,19 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>632079</v>
+        <v>632088</v>
       </c>
       <c r="B68" t="str">
-        <v>MILANESA HUEVO J.K.</v>
+        <v>MORTAD. FINA PF</v>
       </c>
       <c r="C68" t="str">
         <v/>
       </c>
       <c r="D68" t="str">
-        <v>32079</v>
+        <v>32088</v>
       </c>
       <c r="E68" t="str">
-        <v>3002</v>
+        <v>4996</v>
       </c>
       <c r="F68" t="str">
         <v>Por peso</v>
@@ -1761,19 +1761,19 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>632365</v>
+        <v>632079</v>
       </c>
       <c r="B69" t="str">
-        <v>MARISCAL CUGAT</v>
+        <v>MILANESA HUEVO J.K.</v>
       </c>
       <c r="C69" t="str">
         <v/>
       </c>
       <c r="D69" t="str">
-        <v>32365</v>
+        <v>32079</v>
       </c>
       <c r="E69" t="str">
-        <v>2996</v>
+        <v>3002</v>
       </c>
       <c r="F69" t="str">
         <v>Por peso</v>
@@ -1781,19 +1781,19 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>632174</v>
+        <v>632365</v>
       </c>
       <c r="B70" t="str">
-        <v>JAMONADA SJ KG</v>
+        <v>MARISCAL CUGAT</v>
       </c>
       <c r="C70" t="str">
         <v/>
       </c>
       <c r="D70" t="str">
-        <v>32174</v>
+        <v>32365</v>
       </c>
       <c r="E70" t="str">
-        <v>7196</v>
+        <v>2996</v>
       </c>
       <c r="F70" t="str">
         <v>Por peso</v>
@@ -1801,19 +1801,19 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>632073</v>
+        <v>632174</v>
       </c>
       <c r="B71" t="str">
-        <v>JAMONADA DE POLLO D9 PF KG.</v>
+        <v>JAMONADA SJ KG</v>
       </c>
       <c r="C71" t="str">
         <v/>
       </c>
       <c r="D71" t="str">
-        <v>32073</v>
+        <v>32174</v>
       </c>
       <c r="E71" t="str">
-        <v>9996</v>
+        <v>7196</v>
       </c>
       <c r="F71" t="str">
         <v>Por peso</v>
@@ -1821,19 +1821,19 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>632149</v>
+        <v>632073</v>
       </c>
       <c r="B72" t="str">
-        <v>ARROLLADO ITALIANO S.JORGE</v>
+        <v>JAMONADA DE POLLO D9 PF KG.</v>
       </c>
       <c r="C72" t="str">
         <v/>
       </c>
       <c r="D72" t="str">
-        <v>32149</v>
+        <v>32073</v>
       </c>
       <c r="E72" t="str">
-        <v>2916</v>
+        <v>9996</v>
       </c>
       <c r="F72" t="str">
         <v>Por peso</v>
@@ -1841,19 +1841,19 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>632061</v>
+        <v>632149</v>
       </c>
       <c r="B73" t="str">
-        <v>JAMON AHUMADO SUPER KG</v>
+        <v>ARROLLADO ITALIANO S.JORGE</v>
       </c>
       <c r="C73" t="str">
         <v/>
       </c>
       <c r="D73" t="str">
-        <v>32061</v>
+        <v>32149</v>
       </c>
       <c r="E73" t="str">
-        <v>8796</v>
+        <v>2916</v>
       </c>
       <c r="F73" t="str">
         <v>Por peso</v>
@@ -1861,19 +1861,19 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>632068</v>
+        <v>632061</v>
       </c>
       <c r="B74" t="str">
-        <v>JAMON PIERNA ACARAM. G1 WINTERKG</v>
+        <v>JAMON AHUMADO SUPER KG</v>
       </c>
       <c r="C74" t="str">
         <v/>
       </c>
       <c r="D74" t="str">
-        <v>32068</v>
+        <v>32061</v>
       </c>
       <c r="E74" t="str">
-        <v>11996</v>
+        <v>8796</v>
       </c>
       <c r="F74" t="str">
         <v>Por peso</v>
@@ -1881,19 +1881,19 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>632171</v>
+        <v>632068</v>
       </c>
       <c r="B75" t="str">
-        <v>ARROLLADO HUASO CON AJI SJ KG</v>
+        <v>JAMON PIERNA ACARAM. G1 WINTERKG</v>
       </c>
       <c r="C75" t="str">
         <v/>
       </c>
       <c r="D75" t="str">
-        <v>32171</v>
+        <v>32068</v>
       </c>
       <c r="E75" t="str">
-        <v>9596</v>
+        <v>11996</v>
       </c>
       <c r="F75" t="str">
         <v>Por peso</v>
@@ -1901,19 +1901,19 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>632533</v>
+        <v>632171</v>
       </c>
       <c r="B76" t="str">
-        <v>JAMON COCIDO FASTDELLI KG.</v>
+        <v>ARROLLADO HUASO CON AJI SJ KG</v>
       </c>
       <c r="C76" t="str">
         <v/>
       </c>
       <c r="D76" t="str">
-        <v>32533</v>
+        <v>32171</v>
       </c>
       <c r="E76" t="str">
-        <v>2396</v>
+        <v>9596</v>
       </c>
       <c r="F76" t="str">
         <v>Por peso</v>
@@ -1921,19 +1921,19 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>632058</v>
+        <v>632533</v>
       </c>
       <c r="B77" t="str">
-        <v>FIAMBRE JAMON SANDWICH WINTER KG</v>
+        <v>JAMON COCIDO FASTDELLI KG.</v>
       </c>
       <c r="C77" t="str">
         <v/>
       </c>
       <c r="D77" t="str">
-        <v>32058</v>
+        <v>32533</v>
       </c>
       <c r="E77" t="str">
-        <v>7996</v>
+        <v>2396</v>
       </c>
       <c r="F77" t="str">
         <v>Por peso</v>
@@ -1941,19 +1941,19 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>632052</v>
+        <v>632058</v>
       </c>
       <c r="B78" t="str">
-        <v>FIAMBRE JAMON SANDWICH SJ KG</v>
+        <v>FIAMBRE JAMON SANDWICH WINTER KG</v>
       </c>
       <c r="C78" t="str">
         <v/>
       </c>
       <c r="D78" t="str">
-        <v>32052</v>
+        <v>32058</v>
       </c>
       <c r="E78" t="str">
-        <v>7196</v>
+        <v>7996</v>
       </c>
       <c r="F78" t="str">
         <v>Por peso</v>
@@ -1961,19 +1961,19 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>632123</v>
+        <v>632052</v>
       </c>
       <c r="B79" t="str">
-        <v>SALCHICHON CERV. PF CS DELGADO</v>
+        <v>FIAMBRE JAMON SANDWICH SJ KG</v>
       </c>
       <c r="C79" t="str">
         <v/>
       </c>
       <c r="D79" t="str">
-        <v>32123</v>
+        <v>32052</v>
       </c>
       <c r="E79" t="str">
-        <v>8996</v>
+        <v>7196</v>
       </c>
       <c r="F79" t="str">
         <v>Por peso</v>
@@ -1981,19 +1981,19 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>632125</v>
+        <v>632123</v>
       </c>
       <c r="B80" t="str">
-        <v>SALCHICHON CERV. WINTER KG</v>
+        <v>SALCHICHON CERV. PF CS DELGADO</v>
       </c>
       <c r="C80" t="str">
         <v/>
       </c>
       <c r="D80" t="str">
-        <v>32125</v>
+        <v>32123</v>
       </c>
       <c r="E80" t="str">
-        <v>6996</v>
+        <v>8996</v>
       </c>
       <c r="F80" t="str">
         <v>Por peso</v>
@@ -2001,19 +2001,19 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>632563</v>
+        <v>632125</v>
       </c>
       <c r="B81" t="str">
-        <v>SALCHICHON CERV. PAULINA KG.</v>
+        <v>SALCHICHON CERV. WINTER KG</v>
       </c>
       <c r="C81" t="str">
         <v/>
       </c>
       <c r="D81" t="str">
-        <v>32563</v>
+        <v>32125</v>
       </c>
       <c r="E81" t="str">
-        <v>3396</v>
+        <v>6996</v>
       </c>
       <c r="F81" t="str">
         <v>Por peso</v>
@@ -2021,19 +2021,19 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>632016</v>
+        <v>632563</v>
       </c>
       <c r="B82" t="str">
-        <v>COPPA ITALIANA IT PF</v>
+        <v>SALCHICHON CERV. PAULINA KG.</v>
       </c>
       <c r="C82" t="str">
         <v/>
       </c>
       <c r="D82" t="str">
-        <v>32016</v>
+        <v>32563</v>
       </c>
       <c r="E82" t="str">
-        <v>7196</v>
+        <v>3396</v>
       </c>
       <c r="F82" t="str">
         <v>Por peso</v>
@@ -2041,19 +2041,19 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>632117</v>
+        <v>632016</v>
       </c>
       <c r="B83" t="str">
-        <v>SALAMIN AHUMADO SUPER</v>
+        <v>COPPA ITALIANA IT PF</v>
       </c>
       <c r="C83" t="str">
         <v/>
       </c>
       <c r="D83" t="str">
-        <v>32117</v>
+        <v>32016</v>
       </c>
       <c r="E83" t="str">
-        <v>4636</v>
+        <v>7196</v>
       </c>
       <c r="F83" t="str">
         <v>Por peso</v>
@@ -2061,19 +2061,19 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>632011</v>
+        <v>632117</v>
       </c>
       <c r="B84" t="str">
-        <v>BRAZUELO 1</v>
+        <v>SALAMIN AHUMADO SUPER</v>
       </c>
       <c r="C84" t="str">
         <v/>
       </c>
       <c r="D84" t="str">
-        <v>32011</v>
+        <v>32117</v>
       </c>
       <c r="E84" t="str">
-        <v>1541</v>
+        <v>4636</v>
       </c>
       <c r="F84" t="str">
         <v>Por peso</v>
@@ -2081,19 +2081,19 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>632312</v>
+        <v>632011</v>
       </c>
       <c r="B85" t="str">
-        <v>PECHUGA COCIDA SOPRAVAL KG</v>
+        <v>BRAZUELO 1</v>
       </c>
       <c r="C85" t="str">
         <v/>
       </c>
       <c r="D85" t="str">
-        <v>32312</v>
+        <v>32011</v>
       </c>
       <c r="E85" t="str">
-        <v>12996</v>
+        <v>1541</v>
       </c>
       <c r="F85" t="str">
         <v>Por peso</v>
@@ -2101,16 +2101,16 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>632313</v>
+        <v>632312</v>
       </c>
       <c r="B86" t="str">
-        <v>PECHUGA ASADA SOPRAVAL KG</v>
+        <v>PECHUGA COCIDA SOPRAVAL KG</v>
       </c>
       <c r="C86" t="str">
         <v/>
       </c>
       <c r="D86" t="str">
-        <v>32313</v>
+        <v>32312</v>
       </c>
       <c r="E86" t="str">
         <v>12996</v>
@@ -2121,19 +2121,19 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>632097</v>
+        <v>632313</v>
       </c>
       <c r="B87" t="str">
-        <v>MORTAD. POLLO PIMENTON SUPER KG</v>
+        <v>PECHUGA ASADA SOPRAVAL KG</v>
       </c>
       <c r="C87" t="str">
         <v/>
       </c>
       <c r="D87" t="str">
-        <v>32097</v>
+        <v>32313</v>
       </c>
       <c r="E87" t="str">
-        <v>6196</v>
+        <v>12996</v>
       </c>
       <c r="F87" t="str">
         <v>Por peso</v>
@@ -2141,19 +2141,19 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>632415</v>
+        <v>632097</v>
       </c>
       <c r="B88" t="str">
-        <v>PECHUGA PAVO AHUM.ARIZTIA KG 8011BF</v>
+        <v>MORTAD. POLLO PIMENTON SUPER KG</v>
       </c>
       <c r="C88" t="str">
         <v/>
       </c>
       <c r="D88" t="str">
-        <v>32415</v>
+        <v>32097</v>
       </c>
       <c r="E88" t="str">
-        <v>13996</v>
+        <v>6196</v>
       </c>
       <c r="F88" t="str">
         <v>Por peso</v>
@@ -2161,19 +2161,19 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>632087</v>
+        <v>632415</v>
       </c>
       <c r="B89" t="str">
-        <v>MORTAD. LISA C/PEREJIL JK KG</v>
+        <v>PECHUGA PAVO AHUM.ARIZTIA KG 8011BF</v>
       </c>
       <c r="C89" t="str">
         <v/>
       </c>
       <c r="D89" t="str">
-        <v>32087</v>
+        <v>32415</v>
       </c>
       <c r="E89" t="str">
-        <v>1396</v>
+        <v>13996</v>
       </c>
       <c r="F89" t="str">
         <v>Por peso</v>
@@ -2181,19 +2181,19 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>632402</v>
+        <v>632087</v>
       </c>
       <c r="B90" t="str">
-        <v>MORTAD.LISA 200GR</v>
+        <v>MORTAD. LISA C/PEREJIL JK KG</v>
       </c>
       <c r="C90" t="str">
         <v/>
       </c>
       <c r="D90" t="str">
-        <v>32402</v>
+        <v>32087</v>
       </c>
       <c r="E90" t="str">
-        <v>779</v>
+        <v>1396</v>
       </c>
       <c r="F90" t="str">
         <v>Por peso</v>
@@ -2201,19 +2201,19 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>634513</v>
+        <v>632402</v>
       </c>
       <c r="B91" t="str">
-        <v>ARROLLADO LOMO S AJI SJ KG</v>
+        <v>MORTAD.LISA 200GR</v>
       </c>
       <c r="C91" t="str">
         <v/>
       </c>
       <c r="D91" t="str">
-        <v>34513</v>
+        <v>32402</v>
       </c>
       <c r="E91" t="str">
-        <v>9596</v>
+        <v>779</v>
       </c>
       <c r="F91" t="str">
         <v>Por peso</v>
@@ -2221,19 +2221,19 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>634505</v>
+        <v>634513</v>
       </c>
       <c r="B92" t="str">
-        <v>JAMON PIERNA ACAR. G1 JG PF KILO</v>
+        <v>ARROLLADO LOMO S AJI SJ KG</v>
       </c>
       <c r="C92" t="str">
         <v/>
       </c>
       <c r="D92" t="str">
-        <v>34505</v>
+        <v>34513</v>
       </c>
       <c r="E92" t="str">
-        <v>12396</v>
+        <v>9596</v>
       </c>
       <c r="F92" t="str">
         <v>Por peso</v>
@@ -2241,19 +2241,19 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>634506</v>
+        <v>634505</v>
       </c>
       <c r="B93" t="str">
-        <v>JAMON PAVO ACAR.SOPRAVAL KG</v>
+        <v>JAMON PIERNA ACAR. G1 JG PF KILO</v>
       </c>
       <c r="C93" t="str">
         <v/>
       </c>
       <c r="D93" t="str">
-        <v>34506</v>
+        <v>34505</v>
       </c>
       <c r="E93" t="str">
-        <v>14996</v>
+        <v>12396</v>
       </c>
       <c r="F93" t="str">
         <v>Por peso</v>
@@ -2261,19 +2261,19 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>634496</v>
+        <v>634506</v>
       </c>
       <c r="B94" t="str">
-        <v>PECHUGA AHUMADA POLLO SUPER KG</v>
+        <v>JAMON PAVO ACAR.SOPRAVAL KG</v>
       </c>
       <c r="C94" t="str">
         <v/>
       </c>
       <c r="D94" t="str">
-        <v>34496</v>
+        <v>34506</v>
       </c>
       <c r="E94" t="str">
-        <v>10996</v>
+        <v>14996</v>
       </c>
       <c r="F94" t="str">
         <v>Por peso</v>
@@ -2281,16 +2281,16 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>634495</v>
+        <v>634496</v>
       </c>
       <c r="B95" t="str">
-        <v>PECHUGA ACARAMELADA POLLO SUPER KG</v>
+        <v>PECHUGA AHUMADA POLLO SUPER KG</v>
       </c>
       <c r="C95" t="str">
         <v/>
       </c>
       <c r="D95" t="str">
-        <v>34495</v>
+        <v>34496</v>
       </c>
       <c r="E95" t="str">
         <v>10996</v>
@@ -2301,19 +2301,19 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>632603</v>
+        <v>634495</v>
       </c>
       <c r="B96" t="str">
-        <v>ARROLLADO LOMO PORCIONADO DON RODRIGO</v>
+        <v>PECHUGA ACARAMELADA POLLO SUPER KG</v>
       </c>
       <c r="C96" t="str">
         <v/>
       </c>
       <c r="D96" t="str">
-        <v>32603</v>
+        <v>34495</v>
       </c>
       <c r="E96" t="str">
-        <v>7960</v>
+        <v>10996</v>
       </c>
       <c r="F96" t="str">
         <v>Por peso</v>
@@ -2321,19 +2321,19 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>632119</v>
+        <v>632603</v>
       </c>
       <c r="B97" t="str">
-        <v>SALCHICHON CERVEZA EXT.DOMENCH</v>
+        <v>ARROLLADO LOMO PORCIONADO DON RODRIGO</v>
       </c>
       <c r="C97" t="str">
         <v/>
       </c>
       <c r="D97" t="str">
-        <v>32119</v>
+        <v>32603</v>
       </c>
       <c r="E97" t="str">
-        <v>2916</v>
+        <v>7960</v>
       </c>
       <c r="F97" t="str">
         <v>Por peso</v>
@@ -2341,19 +2341,19 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>632167</v>
+        <v>632119</v>
       </c>
       <c r="B98" t="str">
-        <v>SALCHICHON CERV.PAVO DOMENCH</v>
+        <v>SALCHICHON CERVEZA EXT.DOMENCH</v>
       </c>
       <c r="C98" t="str">
         <v/>
       </c>
       <c r="D98" t="str">
-        <v>32167</v>
+        <v>32119</v>
       </c>
       <c r="E98" t="str">
-        <v>1478</v>
+        <v>2916</v>
       </c>
       <c r="F98" t="str">
         <v>Por peso</v>
@@ -2361,19 +2361,19 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>632602</v>
+        <v>632167</v>
       </c>
       <c r="B99" t="str">
-        <v>MORT.JAMONADA EL POZO KG</v>
+        <v>SALCHICHON CERV.PAVO DOMENCH</v>
       </c>
       <c r="C99" t="str">
         <v/>
       </c>
       <c r="D99" t="str">
-        <v>32602</v>
+        <v>32167</v>
       </c>
       <c r="E99" t="str">
-        <v>1996</v>
+        <v>1478</v>
       </c>
       <c r="F99" t="str">
         <v>Por peso</v>
@@ -2381,19 +2381,19 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>631592</v>
+        <v>632602</v>
       </c>
       <c r="B100" t="str">
-        <v>JAMON PLANCHADO CATALANA KG</v>
+        <v>MORT.JAMONADA EL POZO KG</v>
       </c>
       <c r="C100" t="str">
         <v/>
       </c>
       <c r="D100" t="str">
-        <v>31592</v>
+        <v>32602</v>
       </c>
       <c r="E100" t="str">
-        <v>4760</v>
+        <v>1996</v>
       </c>
       <c r="F100" t="str">
         <v>Por peso</v>
@@ -2401,19 +2401,19 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>631058</v>
+        <v>631592</v>
       </c>
       <c r="B101" t="str">
-        <v>PICHANGA ECONOMICA CUGAT KG</v>
+        <v>JAMON PLANCHADO CATALANA KG</v>
       </c>
       <c r="C101" t="str">
         <v/>
       </c>
       <c r="D101" t="str">
-        <v>31058</v>
+        <v>31592</v>
       </c>
       <c r="E101" t="str">
-        <v>4996</v>
+        <v>4760</v>
       </c>
       <c r="F101" t="str">
         <v>Por peso</v>
@@ -2421,59 +2421,59 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>631623</v>
+        <v>631058</v>
       </c>
       <c r="B102" t="str">
-        <v>PATITAS DE CERDO COCIDA DEVA</v>
+        <v>PICHANGA ECONOMICA CUGAT KG</v>
       </c>
       <c r="C102" t="str">
         <v/>
       </c>
       <c r="D102" t="str">
-        <v>31623</v>
+        <v>31058</v>
       </c>
       <c r="E102" t="str">
-        <v>490</v>
+        <v>4996</v>
       </c>
       <c r="F102" t="str">
-        <v>Por cantidad</v>
+        <v>Por peso</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>632780</v>
+        <v>631623</v>
       </c>
       <c r="B103" t="str">
-        <v>MORTAD. JAMONADA MYLPAN</v>
+        <v>PATITAS DE CERDO COCIDA DEVA</v>
       </c>
       <c r="C103" t="str">
         <v/>
       </c>
       <c r="D103" t="str">
-        <v>32780</v>
+        <v>31623</v>
       </c>
       <c r="E103" t="str">
-        <v>2796</v>
+        <v>490</v>
       </c>
       <c r="F103" t="str">
-        <v>Por peso</v>
+        <v>Por cantidad</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>632740</v>
+        <v>632780</v>
       </c>
       <c r="B104" t="str">
-        <v>ARROLLADO HUASO MYLPAN</v>
+        <v>MORTAD. JAMONADA MYLPAN</v>
       </c>
       <c r="C104" t="str">
         <v/>
       </c>
       <c r="D104" t="str">
-        <v>32740</v>
+        <v>32780</v>
       </c>
       <c r="E104" t="str">
-        <v>3196</v>
+        <v>2796</v>
       </c>
       <c r="F104" t="str">
         <v>Por peso</v>
@@ -2481,16 +2481,16 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>632750</v>
+        <v>632740</v>
       </c>
       <c r="B105" t="str">
-        <v>ARROLLADO LOMO MYLPAN</v>
+        <v>ARROLLADO HUASO MYLPAN</v>
       </c>
       <c r="C105" t="str">
         <v/>
       </c>
       <c r="D105" t="str">
-        <v>32750</v>
+        <v>32740</v>
       </c>
       <c r="E105" t="str">
         <v>3196</v>
@@ -2501,19 +2501,19 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>632760</v>
+        <v>632750</v>
       </c>
       <c r="B106" t="str">
-        <v>SALCHICHON CERV. MYLPAN KG</v>
+        <v>ARROLLADO LOMO MYLPAN</v>
       </c>
       <c r="C106" t="str">
         <v/>
       </c>
       <c r="D106" t="str">
-        <v>32760</v>
+        <v>32750</v>
       </c>
       <c r="E106" t="str">
-        <v>2796</v>
+        <v>3196</v>
       </c>
       <c r="F106" t="str">
         <v>Por peso</v>
@@ -2521,19 +2521,19 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>631059</v>
+        <v>632760</v>
       </c>
       <c r="B107" t="str">
-        <v>PICHANGA ESPECIAL CUGAT KG</v>
+        <v>SALCHICHON CERV. MYLPAN KG</v>
       </c>
       <c r="C107" t="str">
         <v/>
       </c>
       <c r="D107" t="str">
-        <v>31059</v>
+        <v>32760</v>
       </c>
       <c r="E107" t="str">
-        <v>6796</v>
+        <v>2796</v>
       </c>
       <c r="F107" t="str">
         <v>Por peso</v>
@@ -2541,19 +2541,19 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>632631</v>
+        <v>631059</v>
       </c>
       <c r="B108" t="str">
-        <v>JAMONADA ARUNA ARTESANAL</v>
+        <v>PICHANGA ESPECIAL CUGAT KG</v>
       </c>
       <c r="C108" t="str">
         <v/>
       </c>
       <c r="D108" t="str">
-        <v>32631</v>
+        <v>31059</v>
       </c>
       <c r="E108" t="str">
-        <v>2196</v>
+        <v>6796</v>
       </c>
       <c r="F108" t="str">
         <v>Por peso</v>
@@ -2561,19 +2561,19 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>631626</v>
+        <v>632631</v>
       </c>
       <c r="B109" t="str">
-        <v>CHULETA CENTRO AHUMADO DEVA KG</v>
+        <v>JAMONADA ARUNA ARTESANAL</v>
       </c>
       <c r="C109" t="str">
         <v/>
       </c>
       <c r="D109" t="str">
-        <v>31626</v>
+        <v>32631</v>
       </c>
       <c r="E109" t="str">
-        <v>3990</v>
+        <v>2196</v>
       </c>
       <c r="F109" t="str">
         <v>Por peso</v>
@@ -2581,19 +2581,19 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>632622</v>
+        <v>631626</v>
       </c>
       <c r="B110" t="str">
-        <v>PERNIL COCIDO DEVA KG</v>
+        <v>CHULETA CENTRO AHUMADO DEVA KG</v>
       </c>
       <c r="C110" t="str">
         <v/>
       </c>
       <c r="D110" t="str">
-        <v>32622</v>
+        <v>31626</v>
       </c>
       <c r="E110" t="str">
-        <v>1990</v>
+        <v>3990</v>
       </c>
       <c r="F110" t="str">
         <v>Por peso</v>
@@ -2601,19 +2601,19 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>631190</v>
+        <v>632622</v>
       </c>
       <c r="B111" t="str">
-        <v>JAMON PIERNA MOLDE DEVA KG.</v>
+        <v>PERNIL COCIDO DEVA KG</v>
       </c>
       <c r="C111" t="str">
         <v/>
       </c>
       <c r="D111" t="str">
-        <v>31190</v>
+        <v>32622</v>
       </c>
       <c r="E111" t="str">
-        <v>6396</v>
+        <v>1990</v>
       </c>
       <c r="F111" t="str">
         <v>Por peso</v>
@@ -2621,19 +2621,19 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>631261</v>
+        <v>631190</v>
       </c>
       <c r="B112" t="str">
-        <v>CEBOLLA PERLA KILO LAS LOMAS</v>
+        <v>JAMON PIERNA MOLDE DEVA KG.</v>
       </c>
       <c r="C112" t="str">
         <v/>
       </c>
       <c r="D112" t="str">
-        <v>31261</v>
+        <v>31190</v>
       </c>
       <c r="E112" t="str">
-        <v>4996</v>
+        <v>6396</v>
       </c>
       <c r="F112" t="str">
         <v>Por peso</v>
@@ -2641,19 +2641,19 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>631398</v>
+        <v>631261</v>
       </c>
       <c r="B113" t="str">
-        <v>ACEITUNA SEVILLANA SAJ. KILO</v>
+        <v>CEBOLLA PERLA KILO LAS LOMAS</v>
       </c>
       <c r="C113" t="str">
         <v/>
       </c>
       <c r="D113" t="str">
-        <v>31398</v>
+        <v>31261</v>
       </c>
       <c r="E113" t="str">
-        <v>1669</v>
+        <v>4996</v>
       </c>
       <c r="F113" t="str">
         <v>Por peso</v>
@@ -2661,19 +2661,19 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>631353</v>
+        <v>631398</v>
       </c>
       <c r="B114" t="str">
-        <v>ACEITUNA RELLENA C/AJI</v>
+        <v>ACEITUNA SEVILLANA SAJ. KILO</v>
       </c>
       <c r="C114" t="str">
         <v/>
       </c>
       <c r="D114" t="str">
-        <v>31353</v>
+        <v>31398</v>
       </c>
       <c r="E114" t="str">
-        <v>4996</v>
+        <v>1669</v>
       </c>
       <c r="F114" t="str">
         <v>Por peso</v>
@@ -2681,19 +2681,19 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>632657</v>
+        <v>631353</v>
       </c>
       <c r="B115" t="str">
-        <v>CHORIZO 500GR SAN PABLO</v>
+        <v>ACEITUNA RELLENA C/AJI</v>
       </c>
       <c r="C115" t="str">
         <v/>
       </c>
       <c r="D115" t="str">
-        <v>32657</v>
+        <v>31353</v>
       </c>
       <c r="E115" t="str">
-        <v>1436</v>
+        <v>4996</v>
       </c>
       <c r="F115" t="str">
         <v>Por peso</v>
@@ -2701,19 +2701,19 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>634489</v>
+        <v>632657</v>
       </c>
       <c r="B116" t="str">
-        <v>COPA SAN PABLO KG</v>
+        <v>CHORIZO 500GR SAN PABLO</v>
       </c>
       <c r="C116" t="str">
         <v/>
       </c>
       <c r="D116" t="str">
-        <v>34489</v>
+        <v>32657</v>
       </c>
       <c r="E116" t="str">
-        <v>6996</v>
+        <v>1436</v>
       </c>
       <c r="F116" t="str">
         <v>Por peso</v>
@@ -2721,19 +2721,19 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>631549</v>
+        <v>634489</v>
       </c>
       <c r="B117" t="str">
-        <v>ARROLLADO LOMO CATALANA C/AJI</v>
+        <v>COPA SAN PABLO KG</v>
       </c>
       <c r="C117" t="str">
         <v/>
       </c>
       <c r="D117" t="str">
-        <v>31549</v>
+        <v>34489</v>
       </c>
       <c r="E117" t="str">
-        <v>4360</v>
+        <v>6996</v>
       </c>
       <c r="F117" t="str">
         <v>Por peso</v>
@@ -2741,16 +2741,16 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>631591</v>
+        <v>631549</v>
       </c>
       <c r="B118" t="str">
-        <v>ARROLLADO LOMO CATALANA S/AJI KG</v>
+        <v>ARROLLADO LOMO CATALANA C/AJI</v>
       </c>
       <c r="C118" t="str">
         <v/>
       </c>
       <c r="D118" t="str">
-        <v>31591</v>
+        <v>31549</v>
       </c>
       <c r="E118" t="str">
         <v>4360</v>
@@ -2761,19 +2761,19 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>632676</v>
+        <v>631591</v>
       </c>
       <c r="B119" t="str">
-        <v>JAMONADA DE AVE SJ KG</v>
+        <v>ARROLLADO LOMO CATALANA S/AJI KG</v>
       </c>
       <c r="C119" t="str">
         <v/>
       </c>
       <c r="D119" t="str">
-        <v>32676</v>
+        <v>31591</v>
       </c>
       <c r="E119" t="str">
-        <v>6996</v>
+        <v>4360</v>
       </c>
       <c r="F119" t="str">
         <v>Por peso</v>
@@ -2781,19 +2781,19 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>632671</v>
+        <v>632676</v>
       </c>
       <c r="B120" t="str">
-        <v>JAMON ACARAMELADO SJ KG</v>
+        <v>JAMONADA DE AVE SJ KG</v>
       </c>
       <c r="C120" t="str">
         <v/>
       </c>
       <c r="D120" t="str">
-        <v>32671</v>
+        <v>32676</v>
       </c>
       <c r="E120" t="str">
-        <v>12996</v>
+        <v>6996</v>
       </c>
       <c r="F120" t="str">
         <v>Por peso</v>
@@ -2801,19 +2801,19 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>632674</v>
+        <v>632671</v>
       </c>
       <c r="B121" t="str">
-        <v>MORTAD. POLLO SJ KG</v>
+        <v>JAMON ACARAMELADO SJ KG</v>
       </c>
       <c r="C121" t="str">
         <v/>
       </c>
       <c r="D121" t="str">
-        <v>32674</v>
+        <v>32671</v>
       </c>
       <c r="E121" t="str">
-        <v>4996</v>
+        <v>12996</v>
       </c>
       <c r="F121" t="str">
         <v>Por peso</v>
@@ -2821,19 +2821,19 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>632568</v>
+        <v>632674</v>
       </c>
       <c r="B122" t="str">
-        <v>MORTAD. JAMONADA WINTER KG</v>
+        <v>MORTAD. POLLO SJ KG</v>
       </c>
       <c r="C122" t="str">
         <v/>
       </c>
       <c r="D122" t="str">
-        <v>32568</v>
+        <v>32674</v>
       </c>
       <c r="E122" t="str">
-        <v>6196</v>
+        <v>4996</v>
       </c>
       <c r="F122" t="str">
         <v>Por peso</v>
@@ -2841,19 +2841,19 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>631003</v>
+        <v>632568</v>
       </c>
       <c r="B123" t="str">
-        <v>PATE DE PAVO SOPRAVAL 125.</v>
+        <v>MORTAD. JAMONADA WINTER KG</v>
       </c>
       <c r="C123" t="str">
         <v/>
       </c>
       <c r="D123" t="str">
-        <v>31003</v>
+        <v>32568</v>
       </c>
       <c r="E123" t="str">
-        <v>279</v>
+        <v>6196</v>
       </c>
       <c r="F123" t="str">
         <v>Por peso</v>
@@ -2861,19 +2861,19 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>631012</v>
+        <v>631003</v>
       </c>
       <c r="B124" t="str">
-        <v>LONGANIZA KG SUPER</v>
+        <v>PATE DE PAVO SOPRAVAL 125.</v>
       </c>
       <c r="C124" t="str">
         <v/>
       </c>
       <c r="D124" t="str">
-        <v>31012</v>
+        <v>31003</v>
       </c>
       <c r="E124" t="str">
-        <v>3116</v>
+        <v>279</v>
       </c>
       <c r="F124" t="str">
         <v>Por peso</v>
@@ -2881,19 +2881,19 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>631143</v>
+        <v>631012</v>
       </c>
       <c r="B125" t="str">
-        <v>LONGANIZA CHILLAN AHUMADA KILO</v>
+        <v>LONGANIZA KG SUPER</v>
       </c>
       <c r="C125" t="str">
         <v/>
       </c>
       <c r="D125" t="str">
-        <v>31143</v>
+        <v>31012</v>
       </c>
       <c r="E125" t="str">
-        <v>10996</v>
+        <v>3116</v>
       </c>
       <c r="F125" t="str">
         <v>Por peso</v>
@@ -2901,19 +2901,19 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>631265</v>
+        <v>631143</v>
       </c>
       <c r="B126" t="str">
-        <v>CHORIZO LA CRIANZA GRANEL KG.</v>
+        <v>LONGANIZA CHILLAN AHUMADA KILO</v>
       </c>
       <c r="C126" t="str">
         <v/>
       </c>
       <c r="D126" t="str">
-        <v>31265</v>
+        <v>31143</v>
       </c>
       <c r="E126" t="str">
-        <v>3516</v>
+        <v>10996</v>
       </c>
       <c r="F126" t="str">
         <v>Por peso</v>
@@ -2921,19 +2921,19 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>632633</v>
+        <v>631265</v>
       </c>
       <c r="B127" t="str">
-        <v>SALCHICHON CERV. ARUNA ARTESANAL KG</v>
+        <v>CHORIZO LA CRIANZA GRANEL KG.</v>
       </c>
       <c r="C127" t="str">
         <v/>
       </c>
       <c r="D127" t="str">
-        <v>32633</v>
+        <v>31265</v>
       </c>
       <c r="E127" t="str">
-        <v>3560</v>
+        <v>3516</v>
       </c>
       <c r="F127" t="str">
         <v>Por peso</v>
@@ -2941,19 +2941,19 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>632644</v>
+        <v>632633</v>
       </c>
       <c r="B128" t="str">
-        <v>CERVECIN VON UNGER</v>
+        <v>SALCHICHON CERV. ARUNA ARTESANAL KG</v>
       </c>
       <c r="C128" t="str">
         <v/>
       </c>
       <c r="D128" t="str">
-        <v>32644</v>
+        <v>32633</v>
       </c>
       <c r="E128" t="str">
-        <v>2760</v>
+        <v>3560</v>
       </c>
       <c r="F128" t="str">
         <v>Por peso</v>
@@ -2961,19 +2961,19 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>632618</v>
+        <v>632644</v>
       </c>
       <c r="B129" t="str">
-        <v>ARROLLADO LOMO CHILLAN KG</v>
+        <v>CERVECIN VON UNGER</v>
       </c>
       <c r="C129" t="str">
         <v/>
       </c>
       <c r="D129" t="str">
-        <v>32618</v>
+        <v>32644</v>
       </c>
       <c r="E129" t="str">
-        <v>11996</v>
+        <v>2760</v>
       </c>
       <c r="F129" t="str">
         <v>Por peso</v>
@@ -2981,19 +2981,19 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>633128</v>
+        <v>632618</v>
       </c>
       <c r="B130" t="str">
-        <v>CHORIZO PARRILLERO ROJO C CATALANA KG</v>
+        <v>ARROLLADO LOMO CHILLAN KG</v>
       </c>
       <c r="C130" t="str">
         <v/>
       </c>
       <c r="D130" t="str">
-        <v>33128</v>
+        <v>32618</v>
       </c>
       <c r="E130" t="str">
-        <v>1836</v>
+        <v>11996</v>
       </c>
       <c r="F130" t="str">
         <v>Por peso</v>
@@ -3001,19 +3001,19 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>631375</v>
+        <v>633128</v>
       </c>
       <c r="B131" t="str">
-        <v>MORTAD. ALEMANA FRANK 4911</v>
+        <v>CHORIZO PARRILLERO ROJO C CATALANA KG</v>
       </c>
       <c r="C131" t="str">
         <v/>
       </c>
       <c r="D131" t="str">
-        <v>31375</v>
+        <v>33128</v>
       </c>
       <c r="E131" t="str">
-        <v>1796</v>
+        <v>1836</v>
       </c>
       <c r="F131" t="str">
         <v>Por peso</v>
@@ -3021,19 +3021,19 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>631351</v>
+        <v>631375</v>
       </c>
       <c r="B132" t="str">
-        <v>JAMONADA MONTINA KG 5371AF</v>
+        <v>MORTAD. ALEMANA FRANK 4911</v>
       </c>
       <c r="C132" t="str">
         <v/>
       </c>
       <c r="D132" t="str">
-        <v>31351</v>
+        <v>31375</v>
       </c>
       <c r="E132" t="str">
-        <v>5996</v>
+        <v>1796</v>
       </c>
       <c r="F132" t="str">
         <v>Por peso</v>
@@ -3041,19 +3041,19 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>631538</v>
+        <v>631351</v>
       </c>
       <c r="B133" t="str">
-        <v>JAMONADA PAVO BALANCE KG PF</v>
+        <v>JAMONADA MONTINA KG 5371AF</v>
       </c>
       <c r="C133" t="str">
         <v/>
       </c>
       <c r="D133" t="str">
-        <v>31538</v>
+        <v>31351</v>
       </c>
       <c r="E133" t="str">
-        <v>10196</v>
+        <v>5996</v>
       </c>
       <c r="F133" t="str">
         <v>Por peso</v>
@@ -3061,19 +3061,19 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>631536</v>
+        <v>631538</v>
       </c>
       <c r="B134" t="str">
-        <v>ARROLLADO LOMO A4 S/AJI KG.</v>
+        <v>JAMONADA PAVO BALANCE KG PF</v>
       </c>
       <c r="C134" t="str">
         <v/>
       </c>
       <c r="D134" t="str">
-        <v>31536</v>
+        <v>31538</v>
       </c>
       <c r="E134" t="str">
-        <v>3356</v>
+        <v>10196</v>
       </c>
       <c r="F134" t="str">
         <v>Por peso</v>
@@ -3081,19 +3081,19 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>631496</v>
+        <v>631536</v>
       </c>
       <c r="B135" t="str">
-        <v>JAMON SANDWICH JW PF KILO</v>
+        <v>ARROLLADO LOMO A4 S/AJI KG.</v>
       </c>
       <c r="C135" t="str">
         <v/>
       </c>
       <c r="D135" t="str">
-        <v>31496</v>
+        <v>31536</v>
       </c>
       <c r="E135" t="str">
-        <v>7996</v>
+        <v>3356</v>
       </c>
       <c r="F135" t="str">
         <v>Por peso</v>
@@ -3101,19 +3101,19 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>631488</v>
+        <v>631496</v>
       </c>
       <c r="B136" t="str">
-        <v>ARROLLADO LOMO AR PF KILO</v>
+        <v>JAMON SANDWICH JW PF KILO</v>
       </c>
       <c r="C136" t="str">
         <v/>
       </c>
       <c r="D136" t="str">
-        <v>31488</v>
+        <v>31496</v>
       </c>
       <c r="E136" t="str">
-        <v>9596</v>
+        <v>7996</v>
       </c>
       <c r="F136" t="str">
         <v>Por peso</v>
@@ -3121,19 +3121,19 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>631121</v>
+        <v>631488</v>
       </c>
       <c r="B137" t="str">
-        <v>JAMON PLANCHADO SJ KG</v>
+        <v>ARROLLADO LOMO AR PF KILO</v>
       </c>
       <c r="C137" t="str">
         <v/>
       </c>
       <c r="D137" t="str">
-        <v>31121</v>
+        <v>31488</v>
       </c>
       <c r="E137" t="str">
-        <v>9996</v>
+        <v>9596</v>
       </c>
       <c r="F137" t="str">
         <v>Por peso</v>
@@ -3141,19 +3141,19 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>631166</v>
+        <v>631121</v>
       </c>
       <c r="B138" t="str">
-        <v>JAMON PIERNA LP KG</v>
+        <v>JAMON PLANCHADO SJ KG</v>
       </c>
       <c r="C138" t="str">
         <v/>
       </c>
       <c r="D138" t="str">
-        <v>31166</v>
+        <v>31121</v>
       </c>
       <c r="E138" t="str">
-        <v>13996</v>
+        <v>9996</v>
       </c>
       <c r="F138" t="str">
         <v>Por peso</v>
@@ -3161,19 +3161,19 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>631090</v>
+        <v>631166</v>
       </c>
       <c r="B139" t="str">
-        <v>JAMON PIERNA AHUM.WINTER</v>
+        <v>JAMON PIERNA LP KG</v>
       </c>
       <c r="C139" t="str">
         <v/>
       </c>
       <c r="D139" t="str">
-        <v>31090</v>
+        <v>31166</v>
       </c>
       <c r="E139" t="str">
-        <v>11996</v>
+        <v>13996</v>
       </c>
       <c r="F139" t="str">
         <v>Por peso</v>
@@ -3181,19 +3181,19 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>631006</v>
+        <v>631090</v>
       </c>
       <c r="B140" t="str">
-        <v>JAMON PECHUGA PAVO ACARAM.ARIZTIA</v>
+        <v>JAMON PIERNA AHUM.WINTER</v>
       </c>
       <c r="C140" t="str">
         <v/>
       </c>
       <c r="D140" t="str">
-        <v>31006</v>
+        <v>31090</v>
       </c>
       <c r="E140" t="str">
-        <v>13996</v>
+        <v>11996</v>
       </c>
       <c r="F140" t="str">
         <v>Por peso</v>
@@ -3201,16 +3201,16 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>631421</v>
+        <v>631006</v>
       </c>
       <c r="B141" t="str">
-        <v>ARROLLADO HUASO LP KG</v>
+        <v>JAMON PECHUGA PAVO ACARAM.ARIZTIA</v>
       </c>
       <c r="C141" t="str">
         <v/>
       </c>
       <c r="D141" t="str">
-        <v>31421</v>
+        <v>31006</v>
       </c>
       <c r="E141" t="str">
         <v>13996</v>
@@ -3221,19 +3221,19 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>631528</v>
+        <v>631421</v>
       </c>
       <c r="B142" t="str">
-        <v>JAMON PAVO ACARAM. PF KG.</v>
+        <v>ARROLLADO HUASO LP KG</v>
       </c>
       <c r="C142" t="str">
         <v/>
       </c>
       <c r="D142" t="str">
-        <v>31528</v>
+        <v>31421</v>
       </c>
       <c r="E142" t="str">
-        <v>11996</v>
+        <v>13996</v>
       </c>
       <c r="F142" t="str">
         <v>Por peso</v>
@@ -3241,19 +3241,19 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>631493</v>
+        <v>631528</v>
       </c>
       <c r="B143" t="str">
-        <v>JAMON AHUMADO G1 JH PF KILO</v>
+        <v>JAMON PAVO ACARAM. PF KG.</v>
       </c>
       <c r="C143" t="str">
         <v/>
       </c>
       <c r="D143" t="str">
-        <v>31493</v>
+        <v>31528</v>
       </c>
       <c r="E143" t="str">
-        <v>12396</v>
+        <v>11996</v>
       </c>
       <c r="F143" t="str">
         <v>Por peso</v>
@@ -3261,19 +3261,19 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>631361</v>
+        <v>631493</v>
       </c>
       <c r="B144" t="str">
-        <v>ARROLLADO HUASO CON AJI LC KG</v>
+        <v>JAMON AHUMADO G1 JH PF KILO</v>
       </c>
       <c r="C144" t="str">
         <v/>
       </c>
       <c r="D144" t="str">
-        <v>31361</v>
+        <v>31493</v>
       </c>
       <c r="E144" t="str">
-        <v>9996</v>
+        <v>12396</v>
       </c>
       <c r="F144" t="str">
         <v>Por peso</v>
@@ -3281,19 +3281,19 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>631243</v>
+        <v>631361</v>
       </c>
       <c r="B145" t="str">
-        <v>COPPA C A WINTER KG</v>
+        <v>ARROLLADO HUASO CON AJI LC KG</v>
       </c>
       <c r="C145" t="str">
         <v/>
       </c>
       <c r="D145" t="str">
-        <v>31243</v>
+        <v>31361</v>
       </c>
       <c r="E145" t="str">
-        <v>6996</v>
+        <v>9996</v>
       </c>
       <c r="F145" t="str">
         <v>Por peso</v>
@@ -3301,19 +3301,19 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>631264</v>
+        <v>631243</v>
       </c>
       <c r="B146" t="str">
-        <v>SALCHICHON CERV. AHUMADO KG.</v>
+        <v>COPPA C A WINTER KG</v>
       </c>
       <c r="C146" t="str">
         <v/>
       </c>
       <c r="D146" t="str">
-        <v>31264</v>
+        <v>31243</v>
       </c>
       <c r="E146" t="str">
-        <v>2159</v>
+        <v>6996</v>
       </c>
       <c r="F146" t="str">
         <v>Por peso</v>
@@ -3321,19 +3321,19 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>631122</v>
+        <v>631264</v>
       </c>
       <c r="B147" t="str">
-        <v>SALCHICHON CERV. S.JORGE KG</v>
+        <v>SALCHICHON CERV. AHUMADO KG.</v>
       </c>
       <c r="C147" t="str">
         <v/>
       </c>
       <c r="D147" t="str">
-        <v>31122</v>
+        <v>31264</v>
       </c>
       <c r="E147" t="str">
-        <v>6996</v>
+        <v>2159</v>
       </c>
       <c r="F147" t="str">
         <v>Por peso</v>
@@ -3341,19 +3341,19 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>631016</v>
+        <v>631122</v>
       </c>
       <c r="B148" t="str">
-        <v>PECHUGA DE PAVO AHUMADAPF KG.</v>
+        <v>SALCHICHON CERV. S.JORGE KG</v>
       </c>
       <c r="C148" t="str">
         <v/>
       </c>
       <c r="D148" t="str">
-        <v>31016</v>
+        <v>31122</v>
       </c>
       <c r="E148" t="str">
-        <v>14396</v>
+        <v>6996</v>
       </c>
       <c r="F148" t="str">
         <v>Por peso</v>
@@ -3361,19 +3361,19 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>631454</v>
+        <v>631016</v>
       </c>
       <c r="B149" t="str">
-        <v>PECHUGA PAVO COC.ARIZTIA 40303BF</v>
+        <v>PECHUGA DE PAVO AHUMADAPF KG.</v>
       </c>
       <c r="C149" t="str">
         <v/>
       </c>
       <c r="D149" t="str">
-        <v>31454</v>
+        <v>31016</v>
       </c>
       <c r="E149" t="str">
-        <v>13996</v>
+        <v>14396</v>
       </c>
       <c r="F149" t="str">
         <v>Por peso</v>
@@ -3381,19 +3381,19 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>631128</v>
+        <v>631454</v>
       </c>
       <c r="B150" t="str">
-        <v>PECHUGA AHUMADA SOPRAVAL KG</v>
+        <v>PECHUGA PAVO COC.ARIZTIA 40303BF</v>
       </c>
       <c r="C150" t="str">
         <v/>
       </c>
       <c r="D150" t="str">
-        <v>31128</v>
+        <v>31454</v>
       </c>
       <c r="E150" t="str">
-        <v>12996</v>
+        <v>13996</v>
       </c>
       <c r="F150" t="str">
         <v>Por peso</v>
@@ -3401,19 +3401,19 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>631464</v>
+        <v>631128</v>
       </c>
       <c r="B151" t="str">
-        <v>PATA RELLENA SUPER KG</v>
+        <v>PECHUGA AHUMADA SOPRAVAL KG</v>
       </c>
       <c r="C151" t="str">
         <v/>
       </c>
       <c r="D151" t="str">
-        <v>31464</v>
+        <v>31128</v>
       </c>
       <c r="E151" t="str">
-        <v>1239</v>
+        <v>12996</v>
       </c>
       <c r="F151" t="str">
         <v>Por peso</v>
@@ -3421,19 +3421,19 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>631409</v>
+        <v>631464</v>
       </c>
       <c r="B152" t="str">
-        <v>PECHUGA AHUM. ARIZTIA 5160</v>
+        <v>PATA RELLENA SUPER KG</v>
       </c>
       <c r="C152" t="str">
         <v/>
       </c>
       <c r="D152" t="str">
-        <v>31409</v>
+        <v>31464</v>
       </c>
       <c r="E152" t="str">
-        <v>3996</v>
+        <v>1239</v>
       </c>
       <c r="F152" t="str">
         <v>Por peso</v>
@@ -3441,19 +3441,19 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>631500</v>
+        <v>631409</v>
       </c>
       <c r="B153" t="str">
-        <v>ARROLLADO ARTESANAL R.ABUELO KG</v>
+        <v>PECHUGA AHUM. ARIZTIA 5160</v>
       </c>
       <c r="C153" t="str">
         <v/>
       </c>
       <c r="D153" t="str">
-        <v>31500</v>
+        <v>31409</v>
       </c>
       <c r="E153" t="str">
-        <v>11996</v>
+        <v>3996</v>
       </c>
       <c r="F153" t="str">
         <v>Por peso</v>
@@ -3461,19 +3461,19 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>631322</v>
+        <v>631500</v>
       </c>
       <c r="B154" t="str">
-        <v>JAMON AVE COCIDA FR PF KG</v>
+        <v>ARROLLADO ARTESANAL R.ABUELO KG</v>
       </c>
       <c r="C154" t="str">
         <v/>
       </c>
       <c r="D154" t="str">
-        <v>31322</v>
+        <v>31500</v>
       </c>
       <c r="E154" t="str">
-        <v>10996</v>
+        <v>11996</v>
       </c>
       <c r="F154" t="str">
         <v>Por peso</v>
@@ -3481,19 +3481,19 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>632722</v>
+        <v>631322</v>
       </c>
       <c r="B155" t="str">
-        <v>PECHUGA DE PAVO COCIDA PF KG</v>
+        <v>JAMON AVE COCIDA FR PF KG</v>
       </c>
       <c r="C155" t="str">
         <v/>
       </c>
       <c r="D155" t="str">
-        <v>32722</v>
+        <v>31322</v>
       </c>
       <c r="E155" t="str">
-        <v>14396</v>
+        <v>10996</v>
       </c>
       <c r="F155" t="str">
         <v>Por peso</v>
@@ -3501,39 +3501,39 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>632648</v>
+        <v>632722</v>
       </c>
       <c r="B156" t="str">
-        <v>M. LISA ARUNA MAZO</v>
+        <v>PECHUGA DE PAVO COCIDA PF KG</v>
       </c>
       <c r="C156" t="str">
         <v/>
       </c>
       <c r="D156" t="str">
-        <v>32648</v>
+        <v>32722</v>
       </c>
       <c r="E156" t="str">
-        <v>3890</v>
+        <v>14396</v>
       </c>
       <c r="F156" t="str">
-        <v>Por cantidad</v>
+        <v>Por peso</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>631099</v>
+        <v>632648</v>
       </c>
       <c r="B157" t="str">
-        <v>PIZZA DE MARISCOS FAMILIAR</v>
+        <v>M. LISA ARUNA MAZO</v>
       </c>
       <c r="C157" t="str">
         <v/>
       </c>
       <c r="D157" t="str">
-        <v>31099</v>
+        <v>32648</v>
       </c>
       <c r="E157" t="str">
-        <v>2490</v>
+        <v>3890</v>
       </c>
       <c r="F157" t="str">
         <v>Por cantidad</v>
@@ -3541,39 +3541,39 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>632790</v>
+        <v>631099</v>
       </c>
       <c r="B158" t="str">
-        <v>LONGANIZA KG HACIENDA DE NUBLE</v>
+        <v>PIZZA DE MARISCOS FAMILIAR</v>
       </c>
       <c r="C158" t="str">
         <v/>
       </c>
       <c r="D158" t="str">
-        <v>32790</v>
+        <v>31099</v>
       </c>
       <c r="E158" t="str">
-        <v>2990</v>
+        <v>2490</v>
       </c>
       <c r="F158" t="str">
-        <v>Por peso</v>
+        <v>Por cantidad</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>632660</v>
+        <v>632790</v>
       </c>
       <c r="B159" t="str">
-        <v>SALAME AHUMADO CORTE PF 3F</v>
+        <v>LONGANIZA KG HACIENDA DE NUBLE</v>
       </c>
       <c r="C159" t="str">
         <v/>
       </c>
       <c r="D159" t="str">
-        <v>32660</v>
+        <v>32790</v>
       </c>
       <c r="E159" t="str">
-        <v>13996</v>
+        <v>2990</v>
       </c>
       <c r="F159" t="str">
         <v>Por peso</v>
@@ -3581,16 +3581,16 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>632661</v>
+        <v>632660</v>
       </c>
       <c r="B160" t="str">
-        <v>SALAME ITALIANO CORTPF 3E</v>
+        <v>SALAME AHUMADO CORTE PF 3F</v>
       </c>
       <c r="C160" t="str">
         <v/>
       </c>
       <c r="D160" t="str">
-        <v>32661</v>
+        <v>32660</v>
       </c>
       <c r="E160" t="str">
         <v>13996</v>
@@ -3601,16 +3601,16 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>632659</v>
+        <v>632661</v>
       </c>
       <c r="B161" t="str">
-        <v>JAMON ARTESANAL G1 RDA A9 KG</v>
+        <v>SALAME ITALIANO CORTPF 3E</v>
       </c>
       <c r="C161" t="str">
         <v/>
       </c>
       <c r="D161" t="str">
-        <v>32659</v>
+        <v>32661</v>
       </c>
       <c r="E161" t="str">
         <v>13996</v>
@@ -3621,19 +3621,19 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>631134</v>
+        <v>632659</v>
       </c>
       <c r="B162" t="str">
-        <v>PECHUGA ASADA POLLO SUPER KG</v>
+        <v>JAMON ARTESANAL G1 RDA A9 KG</v>
       </c>
       <c r="C162" t="str">
         <v/>
       </c>
       <c r="D162" t="str">
-        <v>31134</v>
+        <v>32659</v>
       </c>
       <c r="E162" t="str">
-        <v>10996</v>
+        <v>13996</v>
       </c>
       <c r="F162" t="str">
         <v>Por peso</v>
@@ -3641,19 +3641,19 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>632397</v>
+        <v>631134</v>
       </c>
       <c r="B163" t="str">
-        <v>ARROLLADO HUASO FASTD.(334)KG.</v>
+        <v>PECHUGA ASADA POLLO SUPER KG</v>
       </c>
       <c r="C163" t="str">
         <v/>
       </c>
       <c r="D163" t="str">
-        <v>32397</v>
+        <v>31134</v>
       </c>
       <c r="E163" t="str">
-        <v>2876</v>
+        <v>10996</v>
       </c>
       <c r="F163" t="str">
         <v>Por peso</v>
@@ -3661,19 +3661,19 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>631188</v>
+        <v>632397</v>
       </c>
       <c r="B164" t="str">
-        <v>PECHUGA PAVO ASADA ARIZTIA KG 40036BF</v>
+        <v>ARROLLADO HUASO FASTD.(334)KG.</v>
       </c>
       <c r="C164" t="str">
         <v/>
       </c>
       <c r="D164" t="str">
-        <v>31188</v>
+        <v>32397</v>
       </c>
       <c r="E164" t="str">
-        <v>13996</v>
+        <v>2876</v>
       </c>
       <c r="F164" t="str">
         <v>Por peso</v>
@@ -3681,19 +3681,19 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>631184</v>
+        <v>631188</v>
       </c>
       <c r="B165" t="str">
-        <v>PATA RELLENA CATALANA KG</v>
+        <v>PECHUGA PAVO ASADA ARIZTIA KG 40036BF</v>
       </c>
       <c r="C165" t="str">
         <v/>
       </c>
       <c r="D165" t="str">
-        <v>31184</v>
+        <v>31188</v>
       </c>
       <c r="E165" t="str">
-        <v>2996</v>
+        <v>13996</v>
       </c>
       <c r="F165" t="str">
         <v>Por peso</v>
@@ -3701,19 +3701,19 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>631594</v>
+        <v>631184</v>
       </c>
       <c r="B166" t="str">
-        <v>SALAME KIDS CATALANA KG</v>
+        <v>PATA RELLENA CATALANA KG</v>
       </c>
       <c r="C166" t="str">
         <v/>
       </c>
       <c r="D166" t="str">
-        <v>31594</v>
+        <v>31184</v>
       </c>
       <c r="E166" t="str">
-        <v>3880</v>
+        <v>2996</v>
       </c>
       <c r="F166" t="str">
         <v>Por peso</v>
@@ -3721,19 +3721,19 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>631187</v>
+        <v>631594</v>
       </c>
       <c r="B167" t="str">
-        <v>SALCHICHON CAMPING CATALANA KG</v>
+        <v>SALAME KIDS CATALANA KG</v>
       </c>
       <c r="C167" t="str">
         <v/>
       </c>
       <c r="D167" t="str">
-        <v>31187</v>
+        <v>31594</v>
       </c>
       <c r="E167" t="str">
-        <v>1876</v>
+        <v>3880</v>
       </c>
       <c r="F167" t="str">
         <v>Por peso</v>
@@ -3741,19 +3741,19 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>631183</v>
+        <v>631187</v>
       </c>
       <c r="B168" t="str">
-        <v>MILANESA CATALANA KG</v>
+        <v>SALCHICHON CAMPING CATALANA KG</v>
       </c>
       <c r="C168" t="str">
         <v/>
       </c>
       <c r="D168" t="str">
-        <v>31183</v>
+        <v>31187</v>
       </c>
       <c r="E168" t="str">
-        <v>2796</v>
+        <v>1876</v>
       </c>
       <c r="F168" t="str">
         <v>Por peso</v>
@@ -3761,19 +3761,19 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>632456</v>
+        <v>631183</v>
       </c>
       <c r="B169" t="str">
-        <v>LONGANIZA ARTESANAL KG ARUNA</v>
+        <v>MILANESA CATALANA KG</v>
       </c>
       <c r="C169" t="str">
         <v/>
       </c>
       <c r="D169" t="str">
-        <v>42456</v>
+        <v>31183</v>
       </c>
       <c r="E169" t="str">
-        <v>2490</v>
+        <v>2796</v>
       </c>
       <c r="F169" t="str">
         <v>Por peso</v>
@@ -3781,19 +3781,19 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>631427</v>
+        <v>632456</v>
       </c>
       <c r="B170" t="str">
-        <v>TOCINO MONTS KG</v>
+        <v>LONGANIZA ARTESANAL KG ARUNA</v>
       </c>
       <c r="C170" t="str">
         <v/>
       </c>
       <c r="D170" t="str">
-        <v>31427</v>
+        <v>42456</v>
       </c>
       <c r="E170" t="str">
-        <v>10760</v>
+        <v>2490</v>
       </c>
       <c r="F170" t="str">
         <v>Por peso</v>
@@ -3801,19 +3801,19 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>631124</v>
+        <v>631427</v>
       </c>
       <c r="B171" t="str">
-        <v>JAMON ARTESANAL G2 PF EB</v>
+        <v>TOCINO MONTS KG</v>
       </c>
       <c r="C171" t="str">
         <v/>
       </c>
       <c r="D171" t="str">
-        <v>31124</v>
+        <v>31427</v>
       </c>
       <c r="E171" t="str">
-        <v>9996</v>
+        <v>10760</v>
       </c>
       <c r="F171" t="str">
         <v>Por peso</v>
@@ -3821,19 +3821,19 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>633229</v>
+        <v>631124</v>
       </c>
       <c r="B172" t="str">
-        <v>ACEITUNA AZAPA SEGUNDA CUGAT</v>
+        <v>JAMON ARTESANAL G2 PF EB</v>
       </c>
       <c r="C172" t="str">
         <v/>
       </c>
       <c r="D172" t="str">
-        <v>33229</v>
+        <v>31124</v>
       </c>
       <c r="E172" t="str">
-        <v>2796</v>
+        <v>9996</v>
       </c>
       <c r="F172" t="str">
         <v>Por peso</v>
@@ -3841,19 +3841,19 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>631781</v>
+        <v>633229</v>
       </c>
       <c r="B173" t="str">
-        <v>ACEITUNA AZAPA KILO</v>
+        <v>ACEITUNA AZAPA SEGUNDA CUGAT</v>
       </c>
       <c r="C173" t="str">
         <v/>
       </c>
       <c r="D173" t="str">
-        <v>31781</v>
+        <v>33229</v>
       </c>
       <c r="E173" t="str">
-        <v>8396</v>
+        <v>2796</v>
       </c>
       <c r="F173" t="str">
         <v>Por peso</v>
@@ -3861,19 +3861,19 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>631786</v>
+        <v>631781</v>
       </c>
       <c r="B174" t="str">
-        <v>PICKLE KILO</v>
+        <v>ACEITUNA AZAPA KILO</v>
       </c>
       <c r="C174" t="str">
         <v/>
       </c>
       <c r="D174" t="str">
-        <v>31786</v>
+        <v>31781</v>
       </c>
       <c r="E174" t="str">
-        <v>5396</v>
+        <v>8396</v>
       </c>
       <c r="F174" t="str">
         <v>Por peso</v>
@@ -3881,19 +3881,19 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>631787</v>
+        <v>631786</v>
       </c>
       <c r="B175" t="str">
-        <v>SALSA AMERICANA KILO</v>
+        <v>PICKLE KILO</v>
       </c>
       <c r="C175" t="str">
         <v/>
       </c>
       <c r="D175" t="str">
-        <v>31787</v>
+        <v>31786</v>
       </c>
       <c r="E175" t="str">
-        <v>2996</v>
+        <v>5396</v>
       </c>
       <c r="F175" t="str">
         <v>Por peso</v>
@@ -3901,19 +3901,19 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>631784</v>
+        <v>631787</v>
       </c>
       <c r="B176" t="str">
-        <v>CEBOLLA EN ESCABECHE·</v>
+        <v>SALSA AMERICANA KILO</v>
       </c>
       <c r="C176" t="str">
         <v/>
       </c>
       <c r="D176" t="str">
-        <v>31784</v>
+        <v>31787</v>
       </c>
       <c r="E176" t="str">
-        <v>5996</v>
+        <v>2996</v>
       </c>
       <c r="F176" t="str">
         <v>Por peso</v>
@@ -3921,19 +3921,19 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>631777</v>
+        <v>631784</v>
       </c>
       <c r="B177" t="str">
-        <v>JAMON COLONIAL AHUMADO</v>
+        <v>CEBOLLA EN ESCABECHE·</v>
       </c>
       <c r="C177" t="str">
         <v/>
       </c>
       <c r="D177" t="str">
-        <v>31777</v>
+        <v>31784</v>
       </c>
       <c r="E177" t="str">
-        <v>6760</v>
+        <v>5996</v>
       </c>
       <c r="F177" t="str">
         <v>Por peso</v>
@@ -3941,19 +3941,19 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>631775</v>
+        <v>631777</v>
       </c>
       <c r="B178" t="str">
-        <v>LONGANIZA CHILENA KG BIELEFELDT</v>
+        <v>JAMON COLONIAL AHUMADO</v>
       </c>
       <c r="C178" t="str">
         <v/>
       </c>
       <c r="D178" t="str">
-        <v>31775</v>
+        <v>31777</v>
       </c>
       <c r="E178" t="str">
-        <v>2199</v>
+        <v>6760</v>
       </c>
       <c r="F178" t="str">
         <v>Por peso</v>
@@ -3961,19 +3961,19 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>631774</v>
+        <v>631775</v>
       </c>
       <c r="B179" t="str">
-        <v>LONGANIZA CASERA KG BIELEFELDT</v>
+        <v>LONGANIZA CHILENA KG BIELEFELDT</v>
       </c>
       <c r="C179" t="str">
         <v/>
       </c>
       <c r="D179" t="str">
-        <v>31774</v>
+        <v>31775</v>
       </c>
       <c r="E179" t="str">
-        <v>3199</v>
+        <v>2199</v>
       </c>
       <c r="F179" t="str">
         <v>Por peso</v>
@@ -3981,19 +3981,19 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>631773</v>
+        <v>631774</v>
       </c>
       <c r="B180" t="str">
-        <v>ARROLLADO BIELEFELDT</v>
+        <v>LONGANIZA CASERA KG BIELEFELDT</v>
       </c>
       <c r="C180" t="str">
         <v/>
       </c>
       <c r="D180" t="str">
-        <v>31773</v>
+        <v>31774</v>
       </c>
       <c r="E180" t="str">
-        <v>4390</v>
+        <v>3199</v>
       </c>
       <c r="F180" t="str">
         <v>Por peso</v>
@@ -4001,19 +4001,19 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>631776</v>
+        <v>631773</v>
       </c>
       <c r="B181" t="str">
-        <v>QUESO CHANCHO BIELEFELDT</v>
+        <v>ARROLLADO BIELEFELDT</v>
       </c>
       <c r="C181" t="str">
         <v/>
       </c>
       <c r="D181" t="str">
-        <v>31776</v>
+        <v>31773</v>
       </c>
       <c r="E181" t="str">
-        <v>3199</v>
+        <v>4390</v>
       </c>
       <c r="F181" t="str">
         <v>Por peso</v>
@@ -4021,19 +4021,19 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>631689</v>
+        <v>631776</v>
       </c>
       <c r="B182" t="str">
-        <v>QUESO DE CERDO PITRUFQUEN</v>
+        <v>QUESO CHANCHO BIELEFELDT</v>
       </c>
       <c r="C182" t="str">
         <v/>
       </c>
       <c r="D182" t="str">
-        <v>31689</v>
+        <v>31776</v>
       </c>
       <c r="E182" t="str">
-        <v>10196</v>
+        <v>3199</v>
       </c>
       <c r="F182" t="str">
         <v>Por peso</v>
@@ -4041,19 +4041,19 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>631686</v>
+        <v>631689</v>
       </c>
       <c r="B183" t="str">
-        <v>ARROLLADO HUASO PITRUFQUEN</v>
+        <v>QUESO DE CERDO PITRUFQUEN</v>
       </c>
       <c r="C183" t="str">
         <v/>
       </c>
       <c r="D183" t="str">
-        <v>31686</v>
+        <v>31689</v>
       </c>
       <c r="E183" t="str">
-        <v>12996</v>
+        <v>10196</v>
       </c>
       <c r="F183" t="str">
         <v>Por peso</v>
@@ -4061,19 +4061,19 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>631687</v>
+        <v>631686</v>
       </c>
       <c r="B184" t="str">
-        <v>LONGANIZA KG PITRUFQUEN</v>
+        <v>ARROLLADO HUASO PITRUFQUEN</v>
       </c>
       <c r="C184" t="str">
         <v/>
       </c>
       <c r="D184" t="str">
-        <v>31687</v>
+        <v>31686</v>
       </c>
       <c r="E184" t="str">
-        <v>9596</v>
+        <v>12996</v>
       </c>
       <c r="F184" t="str">
         <v>Por peso</v>
@@ -4081,19 +4081,19 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>631688</v>
+        <v>631687</v>
       </c>
       <c r="B185" t="str">
-        <v>PATE DE CERDO PITRUFQUEN</v>
+        <v>LONGANIZA KG PITRUFQUEN</v>
       </c>
       <c r="C185" t="str">
         <v/>
       </c>
       <c r="D185" t="str">
-        <v>31688</v>
+        <v>31687</v>
       </c>
       <c r="E185" t="str">
-        <v>9696</v>
+        <v>9596</v>
       </c>
       <c r="F185" t="str">
         <v>Por peso</v>
@@ -4101,19 +4101,19 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>633668</v>
+        <v>631688</v>
       </c>
       <c r="B186" t="str">
-        <v>JAMON PIERNA PAVO AHUM ARIZTIA KG</v>
+        <v>PATE DE CERDO PITRUFQUEN</v>
       </c>
       <c r="C186" t="str">
         <v/>
       </c>
       <c r="D186" t="str">
-        <v>33668</v>
+        <v>31688</v>
       </c>
       <c r="E186" t="str">
-        <v>11996</v>
+        <v>9696</v>
       </c>
       <c r="F186" t="str">
         <v>Por peso</v>
@@ -4121,19 +4121,19 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>633445</v>
+        <v>633668</v>
       </c>
       <c r="B187" t="str">
-        <v>ACEITUNA AZAPA PRIMERA CUGAT</v>
+        <v>JAMON PIERNA PAVO AHUM ARIZTIA KG</v>
       </c>
       <c r="C187" t="str">
         <v/>
       </c>
       <c r="D187" t="str">
-        <v>33445</v>
+        <v>33668</v>
       </c>
       <c r="E187" t="str">
-        <v>2996</v>
+        <v>11996</v>
       </c>
       <c r="F187" t="str">
         <v>Por peso</v>
@@ -4141,19 +4141,19 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>633660</v>
+        <v>633445</v>
       </c>
       <c r="B188" t="str">
-        <v>ACEITUNA CUGAT RELLENA ROCOTO</v>
+        <v>ACEITUNA AZAPA PRIMERA CUGAT</v>
       </c>
       <c r="C188" t="str">
         <v/>
       </c>
       <c r="D188" t="str">
-        <v>33660</v>
+        <v>33445</v>
       </c>
       <c r="E188" t="str">
-        <v>3916</v>
+        <v>2996</v>
       </c>
       <c r="F188" t="str">
         <v>Por peso</v>
@@ -4161,19 +4161,19 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>633663</v>
+        <v>633660</v>
       </c>
       <c r="B189" t="str">
-        <v>ACEITUNA CUGAT RELLENA ALMENDRA</v>
+        <v>ACEITUNA CUGAT RELLENA ROCOTO</v>
       </c>
       <c r="C189" t="str">
         <v/>
       </c>
       <c r="D189" t="str">
-        <v>33663</v>
+        <v>33660</v>
       </c>
       <c r="E189" t="str">
-        <v>3960</v>
+        <v>3916</v>
       </c>
       <c r="F189" t="str">
         <v>Por peso</v>
@@ -4181,19 +4181,19 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>631879</v>
+        <v>633663</v>
       </c>
       <c r="B190" t="str">
-        <v>ACEITUNA NEGRA 100/120 PRIMERA AMARGA</v>
+        <v>ACEITUNA CUGAT RELLENA ALMENDRA</v>
       </c>
       <c r="C190" t="str">
         <v/>
       </c>
       <c r="D190" t="str">
-        <v>31879</v>
+        <v>33663</v>
       </c>
       <c r="E190" t="str">
-        <v>4796</v>
+        <v>3960</v>
       </c>
       <c r="F190" t="str">
         <v>Por peso</v>
@@ -4201,19 +4201,19 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>631880</v>
+        <v>631879</v>
       </c>
       <c r="B191" t="str">
-        <v>ACEITUNA SEVILLANA 90/100 EXTRA GRANEL</v>
+        <v>ACEITUNA NEGRA 100/120 PRIMERA AMARGA</v>
       </c>
       <c r="C191" t="str">
         <v/>
       </c>
       <c r="D191" t="str">
-        <v>31880</v>
+        <v>31879</v>
       </c>
       <c r="E191" t="str">
-        <v>3996</v>
+        <v>4796</v>
       </c>
       <c r="F191" t="str">
         <v>Por peso</v>
@@ -4221,19 +4221,19 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>631897</v>
+        <v>631880</v>
       </c>
       <c r="B192" t="str">
-        <v>LONGANIZA CASERA KG SAN FELIPE</v>
+        <v>ACEITUNA SEVILLANA 90/100 EXTRA GRANEL</v>
       </c>
       <c r="C192" t="str">
         <v/>
       </c>
       <c r="D192" t="str">
-        <v>31897</v>
+        <v>31880</v>
       </c>
       <c r="E192" t="str">
-        <v>3596</v>
+        <v>3996</v>
       </c>
       <c r="F192" t="str">
         <v>Por peso</v>
@@ -4241,16 +4241,16 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>631587</v>
+        <v>631897</v>
       </c>
       <c r="B193" t="str">
-        <v>CHORIZO ESPECIAL SAN FELIPE KG</v>
+        <v>LONGANIZA CASERA KG SAN FELIPE</v>
       </c>
       <c r="C193" t="str">
         <v/>
       </c>
       <c r="D193" t="str">
-        <v>31587</v>
+        <v>31897</v>
       </c>
       <c r="E193" t="str">
         <v>3596</v>
@@ -4261,19 +4261,19 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>631568</v>
+        <v>631587</v>
       </c>
       <c r="B194" t="str">
-        <v>QUESO CABEZA WINTER KG</v>
+        <v>CHORIZO ESPECIAL SAN FELIPE KG</v>
       </c>
       <c r="C194" t="str">
         <v/>
       </c>
       <c r="D194" t="str">
-        <v>31568</v>
+        <v>31587</v>
       </c>
       <c r="E194" t="str">
-        <v>6196</v>
+        <v>3596</v>
       </c>
       <c r="F194" t="str">
         <v>Por peso</v>
@@ -4281,19 +4281,19 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>631635</v>
+        <v>631568</v>
       </c>
       <c r="B195" t="str">
-        <v>PATE CERDO HICAR KG SN FELIPE</v>
+        <v>QUESO CABEZA WINTER KG</v>
       </c>
       <c r="C195" t="str">
         <v/>
       </c>
       <c r="D195" t="str">
-        <v>31635</v>
+        <v>31568</v>
       </c>
       <c r="E195" t="str">
-        <v>3996</v>
+        <v>6196</v>
       </c>
       <c r="F195" t="str">
         <v>Por peso</v>
@@ -4301,19 +4301,19 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>631898</v>
+        <v>631635</v>
       </c>
       <c r="B196" t="str">
-        <v>AJI ORO KILO LAS LOMAS</v>
+        <v>PATE CERDO HICAR KG SN FELIPE</v>
       </c>
       <c r="C196" t="str">
         <v/>
       </c>
       <c r="D196" t="str">
-        <v>31898</v>
+        <v>31635</v>
       </c>
       <c r="E196" t="str">
-        <v>4360</v>
+        <v>3996</v>
       </c>
       <c r="F196" t="str">
         <v>Por peso</v>
@@ -4321,19 +4321,19 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>631896</v>
+        <v>631898</v>
       </c>
       <c r="B197" t="str">
-        <v>ACEITUNA HUASCO SEGUNDA</v>
+        <v>AJI ORO KILO LAS LOMAS</v>
       </c>
       <c r="C197" t="str">
         <v/>
       </c>
       <c r="D197" t="str">
-        <v>31896</v>
+        <v>31898</v>
       </c>
       <c r="E197" t="str">
-        <v>3596</v>
+        <v>4360</v>
       </c>
       <c r="F197" t="str">
         <v>Por peso</v>
@@ -4341,19 +4341,19 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>631895</v>
+        <v>631896</v>
       </c>
       <c r="B198" t="str">
-        <v>ACEITUNA NEGRA 90/100 EXTRA AMARGA</v>
+        <v>ACEITUNA HUASCO SEGUNDA</v>
       </c>
       <c r="C198" t="str">
         <v/>
       </c>
       <c r="D198" t="str">
-        <v>31895</v>
+        <v>31896</v>
       </c>
       <c r="E198" t="str">
-        <v>3996</v>
+        <v>3596</v>
       </c>
       <c r="F198" t="str">
         <v>Por peso</v>
@@ -4361,19 +4361,19 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>631894</v>
+        <v>631895</v>
       </c>
       <c r="B199" t="str">
-        <v>PEPINO DILL CORNICHON KILOS LAS LOMAS</v>
+        <v>ACEITUNA NEGRA 90/100 EXTRA AMARGA</v>
       </c>
       <c r="C199" t="str">
         <v/>
       </c>
       <c r="D199" t="str">
-        <v>31894</v>
+        <v>31895</v>
       </c>
       <c r="E199" t="str">
-        <v>5596</v>
+        <v>3996</v>
       </c>
       <c r="F199" t="str">
         <v>Por peso</v>
@@ -4381,19 +4381,19 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>631893</v>
+        <v>631894</v>
       </c>
       <c r="B200" t="str">
-        <v>PEPINO DILL MEDIANO KILO LAS LOMAS</v>
+        <v>PEPINO DILL CORNICHON KILOS LAS LOMAS</v>
       </c>
       <c r="C200" t="str">
         <v/>
       </c>
       <c r="D200" t="str">
-        <v>31893</v>
+        <v>31894</v>
       </c>
       <c r="E200" t="str">
-        <v>5160</v>
+        <v>5596</v>
       </c>
       <c r="F200" t="str">
         <v>Por peso</v>
@@ -4401,19 +4401,19 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>631892</v>
+        <v>631893</v>
       </c>
       <c r="B201" t="str">
-        <v>PICKLES FINO KILO LAS LOMAS</v>
+        <v>PEPINO DILL MEDIANO KILO LAS LOMAS</v>
       </c>
       <c r="C201" t="str">
         <v/>
       </c>
       <c r="D201" t="str">
-        <v>31892</v>
+        <v>31893</v>
       </c>
       <c r="E201" t="str">
-        <v>3160</v>
+        <v>5160</v>
       </c>
       <c r="F201" t="str">
         <v>Por peso</v>
@@ -4421,19 +4421,19 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>631267</v>
+        <v>631892</v>
       </c>
       <c r="B202" t="str">
-        <v>LONGANIZA KG SCHWENCKE</v>
+        <v>PICKLES FINO KILO LAS LOMAS</v>
       </c>
       <c r="C202" t="str">
         <v/>
       </c>
       <c r="D202" t="str">
-        <v>31267</v>
+        <v>31892</v>
       </c>
       <c r="E202" t="str">
-        <v>10396</v>
+        <v>3160</v>
       </c>
       <c r="F202" t="str">
         <v>Por peso</v>
@@ -4441,19 +4441,19 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>631266</v>
+        <v>631267</v>
       </c>
       <c r="B203" t="str">
-        <v>LONGANIZA ESPECIAL KG DON MATIAS</v>
+        <v>LONGANIZA KG SCHWENCKE</v>
       </c>
       <c r="C203" t="str">
         <v/>
       </c>
       <c r="D203" t="str">
-        <v>31266</v>
+        <v>31267</v>
       </c>
       <c r="E203" t="str">
-        <v>8396</v>
+        <v>10396</v>
       </c>
       <c r="F203" t="str">
         <v>Por peso</v>
@@ -4461,19 +4461,19 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>631269</v>
+        <v>631266</v>
       </c>
       <c r="B204" t="str">
-        <v>QUESO CABEZA KG SCHWENCKE</v>
+        <v>LONGANIZA ESPECIAL KG DON MATIAS</v>
       </c>
       <c r="C204" t="str">
         <v/>
       </c>
       <c r="D204" t="str">
-        <v>31269</v>
+        <v>31266</v>
       </c>
       <c r="E204" t="str">
-        <v>11596</v>
+        <v>8396</v>
       </c>
       <c r="F204" t="str">
         <v>Por peso</v>
@@ -4481,19 +4481,19 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>631274</v>
+        <v>631269</v>
       </c>
       <c r="B205" t="str">
-        <v>MORTAD. LISA SCHWENCKE KG</v>
+        <v>QUESO CABEZA KG SCHWENCKE</v>
       </c>
       <c r="C205" t="str">
         <v/>
       </c>
       <c r="D205" t="str">
-        <v>31274</v>
+        <v>31269</v>
       </c>
       <c r="E205" t="str">
-        <v>9196</v>
+        <v>11596</v>
       </c>
       <c r="F205" t="str">
         <v>Por peso</v>
@@ -4501,19 +4501,19 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>631072</v>
+        <v>631274</v>
       </c>
       <c r="B206" t="str">
-        <v>MORTAD. JAMONADA SCHWENCKE KG</v>
+        <v>MORTAD. LISA SCHWENCKE KG</v>
       </c>
       <c r="C206" t="str">
         <v/>
       </c>
       <c r="D206" t="str">
-        <v>31072</v>
+        <v>31274</v>
       </c>
       <c r="E206" t="str">
-        <v>9996</v>
+        <v>9196</v>
       </c>
       <c r="F206" t="str">
         <v>Por peso</v>
@@ -4521,19 +4521,19 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>631301</v>
+        <v>631072</v>
       </c>
       <c r="B207" t="str">
-        <v>MORTAD. LISA PACEL KG</v>
+        <v>MORTAD. JAMONADA SCHWENCKE KG</v>
       </c>
       <c r="C207" t="str">
         <v/>
       </c>
       <c r="D207" t="str">
-        <v>31301</v>
+        <v>31072</v>
       </c>
       <c r="E207" t="str">
-        <v>10996</v>
+        <v>9996</v>
       </c>
       <c r="F207" t="str">
         <v>Por peso</v>
@@ -4541,19 +4541,19 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>631302</v>
+        <v>631301</v>
       </c>
       <c r="B208" t="str">
-        <v>MORTAD. JAMONADA PACEL KG</v>
+        <v>MORTAD. LISA PACEL KG</v>
       </c>
       <c r="C208" t="str">
         <v/>
       </c>
       <c r="D208" t="str">
-        <v>31302</v>
+        <v>31301</v>
       </c>
       <c r="E208" t="str">
-        <v>11996</v>
+        <v>10996</v>
       </c>
       <c r="F208" t="str">
         <v>Por peso</v>
@@ -4561,19 +4561,19 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>631303</v>
+        <v>631302</v>
       </c>
       <c r="B209" t="str">
-        <v>MORTAD. ALEMANA PACEL KG.</v>
+        <v>MORTAD. JAMONADA PACEL KG</v>
       </c>
       <c r="C209" t="str">
         <v/>
       </c>
       <c r="D209" t="str">
-        <v>31303</v>
+        <v>31302</v>
       </c>
       <c r="E209" t="str">
-        <v>10996</v>
+        <v>11996</v>
       </c>
       <c r="F209" t="str">
         <v>Por peso</v>
@@ -4581,19 +4581,19 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>631306</v>
+        <v>631303</v>
       </c>
       <c r="B210" t="str">
-        <v>LONGANIZA ARTESANAL PACEL KG</v>
+        <v>MORTAD. ALEMANA PACEL KG.</v>
       </c>
       <c r="C210" t="str">
         <v/>
       </c>
       <c r="D210" t="str">
-        <v>31306</v>
+        <v>31303</v>
       </c>
       <c r="E210" t="str">
-        <v>12996</v>
+        <v>10996</v>
       </c>
       <c r="F210" t="str">
         <v>Por peso</v>
@@ -4601,19 +4601,19 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>631307</v>
+        <v>631306</v>
       </c>
       <c r="B211" t="str">
-        <v>PRIETA PACEL KG</v>
+        <v>LONGANIZA ARTESANAL PACEL KG</v>
       </c>
       <c r="C211" t="str">
         <v/>
       </c>
       <c r="D211" t="str">
-        <v>31307</v>
+        <v>31306</v>
       </c>
       <c r="E211" t="str">
-        <v>9996</v>
+        <v>12996</v>
       </c>
       <c r="F211" t="str">
         <v>Por peso</v>
@@ -4621,19 +4621,19 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>631308</v>
+        <v>631307</v>
       </c>
       <c r="B212" t="str">
-        <v>ARROLLADO HUASO PACEL KG.</v>
+        <v>PRIETA PACEL KG</v>
       </c>
       <c r="C212" t="str">
         <v/>
       </c>
       <c r="D212" t="str">
-        <v>31308</v>
+        <v>31307</v>
       </c>
       <c r="E212" t="str">
-        <v>14996</v>
+        <v>9996</v>
       </c>
       <c r="F212" t="str">
         <v>Por peso</v>
@@ -4641,19 +4641,19 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>632890</v>
+        <v>631308</v>
       </c>
       <c r="B213" t="str">
-        <v>JAMON COLONIAL G1 PF KG</v>
+        <v>ARROLLADO HUASO PACEL KG.</v>
       </c>
       <c r="C213" t="str">
         <v/>
       </c>
       <c r="D213" t="str">
-        <v>32890</v>
+        <v>31308</v>
       </c>
       <c r="E213" t="str">
-        <v>11996</v>
+        <v>14996</v>
       </c>
       <c r="F213" t="str">
         <v>Por peso</v>
@@ -4661,19 +4661,19 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>631990</v>
+        <v>632890</v>
       </c>
       <c r="B214" t="str">
-        <v>ACEITUNA AZAPA SUPER·90-100 KG</v>
+        <v>JAMON COLONIAL G1 PF KG</v>
       </c>
       <c r="C214" t="str">
         <v/>
       </c>
       <c r="D214" t="str">
-        <v>31990</v>
+        <v>32890</v>
       </c>
       <c r="E214" t="str">
-        <v>6396</v>
+        <v>11996</v>
       </c>
       <c r="F214" t="str">
         <v>Por peso</v>
@@ -4681,19 +4681,19 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>631904</v>
+        <v>631990</v>
       </c>
       <c r="B215" t="str">
-        <v>COSTILLAR AHUMADO PACEL KG</v>
+        <v>ACEITUNA AZAPA SUPER·90-100 KG</v>
       </c>
       <c r="C215" t="str">
         <v/>
       </c>
       <c r="D215" t="str">
-        <v>31904</v>
+        <v>31990</v>
       </c>
       <c r="E215" t="str">
-        <v>16996</v>
+        <v>6396</v>
       </c>
       <c r="F215" t="str">
         <v>Por peso</v>
@@ -4701,19 +4701,19 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>631340</v>
+        <v>631904</v>
       </c>
       <c r="B216" t="str">
-        <v>PICKLE ESPECIAL FINO KG. SOLIS</v>
+        <v>COSTILLAR AHUMADO PACEL KG</v>
       </c>
       <c r="C216" t="str">
         <v/>
       </c>
       <c r="D216" t="str">
-        <v>31340</v>
+        <v>31904</v>
       </c>
       <c r="E216" t="str">
-        <v>4396</v>
+        <v>16996</v>
       </c>
       <c r="F216" t="str">
         <v>Por peso</v>
@@ -4721,19 +4721,19 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>631341</v>
+        <v>631340</v>
       </c>
       <c r="B217" t="str">
-        <v>CEBOLLA ESCABECHE KG. SOLIS</v>
+        <v>PICKLE ESPECIAL FINO KG. SOLIS</v>
       </c>
       <c r="C217" t="str">
         <v/>
       </c>
       <c r="D217" t="str">
-        <v>31341</v>
+        <v>31340</v>
       </c>
       <c r="E217" t="str">
-        <v>3996</v>
+        <v>4396</v>
       </c>
       <c r="F217" t="str">
         <v>Por peso</v>
@@ -4741,19 +4741,19 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>631342</v>
+        <v>631341</v>
       </c>
       <c r="B218" t="str">
-        <v>CEBOLLA PERLA KG. SOLIS</v>
+        <v>CEBOLLA ESCABECHE KG. SOLIS</v>
       </c>
       <c r="C218" t="str">
         <v/>
       </c>
       <c r="D218" t="str">
-        <v>31342</v>
+        <v>31341</v>
       </c>
       <c r="E218" t="str">
-        <v>4690</v>
+        <v>3996</v>
       </c>
       <c r="F218" t="str">
         <v>Por peso</v>
@@ -4761,19 +4761,19 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>631343</v>
+        <v>631342</v>
       </c>
       <c r="B219" t="str">
-        <v>AJI ORO KG. SOLIS</v>
+        <v>CEBOLLA PERLA KG. SOLIS</v>
       </c>
       <c r="C219" t="str">
         <v/>
       </c>
       <c r="D219" t="str">
-        <v>31343</v>
+        <v>31342</v>
       </c>
       <c r="E219" t="str">
-        <v>4396</v>
+        <v>4690</v>
       </c>
       <c r="F219" t="str">
         <v>Por peso</v>
@@ -4781,19 +4781,19 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>631344</v>
+        <v>631343</v>
       </c>
       <c r="B220" t="str">
-        <v>PEPINILLO DILL KG. SOLIS</v>
+        <v>AJI ORO KG. SOLIS</v>
       </c>
       <c r="C220" t="str">
         <v/>
       </c>
       <c r="D220" t="str">
-        <v>31344</v>
+        <v>31343</v>
       </c>
       <c r="E220" t="str">
-        <v>4696</v>
+        <v>4396</v>
       </c>
       <c r="F220" t="str">
         <v>Por peso</v>
@@ -4801,16 +4801,16 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>631346</v>
+        <v>631344</v>
       </c>
       <c r="B221" t="str">
-        <v>PEPINO FINO CHICO KG SOLIS</v>
+        <v>PEPINILLO DILL KG. SOLIS</v>
       </c>
       <c r="C221" t="str">
         <v/>
       </c>
       <c r="D221" t="str">
-        <v>31346</v>
+        <v>31344</v>
       </c>
       <c r="E221" t="str">
         <v>4696</v>
@@ -4821,19 +4821,19 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>631350</v>
+        <v>631346</v>
       </c>
       <c r="B222" t="str">
-        <v>AMERICANAKG. SOLIS</v>
+        <v>PEPINO FINO CHICO KG SOLIS</v>
       </c>
       <c r="C222" t="str">
         <v/>
       </c>
       <c r="D222" t="str">
-        <v>31350</v>
+        <v>31346</v>
       </c>
       <c r="E222" t="str">
-        <v>2996</v>
+        <v>4696</v>
       </c>
       <c r="F222" t="str">
         <v>Por peso</v>
@@ -4841,19 +4841,19 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>631339</v>
+        <v>631350</v>
       </c>
       <c r="B223" t="str">
-        <v>ACEITUNA AZAPA EXTRA KG SOLIS</v>
+        <v>AMERICANAKG. SOLIS</v>
       </c>
       <c r="C223" t="str">
         <v/>
       </c>
       <c r="D223" t="str">
-        <v>31339</v>
+        <v>31350</v>
       </c>
       <c r="E223" t="str">
-        <v>9396</v>
+        <v>2996</v>
       </c>
       <c r="F223" t="str">
         <v>Por peso</v>
@@ -4861,19 +4861,19 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>631499</v>
+        <v>631339</v>
       </c>
       <c r="B224" t="str">
-        <v>JAMON GLACE G2 C9 PF KG</v>
+        <v>ACEITUNA AZAPA EXTRA KG SOLIS</v>
       </c>
       <c r="C224" t="str">
         <v/>
       </c>
       <c r="D224" t="str">
-        <v>31499</v>
+        <v>31339</v>
       </c>
       <c r="E224" t="str">
-        <v>9996</v>
+        <v>9396</v>
       </c>
       <c r="F224" t="str">
         <v>Por peso</v>
@@ -4881,19 +4881,19 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>634515</v>
+        <v>631499</v>
       </c>
       <c r="B225" t="str">
-        <v>SALAME KG PREFERIDA</v>
+        <v>JAMON GLACE G2 C9 PF KG</v>
       </c>
       <c r="C225" t="str">
         <v/>
       </c>
       <c r="D225" t="str">
-        <v>34515</v>
+        <v>31499</v>
       </c>
       <c r="E225" t="str">
-        <v>15996</v>
+        <v>9996</v>
       </c>
       <c r="F225" t="str">
         <v>Por peso</v>
@@ -4901,19 +4901,19 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>633096</v>
+        <v>634515</v>
       </c>
       <c r="B226" t="str">
-        <v>PECHUGA POLLO COCIDA SAN JORGE KG</v>
+        <v>SALAME KG PREFERIDA</v>
       </c>
       <c r="C226" t="str">
         <v/>
       </c>
       <c r="D226" t="str">
-        <v>33096</v>
+        <v>34515</v>
       </c>
       <c r="E226" t="str">
-        <v>10996</v>
+        <v>15996</v>
       </c>
       <c r="F226" t="str">
         <v>Por peso</v>
@@ -4921,19 +4921,19 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>633403</v>
+        <v>633096</v>
       </c>
       <c r="B227" t="str">
-        <v>ACEITUNA SEVILLANA CUGAT KILO</v>
+        <v>PECHUGA POLLO COCIDA SAN JORGE KG</v>
       </c>
       <c r="C227" t="str">
         <v/>
       </c>
       <c r="D227" t="str">
-        <v>33403</v>
+        <v>33096</v>
       </c>
       <c r="E227" t="str">
-        <v>2996</v>
+        <v>10996</v>
       </c>
       <c r="F227" t="str">
         <v>Por peso</v>
@@ -4941,19 +4941,19 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>635072</v>
+        <v>633403</v>
       </c>
       <c r="B228" t="str">
-        <v>COSTILLAR AHUMADO KILO BRAUNAU</v>
+        <v>ACEITUNA SEVILLANA CUGAT KILO</v>
       </c>
       <c r="C228" t="str">
         <v/>
       </c>
       <c r="D228" t="str">
-        <v>35072</v>
+        <v>33403</v>
       </c>
       <c r="E228" t="str">
-        <v>15996</v>
+        <v>2996</v>
       </c>
       <c r="F228" t="str">
         <v>Por peso</v>
@@ -4961,19 +4961,19 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>635074</v>
+        <v>635072</v>
       </c>
       <c r="B229" t="str">
-        <v>LONGANIZA KG BRAUNAU</v>
+        <v>COSTILLAR AHUMADO KILO BRAUNAU</v>
       </c>
       <c r="C229" t="str">
         <v/>
       </c>
       <c r="D229" t="str">
-        <v>35074</v>
+        <v>35072</v>
       </c>
       <c r="E229" t="str">
-        <v>14796</v>
+        <v>15996</v>
       </c>
       <c r="F229" t="str">
         <v>Por peso</v>
@@ -4981,19 +4981,19 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>635077</v>
+        <v>635074</v>
       </c>
       <c r="B230" t="str">
-        <v>PATE FINAS HIERBAS BRAUNAU</v>
+        <v>LONGANIZA KG BRAUNAU</v>
       </c>
       <c r="C230" t="str">
         <v/>
       </c>
       <c r="D230" t="str">
-        <v>35077</v>
+        <v>35074</v>
       </c>
       <c r="E230" t="str">
-        <v>9960</v>
+        <v>14796</v>
       </c>
       <c r="F230" t="str">
         <v>Por peso</v>
@@ -5001,19 +5001,19 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>635079</v>
+        <v>635077</v>
       </c>
       <c r="B231" t="str">
-        <v>QUESO CABEZA KG BRAUNAU</v>
+        <v>PATE FINAS HIERBAS BRAUNAU</v>
       </c>
       <c r="C231" t="str">
         <v/>
       </c>
       <c r="D231" t="str">
-        <v>35079</v>
+        <v>35077</v>
       </c>
       <c r="E231" t="str">
-        <v>11196</v>
+        <v>9960</v>
       </c>
       <c r="F231" t="str">
         <v>Por peso</v>
@@ -5021,19 +5021,19 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>635080</v>
+        <v>635079</v>
       </c>
       <c r="B232" t="str">
-        <v>QUESO SANGRE BRAUNAU KG</v>
+        <v>QUESO CABEZA KG BRAUNAU</v>
       </c>
       <c r="C232" t="str">
         <v/>
       </c>
       <c r="D232" t="str">
-        <v>35080</v>
+        <v>35079</v>
       </c>
       <c r="E232" t="str">
-        <v>10886</v>
+        <v>11196</v>
       </c>
       <c r="F232" t="str">
         <v>Por peso</v>
@@ -5041,19 +5041,19 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>635541</v>
+        <v>635080</v>
       </c>
       <c r="B233" t="str">
-        <v>JAMON COLONIAL SUPER CERDO KG</v>
+        <v>QUESO SANGRE BRAUNAU KG</v>
       </c>
       <c r="C233" t="str">
         <v/>
       </c>
       <c r="D233" t="str">
-        <v>35541</v>
+        <v>35080</v>
       </c>
       <c r="E233" t="str">
-        <v>8396</v>
+        <v>10886</v>
       </c>
       <c r="F233" t="str">
         <v>Por peso</v>
@@ -5061,19 +5061,19 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>635542</v>
+        <v>635541</v>
       </c>
       <c r="B234" t="str">
-        <v>JAMON ACARAMELA SUPER CERDO KG</v>
+        <v>JAMON COLONIAL SUPER CERDO KG</v>
       </c>
       <c r="C234" t="str">
         <v/>
       </c>
       <c r="D234" t="str">
-        <v>35542</v>
+        <v>35541</v>
       </c>
       <c r="E234" t="str">
-        <v>8796</v>
+        <v>8396</v>
       </c>
       <c r="F234" t="str">
         <v>Por peso</v>
@@ -5081,19 +5081,19 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>634571</v>
+        <v>635542</v>
       </c>
       <c r="B235" t="str">
-        <v>ACEITUNA SEVILLANA ECONOMICA KG SOLIS</v>
+        <v>JAMON ACARAMELA SUPER CERDO KG</v>
       </c>
       <c r="C235" t="str">
         <v/>
       </c>
       <c r="D235" t="str">
-        <v>34571</v>
+        <v>35542</v>
       </c>
       <c r="E235" t="str">
-        <v>6196</v>
+        <v>8796</v>
       </c>
       <c r="F235" t="str">
         <v>Por peso</v>
@@ -5101,19 +5101,19 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>631780</v>
+        <v>634571</v>
       </c>
       <c r="B236" t="str">
-        <v>LONGANIZA ARTESANAL KG MOLINO VIEJO</v>
+        <v>ACEITUNA SEVILLANA ECONOMICA KG SOLIS</v>
       </c>
       <c r="C236" t="str">
         <v/>
       </c>
       <c r="D236" t="str">
-        <v>31780</v>
+        <v>34571</v>
       </c>
       <c r="E236" t="str">
-        <v>10360</v>
+        <v>6196</v>
       </c>
       <c r="F236" t="str">
         <v>Por peso</v>
@@ -5121,19 +5121,19 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>635550</v>
+        <v>631780</v>
       </c>
       <c r="B237" t="str">
-        <v>CEBOLLA ESCABECHE KILO LAS LOMAS</v>
+        <v>LONGANIZA ARTESANAL KG MOLINO VIEJO</v>
       </c>
       <c r="C237" t="str">
         <v/>
       </c>
       <c r="D237" t="str">
-        <v>35550</v>
+        <v>31780</v>
       </c>
       <c r="E237" t="str">
-        <v>3596</v>
+        <v>10360</v>
       </c>
       <c r="F237" t="str">
         <v>Por peso</v>
@@ -5141,19 +5141,19 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>635551</v>
+        <v>635550</v>
       </c>
       <c r="B238" t="str">
-        <v>CHUCRUT KILO LAS LOMAS</v>
+        <v>CEBOLLA ESCABECHE KILO LAS LOMAS</v>
       </c>
       <c r="C238" t="str">
         <v/>
       </c>
       <c r="D238" t="str">
-        <v>35551</v>
+        <v>35550</v>
       </c>
       <c r="E238" t="str">
-        <v>2996</v>
+        <v>3596</v>
       </c>
       <c r="F238" t="str">
         <v>Por peso</v>
@@ -5161,19 +5161,19 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>635552</v>
+        <v>635551</v>
       </c>
       <c r="B239" t="str">
-        <v>SALSA AMERICANA KILO LAS LOMAS</v>
+        <v>CHUCRUT KILO LAS LOMAS</v>
       </c>
       <c r="C239" t="str">
         <v/>
       </c>
       <c r="D239" t="str">
-        <v>35552</v>
+        <v>35551</v>
       </c>
       <c r="E239" t="str">
-        <v>3160</v>
+        <v>2996</v>
       </c>
       <c r="F239" t="str">
         <v>Por peso</v>
@@ -5181,19 +5181,19 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>634541</v>
+        <v>635552</v>
       </c>
       <c r="B240" t="str">
-        <v>MORTAD. JAMONADA CENTENARIO LP KG</v>
+        <v>SALSA AMERICANA KILO LAS LOMAS</v>
       </c>
       <c r="C240" t="str">
         <v/>
       </c>
       <c r="D240" t="str">
-        <v>34541</v>
+        <v>35552</v>
       </c>
       <c r="E240" t="str">
-        <v>9196</v>
+        <v>3160</v>
       </c>
       <c r="F240" t="str">
         <v>Por peso</v>
@@ -5201,19 +5201,19 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>633099</v>
+        <v>634541</v>
       </c>
       <c r="B241" t="str">
-        <v>LONGANIZA CASERA KG CASTILLA</v>
+        <v>MORTAD. JAMONADA CENTENARIO LP KG</v>
       </c>
       <c r="C241" t="str">
         <v/>
       </c>
       <c r="D241" t="str">
-        <v>33099</v>
+        <v>34541</v>
       </c>
       <c r="E241" t="str">
-        <v>8596</v>
+        <v>9196</v>
       </c>
       <c r="F241" t="str">
         <v>Por peso</v>
@@ -5221,19 +5221,19 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>633098</v>
+        <v>633099</v>
       </c>
       <c r="B242" t="str">
-        <v>ARROLLADO HUASO CASTILLA KILO</v>
+        <v>LONGANIZA CASERA KG CASTILLA</v>
       </c>
       <c r="C242" t="str">
         <v/>
       </c>
       <c r="D242" t="str">
-        <v>33098</v>
+        <v>33099</v>
       </c>
       <c r="E242" t="str">
-        <v>9996</v>
+        <v>8596</v>
       </c>
       <c r="F242" t="str">
         <v>Por peso</v>
@@ -5241,16 +5241,16 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>633103</v>
+        <v>633098</v>
       </c>
       <c r="B243" t="str">
-        <v>ARROLLADOCAJI CASTILLA KILO</v>
+        <v>ARROLLADO HUASO CASTILLA KILO</v>
       </c>
       <c r="C243" t="str">
         <v/>
       </c>
       <c r="D243" t="str">
-        <v>33103</v>
+        <v>33098</v>
       </c>
       <c r="E243" t="str">
         <v>9996</v>
@@ -5261,16 +5261,16 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>633104</v>
+        <v>633103</v>
       </c>
       <c r="B244" t="str">
-        <v>QUESO CABEZA KG CASTILLA</v>
+        <v>ARROLLADOCAJI CASTILLA KILO</v>
       </c>
       <c r="C244" t="str">
         <v/>
       </c>
       <c r="D244" t="str">
-        <v>33104</v>
+        <v>33103</v>
       </c>
       <c r="E244" t="str">
         <v>9996</v>
@@ -5281,19 +5281,19 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>633330</v>
+        <v>633104</v>
       </c>
       <c r="B245" t="str">
-        <v>COSTILLAR CERDO AHUMADO CASTILLA KILO</v>
+        <v>QUESO CABEZA KG CASTILLA</v>
       </c>
       <c r="C245" t="str">
         <v/>
       </c>
       <c r="D245" t="str">
-        <v>33330</v>
+        <v>33104</v>
       </c>
       <c r="E245" t="str">
-        <v>14796</v>
+        <v>9996</v>
       </c>
       <c r="F245" t="str">
         <v>Por peso</v>
@@ -5301,19 +5301,19 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>634292</v>
+        <v>633330</v>
       </c>
       <c r="B246" t="str">
-        <v>PEPINO COCKTAIL HP KILO</v>
+        <v>COSTILLAR CERDO AHUMADO CASTILLA KILO</v>
       </c>
       <c r="C246" t="str">
         <v/>
       </c>
       <c r="D246" t="str">
-        <v>34292</v>
+        <v>33330</v>
       </c>
       <c r="E246" t="str">
-        <v>4996</v>
+        <v>14796</v>
       </c>
       <c r="F246" t="str">
         <v>Por peso</v>
@@ -5321,19 +5321,19 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>638989</v>
+        <v>634292</v>
       </c>
       <c r="B247" t="str">
-        <v>QUESO DE CABEZA DON RODRIGO</v>
+        <v>PEPINO COCKTAIL HP KILO</v>
       </c>
       <c r="C247" t="str">
         <v/>
       </c>
       <c r="D247" t="str">
-        <v>38989</v>
+        <v>34292</v>
       </c>
       <c r="E247" t="str">
-        <v>5996</v>
+        <v>4996</v>
       </c>
       <c r="F247" t="str">
         <v>Por peso</v>
@@ -5341,19 +5341,19 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>638485</v>
+        <v>638989</v>
       </c>
       <c r="B248" t="str">
-        <v>ARROLLADO DE LOMO SIN AJI DON RODRIGO</v>
+        <v>QUESO DE CABEZA DON RODRIGO</v>
       </c>
       <c r="C248" t="str">
         <v/>
       </c>
       <c r="D248" t="str">
-        <v>38485</v>
+        <v>38989</v>
       </c>
       <c r="E248" t="str">
-        <v>8996</v>
+        <v>5996</v>
       </c>
       <c r="F248" t="str">
         <v>Por peso</v>
@@ -5361,19 +5361,19 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>638486</v>
+        <v>638485</v>
       </c>
       <c r="B249" t="str">
-        <v>QUESO CABEZA CHILENO PORCIONADO DON RODRIGO</v>
+        <v>ARROLLADO DE LOMO SIN AJI DON RODRIGO</v>
       </c>
       <c r="C249" t="str">
         <v/>
       </c>
       <c r="D249" t="str">
-        <v>38486</v>
+        <v>38485</v>
       </c>
       <c r="E249" t="str">
-        <v>5996</v>
+        <v>8996</v>
       </c>
       <c r="F249" t="str">
         <v>Por peso</v>
@@ -5381,19 +5381,19 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>634801</v>
+        <v>638486</v>
       </c>
       <c r="B250" t="str">
-        <v>LONGANIZA BLANCA DON RODRIGO</v>
+        <v>QUESO CABEZA CHILENO PORCIONADO DON RODRIGO</v>
       </c>
       <c r="C250" t="str">
         <v/>
       </c>
       <c r="D250" t="str">
-        <v>34801</v>
+        <v>38486</v>
       </c>
       <c r="E250" t="str">
-        <v>4390</v>
+        <v>5996</v>
       </c>
       <c r="F250" t="str">
         <v>Por peso</v>
@@ -5401,19 +5401,19 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>634802</v>
+        <v>634801</v>
       </c>
       <c r="B251" t="str">
-        <v>QUESO CABEZA PORCIONADO DON RODRIGO</v>
+        <v>LONGANIZA BLANCA DON RODRIGO</v>
       </c>
       <c r="C251" t="str">
         <v/>
       </c>
       <c r="D251" t="str">
-        <v>34802</v>
+        <v>34801</v>
       </c>
       <c r="E251" t="str">
-        <v>5996</v>
+        <v>4390</v>
       </c>
       <c r="F251" t="str">
         <v>Por peso</v>
@@ -5421,19 +5421,19 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>636421</v>
+        <v>634802</v>
       </c>
       <c r="B252" t="str">
-        <v>LONGANIZA BELEN KG</v>
+        <v>QUESO CABEZA PORCIONADO DON RODRIGO</v>
       </c>
       <c r="C252" t="str">
         <v/>
       </c>
       <c r="D252" t="str">
-        <v>36421</v>
+        <v>34802</v>
       </c>
       <c r="E252" t="str">
-        <v>7196</v>
+        <v>5996</v>
       </c>
       <c r="F252" t="str">
         <v>Por peso</v>
@@ -5441,19 +5441,19 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>636422</v>
+        <v>636421</v>
       </c>
       <c r="B253" t="str">
-        <v>LONGANIZA BELEN MERKEN KG</v>
+        <v>LONGANIZA BELEN KG</v>
       </c>
       <c r="C253" t="str">
         <v/>
       </c>
       <c r="D253" t="str">
-        <v>36422</v>
+        <v>36421</v>
       </c>
       <c r="E253" t="str">
-        <v>7996</v>
+        <v>7196</v>
       </c>
       <c r="F253" t="str">
         <v>Por peso</v>
@@ -5461,19 +5461,19 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>636423</v>
+        <v>636422</v>
       </c>
       <c r="B254" t="str">
-        <v>ARROLLADO BELEN KG</v>
+        <v>LONGANIZA BELEN MERKEN KG</v>
       </c>
       <c r="C254" t="str">
         <v/>
       </c>
       <c r="D254" t="str">
-        <v>36423</v>
+        <v>36422</v>
       </c>
       <c r="E254" t="str">
-        <v>9196</v>
+        <v>7996</v>
       </c>
       <c r="F254" t="str">
         <v>Por peso</v>
@@ -5481,19 +5481,19 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>636424</v>
+        <v>636423</v>
       </c>
       <c r="B255" t="str">
-        <v>AROLLADO BELEN MERKEN KG</v>
+        <v>ARROLLADO BELEN KG</v>
       </c>
       <c r="C255" t="str">
         <v/>
       </c>
       <c r="D255" t="str">
-        <v>36424</v>
+        <v>36423</v>
       </c>
       <c r="E255" t="str">
-        <v>9396</v>
+        <v>9196</v>
       </c>
       <c r="F255" t="str">
         <v>Por peso</v>
@@ -5501,19 +5501,19 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>636425</v>
+        <v>636424</v>
       </c>
       <c r="B256" t="str">
-        <v>QUESO CERDO BELEN KG</v>
+        <v>AROLLADO BELEN MERKEN KG</v>
       </c>
       <c r="C256" t="str">
         <v/>
       </c>
       <c r="D256" t="str">
-        <v>36425</v>
+        <v>36424</v>
       </c>
       <c r="E256" t="str">
-        <v>5996</v>
+        <v>9396</v>
       </c>
       <c r="F256" t="str">
         <v>Por peso</v>
@@ -5521,19 +5521,19 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>636000</v>
+        <v>636425</v>
       </c>
       <c r="B257" t="str">
-        <v>PICKLE PORTAL DEL SUR KG</v>
+        <v>QUESO CERDO BELEN KG</v>
       </c>
       <c r="C257" t="str">
         <v/>
       </c>
       <c r="D257" t="str">
-        <v>36000</v>
+        <v>36425</v>
       </c>
       <c r="E257" t="str">
-        <v>3490</v>
+        <v>5996</v>
       </c>
       <c r="F257" t="str">
         <v>Por peso</v>
@@ -5541,19 +5541,19 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>636001</v>
+        <v>636000</v>
       </c>
       <c r="B258" t="str">
-        <v>AJI ORO PORTAL DEL SUR KG</v>
+        <v>PICKLE PORTAL DEL SUR KG</v>
       </c>
       <c r="C258" t="str">
         <v/>
       </c>
       <c r="D258" t="str">
-        <v>36001</v>
+        <v>36000</v>
       </c>
       <c r="E258" t="str">
-        <v>3890</v>
+        <v>3490</v>
       </c>
       <c r="F258" t="str">
         <v>Por peso</v>
@@ -5561,19 +5561,19 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>636002</v>
+        <v>636001</v>
       </c>
       <c r="B259" t="str">
-        <v>CEBOLLA PERLA PORTAL DEL SUR KG</v>
+        <v>AJI ORO PORTAL DEL SUR KG</v>
       </c>
       <c r="C259" t="str">
         <v/>
       </c>
       <c r="D259" t="str">
-        <v>36002</v>
+        <v>36001</v>
       </c>
       <c r="E259" t="str">
-        <v>4990</v>
+        <v>3890</v>
       </c>
       <c r="F259" t="str">
         <v>Por peso</v>
@@ -5581,19 +5581,19 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>636003</v>
+        <v>636002</v>
       </c>
       <c r="B260" t="str">
-        <v>PEPINILLO PORTAL DEL SUR KG</v>
+        <v>CEBOLLA PERLA PORTAL DEL SUR KG</v>
       </c>
       <c r="C260" t="str">
         <v/>
       </c>
       <c r="D260" t="str">
-        <v>36003</v>
+        <v>36002</v>
       </c>
       <c r="E260" t="str">
-        <v>4698</v>
+        <v>4990</v>
       </c>
       <c r="F260" t="str">
         <v>Por peso</v>
@@ -5601,19 +5601,19 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>636004</v>
+        <v>636003</v>
       </c>
       <c r="B261" t="str">
-        <v>CHUCRUT PORTAL DEL SUR KG</v>
+        <v>PEPINILLO PORTAL DEL SUR KG</v>
       </c>
       <c r="C261" t="str">
         <v/>
       </c>
       <c r="D261" t="str">
-        <v>36004</v>
+        <v>36003</v>
       </c>
       <c r="E261" t="str">
-        <v>3290</v>
+        <v>4698</v>
       </c>
       <c r="F261" t="str">
         <v>Por peso</v>
@@ -5621,19 +5621,19 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>636005</v>
+        <v>636004</v>
       </c>
       <c r="B262" t="str">
-        <v>SALSA AMERICANA PORTAL DEL SUR KG</v>
+        <v>CHUCRUT PORTAL DEL SUR KG</v>
       </c>
       <c r="C262" t="str">
         <v/>
       </c>
       <c r="D262" t="str">
-        <v>36005</v>
+        <v>36004</v>
       </c>
       <c r="E262" t="str">
-        <v>2990</v>
+        <v>3290</v>
       </c>
       <c r="F262" t="str">
         <v>Por peso</v>
@@ -5641,19 +5641,19 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>636006</v>
+        <v>636005</v>
       </c>
       <c r="B263" t="str">
-        <v>ACEITUNA CHICA PORTAL DEL SUR KG</v>
+        <v>SALSA AMERICANA PORTAL DEL SUR KG</v>
       </c>
       <c r="C263" t="str">
         <v/>
       </c>
       <c r="D263" t="str">
-        <v>36006</v>
+        <v>36005</v>
       </c>
       <c r="E263" t="str">
-        <v>3290</v>
+        <v>2990</v>
       </c>
       <c r="F263" t="str">
         <v>Por peso</v>
@@ -5661,19 +5661,19 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>636007</v>
+        <v>636006</v>
       </c>
       <c r="B264" t="str">
-        <v>ACEITUNA AZAPA PORTAL DEL SUR KG</v>
+        <v>ACEITUNA CHICA PORTAL DEL SUR KG</v>
       </c>
       <c r="C264" t="str">
         <v/>
       </c>
       <c r="D264" t="str">
-        <v>36007</v>
+        <v>36006</v>
       </c>
       <c r="E264" t="str">
-        <v>4990</v>
+        <v>3290</v>
       </c>
       <c r="F264" t="str">
         <v>Por peso</v>
@@ -5681,19 +5681,19 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>631178</v>
+        <v>636007</v>
       </c>
       <c r="B265" t="str">
-        <v>LONGANIZA CORDILLERA GRANEL KG</v>
+        <v>ACEITUNA AZAPA PORTAL DEL SUR KG</v>
       </c>
       <c r="C265" t="str">
         <v/>
       </c>
       <c r="D265" t="str">
-        <v>31178</v>
+        <v>36007</v>
       </c>
       <c r="E265" t="str">
-        <v>6996</v>
+        <v>4990</v>
       </c>
       <c r="F265" t="str">
         <v>Por peso</v>
@@ -5701,19 +5701,19 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>631586</v>
+        <v>631178</v>
       </c>
       <c r="B266" t="str">
-        <v>PRIETAS CORDILLERA GRANEL KG</v>
+        <v>LONGANIZA CORDILLERA GRANEL KG</v>
       </c>
       <c r="C266" t="str">
         <v/>
       </c>
       <c r="D266" t="str">
-        <v>31586</v>
+        <v>31178</v>
       </c>
       <c r="E266" t="str">
-        <v>4596</v>
+        <v>6996</v>
       </c>
       <c r="F266" t="str">
         <v>Por peso</v>
@@ -5721,19 +5721,19 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>631699</v>
+        <v>631586</v>
       </c>
       <c r="B267" t="str">
-        <v>ARROLLADO CORDILLERA GRANEL KG</v>
+        <v>PRIETAS CORDILLERA GRANEL KG</v>
       </c>
       <c r="C267" t="str">
         <v/>
       </c>
       <c r="D267" t="str">
-        <v>31699</v>
+        <v>31586</v>
       </c>
       <c r="E267" t="str">
-        <v>7396</v>
+        <v>4596</v>
       </c>
       <c r="F267" t="str">
         <v>Por peso</v>
@@ -5741,19 +5741,19 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>631583</v>
+        <v>631699</v>
       </c>
       <c r="B268" t="str">
-        <v>QUESO CABEZA GRANEL KG</v>
+        <v>ARROLLADO CORDILLERA GRANEL KG</v>
       </c>
       <c r="C268" t="str">
         <v/>
       </c>
       <c r="D268" t="str">
-        <v>31583</v>
+        <v>31699</v>
       </c>
       <c r="E268" t="str">
-        <v>5196</v>
+        <v>7396</v>
       </c>
       <c r="F268" t="str">
         <v>Por peso</v>
@@ -5761,19 +5761,19 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>631258</v>
+        <v>631583</v>
       </c>
       <c r="B269" t="str">
-        <v>JAMON PIERNA ARTESANAL DON RODRIGO</v>
+        <v>QUESO CABEZA GRANEL KG</v>
       </c>
       <c r="C269" t="str">
         <v/>
       </c>
       <c r="D269" t="str">
-        <v>31258</v>
+        <v>31583</v>
       </c>
       <c r="E269" t="str">
-        <v>11996</v>
+        <v>5196</v>
       </c>
       <c r="F269" t="str">
         <v>Por peso</v>
@@ -5781,19 +5781,19 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>631479</v>
+        <v>631258</v>
       </c>
       <c r="B270" t="str">
-        <v>ARROLLADO CHILENO PORCIONADO DON RODRIGO</v>
+        <v>JAMON PIERNA ARTESANAL DON RODRIGO</v>
       </c>
       <c r="C270" t="str">
         <v/>
       </c>
       <c r="D270" t="str">
-        <v>31479</v>
+        <v>31258</v>
       </c>
       <c r="E270" t="str">
-        <v>8990</v>
+        <v>11996</v>
       </c>
       <c r="F270" t="str">
         <v>Por peso</v>
@@ -5801,19 +5801,19 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>631965</v>
+        <v>631479</v>
       </c>
       <c r="B271" t="str">
-        <v>JAMON PIERNA ARTESANAL WINTER KG</v>
+        <v>ARROLLADO CHILENO PORCIONADO DON RODRIGO</v>
       </c>
       <c r="C271" t="str">
         <v/>
       </c>
       <c r="D271" t="str">
-        <v>31965</v>
+        <v>31479</v>
       </c>
       <c r="E271" t="str">
-        <v>9996</v>
+        <v>8990</v>
       </c>
       <c r="F271" t="str">
         <v>Por peso</v>
@@ -5821,19 +5821,19 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>636518</v>
+        <v>631965</v>
       </c>
       <c r="B272" t="str">
-        <v>LONGANIZA DON CARLOS KG</v>
+        <v>JAMON PIERNA ARTESANAL WINTER KG</v>
       </c>
       <c r="C272" t="str">
         <v/>
       </c>
       <c r="D272" t="str">
-        <v>36518</v>
+        <v>31965</v>
       </c>
       <c r="E272" t="str">
-        <v>4796</v>
+        <v>9996</v>
       </c>
       <c r="F272" t="str">
         <v>Por peso</v>
@@ -5841,19 +5841,19 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>639134</v>
+        <v>636518</v>
       </c>
       <c r="B273" t="str">
-        <v>ARROLLADO LOMO CON AJI DON CARLOS KG</v>
+        <v>LONGANIZA DON CARLOS KG</v>
       </c>
       <c r="C273" t="str">
         <v/>
       </c>
       <c r="D273" t="str">
-        <v>39134</v>
+        <v>36518</v>
       </c>
       <c r="E273" t="str">
-        <v>6396</v>
+        <v>4796</v>
       </c>
       <c r="F273" t="str">
         <v>Por peso</v>
@@ -5861,19 +5861,19 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>636173</v>
+        <v>639134</v>
       </c>
       <c r="B274" t="str">
-        <v>PRIETAS DON CARLOS KG</v>
+        <v>ARROLLADO LOMO CON AJI DON CARLOS KG</v>
       </c>
       <c r="C274" t="str">
         <v/>
       </c>
       <c r="D274" t="str">
-        <v>36173</v>
+        <v>39134</v>
       </c>
       <c r="E274" t="str">
-        <v>4796</v>
+        <v>6396</v>
       </c>
       <c r="F274" t="str">
         <v>Por peso</v>
@@ -5881,19 +5881,19 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>636913</v>
+        <v>636173</v>
       </c>
       <c r="B275" t="str">
-        <v>COSTILLAR AHUMADO DON CARLOS KG</v>
+        <v>PRIETAS DON CARLOS KG</v>
       </c>
       <c r="C275" t="str">
         <v/>
       </c>
       <c r="D275" t="str">
-        <v>36913</v>
+        <v>36173</v>
       </c>
       <c r="E275" t="str">
-        <v>7596</v>
+        <v>4796</v>
       </c>
       <c r="F275" t="str">
         <v>Por peso</v>
@@ -5901,19 +5901,19 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>636942</v>
+        <v>636913</v>
       </c>
       <c r="B276" t="str">
-        <v>PERNIL COCIDO MANO DON CARLOS.KG</v>
+        <v>COSTILLAR AHUMADO DON CARLOS KG</v>
       </c>
       <c r="C276" t="str">
         <v/>
       </c>
       <c r="D276" t="str">
-        <v>36942</v>
+        <v>36913</v>
       </c>
       <c r="E276" t="str">
-        <v>4996</v>
+        <v>7596</v>
       </c>
       <c r="F276" t="str">
         <v>Por peso</v>
@@ -5921,19 +5921,19 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>636981</v>
+        <v>636942</v>
       </c>
       <c r="B277" t="str">
-        <v>QUESO CABEZA DON CARLOS KG</v>
+        <v>PERNIL COCIDO MANO DON CARLOS.KG</v>
       </c>
       <c r="C277" t="str">
         <v/>
       </c>
       <c r="D277" t="str">
-        <v>36981</v>
+        <v>36942</v>
       </c>
       <c r="E277" t="str">
-        <v>4796</v>
+        <v>4996</v>
       </c>
       <c r="F277" t="str">
         <v>Por peso</v>
@@ -5941,19 +5941,19 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>631003</v>
+        <v>636981</v>
       </c>
       <c r="B278" t="str">
-        <v>LONGANIZA PARRILLERA CHILLAN KG</v>
+        <v>QUESO CABEZA DON CARLOS KG</v>
       </c>
       <c r="C278" t="str">
         <v/>
       </c>
       <c r="D278" t="str">
-        <v>31003</v>
+        <v>36981</v>
       </c>
       <c r="E278" t="str">
-        <v>10996</v>
+        <v>4796</v>
       </c>
       <c r="F278" t="str">
         <v>Por peso</v>
@@ -5961,19 +5961,19 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>638990</v>
+        <v>631003</v>
       </c>
       <c r="B279" t="str">
-        <v>ARROLLADO HUASO CHILLAN KG</v>
+        <v>LONGANIZA PARRILLERA CHILLAN KG</v>
       </c>
       <c r="C279" t="str">
         <v/>
       </c>
       <c r="D279" t="str">
-        <v>38990</v>
+        <v>31003</v>
       </c>
       <c r="E279" t="str">
-        <v>13996</v>
+        <v>10996</v>
       </c>
       <c r="F279" t="str">
         <v>Por peso</v>
@@ -5981,19 +5981,19 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>639000</v>
+        <v>638990</v>
       </c>
       <c r="B280" t="str">
-        <v>PERNIL COCIDO SIN HUESO</v>
+        <v>ARROLLADO HUASO CHILLAN KG</v>
       </c>
       <c r="C280" t="str">
         <v/>
       </c>
       <c r="D280" t="str">
-        <v>39000</v>
+        <v>38990</v>
       </c>
       <c r="E280" t="str">
-        <v>11996</v>
+        <v>13996</v>
       </c>
       <c r="F280" t="str">
         <v>Por peso</v>
@@ -6001,19 +6001,19 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>639010</v>
+        <v>639000</v>
       </c>
       <c r="B281" t="str">
-        <v>QUESO DE CABEZA CHILLAN KG</v>
+        <v>PERNIL COCIDO SIN HUESO</v>
       </c>
       <c r="C281" t="str">
         <v/>
       </c>
       <c r="D281" t="str">
-        <v>39010</v>
+        <v>39000</v>
       </c>
       <c r="E281" t="str">
-        <v>10996</v>
+        <v>11996</v>
       </c>
       <c r="F281" t="str">
         <v>Por peso</v>
@@ -6021,19 +6021,19 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>631074</v>
+        <v>639010</v>
       </c>
       <c r="B282" t="str">
-        <v>LONGANICILLA DON RODRIGO VACIO KG</v>
+        <v>QUESO DE CABEZA CHILLAN KG</v>
       </c>
       <c r="C282" t="str">
         <v/>
       </c>
       <c r="D282" t="str">
-        <v>31074</v>
+        <v>39010</v>
       </c>
       <c r="E282" t="str">
-        <v>6996</v>
+        <v>10996</v>
       </c>
       <c r="F282" t="str">
         <v>Por peso</v>
@@ -6041,19 +6041,19 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>631078</v>
+        <v>631074</v>
       </c>
       <c r="B283" t="str">
-        <v>JAMON CENTENARIO COLONIAL LP</v>
+        <v>LONGANICILLA DON RODRIGO VACIO KG</v>
       </c>
       <c r="C283" t="str">
         <v/>
       </c>
       <c r="D283" t="str">
-        <v>31078</v>
+        <v>31074</v>
       </c>
       <c r="E283" t="str">
-        <v>11996</v>
+        <v>6996</v>
       </c>
       <c r="F283" t="str">
         <v>Por peso</v>
@@ -6061,19 +6061,19 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>631080</v>
+        <v>631078</v>
       </c>
       <c r="B284" t="str">
-        <v>QUESO CABEZA CPIMENTON KG DON RODRIGO</v>
+        <v>JAMON CENTENARIO COLONIAL LP</v>
       </c>
       <c r="C284" t="str">
         <v/>
       </c>
       <c r="D284" t="str">
-        <v>31080</v>
+        <v>31078</v>
       </c>
       <c r="E284" t="str">
-        <v>5996</v>
+        <v>11996</v>
       </c>
       <c r="F284" t="str">
         <v>Por peso</v>
@@ -6081,19 +6081,19 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>631084</v>
+        <v>631080</v>
       </c>
       <c r="B285" t="str">
-        <v>JAMON ACARAMELADO DON RODRIGO KG</v>
+        <v>QUESO CABEZA CPIMENTON KG DON RODRIGO</v>
       </c>
       <c r="C285" t="str">
         <v/>
       </c>
       <c r="D285" t="str">
-        <v>31084</v>
+        <v>31080</v>
       </c>
       <c r="E285" t="str">
-        <v>8996</v>
+        <v>5996</v>
       </c>
       <c r="F285" t="str">
         <v>Por peso</v>
@@ -6101,19 +6101,19 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>631087</v>
+        <v>631084</v>
       </c>
       <c r="B286" t="str">
-        <v>ARROLLADO CON CUERO FANDA KG</v>
+        <v>JAMON ACARAMELADO DON RODRIGO KG</v>
       </c>
       <c r="C286" t="str">
         <v/>
       </c>
       <c r="D286" t="str">
-        <v>31087</v>
+        <v>31084</v>
       </c>
       <c r="E286" t="str">
-        <v>8796</v>
+        <v>8996</v>
       </c>
       <c r="F286" t="str">
         <v>Por peso</v>
@@ -6121,19 +6121,19 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>631088</v>
+        <v>631087</v>
       </c>
       <c r="B287" t="str">
-        <v>SALCHICHON CERVECERO RDA KG</v>
+        <v>ARROLLADO CON CUERO FANDA KG</v>
       </c>
       <c r="C287" t="str">
         <v/>
       </c>
       <c r="D287" t="str">
-        <v>31088</v>
+        <v>31087</v>
       </c>
       <c r="E287" t="str">
-        <v>9596</v>
+        <v>8796</v>
       </c>
       <c r="F287" t="str">
         <v>Por peso</v>
@@ -6141,19 +6141,19 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>631089</v>
+        <v>631088</v>
       </c>
       <c r="B288" t="str">
-        <v>JAMONADA DE PAVO RDA 3KG</v>
+        <v>SALCHICHON CERVECERO RDA KG</v>
       </c>
       <c r="C288" t="str">
         <v/>
       </c>
       <c r="D288" t="str">
-        <v>31089</v>
+        <v>31088</v>
       </c>
       <c r="E288" t="str">
-        <v>14196</v>
+        <v>9596</v>
       </c>
       <c r="F288" t="str">
         <v>Por peso</v>
@@ -6161,19 +6161,19 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>631091</v>
+        <v>631089</v>
       </c>
       <c r="B289" t="str">
-        <v>JAMONADA DE POLLO RDA 3KG</v>
+        <v>JAMONADA DE PAVO RDA 3KG</v>
       </c>
       <c r="C289" t="str">
         <v/>
       </c>
       <c r="D289" t="str">
-        <v>31091</v>
+        <v>31089</v>
       </c>
       <c r="E289" t="str">
-        <v>11996</v>
+        <v>14196</v>
       </c>
       <c r="F289" t="str">
         <v>Por peso</v>
@@ -6181,19 +6181,19 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>631092</v>
+        <v>631091</v>
       </c>
       <c r="B290" t="str">
-        <v>JAMON PIERNA SANDWICH RDA KG</v>
+        <v>JAMONADA DE POLLO RDA 3KG</v>
       </c>
       <c r="C290" t="str">
         <v/>
       </c>
       <c r="D290" t="str">
-        <v>31092</v>
+        <v>31091</v>
       </c>
       <c r="E290" t="str">
-        <v>10996</v>
+        <v>11996</v>
       </c>
       <c r="F290" t="str">
         <v>Por peso</v>
@@ -6201,19 +6201,19 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>631093</v>
+        <v>631092</v>
       </c>
       <c r="B291" t="str">
-        <v>TOCINO HUMADO PF KG</v>
+        <v>JAMON PIERNA SANDWICH RDA KG</v>
       </c>
       <c r="C291" t="str">
         <v/>
       </c>
       <c r="D291" t="str">
-        <v>31093</v>
+        <v>31092</v>
       </c>
       <c r="E291" t="str">
-        <v>17996</v>
+        <v>10996</v>
       </c>
       <c r="F291" t="str">
         <v>Por peso</v>
@@ -6221,19 +6221,19 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>631096</v>
+        <v>631093</v>
       </c>
       <c r="B292" t="str">
-        <v>PEPPERONI PF KG</v>
+        <v>TOCINO HUMADO PF KG</v>
       </c>
       <c r="C292" t="str">
         <v/>
       </c>
       <c r="D292" t="str">
-        <v>31096</v>
+        <v>31093</v>
       </c>
       <c r="E292" t="str">
-        <v>14996</v>
+        <v>17996</v>
       </c>
       <c r="F292" t="str">
         <v>Por peso</v>
@@ -6241,19 +6241,19 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>638765</v>
+        <v>631096</v>
       </c>
       <c r="B293" t="str">
-        <v>BUTIFARRA DON RODRIGO</v>
+        <v>PEPPERONI PF KG</v>
       </c>
       <c r="C293" t="str">
         <v/>
       </c>
       <c r="D293" t="str">
-        <v>38765</v>
+        <v>31096</v>
       </c>
       <c r="E293" t="str">
-        <v>4396</v>
+        <v>14996</v>
       </c>
       <c r="F293" t="str">
         <v>Por peso</v>
@@ -6261,19 +6261,19 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>636789</v>
+        <v>638765</v>
       </c>
       <c r="B294" t="str">
-        <v>JAMON FIAMBRE DON RODRIGO</v>
+        <v>BUTIFARRA DON RODRIGO</v>
       </c>
       <c r="C294" t="str">
         <v/>
       </c>
       <c r="D294" t="str">
-        <v>36789</v>
+        <v>38765</v>
       </c>
       <c r="E294" t="str">
-        <v>4996</v>
+        <v>4396</v>
       </c>
       <c r="F294" t="str">
         <v>Por peso</v>
@@ -6281,19 +6281,19 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>630910</v>
+        <v>636789</v>
       </c>
       <c r="B295" t="str">
-        <v>MORTADELA DON RODRIGO</v>
+        <v>JAMON FIAMBRE DON RODRIGO</v>
       </c>
       <c r="C295" t="str">
         <v/>
       </c>
       <c r="D295" t="str">
-        <v>30910</v>
+        <v>36789</v>
       </c>
       <c r="E295" t="str">
-        <v>4396</v>
+        <v>4996</v>
       </c>
       <c r="F295" t="str">
         <v>Por peso</v>
@@ -6301,19 +6301,19 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>632936</v>
+        <v>630910</v>
       </c>
       <c r="B296" t="str">
-        <v>PECHUGA DE POLLO ACARAMELADO SJ KG</v>
+        <v>MORTADELA DON RODRIGO</v>
       </c>
       <c r="C296" t="str">
         <v/>
       </c>
       <c r="D296" t="str">
-        <v>32936</v>
+        <v>30910</v>
       </c>
       <c r="E296" t="str">
-        <v>10996</v>
+        <v>4396</v>
       </c>
       <c r="F296" t="str">
         <v>Por peso</v>
@@ -6321,19 +6321,19 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>636265</v>
+        <v>632936</v>
       </c>
       <c r="B297" t="str">
-        <v>JAMON COCIDO SADIA KG</v>
+        <v>PECHUGA DE POLLO ACARAMELADO SJ KG</v>
       </c>
       <c r="C297" t="str">
         <v/>
       </c>
       <c r="D297" t="str">
-        <v>36265</v>
+        <v>32936</v>
       </c>
       <c r="E297" t="str">
-        <v>7996</v>
+        <v>10996</v>
       </c>
       <c r="F297" t="str">
         <v>Por peso</v>
@@ -6341,19 +6341,19 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>636492</v>
+        <v>636265</v>
       </c>
       <c r="B298" t="str">
-        <v>JAMON COLONIAL WINTER KG</v>
+        <v>JAMON COCIDO SADIA KG</v>
       </c>
       <c r="C298" t="str">
         <v/>
       </c>
       <c r="D298" t="str">
-        <v>36492</v>
+        <v>36265</v>
       </c>
       <c r="E298" t="str">
-        <v>11996</v>
+        <v>7996</v>
       </c>
       <c r="F298" t="str">
         <v>Por peso</v>
@@ -6361,19 +6361,19 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>634525</v>
+        <v>636492</v>
       </c>
       <c r="B299" t="str">
-        <v>JAMON PLANCHADO SUPER KG</v>
+        <v>JAMON COLONIAL WINTER KG</v>
       </c>
       <c r="C299" t="str">
         <v/>
       </c>
       <c r="D299" t="str">
-        <v>34525</v>
+        <v>36492</v>
       </c>
       <c r="E299" t="str">
-        <v>8396</v>
+        <v>11996</v>
       </c>
       <c r="F299" t="str">
         <v>Por peso</v>
@@ -6381,19 +6381,19 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>632323</v>
+        <v>634525</v>
       </c>
       <c r="B300" t="str">
-        <v>ARROLLADO DE LOMO CON AJI DON RODRIGO</v>
+        <v>JAMON PLANCHADO SUPER KG</v>
       </c>
       <c r="C300" t="str">
         <v/>
       </c>
       <c r="D300" t="str">
-        <v>32323</v>
+        <v>34525</v>
       </c>
       <c r="E300" t="str">
-        <v>8996</v>
+        <v>8396</v>
       </c>
       <c r="F300" t="str">
         <v>Por peso</v>
@@ -6401,19 +6401,19 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>634056</v>
+        <v>632323</v>
       </c>
       <c r="B301" t="str">
-        <v>QUESO DE CABEZA DLEON KG</v>
+        <v>ARROLLADO DE LOMO CON AJI DON RODRIGO</v>
       </c>
       <c r="C301" t="str">
         <v/>
       </c>
       <c r="D301" t="str">
-        <v>34056</v>
+        <v>32323</v>
       </c>
       <c r="E301" t="str">
-        <v>10796</v>
+        <v>8996</v>
       </c>
       <c r="F301" t="str">
         <v>Por peso</v>
@@ -6421,19 +6421,19 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>634055</v>
+        <v>634056</v>
       </c>
       <c r="B302" t="str">
-        <v>SALCHICHON CERVEZA AHUM. DLEON KG</v>
+        <v>QUESO DE CABEZA DLEON KG</v>
       </c>
       <c r="C302" t="str">
         <v/>
       </c>
       <c r="D302" t="str">
-        <v>34055</v>
+        <v>34056</v>
       </c>
       <c r="E302" t="str">
-        <v>12996</v>
+        <v>10796</v>
       </c>
       <c r="F302" t="str">
         <v>Por peso</v>
@@ -6441,19 +6441,19 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>634054</v>
+        <v>634055</v>
       </c>
       <c r="B303" t="str">
-        <v>JAMON COLONIAL DLEON KG</v>
+        <v>SALCHICHON CERVEZA AHUM. DLEON KG</v>
       </c>
       <c r="C303" t="str">
         <v/>
       </c>
       <c r="D303" t="str">
-        <v>34054</v>
+        <v>34055</v>
       </c>
       <c r="E303" t="str">
-        <v>15960</v>
+        <v>12996</v>
       </c>
       <c r="F303" t="str">
         <v>Por peso</v>
@@ -6461,19 +6461,19 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>634052</v>
+        <v>634054</v>
       </c>
       <c r="B304" t="str">
-        <v>JAMON PIERNA PLANCHADO DLEON KG</v>
+        <v>JAMON COLONIAL DLEON KG</v>
       </c>
       <c r="C304" t="str">
         <v/>
       </c>
       <c r="D304" t="str">
-        <v>34052</v>
+        <v>34054</v>
       </c>
       <c r="E304" t="str">
-        <v>16990</v>
+        <v>15960</v>
       </c>
       <c r="F304" t="str">
         <v>Por peso</v>
@@ -6481,19 +6481,19 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>634025</v>
+        <v>634052</v>
       </c>
       <c r="B305" t="str">
-        <v>AROLLADO DE HUASO CON AJI DLEON KG</v>
+        <v>JAMON PIERNA PLANCHADO DLEON KG</v>
       </c>
       <c r="C305" t="str">
         <v/>
       </c>
       <c r="D305" t="str">
-        <v>34025</v>
+        <v>34052</v>
       </c>
       <c r="E305" t="str">
-        <v>13996</v>
+        <v>16990</v>
       </c>
       <c r="F305" t="str">
         <v>Por peso</v>
@@ -6501,19 +6501,19 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>634016</v>
+        <v>634025</v>
       </c>
       <c r="B306" t="str">
-        <v>LONGANIZA AHUMADA ESPECIAL DLEON KG</v>
+        <v>AROLLADO DE HUASO CON AJI DLEON KG</v>
       </c>
       <c r="C306" t="str">
         <v/>
       </c>
       <c r="D306" t="str">
-        <v>34016</v>
+        <v>34025</v>
       </c>
       <c r="E306" t="str">
-        <v>10990</v>
+        <v>13996</v>
       </c>
       <c r="F306" t="str">
         <v>Por peso</v>
@@ -6521,19 +6521,19 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>634015</v>
+        <v>634016</v>
       </c>
       <c r="B307" t="str">
-        <v>LONGANIZA RECETADE FAMILIADLEON KG</v>
+        <v>LONGANIZA AHUMADA ESPECIAL DLEON KG</v>
       </c>
       <c r="C307" t="str">
         <v/>
       </c>
       <c r="D307" t="str">
-        <v>34015</v>
+        <v>34016</v>
       </c>
       <c r="E307" t="str">
-        <v>11990</v>
+        <v>10990</v>
       </c>
       <c r="F307" t="str">
         <v>Por peso</v>
@@ -6541,19 +6541,19 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>631362</v>
+        <v>634015</v>
       </c>
       <c r="B308" t="str">
-        <v>MORTAD. JAMONADA KG LC</v>
+        <v>LONGANIZA RECETADE FAMILIADLEON KG</v>
       </c>
       <c r="C308" t="str">
         <v/>
       </c>
       <c r="D308" t="str">
-        <v>31362</v>
+        <v>34015</v>
       </c>
       <c r="E308" t="str">
-        <v>8396</v>
+        <v>11990</v>
       </c>
       <c r="F308" t="str">
         <v>Por peso</v>
@@ -6561,19 +6561,19 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>631390</v>
+        <v>631362</v>
       </c>
       <c r="B309" t="str">
-        <v>JAMON SANDWICH PREFERIDA KG</v>
+        <v>MORTAD. JAMONADA KG LC</v>
       </c>
       <c r="C309" t="str">
         <v/>
       </c>
       <c r="D309" t="str">
-        <v>31390</v>
+        <v>31362</v>
       </c>
       <c r="E309" t="str">
-        <v>9996</v>
+        <v>8396</v>
       </c>
       <c r="F309" t="str">
         <v>Por peso</v>
@@ -6581,19 +6581,19 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>631360</v>
+        <v>631390</v>
       </c>
       <c r="B310" t="str">
-        <v>AROLLADO LOMO CON AJI LCKG</v>
+        <v>JAMON SANDWICH PREFERIDA KG</v>
       </c>
       <c r="C310" t="str">
         <v/>
       </c>
       <c r="D310" t="str">
-        <v>31360</v>
+        <v>31390</v>
       </c>
       <c r="E310" t="str">
-        <v>8996</v>
+        <v>9996</v>
       </c>
       <c r="F310" t="str">
         <v>Por peso</v>
@@ -6601,19 +6601,19 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>634715</v>
+        <v>631360</v>
       </c>
       <c r="B311" t="str">
-        <v>JAMON PLANCHADO G1 E. ALEMAN EMPORIO ALEMAN</v>
+        <v>AROLLADO LOMO CON AJI LCKG</v>
       </c>
       <c r="C311" t="str">
         <v/>
       </c>
       <c r="D311" t="str">
-        <v>34715</v>
+        <v>31360</v>
       </c>
       <c r="E311" t="str">
-        <v>16996</v>
+        <v>8996</v>
       </c>
       <c r="F311" t="str">
         <v>Por peso</v>
@@ -6621,16 +6621,16 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>631312</v>
+        <v>634715</v>
       </c>
       <c r="B312" t="str">
-        <v>JAMON PIERNA G1 E. ALEMAN EMPORIO ALEMAN</v>
+        <v>JAMON PLANCHADO G1 E. ALEMAN EMPORIO ALEMAN</v>
       </c>
       <c r="C312" t="str">
         <v/>
       </c>
       <c r="D312" t="str">
-        <v>31312</v>
+        <v>34715</v>
       </c>
       <c r="E312" t="str">
         <v>16996</v>
@@ -6641,19 +6641,19 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>639562</v>
+        <v>631312</v>
       </c>
       <c r="B313" t="str">
-        <v>ARROLLADO CAMP. C AJI KG E.ALEMAN</v>
+        <v>JAMON PIERNA G1 E. ALEMAN EMPORIO ALEMAN</v>
       </c>
       <c r="C313" t="str">
         <v/>
       </c>
       <c r="D313" t="str">
-        <v>39562</v>
+        <v>31312</v>
       </c>
       <c r="E313" t="str">
-        <v>12996</v>
+        <v>16996</v>
       </c>
       <c r="F313" t="str">
         <v>Por peso</v>
@@ -6661,16 +6661,16 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>639563</v>
+        <v>639562</v>
       </c>
       <c r="B314" t="str">
-        <v>ARROLLADO ART. S AJI KG E.ALEMAN</v>
+        <v>ARROLLADO CAMP. C AJI KG E.ALEMAN</v>
       </c>
       <c r="C314" t="str">
         <v/>
       </c>
       <c r="D314" t="str">
-        <v>39563</v>
+        <v>39562</v>
       </c>
       <c r="E314" t="str">
         <v>12996</v>
@@ -6681,19 +6681,19 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>630200</v>
+        <v>639563</v>
       </c>
       <c r="B315" t="str">
-        <v>LONGANIZA AHUMADA KG E.ALEMAN</v>
+        <v>ARROLLADO ART. S AJI KG E.ALEMAN</v>
       </c>
       <c r="C315" t="str">
         <v/>
       </c>
       <c r="D315" t="str">
-        <v>30200</v>
+        <v>39563</v>
       </c>
       <c r="E315" t="str">
-        <v>11996</v>
+        <v>12996</v>
       </c>
       <c r="F315" t="str">
         <v>Por peso</v>
@@ -6701,19 +6701,19 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>634225</v>
+        <v>630200</v>
       </c>
       <c r="B316" t="str">
-        <v>ACEITUNA AZAPA NEGRA VALLE CHILE KG</v>
+        <v>LONGANIZA AHUMADA KG E.ALEMAN</v>
       </c>
       <c r="C316" t="str">
         <v/>
       </c>
       <c r="D316" t="str">
-        <v>34225</v>
+        <v>30200</v>
       </c>
       <c r="E316" t="str">
-        <v>8596</v>
+        <v>11996</v>
       </c>
       <c r="F316" t="str">
         <v>Por peso</v>
@@ -6721,16 +6721,16 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>634226</v>
+        <v>634225</v>
       </c>
       <c r="B317" t="str">
-        <v>ACEITUNA SEVILLANA VERDE VALLE CHILE KG</v>
+        <v>ACEITUNA AZAPA NEGRA VALLE CHILE KG</v>
       </c>
       <c r="C317" t="str">
         <v/>
       </c>
       <c r="D317" t="str">
-        <v>34226</v>
+        <v>34225</v>
       </c>
       <c r="E317" t="str">
         <v>8596</v>
@@ -6741,19 +6741,19 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>634227</v>
+        <v>634226</v>
       </c>
       <c r="B318" t="str">
-        <v>ACEITUNA RELLENA MORRON VALLE CHILE KG</v>
+        <v>ACEITUNA SEVILLANA VERDE VALLE CHILE KG</v>
       </c>
       <c r="C318" t="str">
         <v/>
       </c>
       <c r="D318" t="str">
-        <v>34227</v>
+        <v>34226</v>
       </c>
       <c r="E318" t="str">
-        <v>8996</v>
+        <v>8596</v>
       </c>
       <c r="F318" t="str">
         <v>Por peso</v>
@@ -6761,19 +6761,19 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>634228</v>
+        <v>634227</v>
       </c>
       <c r="B319" t="str">
-        <v>SALSA AMERICANA VALLE CHILE KG</v>
+        <v>ACEITUNA RELLENA MORRON VALLE CHILE KG</v>
       </c>
       <c r="C319" t="str">
         <v/>
       </c>
       <c r="D319" t="str">
-        <v>34228</v>
+        <v>34227</v>
       </c>
       <c r="E319" t="str">
-        <v>3196</v>
+        <v>8996</v>
       </c>
       <c r="F319" t="str">
         <v>Por peso</v>
@@ -6781,19 +6781,19 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>634229</v>
+        <v>634228</v>
       </c>
       <c r="B320" t="str">
-        <v>CHUCRUT VALLE CHILE KG</v>
+        <v>SALSA AMERICANA VALLE CHILE KG</v>
       </c>
       <c r="C320" t="str">
         <v/>
       </c>
       <c r="D320" t="str">
-        <v>34229</v>
+        <v>34228</v>
       </c>
       <c r="E320" t="str">
-        <v>3596</v>
+        <v>3196</v>
       </c>
       <c r="F320" t="str">
         <v>Por peso</v>
@@ -6801,19 +6801,19 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>634230</v>
+        <v>634229</v>
       </c>
       <c r="B321" t="str">
-        <v>AJI ORO ESCABECHEVALLE CHILE KG</v>
+        <v>CHUCRUT VALLE CHILE KG</v>
       </c>
       <c r="C321" t="str">
         <v/>
       </c>
       <c r="D321" t="str">
-        <v>34230</v>
+        <v>34229</v>
       </c>
       <c r="E321" t="str">
-        <v>4396</v>
+        <v>3596</v>
       </c>
       <c r="F321" t="str">
         <v>Por peso</v>
@@ -6821,19 +6821,19 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>634231</v>
+        <v>634230</v>
       </c>
       <c r="B322" t="str">
-        <v>CEBOLLA PERLA VALLE CHILE KG</v>
+        <v>AJI ORO ESCABECHEVALLE CHILE KG</v>
       </c>
       <c r="C322" t="str">
         <v/>
       </c>
       <c r="D322" t="str">
-        <v>34231</v>
+        <v>34230</v>
       </c>
       <c r="E322" t="str">
-        <v>5396</v>
+        <v>4396</v>
       </c>
       <c r="F322" t="str">
         <v>Por peso</v>
@@ -6841,19 +6841,19 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>634232</v>
+        <v>634231</v>
       </c>
       <c r="B323" t="str">
-        <v>PICKLE ESPECIAL FINO VALLE CHILE KG</v>
+        <v>CEBOLLA PERLA VALLE CHILE KG</v>
       </c>
       <c r="C323" t="str">
         <v/>
       </c>
       <c r="D323" t="str">
-        <v>34232</v>
+        <v>34231</v>
       </c>
       <c r="E323" t="str">
-        <v>4396</v>
+        <v>5396</v>
       </c>
       <c r="F323" t="str">
         <v>Por peso</v>
@@ -6861,19 +6861,19 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>634233</v>
+        <v>634232</v>
       </c>
       <c r="B324" t="str">
-        <v>PEPINILLO FINO VALLE CHILE KG</v>
+        <v>PICKLE ESPECIAL FINO VALLE CHILE KG</v>
       </c>
       <c r="C324" t="str">
         <v/>
       </c>
       <c r="D324" t="str">
-        <v>34233</v>
+        <v>34232</v>
       </c>
       <c r="E324" t="str">
-        <v>6196</v>
+        <v>4396</v>
       </c>
       <c r="F324" t="str">
         <v>Por peso</v>
@@ -6881,19 +6881,19 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>634234</v>
+        <v>634233</v>
       </c>
       <c r="B325" t="str">
-        <v>PEPINILLO DILL VALLE CHILE KG</v>
+        <v>PEPINILLO FINO VALLE CHILE KG</v>
       </c>
       <c r="C325" t="str">
         <v/>
       </c>
       <c r="D325" t="str">
-        <v>34234</v>
+        <v>34233</v>
       </c>
       <c r="E325" t="str">
-        <v>6796</v>
+        <v>6196</v>
       </c>
       <c r="F325" t="str">
         <v>Por peso</v>
@@ -6901,19 +6901,19 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>631120</v>
+        <v>634234</v>
       </c>
       <c r="B326" t="str">
-        <v>TOCINO LP KG</v>
+        <v>PEPINILLO DILL VALLE CHILE KG</v>
       </c>
       <c r="C326" t="str">
         <v/>
       </c>
       <c r="D326" t="str">
-        <v>31120</v>
+        <v>34234</v>
       </c>
       <c r="E326" t="str">
-        <v>14996</v>
+        <v>6796</v>
       </c>
       <c r="F326" t="str">
         <v>Por peso</v>
@@ -6921,19 +6921,19 @@
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>632295</v>
+        <v>631120</v>
       </c>
       <c r="B327" t="str">
-        <v>MORTAD. LISA WINTER KG</v>
+        <v>TOCINO LP KG</v>
       </c>
       <c r="C327" t="str">
         <v/>
       </c>
       <c r="D327" t="str">
-        <v>32295</v>
+        <v>31120</v>
       </c>
       <c r="E327" t="str">
-        <v>4396</v>
+        <v>14996</v>
       </c>
       <c r="F327" t="str">
         <v>Por peso</v>
@@ -6941,19 +6941,19 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>632870</v>
+        <v>632295</v>
       </c>
       <c r="B328" t="str">
-        <v>PECHUGA POLLO COCIDA LP KG</v>
+        <v>MORTAD. LISA WINTER KG</v>
       </c>
       <c r="C328" t="str">
         <v/>
       </c>
       <c r="D328" t="str">
-        <v>32870</v>
+        <v>32295</v>
       </c>
       <c r="E328" t="str">
-        <v>13996</v>
+        <v>4396</v>
       </c>
       <c r="F328" t="str">
         <v>Por peso</v>
@@ -6961,16 +6961,16 @@
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>632871</v>
+        <v>632870</v>
       </c>
       <c r="B329" t="str">
-        <v>PECHUGA POLLO ACARAMELADO LP KG</v>
+        <v>PECHUGA POLLO COCIDA LP KG</v>
       </c>
       <c r="C329" t="str">
         <v/>
       </c>
       <c r="D329" t="str">
-        <v>32871</v>
+        <v>32870</v>
       </c>
       <c r="E329" t="str">
         <v>13996</v>
@@ -6981,19 +6981,19 @@
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>632872</v>
+        <v>632871</v>
       </c>
       <c r="B330" t="str">
-        <v>QUESO CABEZA LP KG</v>
+        <v>PECHUGA POLLO ACARAMELADO LP KG</v>
       </c>
       <c r="C330" t="str">
         <v/>
       </c>
       <c r="D330" t="str">
-        <v>32872</v>
+        <v>32871</v>
       </c>
       <c r="E330" t="str">
-        <v>9996</v>
+        <v>13996</v>
       </c>
       <c r="F330" t="str">
         <v>Por peso</v>
@@ -7001,19 +7001,19 @@
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>633080</v>
+        <v>632872</v>
       </c>
       <c r="B331" t="str">
-        <v>QUESO ROQUEFORT LOS FUNDOS</v>
+        <v>QUESO CABEZA LP KG</v>
       </c>
       <c r="C331" t="str">
         <v/>
       </c>
       <c r="D331" t="str">
-        <v>33080</v>
+        <v>32872</v>
       </c>
       <c r="E331" t="str">
-        <v>6679</v>
+        <v>9996</v>
       </c>
       <c r="F331" t="str">
         <v>Por peso</v>
@@ -7021,19 +7021,19 @@
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>633030</v>
+        <v>633080</v>
       </c>
       <c r="B332" t="str">
-        <v>QUESO CABRA KILO</v>
+        <v>QUESO ROQUEFORT LOS FUNDOS</v>
       </c>
       <c r="C332" t="str">
         <v/>
       </c>
       <c r="D332" t="str">
-        <v>33030</v>
+        <v>33080</v>
       </c>
       <c r="E332" t="str">
-        <v>3196</v>
+        <v>6679</v>
       </c>
       <c r="F332" t="str">
         <v>Por peso</v>
@@ -7041,19 +7041,19 @@
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>633440</v>
+        <v>633030</v>
       </c>
       <c r="B333" t="str">
-        <v>QUESO EDAM QUILLAYES 330 GRS</v>
+        <v>QUESO CABRA KILO</v>
       </c>
       <c r="C333" t="str">
         <v/>
       </c>
       <c r="D333" t="str">
-        <v>33440</v>
+        <v>33030</v>
       </c>
       <c r="E333" t="str">
-        <v>8990</v>
+        <v>3196</v>
       </c>
       <c r="F333" t="str">
         <v>Por peso</v>
@@ -7061,19 +7061,19 @@
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>633480</v>
+        <v>633440</v>
       </c>
       <c r="B334" t="str">
-        <v>QUESO AJI QUILLAYES 330 GRS</v>
+        <v>QUESO EDAM QUILLAYES 330 GRS</v>
       </c>
       <c r="C334" t="str">
         <v/>
       </c>
       <c r="D334" t="str">
-        <v>33480</v>
+        <v>33440</v>
       </c>
       <c r="E334" t="str">
-        <v>7590</v>
+        <v>8990</v>
       </c>
       <c r="F334" t="str">
         <v>Por peso</v>
@@ -7081,19 +7081,19 @@
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>633446</v>
+        <v>633480</v>
       </c>
       <c r="B335" t="str">
-        <v>QUESO PIMIENTA QUILLAYES 330 GRS</v>
+        <v>QUESO AJI QUILLAYES 330 GRS</v>
       </c>
       <c r="C335" t="str">
         <v/>
       </c>
       <c r="D335" t="str">
-        <v>33446</v>
+        <v>33480</v>
       </c>
       <c r="E335" t="str">
-        <v>7890</v>
+        <v>7590</v>
       </c>
       <c r="F335" t="str">
         <v>Por peso</v>
@@ -7101,19 +7101,19 @@
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>633035</v>
+        <v>633446</v>
       </c>
       <c r="B336" t="str">
-        <v>QUESO FRESCO CHACRA LOS FUNDOS</v>
+        <v>QUESO PIMIENTA QUILLAYES 330 GRS</v>
       </c>
       <c r="C336" t="str">
         <v/>
       </c>
       <c r="D336" t="str">
-        <v>33035</v>
+        <v>33446</v>
       </c>
       <c r="E336" t="str">
-        <v>1990</v>
+        <v>7890</v>
       </c>
       <c r="F336" t="str">
         <v>Por peso</v>
@@ -7121,19 +7121,19 @@
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>633217</v>
+        <v>633035</v>
       </c>
       <c r="B337" t="str">
-        <v>QUESO EL ROBLE CHANCO LAM. KG. 8KLCAJA</v>
+        <v>QUESO FRESCO CHACRA LOS FUNDOS</v>
       </c>
       <c r="C337" t="str">
         <v/>
       </c>
       <c r="D337" t="str">
-        <v>33217</v>
+        <v>33035</v>
       </c>
       <c r="E337" t="str">
-        <v>14760</v>
+        <v>1990</v>
       </c>
       <c r="F337" t="str">
         <v>Por peso</v>
@@ -7141,19 +7141,19 @@
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>633220</v>
+        <v>633217</v>
       </c>
       <c r="B338" t="str">
-        <v>QUESO LOS TILOS CABRA KG</v>
+        <v>QUESO EL ROBLE CHANCO LAM. KG. 8KLCAJA</v>
       </c>
       <c r="C338" t="str">
         <v/>
       </c>
       <c r="D338" t="str">
-        <v>33220</v>
+        <v>33217</v>
       </c>
       <c r="E338" t="str">
-        <v>26990</v>
+        <v>14760</v>
       </c>
       <c r="F338" t="str">
         <v>Por peso</v>
@@ -7161,19 +7161,19 @@
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>633336</v>
+        <v>633220</v>
       </c>
       <c r="B339" t="str">
-        <v>QUESO MANTECOSO SAN IGNACIO KG</v>
+        <v>QUESO LOS TILOS CABRA KG</v>
       </c>
       <c r="C339" t="str">
         <v/>
       </c>
       <c r="D339" t="str">
-        <v>33336</v>
+        <v>33220</v>
       </c>
       <c r="E339" t="str">
-        <v>13160</v>
+        <v>26990</v>
       </c>
       <c r="F339" t="str">
         <v>Por peso</v>
@@ -7181,16 +7181,16 @@
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>632620</v>
+        <v>633336</v>
       </c>
       <c r="B340" t="str">
-        <v>QUESO LOS TILOS MANTECOSOKG</v>
+        <v>QUESO MANTECOSO SAN IGNACIO KG</v>
       </c>
       <c r="C340" t="str">
         <v/>
       </c>
       <c r="D340" t="str">
-        <v>32620</v>
+        <v>33336</v>
       </c>
       <c r="E340" t="str">
         <v>13160</v>
@@ -7201,19 +7201,19 @@
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>633002</v>
+        <v>632620</v>
       </c>
       <c r="B341" t="str">
-        <v>QUESO LAMIN.CHANCO LOS ALERCES</v>
+        <v>QUESO LOS TILOS MANTECOSOKG</v>
       </c>
       <c r="C341" t="str">
         <v/>
       </c>
       <c r="D341" t="str">
-        <v>33002</v>
+        <v>32620</v>
       </c>
       <c r="E341" t="str">
-        <v>4799</v>
+        <v>13160</v>
       </c>
       <c r="F341" t="str">
         <v>Por peso</v>
@@ -7221,19 +7221,19 @@
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>633421</v>
+        <v>633002</v>
       </c>
       <c r="B342" t="str">
-        <v>QUESO GAUDA TROZO FRUTILLAR</v>
+        <v>QUESO LAMIN.CHANCO LOS ALERCES</v>
       </c>
       <c r="C342" t="str">
         <v/>
       </c>
       <c r="D342" t="str">
-        <v>33421</v>
+        <v>33002</v>
       </c>
       <c r="E342" t="str">
-        <v>3076</v>
+        <v>4799</v>
       </c>
       <c r="F342" t="str">
         <v>Por peso</v>
@@ -7241,19 +7241,19 @@
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>633419</v>
+        <v>633421</v>
       </c>
       <c r="B343" t="str">
-        <v>QUESO GAUDA TROZO.8K.MULPULMO</v>
+        <v>QUESO GAUDA TROZO FRUTILLAR</v>
       </c>
       <c r="C343" t="str">
         <v/>
       </c>
       <c r="D343" t="str">
-        <v>33419</v>
+        <v>33421</v>
       </c>
       <c r="E343" t="str">
-        <v>3996</v>
+        <v>3076</v>
       </c>
       <c r="F343" t="str">
         <v>Por peso</v>
@@ -7261,19 +7261,19 @@
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>633121</v>
+        <v>633419</v>
       </c>
       <c r="B344" t="str">
-        <v>QUESO GAUDA LOS FUNDOS</v>
+        <v>QUESO GAUDA TROZO.8K.MULPULMO</v>
       </c>
       <c r="C344" t="str">
         <v/>
       </c>
       <c r="D344" t="str">
-        <v>33121</v>
+        <v>33419</v>
       </c>
       <c r="E344" t="str">
-        <v>2469</v>
+        <v>3996</v>
       </c>
       <c r="F344" t="str">
         <v>Por peso</v>
@@ -7281,19 +7281,19 @@
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>633125</v>
+        <v>633121</v>
       </c>
       <c r="B345" t="str">
-        <v>QUESO GAUDA DOS CASTAnOS</v>
+        <v>QUESO GAUDA LOS FUNDOS</v>
       </c>
       <c r="C345" t="str">
         <v/>
       </c>
       <c r="D345" t="str">
-        <v>33125</v>
+        <v>33121</v>
       </c>
       <c r="E345" t="str">
-        <v>2620</v>
+        <v>2469</v>
       </c>
       <c r="F345" t="str">
         <v>Por peso</v>
@@ -7301,19 +7301,19 @@
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>633415</v>
+        <v>633125</v>
       </c>
       <c r="B346" t="str">
-        <v>QUESO GAUDA BARRA 2 KGS PF.UU</v>
+        <v>QUESO GAUDA DOS CASTAnOS</v>
       </c>
       <c r="C346" t="str">
         <v/>
       </c>
       <c r="D346" t="str">
-        <v>33415</v>
+        <v>33125</v>
       </c>
       <c r="E346" t="str">
-        <v>2436</v>
+        <v>2620</v>
       </c>
       <c r="F346" t="str">
         <v>Por peso</v>
@@ -7321,19 +7321,19 @@
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>633397</v>
+        <v>633415</v>
       </c>
       <c r="B347" t="str">
-        <v>QUESO CHANCO TUNCA TROZO</v>
+        <v>QUESO GAUDA BARRA 2 KGS PF.UU</v>
       </c>
       <c r="C347" t="str">
         <v/>
       </c>
       <c r="D347" t="str">
-        <v>33397</v>
+        <v>33415</v>
       </c>
       <c r="E347" t="str">
-        <v>3596</v>
+        <v>2436</v>
       </c>
       <c r="F347" t="str">
         <v>Por peso</v>
@@ -7341,19 +7341,19 @@
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>633126</v>
+        <v>633397</v>
       </c>
       <c r="B348" t="str">
-        <v>QUESO CHANCO DOS CASTAnOS</v>
+        <v>QUESO CHANCO TUNCA TROZO</v>
       </c>
       <c r="C348" t="str">
         <v/>
       </c>
       <c r="D348" t="str">
-        <v>33126</v>
+        <v>33397</v>
       </c>
       <c r="E348" t="str">
-        <v>3097</v>
+        <v>3596</v>
       </c>
       <c r="F348" t="str">
         <v>Por peso</v>
@@ -7361,19 +7361,19 @@
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>633420</v>
+        <v>633126</v>
       </c>
       <c r="B349" t="str">
-        <v>QUESO CHANCO EL SALVADOR LAMIN</v>
+        <v>QUESO CHANCO DOS CASTAnOS</v>
       </c>
       <c r="C349" t="str">
         <v/>
       </c>
       <c r="D349" t="str">
-        <v>33420</v>
+        <v>33126</v>
       </c>
       <c r="E349" t="str">
-        <v>4956</v>
+        <v>3097</v>
       </c>
       <c r="F349" t="str">
         <v>Por peso</v>
@@ -7381,19 +7381,19 @@
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>633187</v>
+        <v>633420</v>
       </c>
       <c r="B350" t="str">
-        <v>QUESO ROCKEFORT TR. VACIO OCTAY</v>
+        <v>QUESO CHANCO EL SALVADOR LAMIN</v>
       </c>
       <c r="C350" t="str">
         <v/>
       </c>
       <c r="D350" t="str">
-        <v>33187</v>
+        <v>33420</v>
       </c>
       <c r="E350" t="str">
-        <v>10370</v>
+        <v>4956</v>
       </c>
       <c r="F350" t="str">
         <v>Por peso</v>
@@ -7401,19 +7401,19 @@
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>633180</v>
+        <v>633187</v>
       </c>
       <c r="B351" t="str">
-        <v>QUESO ALPINO KL OCTAY</v>
+        <v>QUESO ROCKEFORT TR. VACIO OCTAY</v>
       </c>
       <c r="C351" t="str">
         <v/>
       </c>
       <c r="D351" t="str">
-        <v>33180</v>
+        <v>33187</v>
       </c>
       <c r="E351" t="str">
-        <v>7990</v>
+        <v>10370</v>
       </c>
       <c r="F351" t="str">
         <v>Por peso</v>
@@ -7421,16 +7421,16 @@
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>633179</v>
+        <v>633180</v>
       </c>
       <c r="B352" t="str">
-        <v>QUESO EDAM KL OCTAY</v>
+        <v>QUESO ALPINO KL OCTAY</v>
       </c>
       <c r="C352" t="str">
         <v/>
       </c>
       <c r="D352" t="str">
-        <v>33179</v>
+        <v>33180</v>
       </c>
       <c r="E352" t="str">
         <v>7990</v>
@@ -7441,16 +7441,16 @@
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>633118</v>
+        <v>633179</v>
       </c>
       <c r="B353" t="str">
-        <v>QUESO TILSITER KL OCTAY</v>
+        <v>QUESO EDAM KL OCTAY</v>
       </c>
       <c r="C353" t="str">
         <v/>
       </c>
       <c r="D353" t="str">
-        <v>33118</v>
+        <v>33179</v>
       </c>
       <c r="E353" t="str">
         <v>7990</v>
@@ -7461,19 +7461,19 @@
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>633011</v>
+        <v>633118</v>
       </c>
       <c r="B354" t="str">
-        <v>QUESO MANT. RIO CRUCES VALDIVIA PIEZAKG</v>
+        <v>QUESO TILSITER KL OCTAY</v>
       </c>
       <c r="C354" t="str">
         <v/>
       </c>
       <c r="D354" t="str">
-        <v>33011</v>
+        <v>33118</v>
       </c>
       <c r="E354" t="str">
-        <v>13160</v>
+        <v>7990</v>
       </c>
       <c r="F354" t="str">
         <v>Por peso</v>
@@ -7481,19 +7481,19 @@
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>633507</v>
+        <v>633011</v>
       </c>
       <c r="B355" t="str">
-        <v>QUESO CHANCO TUNCA LAMINADO</v>
+        <v>QUESO MANT. RIO CRUCES VALDIVIA PIEZAKG</v>
       </c>
       <c r="C355" t="str">
         <v/>
       </c>
       <c r="D355" t="str">
-        <v>33507</v>
+        <v>33011</v>
       </c>
       <c r="E355" t="str">
-        <v>5196</v>
+        <v>13160</v>
       </c>
       <c r="F355" t="str">
         <v>Por peso</v>
@@ -7501,19 +7501,19 @@
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>633225</v>
+        <v>633507</v>
       </c>
       <c r="B356" t="str">
-        <v>QUESO CON OREGANO QUILLAYES 330 GRS</v>
+        <v>QUESO CHANCO TUNCA LAMINADO</v>
       </c>
       <c r="C356" t="str">
         <v/>
       </c>
       <c r="D356" t="str">
-        <v>33225</v>
+        <v>33507</v>
       </c>
       <c r="E356" t="str">
-        <v>8990</v>
+        <v>5196</v>
       </c>
       <c r="F356" t="str">
         <v>Por peso</v>
@@ -7521,19 +7521,19 @@
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>636310</v>
+        <v>633225</v>
       </c>
       <c r="B357" t="str">
-        <v>QUESO CHANCO BARRA 4KG</v>
+        <v>QUESO CON OREGANO QUILLAYES 330 GRS</v>
       </c>
       <c r="C357" t="str">
         <v/>
       </c>
       <c r="D357" t="str">
-        <v>36310</v>
+        <v>33225</v>
       </c>
       <c r="E357" t="str">
-        <v>11960</v>
+        <v>8990</v>
       </c>
       <c r="F357" t="str">
         <v>Por peso</v>
@@ -7541,19 +7541,19 @@
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>631682</v>
+        <v>636310</v>
       </c>
       <c r="B358" t="str">
-        <v>PICADILLO GAUDA+SALAME PF</v>
+        <v>QUESO CHANCO BARRA 4KG</v>
       </c>
       <c r="C358" t="str">
         <v/>
       </c>
       <c r="D358" t="str">
-        <v>31682</v>
+        <v>36310</v>
       </c>
       <c r="E358" t="str">
-        <v>1990</v>
+        <v>11960</v>
       </c>
       <c r="F358" t="str">
         <v>Por peso</v>
@@ -7561,19 +7561,19 @@
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>633345</v>
+        <v>631682</v>
       </c>
       <c r="B359" t="str">
-        <v>QUESO MANT. SAN PEDRO KG</v>
+        <v>PICADILLO GAUDA+SALAME PF</v>
       </c>
       <c r="C359" t="str">
         <v/>
       </c>
       <c r="D359" t="str">
-        <v>33345</v>
+        <v>31682</v>
       </c>
       <c r="E359" t="str">
-        <v>13160</v>
+        <v>1990</v>
       </c>
       <c r="F359" t="str">
         <v>Por peso</v>
@@ -7581,19 +7581,19 @@
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>634567</v>
+        <v>633345</v>
       </c>
       <c r="B360" t="str">
-        <v>QUESO CHANCO LA TURBINA</v>
+        <v>QUESO MANT. SAN PEDRO KG</v>
       </c>
       <c r="C360" t="str">
         <v/>
       </c>
       <c r="D360" t="str">
-        <v>34567</v>
+        <v>33345</v>
       </c>
       <c r="E360" t="str">
-        <v>5596</v>
+        <v>13160</v>
       </c>
       <c r="F360" t="str">
         <v>Por peso</v>
@@ -7601,19 +7601,19 @@
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>633167</v>
+        <v>634567</v>
       </c>
       <c r="B361" t="str">
-        <v>QUESO FRESCO CHACRA CUÑIHUE</v>
+        <v>QUESO CHANCO LA TURBINA</v>
       </c>
       <c r="C361" t="str">
         <v/>
       </c>
       <c r="D361" t="str">
-        <v>33167</v>
+        <v>34567</v>
       </c>
       <c r="E361" t="str">
-        <v>4396</v>
+        <v>5596</v>
       </c>
       <c r="F361" t="str">
         <v>Por peso</v>
@@ -7621,19 +7621,19 @@
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>635862</v>
+        <v>633167</v>
       </c>
       <c r="B362" t="str">
-        <v>QUESO MANTECOSO CUNIHUE</v>
+        <v>QUESO FRESCO CHACRA CUÑIHUE</v>
       </c>
       <c r="C362" t="str">
         <v/>
       </c>
       <c r="D362" t="str">
-        <v>35862</v>
+        <v>33167</v>
       </c>
       <c r="E362" t="str">
-        <v>12360</v>
+        <v>4396</v>
       </c>
       <c r="F362" t="str">
         <v>Por peso</v>
@@ -7641,19 +7641,19 @@
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>633466</v>
+        <v>635862</v>
       </c>
       <c r="B363" t="str">
-        <v>QUESO MANTECOSO SAN SEBASTIAN</v>
+        <v>QUESO MANTECOSO CUNIHUE</v>
       </c>
       <c r="C363" t="str">
         <v/>
       </c>
       <c r="D363" t="str">
-        <v>33466</v>
+        <v>35862</v>
       </c>
       <c r="E363" t="str">
-        <v>5396</v>
+        <v>12360</v>
       </c>
       <c r="F363" t="str">
         <v>Por peso</v>
@@ -7661,19 +7661,19 @@
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>633467</v>
+        <v>633466</v>
       </c>
       <c r="B364" t="str">
-        <v>QUESO CHANCO PUYEHUE</v>
+        <v>QUESO MANTECOSO SAN SEBASTIAN</v>
       </c>
       <c r="C364" t="str">
         <v/>
       </c>
       <c r="D364" t="str">
-        <v>33467</v>
+        <v>33466</v>
       </c>
       <c r="E364" t="str">
-        <v>5160</v>
+        <v>5396</v>
       </c>
       <c r="F364" t="str">
         <v>Por peso</v>
@@ -7681,19 +7681,19 @@
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>633468</v>
+        <v>633467</v>
       </c>
       <c r="B365" t="str">
-        <v>QUESO CHANCO LAMINADO PUYEHUE.</v>
+        <v>QUESO CHANCO PUYEHUE</v>
       </c>
       <c r="C365" t="str">
         <v/>
       </c>
       <c r="D365" t="str">
-        <v>33468</v>
+        <v>33467</v>
       </c>
       <c r="E365" t="str">
-        <v>4396</v>
+        <v>5160</v>
       </c>
       <c r="F365" t="str">
         <v>Por peso</v>
@@ -7701,19 +7701,19 @@
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>633470</v>
+        <v>633468</v>
       </c>
       <c r="B366" t="str">
-        <v>QUESO GAUDA PUYEHUE</v>
+        <v>QUESO CHANCO LAMINADO PUYEHUE.</v>
       </c>
       <c r="C366" t="str">
         <v/>
       </c>
       <c r="D366" t="str">
-        <v>33470</v>
+        <v>33468</v>
       </c>
       <c r="E366" t="str">
-        <v>3960</v>
+        <v>4396</v>
       </c>
       <c r="F366" t="str">
         <v>Por peso</v>
@@ -7721,16 +7721,16 @@
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>633471</v>
+        <v>633470</v>
       </c>
       <c r="B367" t="str">
-        <v>QUESO GAUDA LAMINADO PUYEHUE</v>
+        <v>QUESO GAUDA PUYEHUE</v>
       </c>
       <c r="C367" t="str">
         <v/>
       </c>
       <c r="D367" t="str">
-        <v>33471</v>
+        <v>33470</v>
       </c>
       <c r="E367" t="str">
         <v>3960</v>
@@ -7741,19 +7741,19 @@
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>633255</v>
+        <v>633471</v>
       </c>
       <c r="B368" t="str">
-        <v>QUESO CHANCO BOLA PTO OCTAY KG</v>
+        <v>QUESO GAUDA LAMINADO PUYEHUE</v>
       </c>
       <c r="C368" t="str">
         <v/>
       </c>
       <c r="D368" t="str">
-        <v>33255</v>
+        <v>33471</v>
       </c>
       <c r="E368" t="str">
-        <v>6396</v>
+        <v>3960</v>
       </c>
       <c r="F368" t="str">
         <v>Por peso</v>
@@ -7761,19 +7761,19 @@
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>633254</v>
+        <v>633255</v>
       </c>
       <c r="B369" t="str">
-        <v>QUESO GAUDA PUERTO VARAS</v>
+        <v>QUESO CHANCO BOLA PTO OCTAY KG</v>
       </c>
       <c r="C369" t="str">
         <v/>
       </c>
       <c r="D369" t="str">
-        <v>33254</v>
+        <v>33255</v>
       </c>
       <c r="E369" t="str">
-        <v>5196</v>
+        <v>6396</v>
       </c>
       <c r="F369" t="str">
         <v>Por peso</v>
@@ -7781,19 +7781,19 @@
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>633366</v>
+        <v>633254</v>
       </c>
       <c r="B370" t="str">
-        <v>DESPUNTE QUESOS</v>
+        <v>QUESO GAUDA PUERTO VARAS</v>
       </c>
       <c r="C370" t="str">
         <v/>
       </c>
       <c r="D370" t="str">
-        <v>33366</v>
+        <v>33254</v>
       </c>
       <c r="E370" t="str">
-        <v>4796</v>
+        <v>5196</v>
       </c>
       <c r="F370" t="str">
         <v>Por peso</v>
@@ -7801,19 +7801,19 @@
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>633661</v>
+        <v>633366</v>
       </c>
       <c r="B371" t="str">
-        <v>QUESO MANTECOSO BIOLECHE</v>
+        <v>DESPUNTE QUESOS</v>
       </c>
       <c r="C371" t="str">
         <v/>
       </c>
       <c r="D371" t="str">
-        <v>33661</v>
+        <v>33366</v>
       </c>
       <c r="E371" t="str">
-        <v>7996</v>
+        <v>4796</v>
       </c>
       <c r="F371" t="str">
         <v>Por peso</v>
@@ -7821,19 +7821,19 @@
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>637700</v>
+        <v>633661</v>
       </c>
       <c r="B372" t="str">
-        <v>QUESO MANTECOSO LONGAVI</v>
+        <v>QUESO MANTECOSO BIOLECHE</v>
       </c>
       <c r="C372" t="str">
         <v/>
       </c>
       <c r="D372" t="str">
-        <v>37700</v>
+        <v>33661</v>
       </c>
       <c r="E372" t="str">
-        <v>6596</v>
+        <v>7996</v>
       </c>
       <c r="F372" t="str">
         <v>Por peso</v>
@@ -7841,19 +7841,19 @@
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>632827</v>
+        <v>637700</v>
       </c>
       <c r="B373" t="str">
-        <v>QUESO GAUDA KG MOLINO VIEJO</v>
+        <v>QUESO MANTECOSO LONGAVI</v>
       </c>
       <c r="C373" t="str">
         <v/>
       </c>
       <c r="D373" t="str">
-        <v>32827</v>
+        <v>37700</v>
       </c>
       <c r="E373" t="str">
-        <v>10360</v>
+        <v>6596</v>
       </c>
       <c r="F373" t="str">
         <v>Por peso</v>
@@ -7861,16 +7861,16 @@
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>633090</v>
+        <v>632827</v>
       </c>
       <c r="B374" t="str">
-        <v>QUESO CHANCO MOLINO VIEJO KG</v>
+        <v>QUESO GAUDA KG MOLINO VIEJO</v>
       </c>
       <c r="C374" t="str">
         <v/>
       </c>
       <c r="D374" t="str">
-        <v>33090</v>
+        <v>32827</v>
       </c>
       <c r="E374" t="str">
         <v>10360</v>
@@ -7881,19 +7881,19 @@
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>633105</v>
+        <v>633090</v>
       </c>
       <c r="B375" t="str">
-        <v>QUESO MANTECOSO LAM. RAFULCO KG</v>
+        <v>QUESO CHANCO MOLINO VIEJO KG</v>
       </c>
       <c r="C375" t="str">
         <v/>
       </c>
       <c r="D375" t="str">
-        <v>33105</v>
+        <v>33090</v>
       </c>
       <c r="E375" t="str">
-        <v>9560</v>
+        <v>10360</v>
       </c>
       <c r="F375" t="str">
         <v>Por peso</v>
@@ -7901,19 +7901,19 @@
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>633092</v>
+        <v>633105</v>
       </c>
       <c r="B376" t="str">
-        <v>QUESO MANTECOSO SC KG. MOLINO VIEJO</v>
+        <v>QUESO MANTECOSO LAM. RAFULCO KG</v>
       </c>
       <c r="C376" t="str">
         <v/>
       </c>
       <c r="D376" t="str">
-        <v>33092</v>
+        <v>33105</v>
       </c>
       <c r="E376" t="str">
-        <v>10360</v>
+        <v>9560</v>
       </c>
       <c r="F376" t="str">
         <v>Por peso</v>
@@ -7921,19 +7921,19 @@
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>633199</v>
+        <v>633092</v>
       </c>
       <c r="B377" t="str">
-        <v>QUESO GAUDA PROV CHI· KG</v>
+        <v>QUESO MANTECOSO SC KG. MOLINO VIEJO</v>
       </c>
       <c r="C377" t="str">
         <v/>
       </c>
       <c r="D377" t="str">
-        <v>33199</v>
+        <v>33092</v>
       </c>
       <c r="E377" t="str">
-        <v>3996</v>
+        <v>10360</v>
       </c>
       <c r="F377" t="str">
         <v>Por peso</v>
@@ -7941,16 +7941,16 @@
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>633298</v>
+        <v>633199</v>
       </c>
       <c r="B378" t="str">
-        <v>QUESO GAUDA PROV CHILCO LAMINADO</v>
+        <v>QUESO GAUDA PROV CHI· KG</v>
       </c>
       <c r="C378" t="str">
         <v/>
       </c>
       <c r="D378" t="str">
-        <v>33298</v>
+        <v>33199</v>
       </c>
       <c r="E378" t="str">
         <v>3996</v>
@@ -7961,19 +7961,19 @@
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>632121</v>
+        <v>633298</v>
       </c>
       <c r="B379" t="str">
-        <v>QUESO CHANCO LAS AGUILAS KILO</v>
+        <v>QUESO GAUDA PROV CHILCO LAMINADO</v>
       </c>
       <c r="C379" t="str">
         <v/>
       </c>
       <c r="D379" t="str">
-        <v>32121</v>
+        <v>33298</v>
       </c>
       <c r="E379" t="str">
-        <v>12360</v>
+        <v>3996</v>
       </c>
       <c r="F379" t="str">
         <v>Por peso</v>
@@ -7981,19 +7981,19 @@
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>632222</v>
+        <v>632121</v>
       </c>
       <c r="B380" t="str">
-        <v>QUESO GAUDA SURLAT LAMINADO KG</v>
+        <v>QUESO CHANCO LAS AGUILAS KILO</v>
       </c>
       <c r="C380" t="str">
         <v/>
       </c>
       <c r="D380" t="str">
-        <v>32222</v>
+        <v>32121</v>
       </c>
       <c r="E380" t="str">
-        <v>11560</v>
+        <v>12360</v>
       </c>
       <c r="F380" t="str">
         <v>Por peso</v>
@@ -8001,19 +8001,19 @@
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>633005</v>
+        <v>632222</v>
       </c>
       <c r="B381" t="str">
-        <v>QUESO GAUDA CALO PIEZA 3KG</v>
+        <v>QUESO GAUDA SURLAT LAMINADO KG</v>
       </c>
       <c r="C381" t="str">
         <v/>
       </c>
       <c r="D381" t="str">
-        <v>33005</v>
+        <v>32222</v>
       </c>
       <c r="E381" t="str">
-        <v>10996</v>
+        <v>11560</v>
       </c>
       <c r="F381" t="str">
         <v>Por peso</v>
@@ -8021,19 +8021,19 @@
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>633620</v>
+        <v>633005</v>
       </c>
       <c r="B382" t="str">
-        <v>QUESO MANT. PIEZA LONGAVI KG</v>
+        <v>QUESO GAUDA CALO PIEZA 3KG</v>
       </c>
       <c r="C382" t="str">
         <v/>
       </c>
       <c r="D382" t="str">
-        <v>33620</v>
+        <v>33005</v>
       </c>
       <c r="E382" t="str">
-        <v>12760</v>
+        <v>10996</v>
       </c>
       <c r="F382" t="str">
         <v>Por peso</v>
@@ -8041,19 +8041,19 @@
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>633621</v>
+        <v>633620</v>
       </c>
       <c r="B383" t="str">
-        <v>QUESO CABRADISLAC</v>
+        <v>QUESO MANT. PIEZA LONGAVI KG</v>
       </c>
       <c r="C383" t="str">
         <v/>
       </c>
       <c r="D383" t="str">
-        <v>33621</v>
+        <v>33620</v>
       </c>
       <c r="E383" t="str">
-        <v>28990</v>
+        <v>12760</v>
       </c>
       <c r="F383" t="str">
         <v>Por peso</v>
@@ -8061,19 +8061,19 @@
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>633249</v>
+        <v>633621</v>
       </c>
       <c r="B384" t="str">
-        <v>QUESO BRIE COEUR DE LION PIEZA</v>
+        <v>QUESO CABRADISLAC</v>
       </c>
       <c r="C384" t="str">
         <v/>
       </c>
       <c r="D384" t="str">
-        <v>33249</v>
+        <v>33621</v>
       </c>
       <c r="E384" t="str">
-        <v>59990</v>
+        <v>28990</v>
       </c>
       <c r="F384" t="str">
         <v>Por peso</v>
@@ -8081,19 +8081,19 @@
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>633581</v>
+        <v>633249</v>
       </c>
       <c r="B385" t="str">
-        <v>QUESO GOUDA SURLAT BARRA 3.55 KG</v>
+        <v>QUESO BRIE COEUR DE LION PIEZA</v>
       </c>
       <c r="C385" t="str">
         <v/>
       </c>
       <c r="D385" t="str">
-        <v>33581</v>
+        <v>33249</v>
       </c>
       <c r="E385" t="str">
-        <v>7960</v>
+        <v>59990</v>
       </c>
       <c r="F385" t="str">
         <v>Por peso</v>
@@ -8101,19 +8101,19 @@
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>633834</v>
+        <v>633581</v>
       </c>
       <c r="B386" t="str">
-        <v>QUESO CHANCO LAMINADO QUILLAYES KG</v>
+        <v>QUESO GOUDA SURLAT BARRA 3.55 KG</v>
       </c>
       <c r="C386" t="str">
         <v/>
       </c>
       <c r="D386" t="str">
-        <v>33834</v>
+        <v>33581</v>
       </c>
       <c r="E386" t="str">
-        <v>11990</v>
+        <v>7960</v>
       </c>
       <c r="F386" t="str">
         <v>Por peso</v>
@@ -8121,19 +8121,19 @@
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>633981</v>
+        <v>633834</v>
       </c>
       <c r="B387" t="str">
-        <v>QUESO GAUDA QUILLAYES LAMINADO GRANEL KG</v>
+        <v>QUESO CHANCO LAMINADO QUILLAYES KG</v>
       </c>
       <c r="C387" t="str">
         <v/>
       </c>
       <c r="D387" t="str">
-        <v>33981</v>
+        <v>33834</v>
       </c>
       <c r="E387" t="str">
-        <v>13160</v>
+        <v>11990</v>
       </c>
       <c r="F387" t="str">
         <v>Por peso</v>
@@ -8141,19 +8141,19 @@
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>634035</v>
+        <v>633981</v>
       </c>
       <c r="B388" t="str">
-        <v>QUESO RALLADO GRANEL</v>
+        <v>QUESO GAUDA QUILLAYES LAMINADO GRANEL KG</v>
       </c>
       <c r="C388" t="str">
         <v/>
       </c>
       <c r="D388" t="str">
-        <v>34035</v>
+        <v>33981</v>
       </c>
       <c r="E388" t="str">
-        <v>4990</v>
+        <v>13160</v>
       </c>
       <c r="F388" t="str">
         <v>Por peso</v>
@@ -8161,19 +8161,19 @@
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>636291</v>
+        <v>634035</v>
       </c>
       <c r="B389" t="str">
-        <v>QUESO MANTECOSO LAM QUILQUE 3.4 KG</v>
+        <v>QUESO RALLADO GRANEL</v>
       </c>
       <c r="C389" t="str">
         <v/>
       </c>
       <c r="D389" t="str">
-        <v>36291</v>
+        <v>34035</v>
       </c>
       <c r="E389" t="str">
-        <v>12990</v>
+        <v>4990</v>
       </c>
       <c r="F389" t="str">
         <v>Por peso</v>
@@ -8181,19 +8181,19 @@
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>633150</v>
+        <v>636291</v>
       </c>
       <c r="B390" t="str">
-        <v>QUESO LAS PARCELAS DE VALDIVIA LAM 2.5KG</v>
+        <v>QUESO MANTECOSO LAM QUILQUE 3.4 KG</v>
       </c>
       <c r="C390" t="str">
         <v/>
       </c>
       <c r="D390" t="str">
-        <v>33150</v>
+        <v>36291</v>
       </c>
       <c r="E390" t="str">
-        <v>17560</v>
+        <v>12990</v>
       </c>
       <c r="F390" t="str">
         <v>Por peso</v>
@@ -8201,19 +8201,19 @@
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>633015</v>
+        <v>633150</v>
       </c>
       <c r="B391" t="str">
-        <v>QUESO MANTECOSO LA VAQUITA BOLSA</v>
+        <v>QUESO LAS PARCELAS DE VALDIVIA LAM 2.5KG</v>
       </c>
       <c r="C391" t="str">
         <v/>
       </c>
       <c r="D391" t="str">
-        <v>33015</v>
+        <v>33150</v>
       </c>
       <c r="E391" t="str">
-        <v>10360</v>
+        <v>17560</v>
       </c>
       <c r="F391" t="str">
         <v>Por peso</v>
@@ -8221,19 +8221,19 @@
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>631053</v>
+        <v>633015</v>
       </c>
       <c r="B392" t="str">
-        <v>QUESO MANT. PRADERAS DEL SURE O KG</v>
+        <v>QUESO MANTECOSO LA VAQUITA BOLSA</v>
       </c>
       <c r="C392" t="str">
         <v/>
       </c>
       <c r="D392" t="str">
-        <v>31053</v>
+        <v>33015</v>
       </c>
       <c r="E392" t="str">
-        <v>13990</v>
+        <v>10360</v>
       </c>
       <c r="F392" t="str">
         <v>Por peso</v>
@@ -8241,19 +8241,19 @@
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>631075</v>
+        <v>631053</v>
       </c>
       <c r="B393" t="str">
-        <v>QUESO GAUDA BARRA ARG FRUTILLAR KG</v>
+        <v>QUESO MANT. PRADERAS DEL SURE O KG</v>
       </c>
       <c r="C393" t="str">
         <v/>
       </c>
       <c r="D393" t="str">
-        <v>31075</v>
+        <v>31053</v>
       </c>
       <c r="E393" t="str">
-        <v>10360</v>
+        <v>13990</v>
       </c>
       <c r="F393" t="str">
         <v>Por peso</v>
@@ -8261,19 +8261,19 @@
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>631082</v>
+        <v>631075</v>
       </c>
       <c r="B394" t="str">
-        <v>QUESO GAUDA HOLANDES KG</v>
+        <v>QUESO GAUDA BARRA ARG FRUTILLAR KG</v>
       </c>
       <c r="C394" t="str">
         <v/>
       </c>
       <c r="D394" t="str">
-        <v>31082</v>
+        <v>31075</v>
       </c>
       <c r="E394" t="str">
-        <v>9160</v>
+        <v>10360</v>
       </c>
       <c r="F394" t="str">
         <v>Por peso</v>
@@ -8281,19 +8281,19 @@
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>631083</v>
+        <v>631082</v>
       </c>
       <c r="B395" t="str">
-        <v>QUESO LLANERO MAD KG - PIEZA 5 KL</v>
+        <v>QUESO GAUDA HOLANDES KG</v>
       </c>
       <c r="C395" t="str">
         <v/>
       </c>
       <c r="D395" t="str">
-        <v>31083</v>
+        <v>31082</v>
       </c>
       <c r="E395" t="str">
-        <v>15960</v>
+        <v>9160</v>
       </c>
       <c r="F395" t="str">
         <v>Por peso</v>
@@ -8301,19 +8301,19 @@
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>632369</v>
+        <v>631083</v>
       </c>
       <c r="B396" t="str">
-        <v>QUESO GAUDA BARRA ROJA LA VAQUITA KG</v>
+        <v>QUESO LLANERO MAD KG - PIEZA 5 KL</v>
       </c>
       <c r="C396" t="str">
         <v/>
       </c>
       <c r="D396" t="str">
-        <v>32369</v>
+        <v>31083</v>
       </c>
       <c r="E396" t="str">
-        <v>9160</v>
+        <v>15960</v>
       </c>
       <c r="F396" t="str">
         <v>Por peso</v>
@@ -8321,19 +8321,19 @@
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>633310</v>
+        <v>632369</v>
       </c>
       <c r="B397" t="str">
-        <v>QUESO EDAM HOLANDES GALLERY KG</v>
+        <v>QUESO GAUDA BARRA ROJA LA VAQUITA KG</v>
       </c>
       <c r="C397" t="str">
         <v/>
       </c>
       <c r="D397" t="str">
-        <v>33310</v>
+        <v>32369</v>
       </c>
       <c r="E397" t="str">
-        <v>9960</v>
+        <v>9160</v>
       </c>
       <c r="F397" t="str">
         <v>Por peso</v>
@@ -8341,19 +8341,19 @@
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>633313</v>
+        <v>633310</v>
       </c>
       <c r="B398" t="str">
-        <v>QUESO CABRA HOLANDES GALLERY KG</v>
+        <v>QUESO EDAM HOLANDES GALLERY KG</v>
       </c>
       <c r="C398" t="str">
         <v/>
       </c>
       <c r="D398" t="str">
-        <v>33313</v>
+        <v>33310</v>
       </c>
       <c r="E398" t="str">
-        <v>15960</v>
+        <v>9960</v>
       </c>
       <c r="F398" t="str">
         <v>Por peso</v>
@@ -8361,19 +8361,19 @@
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>636230</v>
+        <v>633313</v>
       </c>
       <c r="B399" t="str">
-        <v>QUESO RODDA LAM.SOPROLE 2.2KG</v>
+        <v>QUESO CABRA HOLANDES GALLERY KG</v>
       </c>
       <c r="C399" t="str">
         <v/>
       </c>
       <c r="D399" t="str">
-        <v>36230</v>
+        <v>33313</v>
       </c>
       <c r="E399" t="str">
-        <v>11990</v>
+        <v>15960</v>
       </c>
       <c r="F399" t="str">
         <v>Por peso</v>
@@ -8381,19 +8381,19 @@
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>634145</v>
+        <v>636230</v>
       </c>
       <c r="B400" t="str">
-        <v>QUESO MANT. FUNDO DE SURE O KG</v>
+        <v>QUESO RODDA LAM.SOPROLE 2.2KG</v>
       </c>
       <c r="C400" t="str">
         <v/>
       </c>
       <c r="D400" t="str">
-        <v>34145</v>
+        <v>36230</v>
       </c>
       <c r="E400" t="str">
-        <v>12990</v>
+        <v>11990</v>
       </c>
       <c r="F400" t="str">
         <v>Por peso</v>
@@ -8401,19 +8401,19 @@
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>633211</v>
+        <v>634145</v>
       </c>
       <c r="B401" t="str">
-        <v>QUESO EDAM ASTURIANA KG</v>
+        <v>QUESO MANT. FUNDO DE SURE O KG</v>
       </c>
       <c r="C401" t="str">
         <v/>
       </c>
       <c r="D401" t="str">
-        <v>33211</v>
+        <v>34145</v>
       </c>
       <c r="E401" t="str">
-        <v>9560</v>
+        <v>12990</v>
       </c>
       <c r="F401" t="str">
         <v>Por peso</v>

--- a/MaestraPLU_Rotiseria.xlsx
+++ b/MaestraPLU_Rotiseria.xlsx
@@ -1753,7 +1753,7 @@
         <v>32088</v>
       </c>
       <c r="E68" t="str">
-        <v>4996</v>
+        <v>3996</v>
       </c>
       <c r="F68" t="str">
         <v>Por peso</v>
@@ -2253,7 +2253,7 @@
         <v>34505</v>
       </c>
       <c r="E93" t="str">
-        <v>12396</v>
+        <v>8796</v>
       </c>
       <c r="F93" t="str">
         <v>Por peso</v>
@@ -3133,7 +3133,7 @@
         <v>31488</v>
       </c>
       <c r="E137" t="str">
-        <v>9596</v>
+        <v>6996</v>
       </c>
       <c r="F137" t="str">
         <v>Por peso</v>
@@ -3373,7 +3373,7 @@
         <v>31016</v>
       </c>
       <c r="E149" t="str">
-        <v>14396</v>
+        <v>11596</v>
       </c>
       <c r="F149" t="str">
         <v>Por peso</v>
@@ -3513,7 +3513,7 @@
         <v>32722</v>
       </c>
       <c r="E156" t="str">
-        <v>14396</v>
+        <v>11596</v>
       </c>
       <c r="F156" t="str">
         <v>Por peso</v>
@@ -3833,7 +3833,7 @@
         <v>31124</v>
       </c>
       <c r="E172" t="str">
-        <v>9996</v>
+        <v>7196</v>
       </c>
       <c r="F172" t="str">
         <v>Por peso</v>
@@ -4673,7 +4673,7 @@
         <v>32890</v>
       </c>
       <c r="E214" t="str">
-        <v>11996</v>
+        <v>8796</v>
       </c>
       <c r="F214" t="str">
         <v>Por peso</v>
@@ -6173,7 +6173,7 @@
         <v>31089</v>
       </c>
       <c r="E289" t="str">
-        <v>14196</v>
+        <v>8996</v>
       </c>
       <c r="F289" t="str">
         <v>Por peso</v>
@@ -6193,7 +6193,7 @@
         <v>31091</v>
       </c>
       <c r="E290" t="str">
-        <v>11996</v>
+        <v>8996</v>
       </c>
       <c r="F290" t="str">
         <v>Por peso</v>
